--- a/Noticias_Calcario_20260715.xlsx
+++ b/Noticias_Calcario_20260715.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D512"/>
+  <dimension ref="A1:D510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,66 +441,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deputado Neodi pede calcário para atender produtores do PA São Domingos, em Buritis - Ariquemes Online</t>
+          <t>Eficiência do enxofre no solo ganha protagonismo no manejo agrícola brasileiro - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15/07/2026 00:19</t>
+          <t>15/07/2026 11:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOM002b2tRTzBVQi1qWVB6SDR5d1M4eFppUzF1aDZXYVVTdUNIbmpMRmppNjU5am9pbjMxeXFsenlnekQwZ0lhczNXM3NKdHZzUHpBTGVodjl2OW9UVzZtX2QtaWNBb00wNGRLa0dnZkhyam1TQ204ZVVTRG9iTnZ2cExORkVwUDRHaTR0U0RPd1VZZzJPSnVJbkEybnhvWUdheFFJT3BwTkRQN0x5U1V0Sk5zSkdNZjJHUWtEVXZqY2RkS1ZMVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQSkZycWdLVDZKNm5qcVlpdEh5aVBvTGtGNWp5MzRPN2lxcXROR1VxanltZ29OdXY2SDNuTjA1Ym1RdFlYMGhXNlNVMF9ESzE4UFNfTDN4TzdSZnBFS3JaRE5ET3E1NVhjMUJPSG5ZYjR6VlFPNE4xUEN0RU1CaS1YRlQ3dUc1XzZnOGVtWUZGMkRobkVfMFN1R2pIcjlPZHlnbDlXbHpvY0QtV3RfTGo3ZGhRYnFfX3pnaVhoMkJ0NDh1Uk1HNXdjNmZNTmZkMlFCRXlpQ3drV3hZbUNlSEF3RXBpc0dOTzh1a3pv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
+          <t>Deputado Neodi pede calcário para atender produtores do PA São Domingos, em Buritis - Ariquemes Online</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14/07/2026 20:57</t>
+          <t>15/07/2026 00:19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOM002b2tRTzBVQi1qWVB6SDR5d1M4eFppUzF1aDZXYVVTdUNIbmpMRmppNjU5am9pbjMxeXFsenlnekQwZ0lhczNXM3NKdHZzUHpBTGVodjl2OW9UVzZtX2QtaWNBb00wNGRLa0dnZkhyam1TQ204ZVVTRG9iTnZ2cExORkVwUDRHaTR0U0RPd1VZZzJPSnVJbkEybnhvWUdheFFJT3BwTkRQN0x5U1V0Sk5zSkdNZjJHUWtEVXZqY2RkS1ZMVWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Passa Sete adquire distribuidor de calcário para fortalecer atendimento aos produtores rurais - radiosobradinho.com.br</t>
+          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14/07/2026 18:28</t>
+          <t>14/07/2026 20:57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ2R3Y1NoTFE1U1NjTnNxUV9vWnJWcjV4WUxxX2ZJNWt6Q2dmLVI5N2RxT2Y0Ung2QXZQc0ZJakF1OXpBOVNTV0FhRjlXb1NXdDRSeVRiSm55SHo1bGsxR0R3SjJJbUdNN2VEcU1rU2t2dzhiVl9MMkNPMjQ1dDBLekhoNDh6cUlodU50UGNOZFQ2ZFViMlVoT1IxaF8xdnNRSE9fc0djWnV4Nmk2bnZuR1ZveWJCcFdOamZYWWg3REpNVTVRcVdtUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
         </is>
       </c>
     </row>
@@ -512,39 +512,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fertilizante em alerta - Olhar Direto</t>
+          <t>Guerra no Irão: Empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - MSN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14/07/2026 18:27</t>
+          <t>14/07/2026 19:52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1zY1FWdWlnSWxfY2tCYkR5M2Z6YmFhdWUza2tRRTRtQW9hUWFNRGs3N2FGSFU1ekdyUldESy1ESDlJOUhoZWcyZFVGSFpabkl0LUJnU1kwLXQ0MDNpUVNzTzF4eVUtUllSQzJjSllwS21Tems?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxQYVhNZTI3UmVycEpMVFVnb1FySmhoNGRWbnN5eTJnSUgtaWliR3Nqb010TThIcERFOThuRElVbnpOd0NFeS1FQjQ4TWQ5VVRxRzU4aXZwUkdqQ1lad0ZKbUhiTWI2MDI1VXJHbklBWjQ0WkZXcm5QMFFLMUpzR3FEUWFYOWZSZ29CRW84RklmRXhyOFoya285cEFSbzF1WUI3TC1jM0dfcHhiV3ZrOWl5U09GV3lqVG1TQ045aEIzSk1qUTlpdmRwcVF4VzlBck11TTFBTDJmQVhOZm9IWmUzNnNkWU1ZY25GRnlLT0JvNVl2bzEtQTJOM3JiU1B6Slh3Wm1LTWxseEhzWUowbVNsNm43a1Q1dExKRUZoRWFuYmhVSkpm?oc=5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Antigos asteroides podem explicar cristais de enxofre encontrados por Curiosity - Aventuras na História</t>
+          <t>Passa Sete adquire distribuidor de calcário para fortalecer atendimento aos produtores rurais - radiosobradinho.com.br</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14/07/2026 17:58</t>
+          <t>14/07/2026 18:28</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPbk15WHdxRElHSUFTYmRCSDBMQ3hMN3gyY05ZNmo0SlV1ZFp1WnpsZHNFTHNtelcwWi1oemJLaFB6MHhzWnRudEZPajFLVks2aElOUGVDNVhmY3NFcndPZEUxaURaZm14d0daT0MwVEF3TVY4aGlPQ0hFNWY1dkJGSFk0RFhXMGFncEx0enk2WHU4ZTdkeFc3ZkNQRTZuT2JQOEV1TURqRjh4NjZ4Q1Y2cnQxYm1lTGZvUTBiZjh5SU83cW9pdkRCbkRyT3d1Q1IzOVVxYWN5SXM2Y3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ2R3Y1NoTFE1U1NjTnNxUV9vWnJWcjV4WUxxX2ZJNWt6Q2dmLVI5N2RxT2Y0Ung2QXZQc0ZJakF1OXpBOVNTV0FhRjlXb1NXdDRSeVRiSm55SHo1bGsxR0R3SjJJbUdNN2VEcU1rU2t2dzhiVl9MMkNPMjQ1dDBLekhoNDh6cUlodU50UGNOZFQ2ZFViMlVoT1IxaF8xdnNRSE9fc0djWnV4Nmk2bnZuR1ZveWJCcFdOamZYWWg3REpNVTVRcVdtUA?oc=5</t>
         </is>
       </c>
     </row>
@@ -556,171 +556,171 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mário Neto detalha acordo do Metabase para trabalhadores desligados da Mosaic - Badiinho</t>
+          <t>Fertilizante em alerta - Olhar Direto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14/07/2026 17:11</t>
+          <t>14/07/2026 18:27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9sTGRIT05leVVvVHZ3cU1qU3BmLS14TjVtM0xGdVNtNWFxNkg5UW14blZqOEpJMmNEeHNObE1LVm00WDFwT3h4cmJEeUNTLUU3THJrMTE4UHZmekJGUXJheTBybjF1MzB6N2wydzc1U3NNZlJ0alF2edIBfkFVX3lxTE9wQUs4NzNaVFN5c0tBSGlTVEhlUTA5V2h5REE1SWFmbkhfci1iWnA5V3hMTUY0bTg5dy02R0VYU1NxR3BCV0R3NU0xSUlZYUJrRS1TNmhZVDJqVDFrN2xFdG03REJhSXllMF9FYnZMaHdtVjhOSTNIc1Jkc3JhZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1zY1FWdWlnSWxfY2tCYkR5M2Z6YmFhdWUza2tRRTRtQW9hUWFNRGs3N2FGSFU1ekdyUldESy1ESDlJOUhoZWcyZFVGSFpabkl0LUJnU1kwLXQ0MDNpUVNzTzF4eVUtUllSQzJjSllwS21Tems?oc=5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação da unidade de Catalão por falta de enxofre - Badiinho</t>
+          <t>Antigos asteroides podem explicar cristais de enxofre encontrados por Curiosity - Aventuras na História</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14/07/2026 16:09</t>
+          <t>14/07/2026 17:58</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBodUloejIyYmJxUW80NXhoTVUzaXZFMklTTjc1NnRHMzZDZGJOUkVtWUFXT25IWVFwd3o3RGdEeVItVi13ZDdLRk85ZEZHS0t2MFFFMk8xdDQ0VEJRZUc1elhPcHNJcjBzQlBtdUhvLVoxQdIBd0FVX3lxTE1vS1RSMUxsVldiUFVXLTZiTXQta0IyNDdwV3hqMmVFdzZFOVpPTHlxUWhHUHA2djdCRTNCd3YtQndEaTRVT1U1REowc21rMW1nVEc2cWdxcFlEZnR2UG9FTWMxdDlvT2pyaFhiTW9taVFMQmk3NkM4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPbk15WHdxRElHSUFTYmRCSDBMQ3hMN3gyY05ZNmo0SlV1ZFp1WnpsZHNFTHNtelcwWi1oemJLaFB6MHhzWnRudEZPajFLVks2aElOUGVDNVhmY3NFcndPZEUxaURaZm14d0daT0MwVEF3TVY4aGlPQ0hFNWY1dkJGSFk0RFhXMGFncEx0enk2WHU4ZTdkeFc3ZkNQRTZuT2JQOEV1TURqRjh4NjZ4Q1Y2cnQxYm1lTGZvUTBiZjh5SU83cW9pdkRCbkRyT3d1Q1IzOVVxYWN5SXM2Y3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rejeito da indústria de celulose é testado como fertilizante agrícola em MS - Correio do Estado</t>
+          <t>Galeria de Flooring Panels - Dietfurt Limestone - 8 - ArchDaily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14/07/2026 16:00</t>
+          <t>14/07/2026 17:44</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOc25Gb0RtSmNLOHdUa2U1dlhxOW5FLW0xd1g0MTNJVmtSZTI0YmkxTFRPdEZCbElYTEF3TGlMeUlYYXVkd1J5cm1sNERoTTdhamhOanIwMVB4M1I5eTZkS1N3VG5JRkQwRlJkd3huSmtEY3ozR1gwLUVvUXZIWGFMbUk3cTRSSlhqRHdJYWxKbEowaUkxWlIxcDk3REZjZ2t1ZkZ5dmR3VW9nX3dSYVBETF9kQlFld00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOU3dZdDNubHFYdW1VX1hzREJVYkNkTWxFaVRSV19fbVkweVoyQTZKRnJrZzBuM0g0aEh2ZjNScnhfLWJaWFlHUUlrczdBZDFMNUs0SV9RdUpSdHptSVlla0FkNjA0VUhuTjlZRVBJbWhsbG01c2JmNHlLN0pmVWw3aWh6U20xblJMeUdwSTdNRTE4OXd4Qmpzc0hYbVN6aTNEa19LUF9NQklxaGlKN0NlTkV1NHU1Mm1nR0VJVjdrZU1TOC1qLWtMaTBqdGJsQUpLVnRWcExGNEJ1RzNZaDB1blppYWxPdkstVFBsaGpEOS1hYWxGZmQ0WDl3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cientistas criam “recifes elétricos” no fundo do mar com baixa voltagem, fazem minerais grudarem como calcário e testam uma solução capaz de reconstruir barreiras naturais contra erosão costeira antes que o oceano engula praias inteiras - CPG Click Petróleo e Gás</t>
+          <t>Mário Neto detalha acordo do Metabase para trabalhadores desligados da Mosaic - Badiinho</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14/07/2026 14:30</t>
+          <t>14/07/2026 17:11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxPS21PQWhiUmIwcS1UR3h4dXdJMlBFZ29rR2hMdmxDWmhnWVFtVy1lZUtnTFB2SlBwcWI2dkxTNDFYN1UzdDJiNHVPbEVLaEcxbzhuUjlOUkgweURHU0ptQkstNGlmZkYyeG93bmMyWEltQWl6UHpUMFk3TTlDV0h3NmxBeDVwY0Vfd2FZeXh6RDl3RFQ2bWtrVFhFcTJTWlM0dWhpdTZHajZhME52MlZEYmVfR0ZWOW9taWRGeTQ1eVo1N2JLcGwxd1pQSWxpc1pobHVveFgtSFFpVXhreVNFLU9iZUo4Wk1ORlBrUHJZWFVFYXdTQmQ1b25NNFFTaE9nem1WWHVnYjFNenU4RnNtNUhoTHhWcUhXNnIzeEZGT2oyLTlDeFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9sTGRIT05leVVvVHZ3cU1qU3BmLS14TjVtM0xGdVNtNWFxNkg5UW14blZqOEpJMmNEeHNObE1LVm00WDFwT3h4cmJEeUNTLUU3THJrMTE4UHZmekJGUXJheTBybjF1MzB6N2wydzc1U3NNZlJ0alF2edIBfkFVX3lxTE9wQUs4NzNaVFN5c0tBSGlTVEhlUTA5V2h5REE1SWFmbkhfci1iWnA5V3hMTUY0bTg5dy02R0VYU1NxR3BCV0R3NU0xSUlZYUJrRS1TNmhZVDJqVDFrN2xFdG03REJhSXllMF9FYnZMaHdtVjhOSTNIc1Jkc3JhZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Emater retoma a compra conjunta de calcário para beneficiar pequenos produtores - Rádio Santa Cruz FM</t>
+          <t>Mosaic prorroga paralisação da unidade de Catalão por falta de enxofre - Badiinho</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14/07/2026 14:14</t>
+          <t>14/07/2026 16:09</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQeGk0dGtBdVozXzVycTE3Z2tTY0VTVkd1TllzZkdlRmxCSElhSHZqUkVlNi0tS0JHZWsta3pVMmRaMkJQbVJDS1dNMHp1b3Rucm9SQWdxWTZPd3JzczJla0ZwWEh5YVZtZ0tIVjRBbDk1RG9PZHZhNk52RWdfRm52Vy1TMWhYSW1feW5xT1VhMkV3anJwdThrUjJuTlRscHpjMmx2anhWbkNPWW9fN2NxQ2N2emc2bkVDeDFJYVRBMGtvRjBZY0VmRUpFM214SURKaUpaU0c0MjBOMldF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBodUloejIyYmJxUW80NXhoTVUzaXZFMklTTjc1NnRHMzZDZGJOUkVtWUFXT25IWVFwd3o3RGdEeVItVi13ZDdLRk85ZEZHS0t2MFFFMk8xdDQ0VEJRZUc1elhPcHNJcjBzQlBtdUhvLVoxQdIBd0FVX3lxTE1vS1RSMUxsVldiUFVXLTZiTXQta0IyNDdwV3hqMmVFdzZFOVpPTHlxUWhHUHA2djdCRTNCd3YtQndEaTRVT1U1REowc21rMW1nVEc2cWdxcFlEZnR2UG9FTWMxdDlvT2pyaFhiTW9taVFMQmk3NkM4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Crise da Mosaic expõe limites da ação de Uberaba - Rede 98</t>
+          <t>Rejeito da indústria de celulose é testado como fertilizante agrícola em MS - Correio do Estado</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14/07/2026 13:55</t>
+          <t>14/07/2026 16:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNUjNMck12c0xrY2hEOHExdVQ1YkVNNThoV3hPVWd1TEZZSm0xMms2U1ZGRF9fSEVfajhmT2JVdmtoOFRqSHZWem5hY1g5a3BwdmVWbHE5dFYtNHVuSE92VE10TnIzbXBhRjZqTWVWT2lUTHVPakhVbGJBWkhrN20xMDRqT1FaQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOc25Gb0RtSmNLOHdUa2U1dlhxOW5FLW0xd1g0MTNJVmtSZTI0YmkxTFRPdEZCbElYTEF3TGlMeUlYYXVkd1J5cm1sNERoTTdhamhOanIwMVB4M1I5eTZkS1N3VG5JRkQwRlJkd3huSmtEY3ozR1gwLUVvUXZIWGFMbUk3cTRSSlhqRHdJYWxKbEowaUkxWlIxcDk3REZjZ2t1ZkZ5dmR3VW9nX3dSYVBETF9kQlFld00?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Terça-feira 14 de Julho de 2026 - RRMAIS</t>
+          <t>Cientistas criam “recifes elétricos” no fundo do mar com baixa voltagem, fazem minerais grudarem como calcário e testam uma solução capaz de reconstruir barreiras naturais contra erosão costeira antes que o oceano engula praias inteiras - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14/07/2026 13:33</t>
+          <t>14/07/2026 14:30</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTF9kdlZZV0YtSUxvaVBrVnB0ckxnMlNFeXM1SmVkV1FDdjNOOV9MWDZ1TEtBem9PMFhpY3VGdFRnZEJUNjFpR05ZLTh4N1FabkxveDE3Y0xjM0dqNXc3cUJ1eXdJa2lNYjAxMlR5R3ozS3ROUDludmRhck5WbllrRUNzTW1mQUttTV9sOWlyTTFGZUJVRVRPYXp4cWRLaHNLaEhIZndCcEZOVlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxPS21PQWhiUmIwcS1UR3h4dXdJMlBFZ29rR2hMdmxDWmhnWVFtVy1lZUtnTFB2SlBwcWI2dkxTNDFYN1UzdDJiNHVPbEVLaEcxbzhuUjlOUkgweURHU0ptQkstNGlmZkYyeG93bmMyWEltQWl6UHpUMFk3TTlDV0h3NmxBeDVwY0Vfd2FZeXh6RDl3RFQ2bWtrVFhFcTJTWlM0dWhpdTZHajZhME52MlZEYmVfR0ZWOW9taWRGeTQ1eVo1N2JLcGwxd1pQSWxpc1pobHVveFgtSFFpVXhreVNFLU9iZUo4Wk1ORlBrUHJZWFVFYXdTQmQ1b25NNFFTaE9nem1WWHVnYjFNenU4RnNtNUhoTHhWcUhXNnIzeEZGT2oyLTlDeFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Escassez de enxofre paralisa fábricas da Mosaic no Brasil - SpaceMoney</t>
+          <t>Emater retoma a compra conjunta de calcário para beneficiar pequenos produtores - Rádio Santa Cruz FM</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14/07/2026 13:03</t>
+          <t>14/07/2026 14:14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE05YTRCY2tDcnJuMHVGRWpBSVcwNi1NdFVVemZuQjFQT3NZUlYyM0pWM2ZfeUNRWHVvRDZzWU1zREJVcEpoQlotb3V1cFJ0bGZMQW9UOS01OHdESVVnd01YeTAxNnFlTkdiMU1rX2p2X1oyX3oxVS1GWUNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQeGk0dGtBdVozXzVycTE3Z2tTY0VTVkd1TllzZkdlRmxCSElhSHZqUkVlNi0tS0JHZWsta3pVMmRaMkJQbVJDS1dNMHp1b3Rucm9SQWdxWTZPd3JzczJla0ZwWEh5YVZtZ0tIVjRBbDk1RG9PZHZhNk52RWdfRm52Vy1TMWhYSW1feW5xT1VhMkV3anJwdThrUjJuTlRscHpjMmx2anhWbkNPWW9fN2NxQ2N2emc2bkVDeDFJYVRBMGtvRjBZY0VmRUpFM214SURKaUpaU0c0MjBOMldF?oc=5</t>
         </is>
       </c>
     </row>
@@ -732,39 +732,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - Expressão Rondônia</t>
+          <t>Crise da Mosaic expõe limites da ação de Uberaba - Rede 98</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14/07/2026 12:50</t>
+          <t>14/07/2026 13:55</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPQTNMYVlEYXpzcDgtWDE3bzVmSGpXdm42dmxMWnRCd084b2ZPaGs3U2tDM2syNFVxdm1wQlZXQlJGMVlFcDlYb3ZzQl9RckZvZlAtVlZuazZCcFdfYXdkazFTX0tmU25mNzU1al90Y1hfZWhzV0U5aVNMNjBjR3Z3aVJYRnJvNVE2ZzkyTU5WcFk3cjdpVVVHNHVMbHNPZW5DSk5qTEdaWlVNS19xbWhjeXVfYnljOThfLXhmR1lnelk4UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNUjNMck12c0xrY2hEOHExdVQ1YkVNNThoV3hPVWd1TEZZSm0xMms2U1ZGRF9fSEVfajhmT2JVdmtoOFRqSHZWem5hY1g5a3BwdmVWbHE5dFYtNHVuSE92VE10TnIzbXBhRjZqTWVWT2lUTHVPakhVbGJBWkhrN20xMDRqT1FaQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dependência externa expõe agronegócio brasileiro à volatilidade dos fertilizantes - CompreRural</t>
+          <t>Cotações Agrícolas para esta Terça-feira 14 de Julho de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14/07/2026 12:18</t>
+          <t>14/07/2026 13:33</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOc1NqRkllZTVIa25qaWxreVhzTlVXQmVjUUx6LTMxeTRrcDZsclJvekd6WHhRcGJLaTFlTGpFeWhTZUFEalNubHJaMzQ5dmc2SGdEdEJ3aTVtUkVweXhRN2Z5alVBaHZHSUFCQUNUMnVweUJqb1pDd1hId3ZTTGY1Q3pKUEpYeHJKSEhQMG4xNEdXODYzVTlNQWdoS1VPY3B5VFZkWmx1T184c3JhS0k0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTF9kdlZZV0YtSUxvaVBrVnB0ckxnMlNFeXM1SmVkV1FDdjNOOV9MWDZ1TEtBem9PMFhpY3VGdFRnZEJUNjFpR05ZLTh4N1FabkxveDE3Y0xjM0dqNXc3cUJ1eXdJa2lNYjAxMlR5R3ozS3ROUDludmRhck5WbllrRUNzTW1mQUttTV9sOWlyTTFGZUJVRVRPYXp4cWRLaHNLaEhIZndCcEZOVlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes por falta de enxofre - boca.com.br</t>
+          <t>Escassez de enxofre paralisa fábricas da Mosaic no Brasil - SpaceMoney</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14/07/2026 12:10</t>
+          <t>14/07/2026 13:03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOcHJmVkk1OWdibGhiUWtTWjRveGdzaU44MmoweUtmWXBremlDSkRBalNqNjFlbUprXzJ0U2JveF8xenBhOXZzRmlXZzUzbFNwWTRLTHhsSDIzYUltdzlFSzRpa3QtTVllU3lYejlOQkhVS184ZEpXdDlKV1VFaG9jbl9CTFh4eENrcExETVlENzBnenF3cnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE05YTRCY2tDcnJuMHVGRWpBSVcwNi1NdFVVemZuQjFQT3NZUlYyM0pWM2ZfeUNRWHVvRDZzWU1zREJVcEpoQlotb3V1cFJ0bGZMQW9UOS01OHdESVVnd01YeTAxNnFlTkdiMU1rX2p2X1oyX3oxVS1GWUNn?oc=5</t>
         </is>
       </c>
     </row>
@@ -798,83 +798,83 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - G1</t>
+          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - Expressão Rondônia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14/07/2026 12:01</t>
+          <t>14/07/2026 12:50</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUZhRXRNY2trQVZ1YkFrZTVzNEdyX0xBSkZOdGduN080THhRLWNrRzNRV2piY1hPSkNOaDZxcWh0a2NnNzZOR2hGeHR4Rkh2QjdVNDlDdXhlcFhlRVB5R0JEUHp4c1lhRFh6bmdJdWlRU1h1WEhkQ2VONEhrUWZBVnRJRl81SE1sN0Z3dGx6dGxTd2NDUzYxM01oVHdKTVRVMDlXZXMxZmF0SnFrTjNPUjZtZlRtamVwTmZxaG1SLWtMYWxaa1E3OEVFTlBkQkRQb2ZIQ1AtSkdPVXRwQUN4aHBtdmZXVnNQYUtydUxzeXTSAf8BQVVfeXFMUEtWemJJN0VvVFA5R2c0WE43dWdwQW1qaXZBMGZzdUlzVWc3NXI1LWE1cE9ZT05Fb2JRbVAxdUdVSHZhWVpwa2VDU0NVbFBSNHVZZnNFZVdQN0loOVlUeUtKMll4d2xLclh3dXhTYVZSM3dHNXBSWXNMUGhydEcwYU1Lc1B5RHU4cEpQclFNNEZMZXZjeUp6QjVCc3l2anp4Ymw0M0VmNU9kQ2hlaUMtZ1c4VTg5eWF2eXhoMXh0UERTSUdORlcwQ0hCUDZTd21GUEdVYVM4aEFVTi1mWUxzbVZyUnhQdGhfcF9wdmxzSUtDYmh1dGVqX0pFa1g2QnFV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPQTNMYVlEYXpzcDgtWDE3bzVmSGpXdm42dmxMWnRCd084b2ZPaGs3U2tDM2syNFVxdm1wQlZXQlJGMVlFcDlYb3ZzQl9RckZvZlAtVlZuazZCcFdfYXdkazFTX0tmU25mNzU1al90Y1hfZWhzV0U5aVNMNjBjR3Z3aVJYRnJvNVE2ZzkyTU5WcFk3cjdpVVVHNHVMbHNPZW5DSk5qTEdaWlVNS19xbWhjeXVfYnljOThfLXhmR1lnelk4UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - avozdocampo.com</t>
+          <t>Dependência externa expõe agronegócio brasileiro à volatilidade dos fertilizantes - CompreRural</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14/07/2026 12:01</t>
+          <t>14/07/2026 12:18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNnBteWw0TE1HbHBPOFZNdXp1NmdOaWJYcXNyLUwtUUc5eW9GcUw2WU1jaUZuMjdsZHd1djBmd2JHRkVqdWhhVi1fM3pjdV9fX19zVnBJWUM4UTRHZlpabkFDd3kzWkd6QmJNd093TU53blZ0VWdJbkRmSWIyVEVycGNXRGQ2OU5LR1BkSEJBVU16c0pCMGs2SmRzNks4MmJMc0JYUFZwM2hMTl9oX0VibXZhQ084UkpSZmxvbTZfN21LZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOc1NqRkllZTVIa25qaWxreVhzTlVXQmVjUUx6LTMxeTRrcDZsclJvekd6WHhRcGJLaTFlTGpFeWhTZUFEalNubHJaMzQ5dmc2SGdEdEJ3aTVtUkVweXhRN2Z5alVBaHZHSUFCQUNUMnVweUJqb1pDd1hId3ZTTGY1Q3pKUEpYeHJKSEhQMG4xNEdXODYzVTlNQWdoS1VPY3B5VFZkWmx1T184c3JhS0k0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Galeria de Patios and Terraces - Dietfurt Limestone Gala - 3 - ArchDaily</t>
+          <t>Mosaic reduz produção de fertilizantes por falta de enxofre - boca.com.br</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14/07/2026 11:33</t>
+          <t>14/07/2026 12:10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxORmJVVEVSd2xNTnQ1d1ZfQnFGalNqXy1XU3VyOGQyVmRpS19EM0RsZzBFbzFxQVVCQkRsbHFhN01od1AwVUE0M2xzaUVyaUNiQWhENXlZNE02N2pHNldySGRseFc0a184bW51YUlPV2o0YXBIdnBzRHMzS3lnM2NOdEhzTTFMN1pEQzdfTlhWMUs4c0xhalNOalM2cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOcHJmVkk1OWdibGhiUWtTWjRveGdzaU44MmoweUtmWXBremlDSkRBalNqNjFlbUprXzJ0U2JveF8xenBhOXZzRmlXZzUzbFNwWTRLTHhsSDIzYUltdzlFSzRpa3QtTVllU3lYejlOQkhVS184ZEpXdDlKV1VFaG9jbl9CTFh4eENrcExETVlENzBnenF3cnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Galeria de Facade Panels - Dietfurt Limestone - 8 - ArchDaily</t>
+          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - G1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14/07/2026 10:34</t>
+          <t>14/07/2026 12:01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOa01CT0JCU0J3R01WVno3eXBCcTRlanZoT3RyMWx4UHNQa2tUQnFKZXJ4SGc3dl9hSnNGWjd4cVFOcEVtdXBvaWpKa1RJZU1nQTFhbkVFcTdOSHNLZkZIYncwM2N4UEVzYU96VTl1Qnp0YlQtMVo1U3g2cWd5dWZYQzUxVjV4QmJieHNwLXhOVzhzZ2pCMmVKTGRSLVJGZGhuSDI3VmQ2RTl6Vmhq?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUZhRXRNY2trQVZ1YkFrZTVzNEdyX0xBSkZOdGduN080THhRLWNrRzNRV2piY1hPSkNOaDZxcWh0a2NnNzZOR2hGeHR4Rkh2QjdVNDlDdXhlcFhlRVB5R0JEUHp4c1lhRFh6bmdJdWlRU1h1WEhkQ2VONEhrUWZBVnRJRl81SE1sN0Z3dGx6dGxTd2NDUzYxM01oVHdKTVRVMDlXZXMxZmF0SnFrTjNPUjZtZlRtamVwTmZxaG1SLWtMYWxaa1E3OEVFTlBkQkRQb2ZIQ1AtSkdPVXRwQUN4aHBtdmZXVnNQYUtydUxzeXTSAf8BQVVfeXFMUEtWemJJN0VvVFA5R2c0WE43dWdwQW1qaXZBMGZzdUlzVWc3NXI1LWE1cE9ZT05Fb2JRbVAxdUdVSHZhWVpwa2VDU0NVbFBSNHVZZnNFZVdQN0loOVlUeUtKMll4d2xLclh3dXhTYVZSM3dHNXBSWXNMUGhydEcwYU1Lc1B5RHU4cEpQclFNNEZMZXZjeUp6QjVCc3l2anp4Ymw0M0VmNU9kQ2hlaUMtZ1c4VTg5eWF2eXhoMXh0UERTSUdORlcwQ0hCUDZTd21GUEdVYVM4aEFVTi1mWUxzbVZyUnhQdGhfcF9wdmxzSUtDYmh1dGVqX0pFa1g2QnFV?oc=5</t>
         </is>
       </c>
     </row>
@@ -886,127 +886,127 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes em sete unidades no Brasil e pressiona custos do agro - Economic News Brasil</t>
+          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - avozdocampo.com</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14/07/2026 10:17</t>
+          <t>14/07/2026 12:01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQdWlnLW42MkVwbEVHUUc2LXRpQUhhYjJCbzM5VzE4S0xxcDdrRlptQ1h1YkZDVFJ0SkxzOFN5WS05eVdiZ3FMR2VJdEIyeFpzckJvb1pHZnJRZV9fbEZwakdLTWdGS2Q1NVN3bWIwTmN3MUxJNXNvaWVjTHl1VGdqUWxYaVdpWFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNnBteWw0TE1HbHBPOFZNdXp1NmdOaWJYcXNyLUwtUUc5eW9GcUw2WU1jaUZuMjdsZHd1djBmd2JHRkVqdWhhVi1fM3pjdV9fX19zVnBJWUM4UTRHZlpabkFDd3kzWkd6QmJNd093TU53blZ0VWdJbkRmSWIyVEVycGNXRGQ2OU5LR1BkSEJBVU16c0pCMGs2SmRzNks4MmJMc0JYUFZwM2hMTl9oX0VibXZhQ084UkpSZmxvbTZfN21LZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Caminhão sai com fertilizante e chega com calcário; caso é investigado pela Polícia Civil - JM Online</t>
+          <t>Galeria de Patios and Terraces - Dietfurt Limestone Gala - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14/07/2026 10:13</t>
+          <t>14/07/2026 11:33</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPdzREdE1BVFdYdHRvbk5kOG05ams1aHR5R1hEX0xkckRCMVJyNm5ucG9ZcjRwS2prTllwdzdLcnU2WmFFQU05QmgyS09Fbzh1VFptZFgzcjBHOFBOemNfR3doUDBmTHJtaFdydzJISHpHM0NueTNjRDRwcDhRNEliX0M4QVBKaDlyaDZaYnRJOERXelpLRzdVTklQWVgwaVlZODFPcmFlRnJpdjRBWk9NRkhSZmZudHI3eGpqS0ZxS3o2cjl6Z1FER2FLLW9FcThM0gHQAUFVX3lxTE93NER0TUFUV1h0dG9uTmQ4bTlqazVodHlHWERfTGRyREIxUnI2bm5wb1lyNHBLamtOWXB3N0tydTZaYUVBTTlCaDJLT0VvOHVUWm1kWDNyMEc4UE56Y19Hd2hQMGZMcm1oV3J3MkhIekczQ255M2NENHBwOFE0SWJfQzhBUEpoOXJoNlpidEk4RFd6WktHN1VOSVBZWDBpWVk4MU9yYWVGcml2NEFaT01GSFJmZm50cjd4ampLRnFLejZyOXpnUURHYUstb0VxOEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxORmJVVEVSd2xNTnQ1d1ZfQnFGalNqXy1XU3VyOGQyVmRpS19EM0RsZzBFbzFxQVVCQkRsbHFhN01od1AwVUE0M2xzaUVyaUNiQWhENXlZNE02N2pHNldySGRseFc0a184bW51YUlPV2o0YXBIdnBzRHMzS3lnM2NOdEhzTTFMN1pEQzdfTlhWMUs4c0xhalNOalM2cw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rejeito da indústria de celulose é testado como fertilizante agrícola em MS</t>
+          <t>Mosaic reduz produção de fertilizantes em sete unidades no Brasil e pressiona custos do agro - Economic News Brasil</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14/07/2026 09:00</t>
+          <t>14/07/2026 10:17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a576649f4d14a0fb389bc557577f2cc&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQdWlnLW42MkVwbEVHUUc2LXRpQUhhYjJCbzM5VzE4S0xxcDdrRlptQ1h1YkZDVFJ0SkxzOFN5WS05eVdiZ3FMR2VJdEIyeFpzckJvb1pHZnJRZV9fbEZwakdLTWdGS2Q1NVN3bWIwTmN3MUxJNXNvaWVjTHl1VGdqUWxYaVdpWFU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tecnologia de veículos autônomos MOSAIC: um novo passo em frente na logística militar na Ucrânia. - Vietnam.vn</t>
+          <t>Caminhão sai com fertilizante e chega com calcário; caso é investigado pela Polícia Civil - JM Online</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14/07/2026 08:33</t>
+          <t>14/07/2026 10:13</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPQlRFMVhpVkU0T3A1VW9hZVp5aXMzQUF6bnFCYTFXMVhfZVpFeV8zZmZRc1JwaE9lT0RpZV9yYmVIY1BBRnhmamQydnlpRWI1SE5xdGZSVGlneUxOR19fMzdBdjVncmhWVlNQSnBiMHFtUERxMUxwUXdxeWw5cG9pSGxTbXM1QXo0MlBfaE9KeHd6ZXpTeXBzUy0wYnJXU3ZXR1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPdzREdE1BVFdYdHRvbk5kOG05ams1aHR5R1hEX0xkckRCMVJyNm5ucG9ZcjRwS2prTllwdzdLcnU2WmFFQU05QmgyS09Fbzh1VFptZFgzcjBHOFBOemNfR3doUDBmTHJtaFdydzJISHpHM0NueTNjRDRwcDhRNEliX0M4QVBKaDlyaDZaYnRJOERXelpLRzdVTklQWVgwaVlZODFPcmFlRnJpdjRBWk9NRkhSZmZudHI3eGpqS0ZxS3o2cjl6Z1FER2FLLW9FcThM0gHQAUFVX3lxTE93NER0TUFUV1h0dG9uTmQ4bTlqazVodHlHWERfTGRyREIxUnI2bm5wb1lyNHBLamtOWXB3N0tydTZaYUVBTTlCaDJLT0VvOHVUWm1kWDNyMEc4UE56Y19Hd2hQMGZMcm1oV3J3MkhIekczQ255M2NENHBwOFE0SWJfQzhBUEpoOXJoNlpidEk4RFd6WktHN1VOSVBZWDBpWVk4MU9yYWVGcml2NEFaT01GSFJmZm50cjd4ampLRnFLejZyOXpnUURHYUstb0VxOEw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A Quantum Systems está implantando sua tecnologia de caminhões autônomos MOSAIC na Ucrânia. - Vietnam.vn</t>
+          <t>Rejeito da indústria de celulose é testado como fertilizante agrícola em MS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14/07/2026 08:07</t>
+          <t>14/07/2026 09:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOdnRIcnZsb2tadlJHRHRoZlJtTV9ndWYzNEVac0xkRklSc291U1dKT3NyTWhtZUM5ck5kVDl0a0pFaG9MXzlfZEY5WEM3cFJudjRtVTVJenFKMnUycHFFeUk1UjNqMF9lREFKVXFpWGFOYWJlWVlPWFR5R3NhM2FvWTdfQ1BFNEI0WEFMZU5BZ0pBdFFILWJfd3JNdHFOalpUalNNVURR?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a577b6a6e774115926a2634232b3a12&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 5 - ArchDaily</t>
+          <t>Tecnologia de veículos autônomos MOSAIC: um novo passo em frente na logística militar na Ucrânia. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>14/07/2026 05:39</t>
+          <t>14/07/2026 08:33</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxObFlGcnEzcVEzSFVRQmFkaGJaSEdRWDY5a0t1RUZLT0s1TmhEN1RCN25fTVJaV2Rud3lOMDI1VFlmUDE5bi1MbUoyV1RnWGEzU0Rzc1NOWE0tZlNPa3VuQzA4Skg4S1FSQXdJa293QlVqRXAxcE1tQ3UzNkVVbldBS1NkTWZBeWh0SlZhX0xKaWFiMU1nenJ6UDR5cVk2Q2tYNm1HNk1TWXJpNWtPOTM5bXFMVERhZUlvb193aWVtYldnRkxNQUdmSmViZ1FQTmt0WGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPQlRFMVhpVkU0T3A1VW9hZVp5aXMzQUF6bnFCYTFXMVhfZVpFeV8zZmZRc1JwaE9lT0RpZV9yYmVIY1BBRnhmamQydnlpRWI1SE5xdGZSVGlneUxOR19fMzdBdjVncmhWVlNQSnBiMHFtUERxMUxwUXdxeWw5cG9pSGxTbXM1QXo0MlBfaE9KeHd6ZXpTeXBzUy0wYnJXU3ZXR1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -1018,39 +1018,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Urban Chic - 2 - ArchDaily</t>
+          <t>A Quantum Systems está implantando sua tecnologia de caminhões autônomos MOSAIC na Ucrânia. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>14/07/2026 05:03</t>
+          <t>14/07/2026 08:07</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQOE1vRXZKOENleDQtakthaWtvY1dMSl9Hb0sySWdCdFBqSXUzZWxFNGpOX3BndENiTzJnS193VlRjbEVPZjE3U19QV2Y1Um0ydG9sQkU4c2RqeHBCTktLbWphQVIybVJaVndLWVY1N0xwb01JbkZPU1dXWWN6bFlCTDlOWmZVLU5BaHBVTkF5aUwwM2VCZXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOdnRIcnZsb2tadlJHRHRoZlJtTV9ndWYzNEVac0xkRklSc291U1dKT3NyTWhtZUM5ck5kVDl0a0pFaG9MXzlfZEY5WEM3cFJudjRtVTVJenFKMnUycHFFeUk1UjNqMF9lREFKVXFpWGFOYWJlWVlPWFR5R3NhM2FvWTdfQ1BFNEI0WEFMZU5BZ0pBdFFILWJfd3JNdHFOalpUalNNVURR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A queda nos preços da ureia alivia o fardo dos agricultores para a safra de verão-outono. - Vietnam.vn</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 5 - ArchDaily</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>14/07/2026 04:24</t>
+          <t>14/07/2026 05:39</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBvc29iQWxFa2d6al8zOU15R1M0VGd3VGtzLWE5bTVTaDcxOWZYa0phT0JCWUxtSDZ4bEZodHpNOTNoNnZIS1hBczNaV2o1Y1VRN0J5RWNqbHA2SUl5WEtaS0RiaUNITkZxbzBya1hSWnhJV0wtcnM0NWtGUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxObFlGcnEzcVEzSFVRQmFkaGJaSEdRWDY5a0t1RUZLT0s1TmhEN1RCN25fTVJaV2Rud3lOMDI1VFlmUDE5bi1MbUoyV1RnWGEzU0Rzc1NOWE0tZlNPa3VuQzA4Skg4S1FSQXdJa293QlVqRXAxcE1tQ3UzNkVVbldBS1NkTWZBeWh0SlZhX0xKaWFiMU1nenJ6UDR5cVk2Q2tYNm1HNk1TWXJpNWtPOTM5bXFMVERhZUlvb193aWVtYldnRkxNQUdmSmViZ1FQTmt0WGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -1062,61 +1062,61 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - Folha de S.Paulo</t>
+          <t>Galeria de Mosaic Tiles - Urban Chic - 2 - ArchDaily</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>14/07/2026 02:00</t>
+          <t>14/07/2026 05:03</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQOE1vRXZKOENleDQtakthaWtvY1dMSl9Hb0sySWdCdFBqSXUzZWxFNGpOX3BndENiTzJnS193VlRjbEVPZjE3U19QV2Y1Um0ydG9sQkU4c2RqeHBCTktLbWphQVIybVJaVndLWVY1N0xwb01JbkZPU1dXWWN6bFlCTDlOWmZVLU5BaHBVTkF5aUwwM2VCZXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Previsão do tempo Limestone VIC. 14 dias - Meteored Brasil</t>
+          <t>A queda nos preços da ureia alivia o fardo dos agricultores para a safra de verão-outono. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>14/07/2026 00:47</t>
+          <t>14/07/2026 04:24</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5uWS1sR2lPOGZ6UmtZa1l5ZF9uaVJPSXBBa21UcnNsLUFIYkI5VHdfSWdTQW0tNkhRVmxZY1BlNllNN1ZjdUU3eFFCZkRqeFY1VHQwWjdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBvc29iQWxFa2d6al8zOU15R1M0VGd3VGtzLWE5bTVTaDcxOWZYa0phT0JCWUxtSDZ4bEZodHpNOTNoNnZIS1hBczNaV2o1Y1VRN0J5RWNqbHA2SUl5WEtaS0RiaUNITkZxbzBya1hSWnhJV0wtcnM0NWtGUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NASA revela imagens inéditas de enxofre puro em Marte: um “tesouro amarelo” descoberto pelo rover Curiosity - Noticias Ambientales</t>
+          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13/07/2026 21:56</t>
+          <t>14/07/2026 02:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNOGpMbFZtUjdFd1JDQXp4WkVlc0FaLUxYVGU2WHNXRmRkUzVVb0hFcHFrSy1CYTFVUG5GdVZoVDdKQ0tkTC02ZkdSMUNhMS1TalRncjBKTldzUk54MDNHQl9OcE5MS0dkQ1c1LUJtWWQyX05vSGlKUFpnTGJjd2ptMUdjY2JpNEZpem5xOXNDMmo0M2l5R0JtZFcyR3lyTW1tQ2tvaVU3VkpOamdrdldSWTk0SWRMXzlJdDRpMHZ6WUwzVWNkc2ZhTDUtcmVsNXIzOW9VZHVnVVF6UEd4ZTRvcHpn0gHnAUFVX3lxTE9VR2NueC1oS2MzbzFWa3otdmJyS3dlQUV0M2dWQXZ3Q1NrSW9GR21TUTQ5YVZ6LTVrOFpqVkFudmdSTDBzMTlsLWlOTHdoWGJMT093cHpVODVrNHpyME9jUEdMTlNTOVh6Qm41eG13UnhQZ1FUZ1pNZkpTQjZXbXYtVm9aUlptODgzWGstZUJ6bk9BNkhtVld6WEtBODk1bkN3ZjR3WnF0NnhtX25rTkhfajgzSG40MEMzNmVlQnBTTWNCRU1IeDE4VmZwZzY3bjVsc1BBWGpZLWthNTc5b3RzLXhaOFRPUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
         </is>
       </c>
     </row>
@@ -1128,61 +1128,61 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 4 - ArchDaily</t>
+          <t>Previsão do tempo Limestone VIC. 14 dias - Meteored Brasil</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>13/07/2026 20:59</t>
+          <t>14/07/2026 00:47</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPWUJ1VEZxajJHbVRUdm5YQnpJakE4WXlZRTVUQURmYkZRZUJWOG9jQnVVMENoc29FRV94SHlRTC1PUHV5dGtoMXVJTERVZnc5OE5GdFRlNFpvZml2VlZmc0RZRkt4S2JmdjVuMTUxUGxVSnI4c1VxZXdOYzdBQjNRZVVVTU5jSVZOeTJ3QkF0RTR2QWJab3hNTTRWS0lpWkZxd1ZuZ3VYV180ZjRKTjBPSmVQdkVzRkllRWdZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5uWS1sR2lPOGZ6UmtZa1l5ZF9uaVJPSXBBa21UcnNsLUFIYkI5VHdfSWdTQW0tNkhRVmxZY1BlNllNN1ZjdUU3eFFCZkRqeFY1VHQwWjdB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Uberaba propõe reduzir ISS para tentar preservar empregos após hibernação da Mosaic - Regionalzão</t>
+          <t>NASA revela imagens inéditas de enxofre puro em Marte: um “tesouro amarelo” descoberto pelo rover Curiosity - Noticias Ambientales</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>13/07/2026 20:54</t>
+          <t>13/07/2026 21:56</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE4xbkloamZJdlJQX1V6US13ZkFvei1CRk9vVDBVSElYMm1qUVZiMWY4Ynk1UlhEVlQ3bm5Ha1RmNXNrMjl5NEdwQ3pwMFBXNk9GUGppSm13aTdja1U1TzlaR1JQNEtSQzVXNFlXZ1FNbTZJWlRDbHhvRjQzb1BRNDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNOGpMbFZtUjdFd1JDQXp4WkVlc0FaLUxYVGU2WHNXRmRkUzVVb0hFcHFrSy1CYTFVUG5GdVZoVDdKQ0tkTC02ZkdSMUNhMS1TalRncjBKTldzUk54MDNHQl9OcE5MS0dkQ1c1LUJtWWQyX05vSGlKUFpnTGJjd2ptMUdjY2JpNEZpem5xOXNDMmo0M2l5R0JtZFcyR3lyTW1tQ2tvaVU3VkpOamdrdldSWTk0SWRMXzlJdDRpMHZ6WUwzVWNkc2ZhTDUtcmVsNXIzOW9VZHVnVVF6UEd4ZTRvcHpn0gHnAUFVX3lxTE9VR2NueC1oS2MzbzFWa3otdmJyS3dlQUV0M2dWQXZ3Q1NrSW9GR21TUTQ5YVZ6LTVrOFpqVkFudmdSTDBzMTlsLWlOTHdoWGJMT093cHpVODVrNHpyME9jUEdMTlNTOVh6Qm41eG13UnhQZ1FUZ1pNZkpTQjZXbXYtVm9aUlptODgzWGstZUJ6bk9BNkhtVld6WEtBODk1bkN3ZjR3WnF0NnhtX25rTkhfajgzSG40MEMzNmVlQnBTTWNCRU1IeDE4VmZwZzY3bjVsc1BBWGpZLWthNTc5b3RzLXhaOFRPUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Galeria de Kalesinterflex - Calcario Collection - 7 - ArchDaily</t>
+          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>13/07/2026 20:39</t>
+          <t>13/07/2026 20:59</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNVDlHVXpVUFBMa0lkMnhaQllMbll2U2ZzTHNHVlM1Y3ZQQ2p2cl8yRG5ENTBCOHdQWjdFU1E0b3RtVWhhb1I4VEpYOHAxaEdnT3BYV0tYSEVJcHI1OVlKOU9xLTRsWm83Q2FJQlEtSEMtdUh6anp3ZlhZWjM3THpsaDNLUTU1bmRzNDI0R1FIZXpqRnk5ckQwX2NVcXpFNFdVcFhsS0U2anJyX09NUUt0VEY3QURicm1FTHp1SVhfSm1rZWZvV0NUdkExYW1kOFBIU2xLeEoxMzI2cHpPazNjRnlKd19BRkpMS0owdGY1VjU2Wjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPWUJ1VEZxajJHbVRUdm5YQnpJakE4WXlZRTVUQURmYkZRZUJWOG9jQnVVMENoc29FRV94SHlRTC1PUHV5dGtoMXVJTERVZnc5OE5GdFRlNFpvZml2VlZmc0RZRkt4S2JmdjVuMTUxUGxVSnI4c1VxZXdOYzdBQjNRZVVVTU5jSVZOeTJ3QkF0RTR2QWJab3hNTTRWS0lpWkZxd1ZuZ3VYV180ZjRKTjBPSmVQdkVzRkllRWdZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1194,61 +1194,61 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes suspende atividades em Uberaba devido a falta de matéria-prima - boca.com.br</t>
+          <t>Uberaba propõe reduzir ISS para tentar preservar empregos após hibernação da Mosaic - Regionalzão</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>13/07/2026 19:10</t>
+          <t>13/07/2026 20:54</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPbzU1eXRUUF90emdmRXlVemljWE56RG1GV0h6aVA3eHJ2RHBhVTVVQkEwdnVvVjd5aEcxUjVDbmEwVm5UYVhyTF9pSFRmTU1XZlVDVzRuOUtYWUNXekhMYnJnejJYVVNoNkgyeWc1QWx0ODQ4R01XSU1SeHpQOUNocFN4ZkdxaUxSNk0zSnhnOEIwaVVVLXI4dHRWUDZBeGlpbVVuNldEdUtxMGlGWWpSWkxn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE4xbkloamZJdlJQX1V6US13ZkFvei1CRk9vVDBVSElYMm1qUVZiMWY4Ynk1UlhEVlQ3bm5Ha1RmNXNrMjl5NEdwQ3pwMFBXNk9GUGppSm13aTdja1U1TzlaR1JQNEtSQzVXNFlXZ1FNbTZJWlRDbHhvRjQzb1BRNDA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes inicia hibernação em Uberaba devido a falta de enxofre - Canal Rural</t>
+          <t>Galeria de Kalesinterflex - Calcario Collection - 7 - ArchDaily</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>13/07/2026 19:07</t>
+          <t>13/07/2026 20:39</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOV3NNYmk3Z2wtOE5EbW1waDVvbU1Wem1BWU1RcVc1SDNFN1FsZkZXcFFmMkxVYzh0Uml6dlJBcVBmdk9wbDI0cTVEU0lEbWNRc0hnYkZvRFdaYS1rXzFVWDBYRkZmLTA0bldYdERnQ3BRazJFNzdOYUVFZ3M3RFlHbE00YkNydXFaN1ljSEVlelNxMlFzQ0c5N3dqVGxBb095a1pLSGkwa1NZX2trQUJuZFJjMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNVDlHVXpVUFBMa0lkMnhaQllMbll2U2ZzTHNHVlM1Y3ZQQ2p2cl8yRG5ENTBCOHdQWjdFU1E0b3RtVWhhb1I4VEpYOHAxaEdnT3BYV0tYSEVJcHI1OVlKOU9xLTRsWm83Q2FJQlEtSEMtdUh6anp3ZlhZWjM3THpsaDNLUTU1bmRzNDI0R1FIZXpqRnk5ckQwX2NVcXpFNFdVcFhsS0U2anJyX09NUUt0VEY3QURicm1FTHp1SVhfSm1rZWZvV0NUdkExYW1kOFBIU2xLeEoxMzI2cHpPazNjRnlKd19BRkpMS0owdGY1VjU2Wjg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Livro A Rota do Calcário traz fatos curiosos sobre a história econômica de Arcos - Jornal Correio Centro Oeste Arcos</t>
+          <t>Mosaic Fertilizantes suspende atividades em Uberaba devido a falta de matéria-prima - boca.com.br</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>13/07/2026 19:03</t>
+          <t>13/07/2026 19:10</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPazk4R0l0bkdTOGVENHBvc195X3hZMmFrTVBlNXlSMl9SWENKRllNV2Q3THJ5R3k0RW9Qc3lXOXdzeld4WkFZVlN1cWpPZXhNQlRPUXo0ODhnRXlkdEUySEtUNXRucGE5cjJKR1QzTklOdjdocUdvVmszcElRcVh2QlZYVzVLSTkwZThVMWJ1WTBKR3BtMTBSSGhEa0xFUzI4OXdRREdMamhsN19GdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPbzU1eXRUUF90emdmRXlVemljWE56RG1GV0h6aVA3eHJ2RHBhVTVVQkEwdnVvVjd5aEcxUjVDbmEwVm5UYVhyTF9pSFRmTU1XZlVDVzRuOUtYWUNXekhMYnJnejJYVVNoNkgyeWc1QWx0ODQ4R01XSU1SeHpQOUNocFN4ZkdxaUxSNk0zSnhnOEIwaVVVLXI4dHRWUDZBeGlpbVVuNldEdUtxMGlGWWpSWkxn?oc=5</t>
         </is>
       </c>
     </row>
@@ -1260,39 +1260,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação temporária de atividades em Catalão devido à escassez global de enxofre - zapcatalao.com.br</t>
+          <t>Mosaic Fertilizantes inicia hibernação em Uberaba devido a falta de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>13/07/2026 18:45</t>
+          <t>13/07/2026 19:07</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPUGhkU2hMOC1vX0l4SVdHbUszZFpoV1AwcmlqU3l6a0h0aWdUb2dVWExIQ01NSFZuLS1UTGpoa29PQXI5TWhkQnA4Q1d6MEZwcDQtNHRlRGNlU0NhUG5kNFMxb25zLU11OVdORDVmdUR0aXViZldld0ZxUXNITXBTUjR6c0JmUVU4SXo5aGlmY1JTQkZHUFdGNzlub19lc3ByTEhLREd3MHgzY0xwRHBXeUVCM1FOQnQtUElyVTdvT0JBZ3l5SFpSWjFYMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOV3NNYmk3Z2wtOE5EbW1waDVvbU1Wem1BWU1RcVc1SDNFN1FsZkZXcFFmMkxVYzh0Uml6dlJBcVBmdk9wbDI0cTVEU0lEbWNRc0hnYkZvRFdaYS1rXzFVWDBYRkZmLTA0bldYdERnQ3BRazJFNzdOYUVFZ3M3RFlHbE00YkNydXFaN1ljSEVlelNxMlFzQ0c5N3dqVGxBb095a1pLSGkwa1NZX2trQUJuZFJjMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Maior demanda pela ureia interrompe movimento de queda em julho - Farmnews</t>
+          <t>Livro A Rota do Calcário traz fatos curiosos sobre a história econômica de Arcos - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>13/07/2026 17:45</t>
+          <t>13/07/2026 19:03</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNclVqZS1lVldPbUIzS3JZeHhEbHNZeUE2U3ZJa1RvMEdydThWNnp1MGt6UkFaZExEVWo0Nk5JSjV2cFpOUUlyWVZaRUxXZ3VaaHNmckhBRndIR0NTX196OGpnbVEzZDItazdET2xZM0VPQ1NCZVdoM3R6S3J6elE5MXVEM3VFQkRKX1dyMVJ5WWtjTXJkcndOckJWRXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPazk4R0l0bkdTOGVENHBvc195X3hZMmFrTVBlNXlSMl9SWENKRllNV2Q3THJ5R3k0RW9Qc3lXOXdzeld4WkFZVlN1cWpPZXhNQlRPUXo0ODhnRXlkdEUySEtUNXRucGE5cjJKR1QzTklOdjdocUdvVmszcElRcVh2QlZYVzVLSTkwZThVMWJ1WTBKR3BtMTBSSGhEa0xFUzI4OXdRREdMamhsN19GdWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -1304,39 +1304,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Uberaba propõe reduzir ISS após Mosaic anunciar hibernação da produção de fosfato - Diário do Comércio</t>
+          <t>Mosaic anuncia paralisação temporária de atividades em Catalão devido à escassez global de enxofre - zapcatalao.com.br</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>13/07/2026 14:50</t>
+          <t>13/07/2026 18:45</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1xY1VPeFZZNUwzYUc5dWxRWXlSS3JudmpJTEloR09RVUpxMmtjY1hSLUpTbkU2eHNDaEgxZW8tQTZicGpWMlZHb1ZNb21fZFE2aENLTlpGUjB3b2hxMk1hNXNsSnp6TkMtUXZCRExYR1BCSEktUk1idDZJYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPUGhkU2hMOC1vX0l4SVdHbUszZFpoV1AwcmlqU3l6a0h0aWdUb2dVWExIQ01NSFZuLS1UTGpoa29PQXI5TWhkQnA4Q1d6MEZwcDQtNHRlRGNlU0NhUG5kNFMxb25zLU11OVdORDVmdUR0aXViZldld0ZxUXNITXBTUjR6c0JmUVU4SXo5aGlmY1JTQkZHUFdGNzlub19lc3ByTEhLREd3MHgzY0xwRHBXeUVCM1FOQnQtUElyVTdvT0JBZ3l5SFpSWjFYMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tensão em Ormuz afeta produção de fertilizantes no Brasil - CNN Brasil</t>
+          <t>Maior demanda pela ureia interrompe movimento de queda em julho - Farmnews</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>13/07/2026 13:30</t>
+          <t>13/07/2026 17:45</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaU1rV2NIc09fUTUwZVc4TEI3NEhSZ19UcHVqdEJKaDJ5dDNqSDdUaGo2VXlpWUp6OEpoRnU4ZEpCb2MxQ1RURXV3S3dreU1Lc24tVk8wazB0OTBsN2RIMmVER0ROd2hxUE1QOEdPMFZkc01MQVlHcWdDNDN1dVNETzFQQV94cDFwV0VzeGozdldYbXBBMkQ0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNclVqZS1lVldPbUIzS3JZeHhEbHNZeUE2U3ZJa1RvMEdydThWNnp1MGt6UkFaZExEVWo0Nk5JSjV2cFpOUUlyWVZaRUxXZ3VaaHNmckhBRndIR0NTX196OGpnbVEzZDItazdET2xZM0VPQ1NCZVdoM3R6S3J6elE5MXVEM3VFQkRKX1dyMVJ5WWtjTXJkcndOckJWRXI?oc=5</t>
         </is>
       </c>
     </row>
@@ -1348,17 +1348,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação temporária das atividades em Goiás - Poder Goiás</t>
+          <t>Uberaba propõe reduzir ISS após Mosaic anunciar hibernação da produção de fosfato - Diário do Comércio</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>13/07/2026 11:57</t>
+          <t>13/07/2026 14:50</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxObURQMTIzVUVEOUNoMzlHMGY0dl9rWmdjdnRJRTNiLWNkWnNrVFp2WWh3ZmR0dnV0Z2ZwZWpBNmctUGJLV1FadDh5TDF5dHRXX3BtVUtUTnBZUnhyRE9GVmw2Y2VBSlVHYVpMNlprNVBnZ0p6dzEzRF9UWmhxeEQtdkdyQkZuYm5OYmFCM2JGVGUyNEdPcDNnUm53Y0VQbmUyVVZPa2ZpR2o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1xY1VPeFZZNUwzYUc5dWxRWXlSS3JudmpJTEloR09RVUpxMmtjY1hSLUpTbkU2eHNDaEgxZW8tQTZicGpWMlZHb1ZNb21fZFE2aENLTlpGUjB3b2hxMk1hNXNsSnp6TkMtUXZCRExYR1BCSEktUk1idDZJYw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1370,39 +1370,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rover Curiosity encontra cristais de enxofre puro em Marte após esmagar rocha por acidente - Nerdizmo</t>
+          <t>Tensão em Ormuz afeta produção de fertilizantes no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>13/07/2026 11:00</t>
+          <t>13/07/2026 13:30</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQU29hYlBaR21Yamp2VXpDekF6bHp6WnMxaGpaSDhEcEhpSGhsU0htSXg0VzQxMzc1Tjhqd1RFYlNiNmRqTWoyQVhUSFk5dkx4NjhGQjZqZVpaenlGZmRRdkdON3pEcm4ySzBKR2xnVlNKb2stQzhMaS1JQ0VicU1RUHFFUmZVeFZoRXhmbE9EZHljNjBfSXNMVG5LaUdTdmZBbzVCUUZxcGpyT2NXbHF1Y1NYYWxDeUJ0b2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaU1rV2NIc09fUTUwZVc4TEI3NEhSZ19UcHVqdEJKaDJ5dDNqSDdUaGo2VXlpWUp6OEpoRnU4ZEpCb2MxQ1RURXV3S3dreU1Lc24tVk8wazB0OTBsN2RIMmVER0ROd2hxUE1QOEdPMFZkc01MQVlHcWdDNDN1dVNETzFQQV94cDFwV0VzeGozdldYbXBBMkQ0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fertiliza Turmalina amplia atendimento e beneficiará 147 produtores com Agrosilício - csastudiowebradio.com.br</t>
+          <t>Mosaic anuncia paralisação temporária das atividades em Goiás - Poder Goiás</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>13/07/2026 10:58</t>
+          <t>13/07/2026 11:57</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOc2xrV0ZHYzhPOUk2dWlmMXBmZGR3ck52dVRESjJTNmw3TU1razRzR0hobkVHaXA1YjBObk9MTmMyQ2VxVVo5S29EQnhxMXdYb3YtcWVsdzZZUWJIZV9QUjY5aS1uQjJIMENzLXg3SWdwcFVhR3RfVkF5MnVBUkRYdnBKSUpfcnVqS01FVVA0WU1KU29aVThSZ0M3YzcxaFluTmRuYWdVTXlrMjRhMlBzbTNpNkVqNFNWRHV3b3Nfc1dmcy02VnhYRGpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxObURQMTIzVUVEOUNoMzlHMGY0dl9rWmdjdnRJRTNiLWNkWnNrVFp2WWh3ZmR0dnV0Z2ZwZWpBNmctUGJLV1FadDh5TDF5dHRXX3BtVUtUTnBZUnhyRE9GVmw2Y2VBSlVHYVpMNlprNVBnZ0p6dzEzRF9UWmhxeEQtdkdyQkZuYm5OYmFCM2JGVGUyNEdPcDNnUm53Y0VQbmUyVVZPa2ZpR2o?oc=5</t>
         </is>
       </c>
     </row>
@@ -1414,149 +1414,149 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
+          <t>Rover Curiosity encontra cristais de enxofre puro em Marte após esmagar rocha por acidente - Nerdizmo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>13/07/2026 10:31</t>
+          <t>13/07/2026 11:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQU29hYlBaR21Yamp2VXpDekF6bHp6WnMxaGpaSDhEcEhpSGhsU0htSXg0VzQxMzc1Tjhqd1RFYlNiNmRqTWoyQVhUSFk5dkx4NjhGQjZqZVpaenlGZmRRdkdON3pEcm4ySzBKR2xnVlNKb2stQzhMaS1JQ0VicU1RUHFFUmZVeFZoRXhmbE9EZHljNjBfSXNMVG5LaUdTdmZBbzVCUUZxcGpyT2NXbHF1Y1NYYWxDeUJ0b2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes no Brasil e unidade de Catalão terá paralisação temporária - O CORREIO NEWS</t>
+          <t>Fertiliza Turmalina amplia atendimento e beneficiará 147 produtores com Agrosilício - csastudiowebradio.com.br</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>13/07/2026 10:29</t>
+          <t>13/07/2026 10:58</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSGE2ZEdaY3pESWY1LW5oWnVIRW1HSWM1bUJfZ1Z3RVI5RDJvdFJlOGpqZkFaYnAxM05iZHh5T05UeTl1dWZKZHZyUHVRd0NFUTR0d3hkbHF1dFJWZUJocUxVMmQyVnhrclQyQ1lGTXNIV2FmOG9EWnhac01uZmZKOU5DWGxIRnJTaUxaVFA5WklOeHVaakpZZWZsZVhXcWctX0dhdDlOU2VIY2w0MXp6X2NYZWJQUmtyR0UxZ2lVZzFLd0lFQU1GR0ZuQUoySlF3U0ZvOEpiZlA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOc2xrV0ZHYzhPOUk2dWlmMXBmZGR3ck52dVRESjJTNmw3TU1razRzR0hobkVHaXA1YjBObk9MTmMyQ2VxVVo5S29EQnhxMXdYb3YtcWVsdzZZUWJIZV9QUjY5aS1uQjJIMENzLXg3SWdwcFVhR3RfVkF5MnVBUkRYdnBKSUpfcnVqS01FVVA0WU1KU29aVThSZ0M3YzcxaFluTmRuYWdVTXlrMjRhMlBzbTNpNkVqNFNWRHV3b3Nfc1dmcy02VnhYRGpR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação temporária da unidade de Catalão por escassez global de enxofre - Portal Serra Dourada News</t>
+          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>13/07/2026 10:14</t>
+          <t>13/07/2026 10:31</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQTWV4dkpSb09jVG43Rk5yY3oybVJnNXowZjFORV9XWUdMMVl1X3ZvYkVkYnk5d3dtNVIxb05IcC1aeXQzWFJjYVFCbUdjdlFHZHlWS2Naa0ttY0dNaVJodGtNNGRaaWVwYUFja3ctQlluZTZVUVdYNWF6V1MwVE00MlVOOGhDNkJvSFU1VFlqd2wwa3hnczdVNTFyVmpxWTFnTnl3RlU1QjRyUHdBYWI4Z0UxQ09QdHBkQUVrZXExc18tUkptWHNsekp1YnI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Galeria de Masonry Stone Walls - Dietfurt Limestone - 1 - ArchDaily</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil e unidade de Catalão terá paralisação temporária - O CORREIO NEWS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>13/07/2026 09:49</t>
+          <t>13/07/2026 10:29</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxPcHRFajVmOVhoREJOaGxGWkdTTXlmVW9kWGFvaDl6dHByQmFTTzNyMEY1cHdTNE5zeWIzRERxSnNzZDdxMjdMOXBWSVdqaE16bUxFVmQwQW1nbGREWldkekNfOVJUZEo0dWRyTk9zLXotcS1ZT1dka3BOcWptMlZwVm9faVB6czAzcG5vUXc2Mnd3N3B0V2hmcnhkT3JORTJWS2pSeXZuVU9GbWFZempvNFQ4Wlg5VnhzYVY4VHN6Vk5taklscWdfelRxNzJtNURWcXJRM0pVVXdfbkZ0TWxWS0hTY01QTmJyRkJkZlNZcjhwSG5CbmxENEktT2E0YUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSGE2ZEdaY3pESWY1LW5oWnVIRW1HSWM1bUJfZ1Z3RVI5RDJvdFJlOGpqZkFaYnAxM05iZHh5T05UeTl1dWZKZHZyUHVRd0NFUTR0d3hkbHF1dFJWZUJocUxVMmQyVnhrclQyQ1lGTXNIV2FmOG9EWnhac01uZmZKOU5DWGxIRnJTaUxaVFA5WklOeHVaakpZZWZsZVhXcWctX0dhdDlOU2VIY2w0MXp6X2NYZWJQUmtyR0UxZ2lVZzFLd0lFQU1GR0ZuQUoySlF3U0ZvOEpiZlA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Guerra entre EUA e Irã ameaça fertilizantes e acende alerta para agricultores do Brasil - A Referência</t>
+          <t>Mosaic prorroga paralisação temporária da unidade de Catalão por escassez global de enxofre - Portal Serra Dourada News</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>12/07/2026 21:58</t>
+          <t>13/07/2026 10:14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOc0o3SzR2VWFVY3M3RVRIZ3dQUThlTmJpVXpQSnp2X28yMlFsNER4S3RYOFhoQy03YUZCdm9MOG1NRDVaMmR4cXNiVy1vQzNzaXlMdTFDek9kUVZiNWNpSmJxckFCZmJVMkpWY0Y5SURXZks4VG10M1l3dlNkTGlpV2lvMEtNaEpRam5sUUo4bmE2Qk1VSGl0VHY2UjV1M0hKZ0lCUG00ZENSVkFRVnFtY3UzNExaY3pQWkxmX0dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQTWV4dkpSb09jVG43Rk5yY3oybVJnNXowZjFORV9XWUdMMVl1X3ZvYkVkYnk5d3dtNVIxb05IcC1aeXQzWFJjYVFCbUdjdlFHZHlWS2Naa0ttY0dNaVJodGtNNGRaaWVwYUFja3ctQlluZTZVUVdYNWF6V1MwVE00MlVOOGhDNkJvSFU1VFlqd2wwa3hnczdVNTFyVmpxWTFnTnl3RlU1QjRyUHdBYWI4Z0UxQ09QdHBkQUVrZXExc18tUkptWHNsekp1YnI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Um helicóptero despeja 200 toneladas de calcário por dia sobre lagos da Suécia, faz 162 carregamentos em uma única jornada e tenta neutralizar a chuva ácida que alterou a química da água durante décadas - CPG Click Petróleo e Gás</t>
+          <t>Galeria de Masonry Stone Walls - Dietfurt Limestone - 1 - ArchDaily</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>12/07/2026 21:41</t>
+          <t>13/07/2026 09:49</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxPMHBUZUlrOVNEWUdWdW85U1h6YVExN3F4UGhUMDFfaXk1RmRDZ1I2Z3BkaXVwVkNrSzVTdGFvMFNhVk12b3VJajRhRlAwYTJ0QVZPRnI0MTFQeFdybDdBVkFnLUhkS19Oei0yRTJ6bWpxVS0zRUU0Slp3QnZzZG5tZjNJSm9DN25FMTJoTEN2U01oQllxc3MyX1RneGJRVElVeGgxQm9nMHRhVFYzOUlIRDhKcUF5YzJ2dGdQZ0tzR0ZYcUxmUXdsVTFKS3A4RXBvYkczSHV0Zk5ZNW5pbmtLeFpFYTVJeDhzN0JHeHRSQ2hsSk1TZ2JubFVUT0NfN3pTSG40SU85WF9VMEJTYmt5bHdNWW9jTlpHeWhQdzRITUtXV3ltSFoycmttVXRsMGtnSTNTMTEza3E2WXlhUkhtY2dnbzhDUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxPcHRFajVmOVhoREJOaGxGWkdTTXlmVW9kWGFvaDl6dHByQmFTTzNyMEY1cHdTNE5zeWIzRERxSnNzZDdxMjdMOXBWSVdqaE16bUxFVmQwQW1nbGREWldkekNfOVJUZEo0dWRyTk9zLXotcS1ZT1dka3BOcWptMlZwVm9faVB6czAzcG5vUXc2Mnd3N3B0V2hmcnhkT3JORTJWS2pSeXZuVU9GbWFZempvNFQ4Wlg5VnhzYVY4VHN6Vk5taklscWdfelRxNzJtNURWcXJRM0pVVXdfbkZ0TWxWS0hTY01QTmJyRkJkZlNZcjhwSG5CbmxENEktT2E0YUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Desenvolvido ao longo de quase duas décadas num laboratório, o concreto "vivo" com bactérias que fabricam calcário e fecham sozinhas as próprias rachaduras já chegou a áreas do aeroporto de Schiphol e a um estacionamento de 12.000 m² na Holanda - CPG Click Petróleo e Gás</t>
+          <t>Guerra entre EUA e Irã ameaça fertilizantes e acende alerta para agricultores do Brasil - A Referência</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>12/07/2026 20:45</t>
+          <t>12/07/2026 21:58</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxONFI3b2x4REx2NFFYMm5rQTdWTl9YU1JsS1VGa0w0azdsczVXQzdaSHBWbHNXeXpNS1ZtUVlRU1VUUWtSR3ZLc2hhMWdjbklURTk4Q0JycEJpU1l6ZGtNVldqWUV0Q0lzd1pNdGZVNmlhUE84dmhtOTEyRHFLVFRoUnRmaHNYRHZMVzQySG1tQl9UaU1kOUFvS2N5NmZSU0lvNUdPNjBjanF1a2RQVE4wSUdRSVFUY0ZfbnZQT291R0xrX2ZtOWhHaVlNcnI1NVdWZ0JmM0huN0lMV0s2ZkZXLUJ3dnFHZTh1bXZTcVhzMDRFVldaQ3VSZmkyLWRXMGFiZ3p1dUh2by1uLWUyTGM4bXA2dmswVUVkazM5MGluSV9nYVhEUTYwRWF6T1JpSjhKbHFIYXpQVS1Sc0lDSWc5VVNKNjhIS0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOc0o3SzR2VWFVY3M3RVRIZ3dQUThlTmJpVXpQSnp2X28yMlFsNER4S3RYOFhoQy03YUZCdm9MOG1NRDVaMmR4cXNiVy1vQzNzaXlMdTFDek9kUVZiNWNpSmJxckFCZmJVMkpWY0Y5SURXZks4VG10M1l3dlNkTGlpV2lvMEtNaEpRam5sUUo4bmE2Qk1VSGl0VHY2UjV1M0hKZ0lCUG00ZENSVkFRVnFtY3UzNExaY3pQWkxmX0dR?oc=5</t>
         </is>
       </c>
     </row>
@@ -1568,127 +1568,127 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alta nos fosfatados: o desafio do produtor e o papel estratégico do calcário por Surama Geleilate - Conexao 085</t>
+          <t>Um helicóptero despeja 200 toneladas de calcário por dia sobre lagos da Suécia, faz 162 carregamentos em uma única jornada e tenta neutralizar a chuva ácida que alterou a química da água durante décadas - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>12/07/2026 18:04</t>
+          <t>12/07/2026 21:41</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOMWtCT3VtS2lJOWlkOW9RT0JCX29mUi1aTE1Vb0J2TFBIc3p1Z2x6VnhrelhEcHYyQlJfeTVxdndiWUN6Y3V0a2tMOEVnUXlWWFVmMS1uelRvc3ZjMXk3Mmp5NjRTV3lRX3pNUGJ4WkZobFBwSWVJLWh2dGxKUWtKUHluby1jRjhFM1ZFYmNKZEs3Tlk2Q3oxQ2s5eUoxRm9halFVeER3OUp2YWhMaUpCdWZLWUVCUVdfU29ZMWRDd3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxPMHBUZUlrOVNEWUdWdW85U1h6YVExN3F4UGhUMDFfaXk1RmRDZ1I2Z3BkaXVwVkNrSzVTdGFvMFNhVk12b3VJajRhRlAwYTJ0QVZPRnI0MTFQeFdybDdBVkFnLUhkS19Oei0yRTJ6bWpxVS0zRUU0Slp3QnZzZG5tZjNJSm9DN25FMTJoTEN2U01oQllxc3MyX1RneGJRVElVeGgxQm9nMHRhVFYzOUlIRDhKcUF5YzJ2dGdQZ0tzR0ZYcUxmUXdsVTFKS3A4RXBvYkczSHV0Zk5ZNW5pbmtLeFpFYTVJeDhzN0JHeHRSQ2hsSk1TZ2JubFVUT0NfN3pTSG40SU85WF9VMEJTYmt5bHdNWW9jTlpHeWhQdzRITUtXV3ltSFoycmttVXRsMGtnSTNTMTEza3E2WXlhUkhtY2dnbzhDUkE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação em Catalão após crise global no fornecimento de enxofre - Diário da Manhã</t>
+          <t>Desenvolvido ao longo de quase duas décadas num laboratório, o concreto "vivo" com bactérias que fabricam calcário e fecham sozinhas as próprias rachaduras já chegou a áreas do aeroporto de Schiphol e a um estacionamento de 12.000 m² na Holanda - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>12/07/2026 14:31</t>
+          <t>12/07/2026 20:45</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQOWs2WThKNnh3N0pGT0xNMWRoc0xuWS1aSW9ZMFlUWVJmSllnLVZieEpiMVhwSTkwcWVoeUJWSGo4MWVqX09QU0Z2YXlOSXpuZW9saTZJTjBxbU1fOVRRWl9SVFV5eEM4bXRzX2Q2X0trV1RnQzZXb2M2MXVNMXFBM1RkcmJjalJmSW1mOEl0ZGlESHJnUXpuYlJPdkQ0TDNDeEE2QzVMYWx2RHZONS1ldXhoeEdnUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxONFI3b2x4REx2NFFYMm5rQTdWTl9YU1JsS1VGa0w0azdsczVXQzdaSHBWbHNXeXpNS1ZtUVlRU1VUUWtSR3ZLc2hhMWdjbklURTk4Q0JycEJpU1l6ZGtNVldqWUV0Q0lzd1pNdGZVNmlhUE84dmhtOTEyRHFLVFRoUnRmaHNYRHZMVzQySG1tQl9UaU1kOUFvS2N5NmZSU0lvNUdPNjBjanF1a2RQVE4wSUdRSVFUY0ZfbnZQT291R0xrX2ZtOWhHaVlNcnI1NVdWZ0JmM0huN0lMV0s2ZkZXLUJ3dnFHZTh1bXZTcVhzMDRFVldaQ3VSZmkyLWRXMGFiZ3p1dUh2by1uLWUyTGM4bXA2dmswVUVkazM5MGluSV9nYVhEUTYwRWF6T1JpSjhKbHFIYXpQVS1Sc0lDSWc5VVNKNjhIS0U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes no Brasil e unidade de Catalão terá paralisação temporária - Mais Goiás</t>
+          <t>Alta nos fosfatados: o desafio do produtor e o papel estratégico do calcário por Surama Geleilate - Conexao 085</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>12/07/2026 12:51</t>
+          <t>12/07/2026 18:04</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPM3VPUnViV3c5azFIVjI2U2s1QnJuRm90bXJreE0yS2hJVlJOMlY2bm5GNlBBbHIxc0xSZEU1RzE4d1E5bTYzR3NVMy1mNUtIeklma1RJNWFXcWxBTUYzT3VEUndQb0JidTh3S0R6T01XQ3lOQkptQVVoZ2VxWF9fSDRwTHFoa1pLNVFkTE1paU1UTDBIbnhYcEprNndQVHJVekRHd2ZlanRYM0Zra09LR3VSZmVNdzhPMUFqNWFFRFBjNkFMSzZObXdzQnFYa2V6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOMWtCT3VtS2lJOWlkOW9RT0JCX29mUi1aTE1Vb0J2TFBIc3p1Z2x6VnhrelhEcHYyQlJfeTVxdndiWUN6Y3V0a2tMOEVnUXlWWFVmMS1uelRvc3ZjMXk3Mmp5NjRTV3lRX3pNUGJ4WkZobFBwSWVJLWh2dGxKUWtKUHluby1jRjhFM1ZFYmNKZEs3Tlk2Q3oxQ2s5eUoxRm9halFVeER3OUp2YWhMaUpCdWZLWUVCUVdfU29ZMWRDd3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Inteligência artificial decifra as regras de um jogo de tabuleiro romano perdido, encontrado em uma pedra de 20 centímetros na Holanda</t>
+          <t>Mosaic prorroga paralisação em Catalão após crise global no fornecimento de enxofre - Diário da Manhã</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>12/07/2026 12:44</t>
+          <t>12/07/2026 14:31</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57664828474851ae9d3badd71e75f8&amp;url=https%3a%2f%2fclickpetroleoegas.com.br%2finteligencia-artificial-decifra-as-regras-de-um-jogo-de-tabuleiro-romano-perdido-encontrado-em-uma-pedra-de-20-centimetros-na-holanda-flpc96%2f&amp;c=951759223804362979&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQOWs2WThKNnh3N0pGT0xNMWRoc0xuWS1aSW9ZMFlUWVJmSllnLVZieEpiMVhwSTkwcWVoeUJWSGo4MWVqX09QU0Z2YXlOSXpuZW9saTZJTjBxbU1fOVRRWl9SVFV5eEM4bXRzX2Q2X0trV1RnQzZXb2M2MXVNMXFBM1RkcmJjalJmSW1mOEl0ZGlESHJnUXpuYlJPdkQ0TDNDeEE2QzVMYWx2RHZONS1ldXhoeEdnUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 10 - ArchDaily</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil e unidade de Catalão terá paralisação temporária - Mais Goiás</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>12/07/2026 10:11</t>
+          <t>12/07/2026 12:51</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNaWdNVDVyUi1tZURyb1ZtdUlTdnRGNlNvbjJNY1lUa0RwRHVKZ1pyOTEzZ2N2d0xtUUQwSmpOS0RjbmJhUWE2WnYtU1lkZWpwejM3TFU3LWJwQmx2UVlNU1NLQ1RqTkNjLUgxZmN2cEJHVFNaSGFsTzEyLXM2ZXl6ZlZwNnJzWUF2NHlnNzZFZVFpSWEta25zUk5xcXkxYjM3cUw1VUJlUzRQTXNlTWdueVRKS1lmOUtLLWVBZVN1aDhwZnEtX05CUTJrMUN6bFVheGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPM3VPUnViV3c5azFIVjI2U2s1QnJuRm90bXJreE0yS2hJVlJOMlY2bm5GNlBBbHIxc0xSZEU1RzE4d1E5bTYzR3NVMy1mNUtIeklma1RJNWFXcWxBTUYzT3VEUndQb0JidTh3S0R6T01XQ3lOQkptQVVoZ2VxWF9fSDRwTHFoa1pLNVFkTE1paU1UTDBIbnhYcEprNndQVHJVekRHd2ZlanRYM0Zra09LR3VSZmVNdzhPMUFqNWFFRFBjNkFMSzZObXdzQnFYa2V6?oc=5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação temporária das atividades em Goiás - O Popular</t>
+          <t>Inteligência artificial decifra as regras de um jogo de tabuleiro romano perdido, encontrado em uma pedra de 20 centímetros na Holanda</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>12/07/2026 09:03</t>
+          <t>12/07/2026 12:44</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd1hMbnIzRXEzWC13ZTRoRXcxbDhCeUhEbkRYY1ZObjhPczh6RlpSZVEwck9FelpCT0pzcGhST2xDMHNTV1dRdDIyYWQ0T00wRXFnaHd5VDc2SDJqbmlvTzg0Rk95R3VaUktfaUp4VFZBT2FWaXJEbFBoMEloOElESjVtUkNRQnJ6a3A4SGhTZTVWQXdpb3RpZUt0X2EyVmFGSGs2cXBoVQ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a577b6af73c4bbf98758b0ad23a58ba&amp;url=https%3a%2f%2fclickpetroleoegas.com.br%2finteligencia-artificial-decifra-as-regras-de-um-jogo-de-tabuleiro-romano-perdido-encontrado-em-uma-pedra-de-20-centimetros-na-holanda-flpc96%2f&amp;c=951759223804362979&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1700,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 12 - ArchDaily</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 10 - ArchDaily</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>11/07/2026 23:15</t>
+          <t>12/07/2026 10:11</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPSklsTFVWbjJRWGtvNWtSM2lpTFpVT1g0Um93ckxMR3o3RWZKNE5QMmpmWmVNS05QLWdaUFlvXzNmY3FFV0l6d1VDX0R1cWdaS1lqTm9vY1U5U1VEbXhhM2NQa0VKWnJneWsxTGNsb0lHTW1rekdmbUNtc1BoNDFJcUdURVFueWlnZGRrUTBWOW1UOTlhMExHSFcyNGdEVTZQaUZsWXFVVW9XaUoxYklCQWpqdGY0QzNLMFI5WWlZMDhZQlpNV0N6WVdENUhkWlBVeGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNaWdNVDVyUi1tZURyb1ZtdUlTdnRGNlNvbjJNY1lUa0RwRHVKZ1pyOTEzZ2N2d0xtUUQwSmpOS0RjbmJhUWE2WnYtU1lkZWpwejM3TFU3LWJwQmx2UVlNU1NLQ1RqTkNjLUgxZmN2cEJHVFNaSGFsTzEyLXM2ZXl6ZlZwNnJzWUF2NHlnNzZFZVFpSWEta25zUk5xcXkxYjM3cUw1VUJlUzRQTXNlTWdueVRKS1lmOUtLLWVBZVN1aDhwZnEtX05CUTJrMUN6bFVheGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -1722,39 +1722,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Demissão Mosaic Bahia: 500 funcionários serão demitidos - Associação Comercial e Industrial de Araçatuba</t>
+          <t>Mosaic anuncia paralisação temporária das atividades em Goiás - O Popular</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>11/07/2026 04:40</t>
+          <t>12/07/2026 09:03</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB2bXdPVjU4Rmg1U1NwYk9rUnpnbHBSZEgxc3VxcGdabmRCMVVBRXpfMnB5eHRUUFJXT3R5Q3lEWS1YQlNGTnNmZ05OSlEweDljT2lyUkVXYnRiQ2hPdTJnZHQ5cHJUbFoxdEFEbjFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd1hMbnIzRXEzWC13ZTRoRXcxbDhCeUhEbkRYY1ZObjhPczh6RlpSZVEwck9FelpCT0pzcGhST2xDMHNTV1dRdDIyYWQ0T00wRXFnaHd5VDc2SDJqbmlvTzg0Rk95R3VaUktfaUp4VFZBT2FWaXJEbFBoMEloOElESjVtUkNRQnJ6a3A4SGhTZTVWQXdpb3RpZUt0X2EyVmFGSGs2cXBoVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Importação de ureia em junho de 2026: preço sobe e volume cai - Associação Comercial e Industrial de Araçatuba</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 12 - ArchDaily</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>11/07/2026 04:35</t>
+          <t>11/07/2026 23:15</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFB0ZGdwcy1Wb1F1M3dJbm50LTVDZndVVHRyUGp2NGRiN1BQVzdISGZaWWdqRjQxY3RyRTd4S3BQQ2o2ZnZNbFlwOWVNenpGcGl0aERvQzJyYUtZNUdpSVpoZFEwRzZjZFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPSklsTFVWbjJRWGtvNWtSM2lpTFpVT1g0Um93ckxMR3o3RWZKNE5QMmpmWmVNS05QLWdaUFlvXzNmY3FFV0l6d1VDX0R1cWdaS1lqTm9vY1U5U1VEbXhhM2NQa0VKWnJneWsxTGNsb0lHTW1rekdmbUNtc1BoNDFJcUdURVFueWlnZGRrUTBWOW1UOTlhMExHSFcyNGdEVTZQaUZsWXFVVW9XaUoxYklCQWpqdGY0QzNLMFI5WWlZMDhZQlpNV0N6WVdENUhkWlBVeGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -1766,39 +1766,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - MSN</t>
+          <t>Demissão Mosaic Bahia: 500 funcionários serão demitidos - Associação Comercial e Industrial de Araçatuba</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>11/07/2026 00:13</t>
+          <t>11/07/2026 04:40</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOUmNxdWp0UlRQWmJiM3ZlY2FwZ0Nad2NUMzF0M2ZJSE43NXg5U29DT0wxSURtQTlLdnpYdlRUZXhSaFB6UUlpYmxfN09VeUs1X1B4MTd1ODVyb1hpT0w1THpjY0FTVGQwUXdJTkY4akpiVXAxYnFydnlVR0k2ckYtQW5Yckp5TUtBNTFpVDJkek85cnhsbnRYSnF3cjJQbV9zTW9US3lUN1EtVFdjSm5EcWRhRXdtR3d4WVRSZWxwR1NoRHZUTm0tZVhrMUNUMTVwa3N0LXJCREhEUEFJTVd6TUp1QzJ3Mm1kUWNjRVVtczVWWDFa?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB2bXdPVjU4Rmg1U1NwYk9rUnpnbHBSZEgxc3VxcGdabmRCMVVBRXpfMnB5eHRUUFJXT3R5Q3lEWS1YQlNGTnNmZ05OSlEweDljT2lyUkVXYnRiQ2hPdTJnZHQ5cHJUbFoxdEFEbjFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Anderson Adauto articula ação com sindicatos e promete levar crise da Mosaic ao governo federal - Folha de Uberaba</t>
+          <t>Importação de ureia em junho de 2026: preço sobe e volume cai - Associação Comercial e Industrial de Araçatuba</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>10/07/2026 23:16</t>
+          <t>11/07/2026 04:35</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQbjRwcEFiRTF6ZlBDOE9FYmt1ZnJQVjZXN3FmSTJwaENRUDNYWm5rR25PY0dWb1lUdGhxeENUNFMzdS1ubnI4SEZUa3NQbVo0d0t1RVJoT2tuRUM0MFpCMy1yMnc5LVcwZHd2YmgzVDFZc0V3YUZ3ZmhkWnE2VXJNZE5FV3B2eW41ZGhHMDNPS25aNDhxeTloZ1BwU0VQclJfVEs3M3U1a2FYalBqMmcwMFg1MUE2aVVCaXhYNGRLRHhGUXZjYXNF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFB0ZGdwcy1Wb1F1M3dJbm50LTVDZndVVHRyUGp2NGRiN1BQVzdISGZaWWdqRjQxY3RyRTd4S3BQQ2o2ZnZNbFlwOWVNenpGcGl0aERvQzJyYUtZNUdpSVpoZFEwRzZjZFU?oc=5</t>
         </is>
       </c>
     </row>
@@ -1810,17 +1810,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Anderson articula frente em Brasília em defesa dos empregos e da indústria - JM Online</t>
+          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - MSN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>10/07/2026 23:02</t>
+          <t>11/07/2026 00:13</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTEZpWWZfRnhBMFNlTHVkck43ajB5eWM4ZG5Ia1BQRUFHMTdaLTZoZlluV0Zac243OTE4dUhocS1OWUdVMk10RFJHcmRVS29UNWVIX2VsQUdNeVQ3dndyUEEwUkRDSkxzc3VuN1VBVC1XdkFpRjhzRFh1elJzNlowcklvVHlUaEd5aWlOY0pIT2RLbi1FNnFVY2RKbDNWejF0NFJuVXBmNUJIendFWFJYOWVjUHF3S0nSAb8BQVVfeXFMTVo3Yml6b05zemlGcVJoYnlXUk1ER1dXSUpDMXJqbWJZb0l5U2xWbk1sVnF5NHNGUWd4OGdFQXE5YzNCdTZRWmZiblpXdGUza0hKaDVJRXFQa01vSzQxYmp0dTJoRUVYSGdjY0d1eGpPdW1JT1QwQ09RU3BsV0JRamY3ZUhvd2YxcWw5MEZidEN1NDlHZ0ZjMFp6blZWcEQ3R01iUGxiZmw3aDJyMElEX3JDX1dCU0xuS2o5amc0clk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOUmNxdWp0UlRQWmJiM3ZlY2FwZ0Nad2NUMzF0M2ZJSE43NXg5U29DT0wxSURtQTlLdnpYdlRUZXhSaFB6UUlpYmxfN09VeUs1X1B4MTd1ODVyb1hpT0w1THpjY0FTVGQwUXdJTkY4akpiVXAxYnFydnlVR0k2ckYtQW5Yckp5TUtBNTFpVDJkek85cnhsbnRYSnF3cjJQbV9zTW9US3lUN1EtVFdjSm5EcWRhRXdtR3d4WVRSZWxwR1NoRHZUTm0tZVhrMUNUMTVwa3N0LXJCREhEUEFJTVd6TUp1QzJ3Mm1kUWNjRVVtczVWWDFa?oc=5</t>
         </is>
       </c>
     </row>
@@ -1832,17 +1832,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - G1</t>
+          <t>Anderson Adauto articula ação com sindicatos e promete levar crise da Mosaic ao governo federal - Folha de Uberaba</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>10/07/2026 21:55</t>
+          <t>10/07/2026 23:16</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOWTREUFFrb3B2UGF1dWRjQmhXM3lTdFJEX0JyRUhPSWp5R3ZicTk2YWh1YnBwbXpTbnpRSnZ6cUQ3aUx1LVU4b0dub1E2WkFfUnlHZzNmTG1VSkNVYVYzci0tbzRuX2hxSmpRRXlvYzlUcVAwSFdKbXVTOVlqSjlvcGllMVA0YWF0QlhnV2xKYmkyU1FxSlFoam5vcFVFQWZSekhqOFUtc0RNZXJ3eUlmS1VMY0J0cmxXbHlZczZWTjFfNmswMGh3VXRpMXJ6a0RYekhnZFZmUmlKTFl0RHBQUUdzRdIB8gFBVV95cUxNT1QwMkdFYWF6R1V3NHpfSVBHZFFDbHNhTzVOQkFSMmkweGxLaldvZXhOY0I5SkFObWJCcWlmN1FZdk9zOHVwMVZIck5oZHJEb2pRakltU01QS2prLWZublBLekVpNGtHY1JHNlhObHRlelRBM0ZGaTNwTkFZaUNFMTZBNkV1SEZSOWMzRndwd3h5ZGZhdWprczhBOXNlbF9NMlBsV0tEdVFQUXhnT1BMdjdCbnVKY3BWdzVUeDdWLV9HTDZGeVFMd3h1OS1jTWlIMnROQlc5VnRFUmE2VnpXVXJ3Vl9QSGZZTVNhdkFVZE9NZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQbjRwcEFiRTF6ZlBDOE9FYmt1ZnJQVjZXN3FmSTJwaENRUDNYWm5rR25PY0dWb1lUdGhxeENUNFMzdS1ubnI4SEZUa3NQbVo0d0t1RVJoT2tuRUM0MFpCMy1yMnc5LVcwZHd2YmgzVDFZc0V3YUZ3ZmhkWnE2VXJNZE5FV3B2eW41ZGhHMDNPS25aNDhxeTloZ1BwU0VQclJfVEs3M3U1a2FYalBqMmcwMFg1MUE2aVVCaXhYNGRLRHhGUXZjYXNF?oc=5</t>
         </is>
       </c>
     </row>
@@ -1854,39 +1854,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
+          <t>Anderson articula frente em Brasília em defesa dos empregos e da indústria - JM Online</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>10/07/2026 19:30</t>
+          <t>10/07/2026 23:02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTEZpWWZfRnhBMFNlTHVkck43ajB5eWM4ZG5Ia1BQRUFHMTdaLTZoZlluV0Zac243OTE4dUhocS1OWUdVMk10RFJHcmRVS29UNWVIX2VsQUdNeVQ3dndyUEEwUkRDSkxzc3VuN1VBVC1XdkFpRjhzRFh1elJzNlowcklvVHlUaEd5aWlOY0pIT2RLbi1FNnFVY2RKbDNWejF0NFJuVXBmNUJIendFWFJYOWVjUHF3S0nSAb8BQVVfeXFMTVo3Yml6b05zemlGcVJoYnlXUk1ER1dXSUpDMXJqbWJZb0l5U2xWbk1sVnF5NHNGUWd4OGdFQXE5YzNCdTZRWmZiblpXdGUza0hKaDVJRXFQa01vSzQxYmp0dTJoRUVYSGdjY0d1eGpPdW1JT1QwQ09RU3BsV0JRamY3ZUhvd2YxcWw5MEZidEN1NDlHZ0ZjMFp6blZWcEQ3R01iUGxiZmw3aDJyMElEX3JDX1dCU0xuS2o5amc0clk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Disney Dreamlight Valley: Guia da missão Thought, Fog, and Light - games.gg</t>
+          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - G1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>10/07/2026 18:43</t>
+          <t>10/07/2026 21:55</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQTEFYMVVkWnNPUEx1bWRqU2ptdG1xYjlLSnBjbHFlMjFybG85YW80eS1pb2hBT20yazM3dUZ6emJBcXItajNfZlhNVjJwclpjd3R4b1lNMHI1MDQtTUFHU3VhYllpNkJIWlVJSDdOaThOLTg5cDExRy0xVFZReElDbDdvbXFOc24tVjM0RHBPVVhnQVctbURONzdaZFU4al90M2p0MnhEbzc4eXRvYXdmYjZFb2hOLVJXZmluSU16QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOWTREUFFrb3B2UGF1dWRjQmhXM3lTdFJEX0JyRUhPSWp5R3ZicTk2YWh1YnBwbXpTbnpRSnZ6cUQ3aUx1LVU4b0dub1E2WkFfUnlHZzNmTG1VSkNVYVYzci0tbzRuX2hxSmpRRXlvYzlUcVAwSFdKbXVTOVlqSjlvcGllMVA0YWF0QlhnV2xKYmkyU1FxSlFoam5vcFVFQWZSekhqOFUtc0RNZXJ3eUlmS1VMY0J0cmxXbHlZczZWTjFfNmswMGh3VXRpMXJ6a0RYekhnZFZmUmlKTFl0RHBQUUdzRdIB8gFBVV95cUxNT1QwMkdFYWF6R1V3NHpfSVBHZFFDbHNhTzVOQkFSMmkweGxLaldvZXhOY0I5SkFObWJCcWlmN1FZdk9zOHVwMVZIck5oZHJEb2pRakltU01QS2prLWZublBLekVpNGtHY1JHNlhObHRlelRBM0ZGaTNwTkFZaUNFMTZBNkV1SEZSOWMzRndwd3h5ZGZhdWprczhBOXNlbF9NMlBsV0tEdVFQUXhnT1BMdjdCbnVKY3BWdzVUeDdWLV9HTDZGeVFMd3h1OS1jTWlIMnROQlc5VnRFUmE2VnpXVXJ3Vl9QSGZZTVNhdkFVZE9NZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1898,83 +1898,83 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fosfato no Brasil por restrições no fornecimento de enxofre - Canal Rural</t>
+          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>10/07/2026 17:18</t>
+          <t>10/07/2026 19:30</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPeG9YelAzMGdHdy0zZUNKcE9xYUczeVNvb3cxZTVPMEkyLXhUeTNHOUhDRU5hRjdZMzdZT2JzYlNGRW1oUzBPbHRKSnV2WXVlZFRYZ0F2Y3I0RHZxUWpMM3JKMEk5SG4yLTcyTk1PcjhpZFEwYmhKekVEY25razQyeEJURU5SMmE1NGIybVozNTJ2dldsemk4elE4LXhNa3BOeUdDZzBiWi03R0FaWWhYa3ctb1pEcEZhaWgwcldUVTl0MUtoV2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Após tombo nos preços, ureia entra em fase de recuperação - Agrolink</t>
+          <t>Disney Dreamlight Valley: Guia da missão Thought, Fog, and Light - games.gg</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>10/07/2026 17:16</t>
+          <t>10/07/2026 18:43</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOWTRuMG5FVXRzbW5lbTZ4Q182YW9hSUFwWUphaDFuZHlISXZHNEhtX1drcjdFTDZlYWpCNFNqR2l6cDlsMjRrbGxVRnViZWNIZWJ1Q0h4RzRmbzZoVVczNEpyQ0MzZ0FqeUQ3VWw3QjFCdU1qdlJrdmV5WlpSTlJHZ3ZUOFptXzhqR3hqbEV1UTZ4TzYzZExLX0hnSWZLekdacmJMbEtiME1rUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQTEFYMVVkWnNPUEx1bWRqU2ptdG1xYjlLSnBjbHFlMjFybG85YW80eS1pb2hBT20yazM3dUZ6emJBcXItajNfZlhNVjJwclpjd3R4b1lNMHI1MDQtTUFHU3VhYllpNkJIWlVJSDdOaThOLTg5cDExRy0xVFZReElDbDdvbXFOc24tVjM0RHBPVVhnQVctbURONzdaZFU4al90M2p0MnhEbzc4eXRvYXdmYjZFb2hOLVJXZmluSU16QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dados da importação de ureia em junho e expectativa de preço! - Farmnews</t>
+          <t>Mosaic reduz produção de fosfato no Brasil por restrições no fornecimento de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>10/07/2026 15:37</t>
+          <t>10/07/2026 17:18</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPaG9iU21CY05aUGR1OExxRUNPbGtmTGZVOUtISUxJUTY5QThsM0tfNkQyVWNuckN0ckVral9IR05uVThNUDVYOXhvaTVvclhlMzhtQzkyTC1jQnlGbE9iSVVKcDNZM0FOT01nTXBRVWJuVWdLNHR3Xzhvd09QSHZmRU1TcFppeFA2dE9sZzEweHdVOURTZ1JHTlJBRnlybUNlcGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPeG9YelAzMGdHdy0zZUNKcE9xYUczeVNvb3cxZTVPMEkyLXhUeTNHOUhDRU5hRjdZMzdZT2JzYlNGRW1oUzBPbHRKSnV2WXVlZFRYZ0F2Y3I0RHZxUWpMM3JKMEk5SG4yLTcyTk1PcjhpZFEwYmhKekVEY25razQyeEJURU5SMmE1NGIybVozNTJ2dldsemk4elE4LXhNa3BOeUdDZzBiWi03R0FaWWhYa3ctb1pEcEZhaWgwcldUVTl0MUtoV2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mosaic amplia paralisações em Minas Gerais e anuncia hibernação da unidade de Uberaba - Portal Imbiara</t>
+          <t>Após tombo nos preços, ureia entra em fase de recuperação - Agrolink</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>10/07/2026 13:47</t>
+          <t>10/07/2026 17:16</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQR0RFQVNmTDJGRnpaOEoydWZRVU1RLWlhUkRTYmRPaFExWDhrRWJpbDFfQVB6RXhMYkZKNThBUVB1cWwxRlFpZUJXdi1qNTdVenhZbVo4MmZGaUM1Rnl1MkVIY2c3M0ZnRHhCY3NROFJpZmMtRWVSNHNzZFFodS1iOEFULVJoTUw1eUVzc3ZRaEE3NHo4LWF3RUhKdTdPa0ZJVndxWWJTdlpBUVRZMnFPakVKcGtJZEt4aW1vbG84a3JsWEJfazRkMkJDSzR2Y0NkQjVnbUNyVGY0S2NDM3NoZ2ptd05iQ0JQUmM5WHVHYzV1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOWTRuMG5FVXRzbW5lbTZ4Q182YW9hSUFwWUphaDFuZHlISXZHNEhtX1drcjdFTDZlYWpCNFNqR2l6cDlsMjRrbGxVRnViZWNIZWJ1Q0h4RzRmbzZoVVczNEpyQ0MzZ0FqeUQ3VWw3QjFCdU1qdlJrdmV5WlpSTlJHZ3ZUOFptXzhqR3hqbEV1UTZ4TzYzZExLX0hnSWZLekdacmJMbEtiME1rUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1986,105 +1986,105 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Melhora dos preços da soja e recuo do Super Simples conferem relações de troca mais favoráveis ao produtor brasileiro - Notícias Agrícolas</t>
+          <t>Dados da importação de ureia em junho e expectativa de preço! - Farmnews</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>10/07/2026 13:22</t>
+          <t>10/07/2026 15:37</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxOQ1BxcXlmR1RXMnRTWi05ZHpOLTZWNlBPRkRYaHZuOGJaTWtnTDVWWW9vUmZRd1RoaEt3SkVEMVlOSHZTdWowc3d1U0ZjQzZzazFNSEFJZE1MTzZxREgyaS1nZERJMVB1U0FhS0g4ckEzUkNUWEpydjdUS2dBemxRWHNpa180RnZuM3Zfa0pjT2NzNzJOOS1zTk9UZDRXSVdJOUp1VWkyb1VaY0lSOVJvNDRxOWlNeXB5S1ZiSFlpSEg1emtzeG9hWUNHMnBDdF9JazBOQ0dFdkZ6N0lmUzc5dEJQWkRqZlBSTENjQXNNalM4Z2gwOTVJUHNibGI0VFRQeW1tSHdQdjlOdEJ6ZmVQTll6bktwTDZBQXcybW5B0gGjAkFVX3lxTFBQVzY1NHBLeU5Tak81dmlTeml1ZFllWHk4aU9PUDIwaWJDaGpnTzNiZTJXekxWNmtkMW1TX0FLREFET01YVndNWDlyeVg1aElCQWs3Um5NaHNQMzlKOXRlM3JjVkxqNVJwaVVxdVdsSTZlaTdmdWVXcDRaU0FOTDZoZ1ByZE9Jc0RPWEhEMlhLTGpDY2pTb2NBdW00VmZZMlVjWGxaT3RlSEt0OFliRDJiVWJPOG9EczZmaHJsOUJmaTU2YzRJSHZoQnMtY2k1YS1iaEVybjBKTUJJdEpnY1ZHY2VNbF9xMnFXQVZNeVZBVDJkOUNxWmxaR1lrRl9pekxNemVfMzdDRjFBMWVySmZvbEcxYTA1OGlsWFByYzhKeXFzbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPaG9iU21CY05aUGR1OExxRUNPbGtmTGZVOUtISUxJUTY5QThsM0tfNkQyVWNuckN0ckVral9IR05uVThNUDVYOXhvaTVvclhlMzhtQzkyTC1jQnlGbE9iSVVKcDNZM0FOT01nTXBRVWJuVWdLNHR3Xzhvd09QSHZmRU1TcFppeFA2dE9sZzEweHdVOURTZ1JHTlJBRnlybUNlcGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tensões entre EUA e Irã ameaçam fornecimento de fertilizantes para o Brasil - Globo Rural</t>
+          <t>Mosaic amplia paralisações em Minas Gerais e anuncia hibernação da unidade de Uberaba - Portal Imbiara</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10/07/2026 13:15</t>
+          <t>10/07/2026 13:47</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOai1tRmFORnVmWkZnVlNVbzJZcFlfdDFJeDRua0xvVnFZRUlZa05vbHlWMjY0Z1BncGpPVEVmdncwOWMzQWF0MjRqT0VaODllRWpBN0ZZam50TDdCaUxfcmFpVG9sZ282VTZqU1ZTYjItXzRfZUV4NHBrUUtCLVNQdER4VW5pVVhMRGlTa2VrTnhYdXRIaTVYNS12T1luazFTa2Q3Sm9tUXdHZnRsRWV4RTNPS0x6elhqT2xXVmZWblJYSTFRdUdXcmVKamtUeVHSAd4BQVVfeXFMTTJsTWZ0ZS1XM0hIcFpHX2J3d2ZqNmQ3dWllWVFHVEhhNWtNcU95a3loYnpJLVppZzlickRHMDV0YmZsb1ZjTWpubEpFQkQ2QVlEUnIyM3NEbmt2N1V1Tkt3NTgtYk9ybmJUSURNYnJsU3pzaTJlaTEzM19tR2xHTmE4aS1BMElVQ19VWmx6QXBiZklzei12QURCZ050YjhRS3Y3QTFmSEduZ0FCV0RhT3BHeVI5ZVgzQm0wUTZkaTRCaFZJOFBZTGRNd29DRlEyY3B3RXAzOEk5ZmtXalV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQR0RFQVNmTDJGRnpaOEoydWZRVU1RLWlhUkRTYmRPaFExWDhrRWJpbDFfQVB6RXhMYkZKNThBUVB1cWwxRlFpZUJXdi1qNTdVenhZbVo4MmZGaUM1Rnl1MkVIY2c3M0ZnRHhCY3NROFJpZmMtRWVSNHNzZFFodS1iOEFULVJoTUw1eUVzc3ZRaEE3NHo4LWF3RUhKdTdPa0ZJVndxWWJTdlpBUVRZMnFPakVKcGtJZEt4aW1vbG84a3JsWEJfazRkMkJDSzR2Y0NkQjVnbUNyVGY0S2NDM3NoZ2ptd05iQ0JQUmM5WHVHYzV1Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>"Calcário convencional: herança do passado, desafios do futuro" - Revista Attalea Agronegócios</t>
+          <t>Melhora dos preços da soja e recuo do Super Simples conferem relações de troca mais favoráveis ao produtor brasileiro - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>10/07/2026 11:32</t>
+          <t>10/07/2026 13:22</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRXBKODRUMjRqNVVvbmlITmlfVVNET045UHpPY0FoeldGMU5QZXRDdE9YTDU1WExQcXBOUHRTUlVoek1xUjc2NGxwVVhCcjNTV2t4RDlZZFBkY3l3OGZfZDZYNnFCczJ1b25MTmpmMGQ1MkwwVnBISmNOX25jd3BNRnI0NEJMU2ZZVlEtZTVCejlOSFlDdXBDc3dxaEtycEFaSUdwSE00MHhHQWZZQWZGdk5kTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxOQ1BxcXlmR1RXMnRTWi05ZHpOLTZWNlBPRkRYaHZuOGJaTWtnTDVWWW9vUmZRd1RoaEt3SkVEMVlOSHZTdWowc3d1U0ZjQzZzazFNSEFJZE1MTzZxREgyaS1nZERJMVB1U0FhS0g4ckEzUkNUWEpydjdUS2dBemxRWHNpa180RnZuM3Zfa0pjT2NzNzJOOS1zTk9UZDRXSVdJOUp1VWkyb1VaY0lSOVJvNDRxOWlNeXB5S1ZiSFlpSEg1emtzeG9hWUNHMnBDdF9JazBOQ0dFdkZ6N0lmUzc5dEJQWkRqZlBSTENjQXNNalM4Z2gwOTVJUHNibGI0VFRQeW1tSHdQdjlOdEJ6ZmVQTll6bktwTDZBQXcybW5B0gGjAkFVX3lxTFBQVzY1NHBLeU5Tak81dmlTeml1ZFllWHk4aU9PUDIwaWJDaGpnTzNiZTJXekxWNmtkMW1TX0FLREFET01YVndNWDlyeVg1aElCQWs3Um5NaHNQMzlKOXRlM3JjVkxqNVJwaVVxdVdsSTZlaTdmdWVXcDRaU0FOTDZoZ1ByZE9Jc0RPWEhEMlhLTGpDY2pTb2NBdW00VmZZMlVjWGxaT3RlSEt0OFliRDJiVWJPOG9EczZmaHJsOUJmaTU2YzRJSHZoQnMtY2k1YS1iaEVybjBKTUJJdEpnY1ZHY2VNbF9xMnFXQVZNeVZBVDJkOUNxWmxaR1lrRl9pekxNemVfMzdDRjFBMWVySmZvbEcxYTA1OGlsWFByYzhKeXFzbw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Após anúncio de paralisação da Mosaic, Prefeitura cria observatório de fertilizantes em Uberaba - JM Online</t>
+          <t>Tensões entre EUA e Irã ameaçam fornecimento de fertilizantes para o Brasil - Globo Rural</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>10/07/2026 10:36</t>
+          <t>10/07/2026 13:15</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNVWJ0ZEcyc3AyMDBZQ3BPNDVkYV9LdnJPZkNFeWZQSkVINjlqTm5TQUI5NDhWT2lrZ0s4ME52aDc5SnVYMkFieWZmeGthbndlQjRFeFM2NTVfX3I0bmJ4bVFTZmR5YXMteHVMT3NaMXpsYmdqZGVfVXU1YkptN243NnRiVlBxaHlOdEJpMGczcmdDLWppdzRlZ01XZFFxZVJIQ1R2Q05iTjh3N2lOcFM4bi1nd2VBeExEVklueDMzeWRIX1VubXhXVG5BcUl4amxPZmfSAdoBQVVfeXFMTjdGeU03cEdhN0NpRDNUMHozamhOZ3VKT3VjRzlaMnNNR0xaRjhaYUhZUGJOZkE1SEVOM3hhUnlyMm9zX3N1bjVCQ0RlVU9MX0o4RVZNOVlIQkhKRjY1bFlVd2l2aVZCSEhGaTgyVGh2V1Q5UUU1c1lETnY1QlNDT3lUa3Q0Z0FMUUktcENzYmdBTEVzdUtNakJudFRRTFo4UDhncEdDYXJROTd6eGdaUVNOSUVyRjhfeXp4eXlZSmx1ODZpZ1o4VEppc0VVT3laci1YeWE5QnhWTWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOai1tRmFORnVmWkZnVlNVbzJZcFlfdDFJeDRua0xvVnFZRUlZa05vbHlWMjY0Z1BncGpPVEVmdncwOWMzQWF0MjRqT0VaODllRWpBN0ZZam50TDdCaUxfcmFpVG9sZ282VTZqU1ZTYjItXzRfZUV4NHBrUUtCLVNQdER4VW5pVVhMRGlTa2VrTnhYdXRIaTVYNS12T1luazFTa2Q3Sm9tUXdHZnRsRWV4RTNPS0x6elhqT2xXVmZWblJYSTFRdUdXcmVKamtUeVHSAd4BQVVfeXFMTTJsTWZ0ZS1XM0hIcFpHX2J3d2ZqNmQ3dWllWVFHVEhhNWtNcU95a3loYnpJLVppZzlickRHMDV0YmZsb1ZjTWpubEpFQkQ2QVlEUnIyM3NEbmt2N1V1Tkt3NTgtYk9ybmJUSURNYnJsU3pzaTJlaTEzM19tR2xHTmE4aS1BMElVQ19VWmx6QXBiZklzei12QURCZ050YjhRS3Y3QTFmSEduZ0FCV0RhT3BHeVI5ZVgzQm0wUTZkaTRCaFZJOFBZTGRNd29DRlEyY3B3RXAzOEk5ZmtXalV3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
+          <t>"Calcário convencional: herança do passado, desafios do futuro" - Revista Attalea Agronegócios</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10/07/2026 10:16</t>
+          <t>10/07/2026 11:32</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRXBKODRUMjRqNVVvbmlITmlfVVNET045UHpPY0FoeldGMU5QZXRDdE9YTDU1WExQcXBOUHRTUlVoek1xUjc2NGxwVVhCcjNTV2t4RDlZZFBkY3l3OGZfZDZYNnFCczJ1b25MTmpmMGQ1MkwwVnBISmNOX25jd3BNRnI0NEJMU2ZZVlEtZTVCejlOSFlDdXBDc3dxaEtycEFaSUdwSE00MHhHQWZZQWZGdk5kTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2096,17 +2096,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre - brasilagro.com.br</t>
+          <t>Após anúncio de paralisação da Mosaic, Prefeitura cria observatório de fertilizantes em Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>10/07/2026 08:34</t>
+          <t>10/07/2026 10:36</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWjlvdWJTZGZFS0lpRFVleTl2bDV3WWlrazRpXzhuaXp2ZzRtWEUwcVh5dE02VldqaDlza0t2QnB4SXBuV29WVnY2Ti10MF9WN3NhaXViUk4zeXI5YkpUZWpHYWtuOUxsQV8xM2hrN05Edm5OaVMtMXlxT0NON2VYM3F4ek9BTjZ6bWQwS3l6aHF0NzlfMmttd0FqY0pFR0VRRWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNVWJ0ZEcyc3AyMDBZQ3BPNDVkYV9LdnJPZkNFeWZQSkVINjlqTm5TQUI5NDhWT2lrZ0s4ME52aDc5SnVYMkFieWZmeGthbndlQjRFeFM2NTVfX3I0bmJ4bVFTZmR5YXMteHVMT3NaMXpsYmdqZGVfVXU1YkptN243NnRiVlBxaHlOdEJpMGczcmdDLWppdzRlZ01XZFFxZVJIQ1R2Q05iTjh3N2lOcFM4bi1nd2VBeExEVklueDMzeWRIX1VubXhXVG5BcUl4amxPZmfSAdoBQVVfeXFMTjdGeU03cEdhN0NpRDNUMHozamhOZ3VKT3VjRzlaMnNNR0xaRjhaYUhZUGJOZkE1SEVOM3hhUnlyMm9zX3N1bjVCQ0RlVU9MX0o4RVZNOVlIQkhKRjY1bFlVd2l2aVZCSEhGaTgyVGh2V1Q5UUU1c1lETnY1QlNDT3lUa3Q0Z0FMUUktcENzYmdBTEVzdUtNakJudFRRTFo4UDhncEdDYXJROTd6eGdaUVNOSUVyRjhfeXp4eXlZSmx1ODZpZ1o4VEppc0VVT3laci1YeWE5QnhWTWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -2118,39 +2118,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
+          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>10/07/2026 07:00</t>
+          <t>10/07/2026 10:16</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mineradora CMOC firma acordo de R$ 11 milhões por contaminação do solo em Catalão - Tribuna do Planalto</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>09/07/2026 21:17</t>
+          <t>10/07/2026 08:34</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPNVpiSFpMWmIxLXpEWVZOeElNOHlkZ2JZX3c5dzRFd3otN2JCYm96blhvUjd6N09MeVh3U2ZRY09OekVrcEFMcXZGM0xGY0RTTHdPNVVJVWc3aXRnZ3FyZDlQNElsc3hoWktUMTdSNk5KWWtvcnJHN0E1MWZ2aWFLalRwdUZIZzdwVzV5TTFrVEN5SFM4djNjQWVpdVBYTzNLY2NhU1ZQQ2FHSW80UUxNb2xkOHY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWjlvdWJTZGZFS0lpRFVleTl2bDV3WWlrazRpXzhuaXp2ZzRtWEUwcVh5dE02VldqaDlza0t2QnB4SXBuV29WVnY2Ti10MF9WN3NhaXViUk4zeXI5YkpUZWpHYWtuOUxsQV8xM2hrN05Edm5OaVMtMXlxT0NON2VYM3F4ek9BTjZ6bWQwS3l6aHF0NzlfMmttd0FqY0pFR0VRRWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -2162,105 +2162,105 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
+          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>09/07/2026 20:05</t>
+          <t>10/07/2026 07:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Importações de ureia recuam 32% no semestre, mas fosfatados exigem aceleração nas compras - MT Econômico</t>
+          <t>Mineradora CMOC firma acordo de R$ 11 milhões por contaminação do solo em Catalão - Tribuna do Planalto</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>09/07/2026 18:35</t>
+          <t>09/07/2026 21:17</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNc3RsNG8zMnZxOFBSY0J0UmxuTlA1MlNPbmotbGwwZEpxLXhiXzB0cnVqVFlrZGpqek5FY0c3LWxXWF9VYkZHem1KTEtlNHN0SDdNSDFNeUJEd3luVmp5VWhpMlBBVUpSbnVLWVF5NWFXMWpUWE4tb1ZqeURjTzF0bGZKclNPZGJoelJiQ3pwMlVJa2JJelV3c1p5RTNJY3NleWowTndvWlItZl9WX1lUd2U5SnNfU2gzc0pNb2JoUkxhV2dxWi1fOEJQRHg5NjVTWEZHT0lLM1o5RWlRNk85eg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPNVpiSFpMWmIxLXpEWVZOeElNOHlkZ2JZX3c5dzRFd3otN2JCYm96blhvUjd6N09MeVh3U2ZRY09OekVrcEFMcXZGM0xGY0RTTHdPNVVJVWc3aXRnZ3FyZDlQNElsc3hoWktUMTdSNk5KWWtvcnJHN0E1MWZ2aWFLalRwdUZIZzdwVzV5TTFrVEN5SFM4djNjQWVpdVBYTzNLY2NhU1ZQQ2FHSW80UUxNb2xkOHY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Prefeitura de Chuvisca define distribuição de ureia para produtores de leite - Portal ClicR</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>09/07/2026 16:46</t>
+          <t>09/07/2026 20:05</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNdHRaa3pPRVdoSzFsWGJiZElFNEc3QTFhYmpEX1Z1bC1uNk1uQXhqM2Nld2kwTGtqNlBsVTdaZXpBbGdia2xqODlMNU52NlRNaTVsWDl6dG52ek9WQ3dPLVBMS0c2eTNsUUVHUmx1RERiRUVnTXk5dC15X2ttYmxIRmx2VXBjS20waGJJeWFUS1ZTdHJMcGJ0ZHB6M01GcGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
+          <t>Importações de ureia recuam 32% no semestre, mas fosfatados exigem aceleração nas compras - MT Econômico</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>09/07/2026 16:20</t>
+          <t>09/07/2026 18:35</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNc3RsNG8zMnZxOFBSY0J0UmxuTlA1MlNPbmotbGwwZEpxLXhiXzB0cnVqVFlrZGpqek5FY0c3LWxXWF9VYkZHem1KTEtlNHN0SDdNSDFNeUJEd3luVmp5VWhpMlBBVUpSbnVLWVF5NWFXMWpUWE4tb1ZqeURjTzF0bGZKclNPZGJoelJiQ3pwMlVJa2JJelV3c1p5RTNJY3NleWowTndvWlItZl9WX1lUd2U5SnNfU2gzc0pNb2JoUkxhV2dxWi1fOEJQRHg5NjVTWEZHT0lLM1o5RWlRNk85eg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Mineradora CMOC terá que pagar R$ 11 milhões após contaminação ambiental em Catalão - Badiinho</t>
+          <t>Prefeitura de Chuvisca define distribuição de ureia para produtores de leite - Portal ClicR</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>09/07/2026 15:50</t>
+          <t>09/07/2026 16:46</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9jQWwwVVZBV2pHcl94VzJPRV91UkNrUE1NM0FnVUdEMF9FOVBNemZSeDZIblVidnpkYllLZFIxNm5yTThNU1hUa2w1S0Y2bjhJSzBaNmtqNWZMVjRZdk0zak9MdHo5NDF6VkcxS1V5RFRvbHhB0gF6QVVfeXFMTVAwVjRIRVR0Vng1Y05rdjUxT05lU3p3UTl1MWt6NDRnandFcXMyeE1DelE1MVctMTR5eHloN0NsSlVYSVpZRTZvRFJnZnlickNPODNFVFRJSnBjRmVHZHV2cUtZM1N1Q2Y1M3NaU1BhbHA5V1pnaHpnMEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNdHRaa3pPRVdoSzFsWGJiZElFNEc3QTFhYmpEX1Z1bC1uNk1uQXhqM2Nld2kwTGtqNlBsVTdaZXpBbGdia2xqODlMNU52NlRNaTVsWDl6dG52ek9WQ3dPLVBMS0c2eTNsUUVHUmx1RERiRUVnTXk5dC15X2ttYmxIRmx2VXBjS20waGJJeWFUS1ZTdHJMcGJ0ZHB6M01GcGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -2272,61 +2272,61 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
+          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>09/07/2026 14:52</t>
+          <t>09/07/2026 16:20</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mosaic hiberna fábrica de fertilizantes em Uberaba por falta de enxofre - JM Online</t>
+          <t>Mineradora CMOC terá que pagar R$ 11 milhões após contaminação ambiental em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>09/07/2026 14:32</t>
+          <t>09/07/2026 15:50</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQYV84dmVwc0JzTXIyZ0JpTHpucWJaaWZ6bnkzdjVDUmFJZnhVWExfb1QwckthUnRWVnFtR3k3NzZjYTE2dC1JSGJhSDJtSWpSSlQxUlo5Z2xFZkZ4RE0xYndWM1NnZ3N1ZE16N2J1NU0xNWlZc2tCbldBVjU5Skx0aDg4UjB4RXZza2YzS1ZxbXdWRnpNdmh1SXNkT0Z0SmNzV05sRGdXN1o4TThuNTRoM1FnONIBuwFBVV95cUxNaFl6YW9uc2hKWG1QYTVYMllncWZ2TXRvSENGRzJuR0RwbDk3NUR4bmJOS25IU0owc3BZcHFPN280eWV4cG5FWXF6Z3Y2YXhtenZfWndNdE1JVDBwQXI0LU4yV004dko2dVZidmo0R2FXb2w0Z3FERHYtdURrVGRVQkVYZWY0SUh4U0pLRmlETngwRnJqdDJqY05FazNXaTNNRmx0MVRqSmN2bkMwVUE5TUtPVURCaEpUSlo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9jQWwwVVZBV2pHcl94VzJPRV91UkNrUE1NM0FnVUdEMF9FOVBNemZSeDZIblVidnpkYllLZFIxNm5yTThNU1hUa2w1S0Y2bjhJSzBaNmtqNWZMVjRZdk0zak9MdHo5NDF6VkcxS1V5RFRvbHhB0gF6QVVfeXFMTVAwVjRIRVR0Vng1Y05rdjUxT05lU3p3UTl1MWt6NDRnandFcXMyeE1DelE1MVctMTR5eHloN0NsSlVYSVpZRTZvRFJnZnlickNPODNFVFRJSnBjRmVHZHV2cUtZM1N1Q2Y1M3NaU1BhbHA5V1pnaHpnMEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MPGO celebra acordos com a CMOC Brasil e garante R$ 11 milhões para reparação ambiental em Catalão - Diante do Fato Catalão</t>
+          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>09/07/2026 14:00</t>
+          <t>09/07/2026 14:52</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaGNaUEY5c3pNTFRRejZjcy1ON21QYXRNMlVWbTFncHdWMHNnR2k3Y1NnbUxveVEyWXVzY21wemxMSUJoWTNXdmFGZWczV043QW15WkhKUGJjbFc3SF9JczE4OXNabzRPR3FYWEJXNExISmdRMDJ5R0dkSEZSVmJhZElhZF9tclZKVHpkV3dSdFAzMTVJaFR6eG5haEowNWo4LVFGbmtoMld1cEtKTFMxZ1REVDYyWjVwLUZtUWZFT281R2p6Y1RhcWVYVjNxcVIwSWxZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
         </is>
       </c>
     </row>
@@ -2338,39 +2338,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - BPMoney</t>
+          <t>Mosaic hiberna fábrica de fertilizantes em Uberaba por falta de enxofre - JM Online</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>09/07/2026 14:00</t>
+          <t>09/07/2026 14:32</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd191NWgya3M1Mi1KV19TX2x4VnN5a1QtZXJ4Mmcta2NyVEFQajVPNnlMVTBUWTdfNFpORFdsb21KYnZNNlc2MU9WdWdZWWxybm9JeEllY2V4V2hiaTdlMDBNUV9pRVd5Umd6a25TSnU3b0E0cDZVZVRVb0ItNERObUpxczNvWUszbmI4cExUVFlMNUs2SDZfeHNfYnVoQ091MmZvWTVHTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQYV84dmVwc0JzTXIyZ0JpTHpucWJaaWZ6bnkzdjVDUmFJZnhVWExfb1QwckthUnRWVnFtR3k3NzZjYTE2dC1JSGJhSDJtSWpSSlQxUlo5Z2xFZkZ4RE0xYndWM1NnZ3N1ZE16N2J1NU0xNWlZc2tCbldBVjU5Skx0aDg4UjB4RXZza2YzS1ZxbXdWRnpNdmh1SXNkT0Z0SmNzV05sRGdXN1o4TThuNTRoM1FnONIBuwFBVV95cUxNaFl6YW9uc2hKWG1QYTVYMllncWZ2TXRvSENGRzJuR0RwbDk3NUR4bmJOS25IU0owc3BZcHFPN280eWV4cG5FWXF6Z3Y2YXhtenZfWndNdE1JVDBwQXI0LU4yV004dko2dVZidmo0R2FXb2w0Z3FERHYtdURrVGRVQkVYZWY0SUh4U0pLRmlETngwRnJqdDJqY05FazNXaTNNRmx0MVRqSmN2bkMwVUE5TUtPVURCaEpUSlo0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - CompreRural</t>
+          <t>MPGO celebra acordos com a CMOC Brasil e garante R$ 11 milhões para reparação ambiental em Catalão - Diante do Fato Catalão</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>09/07/2026 13:56</t>
+          <t>09/07/2026 14:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmd5aEw0ajhQRGtrcXUxdG1JN2gxeWZVYTZsS1VVTGk4cnBEbThDNzY4WndKQVhONjk5WmhGUi1YNmtxek1fM1dRNmluc0VxOUtJc2xYQ2tCYjhuSnVCLTBnZXc0b3YwUUhpcWp5MkpLTWVTa2lwVjZ4eENrbWdrYXZFakpBYVVvaFRybDNXcXRTbkVJRVpxbUJMRUJXU0JTYzV3RzZsc050WlNOeXhGc0xaYnVaUHV3b3k0Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaGNaUEY5c3pNTFRRejZjcy1ON21QYXRNMlVWbTFncHdWMHNnR2k3Y1NnbUxveVEyWXVzY21wemxMSUJoWTNXdmFGZWczV043QW15WkhKUGJjbFc3SF9JczE4OXNabzRPR3FYWEJXNExISmdRMDJ5R0dkSEZSVmJhZElhZF9tclZKVHpkV3dSdFAzMTVJaFR6eG5haEowNWo4LVFGbmtoMld1cEtKTFMxZ1REVDYyWjVwLUZtUWZFT281R2p6Y1RhcWVYVjNxcVIwSWxZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2382,39 +2382,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil; fábrica em Candeias é desativada - Bahia Notícias</t>
+          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - BPMoney</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>09/07/2026 13:50</t>
+          <t>09/07/2026 14:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQZDVsUG9Xc0YzNTVTYTJBQTVrWDk3R19HSWdJYVBqSUtNY0dTY1phT0dDZTU4NkkzZFNQR0c3UFQwMnFabVN6UFRLWFIzcFBWWm5KXy1WU2E2S3FUSWtYdEZ0Ukw2OThnMnBQeGtLNm5MS3V3QmdxSGZwQUhDYVRrS0FLZDM1UktSTlRFbnpON1Bya2ZLZ1htYzNQSzBqeVd2eC11LWlDY1R0elB0UFZTZ2JyanFHandkLV9HeTVvb2JFTlB6QThoY0ItWVk4b1JzSGZxRnYyV0lOeUhIM08zcUZyM2VRZFZPejUybnJWZGlYcDhQd0ExdVdIbE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd191NWgya3M1Mi1KV19TX2x4VnN5a1QtZXJ4Mmcta2NyVEFQajVPNnlMVTBUWTdfNFpORFdsb21KYnZNNlc2MU9WdWdZWWxybm9JeEllY2V4V2hiaTdlMDBNUV9pRVd5Umd6a25TSnU3b0E0cDZVZVRVb0ItNERObUpxczNvWUszbmI4cExUVFlMNUs2SDZfeHNfYnVoQ091MmZvWTVHTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dano ambiental em Catalão leva mineradora a fazer acordo milionário - Mais Goiás</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - CompreRural</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>09/07/2026 12:28</t>
+          <t>09/07/2026 13:56</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPSldVaDI4S0tmbkFoaXp5UUZ2WUJuNlZOM1Q2RGJEbkJ6RW9ERXk5VjAwV3p2QjkyODF6Ni0wZk0wbEJxdlZueFhKMWJHQlU0RHRlUnU2RVdmM2ZKaHAzZU5LdUNoWlNxc0pTX2JCOU1vRWljaGpyemx2SG1pUU1UbWpkeXdEd2JLTWd2SGRoRnBRZjdKR3JpcDZTb25YUllJWnFEVUZkN0hoSFladUJ1ZFdGend1YVpmd0FxNVlONkdXeU9ZaVdIdTRTWkZTNGw1dkdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmd5aEw0ajhQRGtrcXUxdG1JN2gxeWZVYTZsS1VVTGk4cnBEbThDNzY4WndKQVhONjk5WmhGUi1YNmtxek1fM1dRNmluc0VxOUtJc2xYQ2tCYjhuSnVCLTBnZXc0b3YwUUhpcWp5MkpLTWVTa2lwVjZ4eENrbWdrYXZFakpBYVVvaFRybDNXcXRTbkVJRVpxbUJMRUJXU0JTYzV3RzZsc050WlNOeXhGc0xaYnVaUHV3b3k0Mw?oc=5</t>
         </is>
       </c>
     </row>
@@ -2426,39 +2426,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Misturadora da Mosaic no DIMIC encerra atividades e 22 trabalhadores são demitidos em Catalão - Diante do Fato Catalão</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil; fábrica em Candeias é desativada - Bahia Notícias</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>09/07/2026 12:27</t>
+          <t>09/07/2026 13:50</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPc2dMOGg4WGRhNHZOZEt2NVNnRDdUT3RoN1o4UTZjeGR4bHJxRUxDazBtZzVtRW5JYzBta2tKb3A1WWtSMF9jMWx5c2RVRkkxU1FheFNFd2s2RkktNkNZeHFaeFhPWnhqbmNvRGRfTk1QRGFTckdBVW5RZ0t1UmdKYTFYMmRDdXNfd2g0ejFxanpYOE5kUDJ6aW5Ick0zby1ORVpndEdwUlM4Wi0yR3ppcU5DYko0MkpDa0dLWE5Ca3N2cFliWFR5bTVTWENCZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQZDVsUG9Xc0YzNTVTYTJBQTVrWDk3R19HSWdJYVBqSUtNY0dTY1phT0dDZTU4NkkzZFNQR0c3UFQwMnFabVN6UFRLWFIzcFBWWm5KXy1WU2E2S3FUSWtYdEZ0Ukw2OThnMnBQeGtLNm5MS3V3QmdxSGZwQUhDYVRrS0FLZDM1UktSTlRFbnpON1Bya2ZLZ1htYzNQSzBqeVd2eC11LWlDY1R0elB0UFZTZ2JyanFHandkLV9HeTVvb2JFTlB6QThoY0ItWVk4b1JzSGZxRnYyV0lOeUhIM08zcUZyM2VRZFZPejUybnJWZGlYcDhQd0ExdVdIbE4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pare de jogar as cinzas no lixo: saiba como usar esse pó como um reforço natural para suas plantas e canteiros</t>
+          <t>Dano ambiental em Catalão leva mineradora a fazer acordo milionário - Mais Goiás</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>09/07/2026 09:15</t>
+          <t>09/07/2026 12:28</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a576649f4d14a0fb389bc557577f2cc&amp;url=https%3a%2f%2fwww.em.com.br%2femfoco%2f2026%2f07%2f09%2fpare-de-jogar-as-cinzas-no-lixo-saiba-como-usar-esse-po-como-um-reforco-natural-para-suas-plantas-e-canteiros%2f&amp;c=3336525689791670118&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPSldVaDI4S0tmbkFoaXp5UUZ2WUJuNlZOM1Q2RGJEbkJ6RW9ERXk5VjAwV3p2QjkyODF6Ni0wZk0wbEJxdlZueFhKMWJHQlU0RHRlUnU2RVdmM2ZKaHAzZU5LdUNoWlNxc0pTX2JCOU1vRWljaGpyemx2SG1pUU1UbWpkeXdEd2JLTWd2SGRoRnBRZjdKR3JpcDZTb25YUllJWnFEVUZkN0hoSFladUJ1ZFdGend1YVpmd0FxNVlONkdXeU9ZaVdIdTRTWkZTNGw1dkdV?oc=5</t>
         </is>
       </c>
     </row>
@@ -2470,17 +2470,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - negociosba.com.br</t>
+          <t>Misturadora da Mosaic no DIMIC encerra atividades e 22 trabalhadores são demitidos em Catalão - Diante do Fato Catalão</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>09/07/2026 02:57</t>
+          <t>09/07/2026 12:27</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQZEZja1RxUjJDTWtwU2F1dEtha0RLamR6YXM4X3BnR0RUUkttaktoa1NzQXIyN29ack1Od2lWdFp1a1F6RjFFWlVmTDUtN3JTTmdRRWtMTHZlQ0xhd2NQUV8zT3NQRUZlanJQaTBieG4teG1wUFBSM3hLT1JWRGJ2cXFNWmRDX1V5MWljZWFHd1BfX09wSENFSDV5NEVGcTlMRjJMcml2WUpERkg3RVlv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPc2dMOGg4WGRhNHZOZEt2NVNnRDdUT3RoN1o4UTZjeGR4bHJxRUxDazBtZzVtRW5JYzBta2tKb3A1WWtSMF9jMWx5c2RVRkkxU1FheFNFd2s2RkktNkNZeHFaeFhPWnhqbmNvRGRfTk1QRGFTckdBVW5RZ0t1UmdKYTFYMmRDdXNfd2g0ejFxanpYOE5kUDJ6aW5Ick0zby1ORVpndEdwUlM4Wi0yR3ppcU5DYko0MkpDa0dLWE5Ca3N2cFliWFR5bTVTWENCZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -2492,17 +2492,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
+          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - negociosba.com.br</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>08/07/2026 23:25</t>
+          <t>09/07/2026 02:57</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQZEZja1RxUjJDTWtwU2F1dEtha0RLamR6YXM4X3BnR0RUUkttaktoa1NzQXIyN29ack1Od2lWdFp1a1F6RjFFWlVmTDUtN3JTTmdRRWtMTHZlQ0xhd2NQUV8zT3NQRUZlanJQaTBieG4teG1wUFBSM3hLT1JWRGJ2cXFNWmRDX1V5MWljZWFHd1BfX09wSENFSDV5NEVGcTlMRjJMcml2WUpERkg3RVlv?oc=5</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - TradingView</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2524,117 +2524,117 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5odGhpYmZGMWVBdmQzQ0JLajR0d3NCdmQxOUtrdDdGRWh4UnZTd21JS0Jua3c0eUtyUkVmVEVXVDVoWW5UZXhIcG05R0w2Y2lCcFpkLU5RcjczTHZmeS1ZUExlX3BHZVJFc1hOaEpmRTJ0MFplenpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Justiça homologa acordo de R$ 11 milhões para reparação ambiental em Catalão - Tribuna do Planalto</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - TradingView</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>08/07/2026 21:28</t>
+          <t>08/07/2026 23:25</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQN1d3cHVseUJvTWtEQTVYQUZNVGV0MGJ0MlNTS0VDaVFlNFlVNGxwNXpCcndCaHpDYm13OXFHOHppZF9kcHZhc1Zjd2F2VWhzOVIwalFRRjh5VE9kMmhPZXNCcnJKb1ctQmJta2VWV3NTVHZSaVJyTDN0YVlqWHhpV0JLT3dpbmpSVXpleW5RNlpFMGE3SWtxemplY0c1czJIcVAtbHlwWm5sREtSR1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5odGhpYmZGMWVBdmQzQ0JLajR0d3NCdmQxOUtrdDdGRWh4UnZTd21JS0Jua3c0eUtyUkVmVEVXVDVoWW5UZXhIcG05R0w2Y2lCcFpkLU5RcjczTHZmeS1ZUExlX3BHZVJFc1hOaEpmRTJ0MFplenpB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil com crise de enxofre - boca.com.br</t>
+          <t>Justiça homologa acordo de R$ 11 milhões para reparação ambiental em Catalão - Tribuna do Planalto</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>08/07/2026 21:15</t>
+          <t>08/07/2026 21:28</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQU3dtd1pHdkVKMDlGNnhQM1RZa1FKU2NCMDBFZjJMSVhfbjBXT3M4NTUxWENhenJkdWRmdWxTdjZ5dlI1bDh5Qng1VEFweXRxRUsyWmNVQXNicGIyNnM2Q1JPMGFiMWl5ZllFV2dpQzQ0eG5zdThpVWo4R2V3eW82V18xcWt3OU5jZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQN1d3cHVseUJvTWtEQTVYQUZNVGV0MGJ0MlNTS0VDaVFlNFlVNGxwNXpCcndCaHpDYm13OXFHOHppZF9kcHZhc1Zjd2F2VWhzOVIwalFRRjh5VE9kMmhPZXNCcnJKb1ctQmJta2VWV3NTVHZSaVJyTDN0YVlqWHhpV0JLT3dpbmpSVXpleW5RNlpFMGE3SWtxemplY0c1czJIcVAtbHlwWm5sREtSR1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Henrique Carballal recebe cúpula da multinacional CMOC para alinhar metas ESG na produção de ouro em Santaluz - Classe Politica</t>
+          <t>Mosaic reduz operações no Brasil com crise de enxofre - boca.com.br</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>08/07/2026 19:52</t>
+          <t>08/07/2026 21:15</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOVGdidnBPSEhqUXZwenhwVXg1N0N3V0J4czZJZVJFUzhvR2lOY2g5YWszUHVTcjg5NnVNeF9kVExVb3FGQ0dHMGtqSnZ1QlZCWmMtbTVYTGZkZG1RSFlzVHd2SE5mQ25wSHFWZ2FwLVB3bDFCc1VmVUNveEJ4cDFlMFNNeXdqRmJ1OTBpRkEzdWRiUzNzMG0tM1NBSFREQWZKek5Yelh6WEZxUnRYTW4wUEl1MnZ3WnV5dFV2UjlkSThoa0Zta3dCSk5ZVFFKWFlyZUxhUnpvaVF1d3RJak5ZOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQU3dtd1pHdkVKMDlGNnhQM1RZa1FKU2NCMDBFZjJMSVhfbjBXT3M4NTUxWENhenJkdWRmdWxTdjZ5dlI1bDh5Qng1VEFweXRxRUsyWmNVQXNicGIyNnM2Q1JPMGFiMWl5ZllFV2dpQzQ0eG5zdThpVWo4R2V3eW82V18xcWt3OU5jZ0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SEM ENXOFRE, MINERADORAS PARALISAM E ADUBO PODE SER VILÃO DA PRODUÇÃO DE ALIMENTOS - Jornal de Patrocínio</t>
+          <t>Henrique Carballal recebe cúpula da multinacional CMOC para alinhar metas ESG na produção de ouro em Santaluz - Classe Politica</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>08/07/2026 17:55</t>
+          <t>08/07/2026 19:52</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQaG84bm5LOWVYb0lLb0d2QmZTWkNQUzQ5a1pZVzZVZkMxTmFzaUhwclV6MFBxLWo0WE9hZkJINkkxWjlWMGVMZE9QYkVtXzhoRzRTYWwxdWFpRnN1N1ZQV3hBaVNNWVhpMXN0cVlRc3hGbEc0dFA3aXBaam1UUThoR3YxbUtuUUo3TXFRN2I2SkJxVnZJWTNuRlNtNEVfZzdhNnBUZlFyN0ZhM1VsVHJNR0RTemxzNEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOVGdidnBPSEhqUXZwenhwVXg1N0N3V0J4czZJZVJFUzhvR2lOY2g5YWszUHVTcjg5NnVNeF9kVExVb3FGQ0dHMGtqSnZ1QlZCWmMtbTVYTGZkZG1RSFlzVHd2SE5mQ25wSHFWZ2FwLVB3bDFCc1VmVUNveEJ4cDFlMFNNeXdqRmJ1OTBpRkEzdWRiUzNzMG0tM1NBSFREQWZKek5Yelh6WEZxUnRYTW4wUEl1MnZ3WnV5dFV2UjlkSThoa0Zta3dCSk5ZVFFKWFlyZUxhUnpvaVF1d3RJak5ZOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mais de 500 agricultores de Palmas começam a receber calcário para aumentar a produção rural - jornalprimeirapaginato.com</t>
+          <t>SEM ENXOFRE, MINERADORAS PARALISAM E ADUBO PODE SER VILÃO DA PRODUÇÃO DE ALIMENTOS - Jornal de Patrocínio</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>08/07/2026 17:33</t>
+          <t>08/07/2026 17:55</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSUVMcFY2WlNBZFJRbTZZX0dwbnAwZldlb0xfYnk4WTVfYUZWdmJxc2FCR2JFV3hLWTQtM01OWHJDX3BLTkhRcmNjTEdtUHBXWG9SYXJjVjZOa0pmWEJMekphSGlUMWkwNUFlYjBKZnlGbE4zaHplY0tFQzRMZTRHQlQyeGJZLWZKVU03UWNTd3dRODljMnRsUng0WWpHM2FydUI5dFpOVHJZa1ZaM0J3WW43cWNwSjd2Z05pLVY0SHVGRnlaN28w0gHMAUFVX3lxTE9nWFU2bHF0dEQyV2M2TXFNX0dnYVBySlB5aUJIcVF6Qnl1bk5QM3J6SHVPR3hqbS1iQzJkTkRQdlFabG1Ienk2SDRIZDNNS3dwd2FCVzFKLUg5cmh3Njl6WndDZUh2QXRXYzI5ZzJPa21tSFVtM0otZDNxSWRMYkR2OS10TkNvRWtuS25yQVprU0hlZFk4TG5GQVRMTlpYRUdGUjVQN0xjaGFyMTZFZFp4VV9TVEtrRk9kMUZGblc1aUV0V0poZTFlUWFXZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQaG84bm5LOWVYb0lLb0d2QmZTWkNQUzQ5a1pZVzZVZkMxTmFzaUhwclV6MFBxLWo0WE9hZkJINkkxWjlWMGVMZE9QYkVtXzhoRzRTYWwxdWFpRnN1N1ZQV3hBaVNNWVhpMXN0cVlRc3hGbEc0dFA3aXBaam1UUThoR3YxbUtuUUo3TXFRN2I2SkJxVnZJWTNuRlNtNEVfZzdhNnBUZlFyN0ZhM1VsVHJNR0RTemxzNEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -2646,17 +2646,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Produtores rurais já podem aderir à compra coletiva de calcário e gesso em Itabira; saiba mais - DeFato Online</t>
+          <t>Mais de 500 agricultores de Palmas começam a receber calcário para aumentar a produção rural - jornalprimeirapaginato.com</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>08/07/2026 15:01</t>
+          <t>08/07/2026 17:33</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPOEgxejNHdTFianBzUHZpWXlzNm5OS1hQazhhZE9mcjhKX1hkMk1PeWhQcHM3MGhoWThpUWJZdENPNms1c0praVl0ZFBxNUNobk9iTzZSMUF3SXQzb0dqRnZSUVJZckN1Nk5UZUZybXQ2VXJYNTYwcm9lcGpXQ2ZyU0dwd3BlaUpSUHJSaGlTY1J3Q2cxWEdwVWd1cmNwVUhnQldka3NTMXhxMFlNdVhYaHROamNmSnh0dnZBN2hvWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSUVMcFY2WlNBZFJRbTZZX0dwbnAwZldlb0xfYnk4WTVfYUZWdmJxc2FCR2JFV3hLWTQtM01OWHJDX3BLTkhRcmNjTEdtUHBXWG9SYXJjVjZOa0pmWEJMekphSGlUMWkwNUFlYjBKZnlGbE4zaHplY0tFQzRMZTRHQlQyeGJZLWZKVU03UWNTd3dRODljMnRsUng0WWpHM2FydUI5dFpOVHJZa1ZaM0J3WW43cWNwSjd2Z05pLVY0SHVGRnlaN28w0gHMAUFVX3lxTE9nWFU2bHF0dEQyV2M2TXFNX0dnYVBySlB5aUJIcVF6Qnl1bk5QM3J6SHVPR3hqbS1iQzJkTkRQdlFabG1Ienk2SDRIZDNNS3dwd2FCVzFKLUg5cmh3Njl6WndDZUh2QXRXYzI5ZzJPa21tSFVtM0otZDNxSWRMYkR2OS10TkNvRWtuS25yQVprU0hlZFk4TG5GQVRMTlpYRUdGUjVQN0xjaGFyMTZFZFp4VV9TVEtrRk9kMUZGblc1aUV0V0poZTFlUWFXZQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Programa de distribuição de calcário chega a Palmas e deve fortalecer a produção de mais de 500 agricultores familiares - Sou de Palmas</t>
+          <t>Produtores rurais já podem aderir à compra coletiva de calcário e gesso em Itabira; saiba mais - DeFato Online</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>08/07/2026 14:33</t>
+          <t>08/07/2026 15:01</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOLTIxSVZ3LVJMUFNpZ0U0UlBkanNMekh6blBXRDUydklHbG5QVTFVX2Nha21GT010cm5BOGJBX3BrVU43UEdqT2YycUxMVGRsSDNnWFBVS0kwTVNRWDlyQ0J1NW5PazRKak9MblpMSkRYSEowZVd1RjhEUFRmWmpjMXdoeTRUeEdGTUl2UVlBdm5keWF0RG1vTXVTMXlSYkJMSmtYd2NNOW1VTTVCNC1NcGllSnlhakZkZVZNVTUzRTV3dWIzNy1QLVNSaGNtR0NNYWRhY0d1d0hoNEZiaTFuVXNrTVlqenR2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPOEgxejNHdTFianBzUHZpWXlzNm5OS1hQazhhZE9mcjhKX1hkMk1PeWhQcHM3MGhoWThpUWJZdENPNms1c0praVl0ZFBxNUNobk9iTzZSMUF3SXQzb0dqRnZSUVJZckN1Nk5UZUZybXQ2VXJYNTYwcm9lcGpXQ2ZyU0dwd3BlaUpSUHJSaGlTY1J3Q2cxWEdwVWd1cmNwVUhnQldka3NTMXhxMFlNdVhYaHROamNmSnh0dnZBN2hvWQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2690,61 +2690,61 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Prefeitura de Palmas.</t>
+          <t>Programa de distribuição de calcário chega a Palmas e deve fortalecer a produção de mais de 500 agricultores familiares - Sou de Palmas</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>08/07/2026 14:17</t>
+          <t>08/07/2026 14:33</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNS3BUcG5OdUxkY0tHNFpTWTdHYkhwaWxVSjJKSVJiTVQzUkw4ZXQ0dTJ3UlhETGVFeDNlOVBlM20xdlVaMnMyZU1zS2VxUndPanFwYVJPc0psRENuVTlhOUh3RmxTZXFtTFVMUjMxWWRpUUF5b20yTUVYRVdpYlh4UkRGQUdIbVk1ZjVBc0VtWk51TE11d3VYQkpfVWxXWWtxS2g2c3JWNThsaHcwSFJ4aVpPMG9QcTRXVlpSLXJxWjJYNzh1NXFpTHFUcE5oOXFsQmU3bFE2RlVBc0NBLS1CMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOLTIxSVZ3LVJMUFNpZ0U0UlBkanNMekh6blBXRDUydklHbG5QVTFVX2Nha21GT010cm5BOGJBX3BrVU43UEdqT2YycUxMVGRsSDNnWFBVS0kwTVNRWDlyQ0J1NW5PazRKak9MblpMSkRYSEowZVd1RjhEUFRmWmpjMXdoeTRUeEdGTUl2UVlBdm5keWF0RG1vTXVTMXlSYkJMSmtYd2NNOW1VTTVCNC1NcGllSnlhakZkZVZNVTUzRTV3dWIzNy1QLVNSaGNtR0NNYWRhY0d1d0hoNEZiaTFuVXNrTVlqenR2?oc=5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
+          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Prefeitura de Palmas.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>08/07/2026 14:07</t>
+          <t>08/07/2026 14:17</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5766500a9549779590f6ea96d21460&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNS3BUcG5OdUxkY0tHNFpTWTdHYkhwaWxVSjJKSVJiTVQzUkw4ZXQ0dTJ3UlhETGVFeDNlOVBlM20xdlVaMnMyZU1zS2VxUndPanFwYVJPc0psRENuVTlhOUh3RmxTZXFtTFVMUjMxWWRpUUF5b20yTUVYRVdpYlh4UkRGQUdIbVk1ZjVBc0VtWk51TE11d3VYQkpfVWxXWWtxS2g2c3JWNThsaHcwSFJ4aVpPMG9QcTRXVlpSLXJxWjJYNzh1NXFpTHFUcE5oOXFsQmU3bFE2RlVBc0NBLS1CMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>08/07/2026 13:03</t>
+          <t>08/07/2026 14:07</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a577b709c8a475c8c3471d9290087b9&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -2756,83 +2756,83 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - Prefeitura de Sorriso</t>
+          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>08/07/2026 12:54</t>
+          <t>08/07/2026 13:03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
+          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - Prefeitura de Sorriso</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>08/07/2026 10:32</t>
+          <t>08/07/2026 12:54</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Harsco aposta em resíduos da siderurgia para crescer no agro, infraestrutura e saneamento, diz CEO Wender Alves - Times Brasil | CNBC</t>
+          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>07/07/2026 22:06</t>
+          <t>08/07/2026 10:32</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOOU80elg0ekRhMHpRVkFhVmJGczd3eEQxNHZtU3A1b1hjVU5ULWY2OVZZV2pnSWZFNzdFZk1xdHJWWDlIMGZtRGxWOWttdVQ4U1ZIQlotbDlTRWZfZ18zaF96SS1SMnVNcDBTQkc1SUtlalZucERxTThPXzVzNVlPd2NGUzgtX0lzdnN3X2YwalEwWWw2QUN3ZFdvX0tVMTZYWjRZb3Ztb1NIQlM2M0ZPQnBVUzBxYXRoSy1acHJTRHRNbTBmaTIxUU9yREQ0djRYM1pDVXBvNkNkclJvaGJZbWV4bTl5Y0kyMllPb0pB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
+          <t>Harsco aposta em resíduos da siderurgia para crescer no agro, infraestrutura e saneamento, diz CEO Wender Alves - Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>07/07/2026 18:35</t>
+          <t>07/07/2026 22:06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOOU80elg0ekRhMHpRVkFhVmJGczd3eEQxNHZtU3A1b1hjVU5ULWY2OVZZV2pnSWZFNzdFZk1xdHJWWDlIMGZtRGxWOWttdVQ4U1ZIQlotbDlTRWZfZ18zaF96SS1SMnVNcDBTQkc1SUtlalZucERxTThPXzVzNVlPd2NGUzgtX0lzdnN3X2YwalEwWWw2QUN3ZFdvX0tVMTZYWjRZb3Ztb1NIQlM2M0ZPQnBVUzBxYXRoSy1acHJTRHRNbTBmaTIxUU9yREQ0djRYM1pDVXBvNkNkclJvaGJZbWV4bTl5Y0kyMllPb0pB?oc=5</t>
         </is>
       </c>
     </row>
@@ -2844,39 +2844,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Fertilizantes subiram mais que a inflação com ureia disparada: 149% - MT Econômico</t>
+          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>07/07/2026 18:33</t>
+          <t>07/07/2026 18:35</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNOTlXdllBd0RsRTMwRmZuckFDamxwbDdTVlBYUk01bnVoZHAtOGJEa2lOdmtfMmtCRFBZWFFQOEQ4SnpKSGlJbl9fTFQzdnY3Vlc1M1FnYV9hcFNPVDJMQ0VLY2Y2ZFFFYnBqNDhjSVhRQzhDNi1nLWZiR3BRYnppRDhtMEhoMmxnel85VTJDMFJZS19paFB6WGJ5QmRSWjl6M2ZNYVVSanVZNEF6S2VFUnVHNGZqajJKc0NzREZOQ05BeDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Carreta carregada com calcário tomba após GPS indicar estrada rural em Jandaia do Sul - Canal 38</t>
+          <t>Fertilizantes subiram mais que a inflação com ureia disparada: 149% - MT Econômico</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>07/07/2026 12:48</t>
+          <t>07/07/2026 18:33</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPbjhYdVBoUk5sOTNMN2p4VlEtVzQwM29sU1JlNktjV1B2RkU2UHA3UndrajVhTHhmS3VZdWRGRmprbHRTQjdRSW1GN0pLN05sMnAxcGR1MVAwZkRRTlZuNmt1RE1ndjdYU0JtQjk3OFRaUmhWN2RKck4tSGJlZXJfT3JiQlhzclpWMVpLX3pGcW03anY0NTE2Y25rdDAwZ014bDZneUNyY1NqeV9MSlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNOTlXdllBd0RsRTMwRmZuckFDamxwbDdTVlBYUk01bnVoZHAtOGJEa2lOdmtfMmtCRFBZWFFQOEQ4SnpKSGlJbl9fTFQzdnY3Vlc1M1FnYV9hcFNPVDJMQ0VLY2Y2ZFFFYnBqNDhjSVhRQzhDNi1nLWZiR3BRYnppRDhtMEhoMmxnel85VTJDMFJZS19paFB6WGJ5QmRSWjl6M2ZNYVVSanVZNEF6S2VFUnVHNGZqajJKc0NzREZOQ05BeDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -2888,61 +2888,61 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Vídeo: Caminhão com calcário tomba e interdita rodovia BR-376 - Diário dos Campos</t>
+          <t>Carreta carregada com calcário tomba após GPS indicar estrada rural em Jandaia do Sul - Canal 38</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>07/07/2026 12:25</t>
+          <t>07/07/2026 12:48</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMjBYMUlrTk44Q051SjdWdk5BQWhmV0tZUG1VaV9PSm82NGFLQ3B3RnMtbGVmR2xhYmxTYUpyUnQ4WVVmQXdiVFE0TnBUUUZ0M3I2R2NjS1k2R0NmckF2NG5OMzNVQmtLUU5VbHVLbkdoT1ZfYmdMSE44U0J1b0dtV3RxWm4zM19ZckZSWU54VWpYQnF1M0k40gGcAUFVX3lxTE1OSmhaeUw4dG0tZUl1N1B4RTRORmZpeEtfaHlTc1pMQ183YWpzYWh1Zng0MlBEUGIydDJKeVFHZjNZNzdDVS1xLTdMbU0yVWJ1RUFuOXR6aVpHNUtMZElhWDVuQXlVVEVBWHYwaVVVSVFKRE1sVHdJWHFGdHgzampVSFV3OXd2VHF3X0VDOEVONlJLdEk2QXhiYVdlcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPbjhYdVBoUk5sOTNMN2p4VlEtVzQwM29sU1JlNktjV1B2RkU2UHA3UndrajVhTHhmS3VZdWRGRmprbHRTQjdRSW1GN0pLN05sMnAxcGR1MVAwZkRRTlZuNmt1RE1ndjdYU0JtQjk3OFRaUmhWN2RKck4tSGJlZXJfT3JiQlhzclpWMVpLX3pGcW03anY0NTE2Y25rdDAwZ014bDZneUNyY1NqeV9MSlE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PACAEMBU: AGROPAC AGROPECUÁRIA é referência no fornecimento de calcário e gesso agrícola - Folha Regional - folharegionalnet.com.br</t>
+          <t>Vídeo: Caminhão com calcário tomba e interdita rodovia BR-376 - Diário dos Campos</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>07/07/2026 11:15</t>
+          <t>07/07/2026 12:25</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQRXh4dEJPWk80V3JGOWM2MS1NS1VIbWpWSVJYTENyd2lEX2FBYjRlMEZmYWdxdkNRa3lJU09lSVJBUElxU3Z0T0o2S1pDLVZTOGl6cjd3LWR5NjdDWXJlUGFCZUZrU0ZTR25FWkFqOVlpMDlSeUNPQzg0ajUxRWxNYVVId1NUS0ZTeVo4Szd0WC1WSmt5UTV1UUw4aGt6UVFfaWZLZFVraU1qNHFFTUFGa3R0c0N4aE9PNjlQVUJwZkZlaVY3c0xVMmNKb9IB0AFBVV95cUxPX0hTa0M5REc2M1hFa1ZDRm9xM0JSWjVjdGhJVUVwZUdSRC10M2owbWZpSFBZZHhpQVdMajFPWG1tdzFLS3hFN2FXazZBb1VDell2VVVqYkxwWXZobUdvenRHX1FsWEhyNEhkUFdvNW52NjY0OFJWajBtT1V6c2RadVdqNzc2TEZrRWd3cGVwV19xeGk5QzZubFF5WHN6bnVZYVNtQk5fRkpYNFNzNUpNN1dUWTd2MXFZN2gtQmVBbFdUNGh4a1NIQkZ5X1I4UTlu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMjBYMUlrTk44Q051SjdWdk5BQWhmV0tZUG1VaV9PSm82NGFLQ3B3RnMtbGVmR2xhYmxTYUpyUnQ4WVVmQXdiVFE0TnBUUUZ0M3I2R2NjS1k2R0NmckF2NG5OMzNVQmtLUU5VbHVLbkdoT1ZfYmdMSE44U0J1b0dtV3RxWm4zM19ZckZSWU54VWpYQnF1M0k40gGcAUFVX3lxTE1OSmhaeUw4dG0tZUl1N1B4RTRORmZpeEtfaHlTc1pMQ183YWpzYWh1Zng0MlBEUGIydDJKeVFHZjNZNzdDVS1xLTdMbU0yVWJ1RUFuOXR6aVpHNUtMZElhWDVuQXlVVEVBWHYwaVVVSVFKRE1sVHdJWHFGdHgzampVSFV3OXd2VHF3X0VDOEVONlJLdEk2QXhiYVdlcA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - MINUTO MT</t>
+          <t>PACAEMBU: AGROPAC AGROPECUÁRIA é referência no fornecimento de calcário e gesso agrícola - Folha Regional - folharegionalnet.com.br</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>07/07/2026 09:08</t>
+          <t>07/07/2026 11:15</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNNm9yRHRTbXM3bWkzai03Qjh6eUh5bm5XSmcyZFA0Ymx1Zl82dThtOEFaUF9ieDRLbHNCT0VtbmJ2S2UyTDZLb2pFZllibWstOWM0VHZHR3V3eFRiVU5vdWgxMUoyaEQ4NDVwd2oteDBGdWNfMGVpUnRleFYzV3BRcnZ5R0xHbzNJV2pqRmxlWXgwZnB1UFBKd2F2NkwwV0p3QUw1YWZKSDFBTUQ4djJZNkVBMWp2NE9JdUEtMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQRXh4dEJPWk80V3JGOWM2MS1NS1VIbWpWSVJYTENyd2lEX2FBYjRlMEZmYWdxdkNRa3lJU09lSVJBUElxU3Z0T0o2S1pDLVZTOGl6cjd3LWR5NjdDWXJlUGFCZUZrU0ZTR25FWkFqOVlpMDlSeUNPQzg0ajUxRWxNYVVId1NUS0ZTeVo4Szd0WC1WSmt5UTV1UUw4aGt6UVFfaWZLZFVraU1qNHFFTUFGa3R0c0N4aE9PNjlQVUJwZkZlaVY3c0xVMmNKb9IB0AFBVV95cUxPX0hTa0M5REc2M1hFa1ZDRm9xM0JSWjVjdGhJVUVwZUdSRC10M2owbWZpSFBZZHhpQVdMajFPWG1tdzFLS3hFN2FXazZBb1VDell2VVVqYkxwWXZobUdvenRHX1FsWEhyNEhkUFdvNW52NjY0OFJWajBtT1V6c2RadVdqNzc2TEZrRWd3cGVwV19xeGk5QzZubFF5WHN6bnVZYVNtQk5fRkpYNFNzNUpNN1dUWTd2MXFZN2gtQmVBbFdUNGh4a1NIQkZ5X1I4UTlu?oc=5</t>
         </is>
       </c>
     </row>
@@ -2954,17 +2954,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - RADAR DIGITAL BRASÍLIA</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - MINUTO MT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>07/07/2026 01:32</t>
+          <t>07/07/2026 09:08</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOd0ZxY1VnNE5vV1ZDUW41MHU1MGpadk82Y0lUaU1LQk5xdkM0SmJESmpRWWpmM0VPcC1SdWJaNS1DcFVTYzk5UVF5dm5KdHhqSDNQWFZhUUt2RVExLWxJUUdaQUpId3JncThlMHZKWE12Z3VPRHFzN2J1OUJnWG5JUlBfaEZiUWVOZjZwMTR1ZXBWZzdMTkw2MWxQMXBic0xEeE1DTkJsbHdHLTZESlRweERMSXd5VDBnZU9tLWdDNnFObjU3NmVCUTlsbVFYNmtyWWJQWlJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNNm9yRHRTbXM3bWkzai03Qjh6eUh5bm5XSmcyZFA0Ymx1Zl82dThtOEFaUF9ieDRLbHNCT0VtbmJ2S2UyTDZLb2pFZllibWstOWM0VHZHR3V3eFRiVU5vdWgxMUoyaEQ4NDVwd2oteDBGdWNfMGVpUnRleFYzV3BRcnZ5R0xHbzNJV2pqRmxlWXgwZnB1UFBKd2F2NkwwV0p3QUw1YWZKSDFBTUQ4djJZNkVBMWp2NE9JdUEtMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - BRASIL NOTÍCIA</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>07/07/2026 00:31</t>
+          <t>07/07/2026 01:32</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOWDN6N25ybWpZZE9iX3JvejZSc29pWXVXczdzazFkNzlqMDZaTWVtcmJsQ1BLMTc0cmlQQWxsM3J4bURTMWJlOExWWDJxUkd5U1A4cUxTSGdWSzVQSG5VWkFIOHYxa2VOaXJBcVp6OHp6SmNWdldaaWhwajZ2Nk1mVnBCMm91OS10VEstR2Y4SFo4aDhvck1yNWV5Q08tMEFETmxrMEptMHVDQ1VWVFhySklFaUJ2NXNtM3dsTURCbEJxTjJRRlViNGd1c1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOd0ZxY1VnNE5vV1ZDUW41MHU1MGpadk82Y0lUaU1LQk5xdkM0SmJESmpRWWpmM0VPcC1SdWJaNS1DcFVTYzk5UVF5dm5KdHhqSDNQWFZhUUt2RVExLWxJUUdaQUpId3JncThlMHZKWE12Z3VPRHFzN2J1OUJnWG5JUlBfaEZiUWVOZjZwMTR1ZXBWZzdMTkw2MWxQMXBic0xEeE1DTkJsbHdHLTZESlRweERMSXd5VDBnZU9tLWdDNnFObjU3NmVCUTlsbVFYNmtyWWJQWlJ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Enxofre se torna essencial na agricultura devido a baixa eficiência - boca.com.br</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - BRASIL NOTÍCIA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>06/07/2026 14:15</t>
+          <t>07/07/2026 00:31</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOWVY4VzhicjNjWXdaS0VKLXZpcTE3Z3B6VURpQlIzNFlUUE01QVNxdjBuXzZsSmlLZXV5YzlIVXI1QmQ0Z3BETGFFZWFoUlBPeG5WMlZTX3E3RDlMc3lSU1BsTWJDazZmRTBHUHZhRzdESE5BUkxJczB5bkNFRHhKaGctakVrSndvSWE4QlhQTWNjalZoN01SR1Vra2tkY1hM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOWDN6N25ybWpZZE9iX3JvejZSc29pWXVXczdzazFkNzlqMDZaTWVtcmJsQ1BLMTc0cmlQQWxsM3J4bURTMWJlOExWWDJxUkd5U1A4cUxTSGdWSzVQSG5VWkFIOHYxa2VOaXJBcVp6OHp6SmNWdldaaWhwajZ2Nk1mVnBCMm91OS10VEstR2Y4SFo4aDhvck1yNWV5Q08tMEFETmxrMEptMHVDQ1VWVFhySklFaUJ2NXNtM3dsTURCbEJxTjJRRlViNGd1c1U?oc=5</t>
         </is>
       </c>
     </row>
@@ -3020,17 +3020,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
+          <t>Enxofre se torna essencial na agricultura devido a baixa eficiência - boca.com.br</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>06/07/2026 13:47</t>
+          <t>06/07/2026 14:15</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOWVY4VzhicjNjWXdaS0VKLXZpcTE3Z3B6VURpQlIzNFlUUE01QVNxdjBuXzZsSmlLZXV5YzlIVXI1QmQ0Z3BETGFFZWFoUlBPeG5WMlZTX3E3RDlMc3lSU1BsTWJDazZmRTBHUHZhRzdESE5BUkxJczB5bkNFRHhKaGctakVrSndvSWE4QlhQTWNjalZoN01SR1Vra2tkY1hM?oc=5</t>
         </is>
       </c>
     </row>
@@ -3042,83 +3042,83 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Adolescentes de Enxofre - Minecraft</t>
+          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>06/07/2026 09:03</t>
+          <t>06/07/2026 13:47</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cientistas desenvolvem um novo método de produção de cimento que substitui o calcário pelo basalto para reduzir drasticamente as emissões de CO2 - Estado de Minas</t>
+          <t>Adolescentes de Enxofre - Minecraft</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>05/07/2026 19:45</t>
+          <t>06/07/2026 09:03</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxQRmwtWFVDNTJESDhkNEZGQVhzd0tqT3lYZ0s4ai12bndGV0hRaEwzb1RQc3Z1M21nUWk5bWJvX1BfdmhzbkhfRE9VVjVRNGlvQXpKbVBCM1Vka1F2VWZ2V3pBUU1tbEk5bkZ0WFVHNlc5SVJwYzhLZDQxM0dmOFpSdUhRb2JaWC1nQlNQWlY3UFQyM0k3dVE1M2tqRnc2M3NEb0wyMEVQWU5SeTM2czlQWGR6VVZpRExLNlRsX0lIbFhZeS1wY2h3OHJrVHdPLUFxcVphY19qbzktcWJuaXAyWVFZWnJFa3hsN0RsZ0xkWVFKVFI3aWpBelJUbVNuNlF2QmszRVRHZVc4TFJUcHZFUElib2Zsdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Alta da ureia preocupa produtores e eleva custos da próxima safra - capitalnews.com.br</t>
+          <t>Cientistas desenvolvem um novo método de produção de cimento que substitui o calcário pelo basalto para reduzir drasticamente as emissões de CO2 - Estado de Minas</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>04/07/2026 21:22</t>
+          <t>05/07/2026 19:45</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZHVhcUh1QnEzbldNX2ZwU0FnWTJiTVFLTkpRRkpoemJYbEVMVkJCNV9zR0tJc3otWkhRdEs4M0JxTE5tOWdfY01pWjFveG4yNThjbmdnOE8xTTJPRl8xY25oYlFYR2JGbGd1SzNyVEV0d1haUEhHR0oxdGJNc05ZYTNHcEt6QzBvVmNpbWg2SEFiT2Z1OEpFT3B1bDZ0UmNRUjRadktMU2kzODkzS2w5bFU5UkJVNGJTSndzZzQ0b0llaTZyTjZXaVd6MExkRjBkSkJ6SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxQRmwtWFVDNTJESDhkNEZGQVhzd0tqT3lYZ0s4ai12bndGV0hRaEwzb1RQc3Z1M21nUWk5bWJvX1BfdmhzbkhfRE9VVjVRNGlvQXpKbVBCM1Vka1F2VWZ2V3pBUU1tbEk5bkZ0WFVHNlc5SVJwYzhLZDQxM0dmOFpSdUhRb2JaWC1nQlNQWlY3UFQyM0k3dVE1M2tqRnc2M3NEb0wyMEVQWU5SeTM2czlQWGR6VVZpRExLNlRsX0lIbFhZeS1wY2h3OHJrVHdPLUFxcVphY19qbzktcWJuaXAyWVFZWnJFa3hsN0RsZ0xkWVFKVFI3aWpBelJUbVNuNlF2QmszRVRHZVc4TFJUcHZFUElib2Zsdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
+          <t>Alta da ureia preocupa produtores e eleva custos da próxima safra - capitalnews.com.br</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>04/07/2026 07:00</t>
+          <t>04/07/2026 21:22</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZHVhcUh1QnEzbldNX2ZwU0FnWTJiTVFLTkpRRkpoemJYbEVMVkJCNV9zR0tJc3otWkhRdEs4M0JxTE5tOWdfY01pWjFveG4yNThjbmdnOE8xTTJPRl8xY25oYlFYR2JGbGd1SzNyVEV0d1haUEhHR0oxdGJNc05ZYTNHcEt6QzBvVmNpbWg2SEFiT2Z1OEpFT3B1bDZ0UmNRUjRadktMU2kzODkzS2w5bFU5UkJVNGJTSndzZzQ0b0llaTZyTjZXaVd6MExkRjBkSkJ6SQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3130,61 +3130,61 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Rússia prorroga proibição das exportações de enxofre - GlobalFert</t>
+          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>03/07/2026 18:37</t>
+          <t>04/07/2026 07:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPSDYtNVczb3hScWJXUzkxcVZLMzV1dTRic3hNZ0V5RDJrM3dQalVBaHN3azdoSG5rM2laeVMzUTlVV1poeDl6N2ZCd1pETUsyVktHOHlFcjJsNmFwMXVqSFgza2hMOHZhM3hYbEMweTZYUXhRVkRDVG1jRGV4UngyY2luRXVnRGM1eDlncHhPenNsYUJUX1Q0dmVNNlI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
+          <t>Rússia prorroga proibição das exportações de enxofre - GlobalFert</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>03/07/2026 13:20</t>
+          <t>03/07/2026 18:37</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPSDYtNVczb3hScWJXUzkxcVZLMzV1dTRic3hNZ0V5RDJrM3dQalVBaHN3azdoSG5rM2laeVMzUTlVV1poeDl6N2ZCd1pETUsyVktHOHlFcjJsNmFwMXVqSFgza2hMOHZhM3hYbEMweTZYUXhRVkRDVG1jRGV4UngyY2luRXVnRGM1eDlncHhPenNsYUJUX1Q0dmVNNlI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Alta do enxofre provoca crise na produção de fertilizantes em Minas Gerais - G1</t>
+          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>03/07/2026 07:00</t>
+          <t>03/07/2026 13:20</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQYnY2QmNpaXc4aHRDMDFLUmxTNzhRME9pNWhac1psdWtNMXMwSHJsN3oxeUJqNXZtOHVNWUNaQnNjOUJaLWRhbF91M05Sa3VIM3dsTjM2X2VLSS03ZTlPWFF4T2xLMUdzTlZLdk9tblk1WHRZUWtGT3BmUktDODYzMU1VUTEtbVc3N0VTelc4ZUROZDBkX2xZeFlma01wMjV3WHBISVdRQ0lwYmFseFA5d1ZnNXdFMVpRUk9zeHJpbEUzQ1Y0MUdpbXdiTnlSZ3o2ekJfbnZOYlNJU29nU2FaclhFR1ZqUmFx0gH3AUFVX3lxTE1sQjBVb2UzRGxTdGVBTXd6Y0lwX0pBUmYtOXIxYmU3b2EtLUtLYklfS3FHcHp3VklkU0xtdjlwMHAxYzJtNmcwNHkzOUd6TFBZZVkxa1VWVmJBRFZKLXFSLUpxQnc5al8ySjRJQkNFUnpWRXlmbTctMlp4SXd4OUJSai00ZGxocEd6dUVZbE8zZ0JXaDJ2SEllampRdER2aF9IRlBoMDZ4SHZ4UXhqT1RVYVV5ekFOSTVyUkgxQ0RJNzQ2N2ZfQThQR182WUVGQ2ZVNHBKOUtuVktNNG5LTVBnX2tUbGNHNzhOQkpuMEhjR2RBTHJYVkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
+          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
+          <t>Alta do enxofre provoca crise na produção de fertilizantes em Minas Gerais - G1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3228,195 +3228,195 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQYnY2QmNpaXc4aHRDMDFLUmxTNzhRME9pNWhac1psdWtNMXMwSHJsN3oxeUJqNXZtOHVNWUNaQnNjOUJaLWRhbF91M05Sa3VIM3dsTjM2X2VLSS03ZTlPWFF4T2xLMUdzTlZLdk9tblk1WHRZUWtGT3BmUktDODYzMU1VUTEtbVc3N0VTelc4ZUROZDBkX2xZeFlma01wMjV3WHBISVdRQ0lwYmFseFA5d1ZnNXdFMVpRUk9zeHJpbEUzQ1Y0MUdpbXdiTnlSZ3o2ekJfbnZOYlNJU29nU2FaclhFR1ZqUmFx0gH3AUFVX3lxTE1sQjBVb2UzRGxTdGVBTXd6Y0lwX0pBUmYtOXIxYmU3b2EtLUtLYklfS3FHcHp3VklkU0xtdjlwMHAxYzJtNmcwNHkzOUd6TFBZZVkxa1VWVmJBRFZKLXFSLUpxQnc5al8ySjRJQkNFUnpWRXlmbTctMlp4SXd4OUJSai00ZGxocEd6dUVZbE8zZ0JXaDJ2SEllampRdER2aF9IRlBoMDZ4SHZ4UXhqT1RVYVV5ekFOSTVyUkgxQ0RJNzQ2N2ZfQThQR182WUVGQ2ZVNHBKOUtuVktNNG5LTVBnX2tUbGNHNzhOQkpuMEhjR2RBTHJYVkk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>O Amado Batista. As 84 Toneladas de Calcário. A Dívida de R4 9 Mil Reais e a Cobrança na Justiça - O Antagônico</t>
+          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>03/07/2026 01:28</t>
+          <t>03/07/2026 07:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxON0w1Z1ZmVjZtdTR4dUlMYkFtdXVNXzByY3EtTlRabUxBUE1WYkZtRGpJbEVpNUNiS0s1NE50cnJ1SVJMUzNaX04wZUJhclV6Z3JYQWs1cm4xN0ljRUlyRHVTUGRyMG1teDVPRHBJZWM4X1hseEY0T0ZkNWxnUFF1aWZ4UURBYzN3VEJtZmM5NDhSYl9sei1qeGhQak1tS2dPcEtETkNjN2JlbUZsR0R6NlJ5YzNFeHVKU2ZrN0dwRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Pampa Energía avalia construir planta de ureia para atender o Brasil - Revista O Empreiteiro</t>
+          <t>O Amado Batista. As 84 Toneladas de Calcário. A Dívida de R4 9 Mil Reais e a Cobrança na Justiça - O Antagônico</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>02/07/2026 20:01</t>
+          <t>03/07/2026 01:28</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1xQS16X1g0QnF4SGdXWE05VHVtSGxieGNYYzBFbmh0M2U3S3BKbC12cmFMekR1SlRVd1U1VEh5aS1SazFwQTI1TjdEYWhOYXFTRm5nQldUTGdUaFpHQzJseDNYN1pIZGJJVEdz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxON0w1Z1ZmVjZtdTR4dUlMYkFtdXVNXzByY3EtTlRabUxBUE1WYkZtRGpJbEVpNUNiS0s1NE50cnJ1SVJMUzNaX04wZUJhclV6Z3JYQWs1cm4xN0ljRUlyRHVTUGRyMG1teDVPRHBJZWM4X1hseEY0T0ZkNWxnUFF1aWZ4UURBYzN3VEJtZmM5NDhSYl9sei1qeGhQak1tS2dPcEtETkNjN2JlbUZsR0R6NlJ5YzNFeHVKU2ZrN0dwRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nova técnica de pirólise por plasma transforma borra de café em biocarvão de alto desempenho em apenas 90 segundos, sem secagem prévia, triplica o carbono fixo, remove totalmente o enxofre e ainda cria um material altamente poroso para aplicações e - Folha BV</t>
+          <t>Pampa Energía avalia construir planta de ureia para atender o Brasil - Revista O Empreiteiro</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>02/07/2026 10:59</t>
+          <t>02/07/2026 20:01</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wJBVV95cUxOb0hhdlk1Y09OQVdsSVFqYW5oMDUtMkFqOVlnbTlSSDlSWUNIME12ekVCYTQwNjBQRmh6YUdtdGFRUkNMQnYxdkxGVlNuUlpiamd6aGl1bHdPbnlBcV82NWx0RGVKaXM2dU9pQTNTUlQzS3lKa3pQalRkUThjV2Q1d3kyV3JINHNvRldNbDFSVlhycVYwaWJaVDZGdTNOZXJPcWJ0dDVlb0hGcUxkbWwydWUyZlpDY3ltT0F2Z1ZXUnZFUVgzcldjc01DN09GbFAyR2dlSmZTU25aU1lkQWh6ZG5LMXNYODRWc1g5YkhUWDBLbmEyLVdHWFBzSE5EVmxmSncwOFI4a2dJUllZTVJ4bnZzZlBXeXYyUFpJSkgwXzBveVJzSmwzTGxpMW5TN191VGs3X1ZFTlYwdVBKRGpGY0lvd3J5N1Zsc0NwRnE4bjRBbkN2SmlKQmRrUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1xQS16X1g0QnF4SGdXWE05VHVtSGxieGNYYzBFbmh0M2U3S3BKbC12cmFMekR1SlRVd1U1VEh5aS1SazFwQTI1TjdEYWhOYXFTRm5nQldUTGdUaFpHQzJseDNYN1pIZGJJVEdz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Here’s Why Shark Tank Loved First Saturday Lime Insect Repellent</t>
+          <t>Nova técnica de pirólise por plasma transforma borra de café em biocarvão de alto desempenho em apenas 90 segundos, sem secagem prévia, triplica o carbono fixo, remove totalmente o enxofre e ainda cria um material altamente poroso para aplicações e - Folha BV</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>02/07/2026 08:32</t>
+          <t>02/07/2026 10:59</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57664a7fa24ed6993b612f43031368&amp;url=https%3a%2f%2fsg.news.yahoo.com%2fwhy-shark-tank-loved-first-153245354.html&amp;c=11954638987694979310&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi2wJBVV95cUxOb0hhdlk1Y09OQVdsSVFqYW5oMDUtMkFqOVlnbTlSSDlSWUNIME12ekVCYTQwNjBQRmh6YUdtdGFRUkNMQnYxdkxGVlNuUlpiamd6aGl1bHdPbnlBcV82NWx0RGVKaXM2dU9pQTNTUlQzS3lKa3pQalRkUThjV2Q1d3kyV3JINHNvRldNbDFSVlhycVYwaWJaVDZGdTNOZXJPcWJ0dDVlb0hGcUxkbWwydWUyZlpDY3ltT0F2Z1ZXUnZFUVgzcldjc01DN09GbFAyR2dlSmZTU25aU1lkQWh6ZG5LMXNYODRWc1g5YkhUWDBLbmEyLVdHWFBzSE5EVmxmSncwOFI4a2dJUllZTVJ4bnZzZlBXeXYyUFpJSkgwXzBveVJzSmwzTGxpMW5TN191VGs3X1ZFTlYwdVBKRGpGY0lvd3J5N1Zsc0NwRnE4bjRBbkN2SmlKQmRrUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil - Valor Econômico</t>
+          <t>Here’s Why Shark Tank Loved First Saturday Lime Insect Repellent</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>02/07/2026 07:00</t>
+          <t>02/07/2026 08:32</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUHSAcYBQVVfeXFMTmU1U0hwa0N3YmVjNzRrNWU2MTNfalNtQkNTeVQtTmVWX3k5R2hQU2VnRDA3NmZ2X2RKbVBTd0F2QnJSS0FGRG1tRGx5N0Q0RzVvdlpOb3FrYkI3WmUzdGxWNjdVY0Y1bmFfdmJidF9DeV84ZlFpX1hnSWcxZk9mREwyb1I0cjloeE9vZ2ZQZ3hvMlFsSUllbk5wLUR2cDF1TU12bW01bVFfQlY1UWhzQjJpc194S1dZeENMRXpCMTZxcm1YN0pR?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a577b6c107046e7b9764c41e370862c&amp;url=https%3a%2f%2fsg.news.yahoo.com%2fwhy-shark-tank-loved-first-153245354.html&amp;c=11954638987694979310&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
+          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>01/07/2026 13:48</t>
+          <t>02/07/2026 07:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUHSAcYBQVVfeXFMTmU1U0hwa0N3YmVjNzRrNWU2MTNfalNtQkNTeVQtTmVWX3k5R2hQU2VnRDA3NmZ2X2RKbVBTd0F2QnJSS0FGRG1tRGx5N0Q0RzVvdlpOb3FrYkI3WmUzdGxWNjdVY0Y1bmFfdmJidF9DeV84ZlFpX1hnSWcxZk9mREwyb1I0cjloeE9vZ2ZQZ3hvMlFsSUllbk5wLUR2cDF1TU12bW01bVFfQlY1UWhzQjJpc194S1dZeENMRXpCMTZxcm1YN0pR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Prefeitura garante calcário de graça para fortalecer a agricultura nos bairros de Navegantes - Jornal nos Bairros</t>
+          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>30/06/2026 21:22</t>
+          <t>01/07/2026 13:48</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNWVhCT0tJZHhMbEFaclNMWDVlMjdZQUozR3daYUszUUdoclltNzhBU1hXby16ZnlKVWV2Z01aaUxqVEhkbFNfTmowUEZZdVJSVUluSVM4VGIteTBuV0lpM1V2c2UxR3REZ1NmOXZiMk9QZEhxTXhwd1NRWjFCRFVzNUVicktKWWFBS3F6RGY3cFF4OVpJQnpXVnA1TFJsa0dPSUJ0ZEU4UFdqbi0xWlZPZTR0Q0w1ZGdFQ0hrUnVEUVFiemd6NEthUnUwV2pUbExla2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
+          <t>Prefeitura garante calcário de graça para fortalecer a agricultura nos bairros de Navegantes - Jornal nos Bairros</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>30/06/2026 07:00</t>
+          <t>30/06/2026 21:22</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNWVhCT0tJZHhMbEFaclNMWDVlMjdZQUozR3daYUszUUdoclltNzhBU1hXby16ZnlKVWV2Z01aaUxqVEhkbFNfTmowUEZZdVJSVUluSVM4VGIteTBuV0lpM1V2c2UxR3REZ1NmOXZiMk9QZEhxTXhwd1NRWjFCRFVzNUVicktKWWFBS3F6RGY3cFF4OVpJQnpXVnA1TFJsa0dPSUJ0ZEU4UFdqbi0xWlZPZTR0Q0w1ZGdFQ0hrUnVEUVFiemd6NEthUnUwV2pUbExla2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3426,19 +3426,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Cantor Amado Batista é alvo de processo por dívida de R$ 9 mil em Goiás - G1</t>
+          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3448,29 +3448,29 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNb3o1UmZSV2FwVFpzU2ZTZGJmeDBwSWxkekgxaHNZVXdyT2pIZVJiTC1FczZ0NGFFNDRMOEg5TDRhSk9HbnJDNUFEaEE3cE5uZWc2RXNzMzRBRVFOZ2VCMzhUQWFiQTNKTXBVelNnNGZVSHBPRXlzNS1MYUhyN08wZU15RkJKR3g1cEw0bkhPaGp2Rk1lWjBUTmpOMFg1SzF1Z0Jwd1BNazJIUUNCX3J5MTFTNFBDXzBhWTc3NGJwbUI5VFXSAdIBQVVfeXFMTzQxTjNHRjctYkp3S1NJS3FaaTc3TTJ4T2hNWnpiNVd1cDZtYWVrVl9QcFhrQVZTZWdEOU5xOU9ldjl5SnM1d0o0ekxNakVzYjRfNkhyb0F4eVFMSk1qUk0zWEVuenNVUEx5VHZja0JrZGppMWdsUGtBWkVXdUs3WHMtV3FJT2otQ1pyX2NGa1g5SzE2b2pGT1BTR2JkSTdVVlp0NEhrel9hZUxSLUpWUUFPV3BxMTRsV3hveEU2TnJIMC1EaThONGt6N1Q5elNHenZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Cantor Amado Batista é alvo de processo por dívida de R$ 9 mil em Goiás - G1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>29/06/2026 11:22</t>
+          <t>30/06/2026 07:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNb3o1UmZSV2FwVFpzU2ZTZGJmeDBwSWxkekgxaHNZVXdyT2pIZVJiTC1FczZ0NGFFNDRMOEg5TDRhSk9HbnJDNUFEaEE3cE5uZWc2RXNzMzRBRVFOZ2VCMzhUQWFiQTNKTXBVelNnNGZVSHBPRXlzNS1MYUhyN08wZU15RkJKR3g1cEw0bkhPaGp2Rk1lWjBUTmpOMFg1SzF1Z0Jwd1BNazJIUUNCX3J5MTFTNFBDXzBhWTc3NGJwbUI5VFXSAdIBQVVfeXFMTzQxTjNHRjctYkp3S1NJS3FaaTc3TTJ4T2hNWnpiNVd1cDZtYWVrVl9QcFhrQVZTZWdEOU5xOU9ldjl5SnM1d0o0ekxNakVzYjRfNkhyb0F4eVFMSk1qUk0zWEVuenNVUEx5VHZja0JrZGppMWdsUGtBWkVXdUs3WHMtV3FJT2otQ1pyX2NGa1g5SzE2b2pGT1BTR2JkSTdVVlp0NEhrel9hZUxSLUpWUUFPV3BxMTRsV3hveEU2TnJIMC1EaThONGt6N1Q5elNHenZ3?oc=5</t>
         </is>
       </c>
     </row>
@@ -3504,17 +3504,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Segundo o WSJ, a Martin Marietta e a Lhoist North America vão se fundir em um negócio de US$ 13,5 bilhões - TradingView</t>
+          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>29/06/2026 07:00</t>
+          <t>29/06/2026 11:22</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE85QWpvMXdqUXlsdVlyQ1pRXzUxUWZIY24yVlhHOXpONU5hQjdGM3ZNU1QwMGxBWWxiRGN2UVA2aGFBNHJ3bVQyYVR0T1JzNjI3SWltcmQ1c3BpY25CMC1Pa3BhaXRCTk9QMzFuSzUyNWFZRnNJVFFyYQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3543,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
+          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3558,19 +3558,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
+          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -3592,61 +3592,61 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi</t>
+          <t>Segundo o WSJ, a Martin Marietta e a Lhoist North America vão se fundir em um negócio de US$ 13,5 bilhões - TradingView</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>29/06/2026 03:13</t>
+          <t>29/06/2026 07:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57664b1dd34ddf94f84617f9547c20&amp;url=https%3a%2f%2fvalor.globo.com%2fempresas%2fnoticia%2f2026%2f06%2f29%2fcom-foco-em-data-centers-martin-marietta-acerta-compra-de-fornecedora-de-minerais-por-us-135-bi.ghtml&amp;c=16419230671194560723&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE85QWpvMXdqUXlsdVlyQ1pRXzUxUWZIY24yVlhHOXpONU5hQjdGM3ZNU1QwMGxBWWxiRGN2UVA2aGFBNHJ3bVQyYVR0T1JzNjI3SWltcmQ1c3BpY25CMC1Pa3BhaXRCTk9QMzFuSzUyNWFZRnNJVFFyYQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
+          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>26/06/2026 16:47</t>
+          <t>29/06/2026 03:13</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a577b6c5bef4df0914d1a9c2b611c6d&amp;url=https%3a%2f%2fvalor.globo.com%2fempresas%2fnoticia%2f2026%2f06%2f29%2fcom-foco-em-data-centers-martin-marietta-acerta-compra-de-fornecedora-de-minerais-por-us-135-bi.ghtml&amp;c=16419230671194560723&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
+          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>26/06/2026 07:00</t>
+          <t>26/06/2026 16:47</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Embarques de fertilizantes crescem após acordo no estreito de Ormuz - CNN Brasil</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcENnZnlBVWF1ZEVFeElfLU56Y1RaZ2ZiQkdOck1KdnJkbzUwa1Z3dUo3aTItQmJrRjNKVVZKLW9NNHdhSE9FejZXb3ZiMDZZSTBGdk16SmZ2ckd1UHB2TXlNYnFZc1c2V0hlaXF4ZEpRT1pWcktSM055QXBtS3d2bVMtU1BFWkRkQmt6alZiYWFldVR0ZWp1N2hGMjRFLUlnMkxNTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
+          <t>Embarques de fertilizantes crescem após acordo no estreito de Ormuz - CNN Brasil</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3690,41 +3690,41 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcENnZnlBVWF1ZEVFeElfLU56Y1RaZ2ZiQkdOck1KdnJkbzUwa1Z3dUo3aTItQmJrRjNKVVZKLW9NNHdhSE9FejZXb3ZiMDZZSTBGdk16SmZ2ckd1UHB2TXlNYnFZc1c2V0hlaXF4ZEpRT1pWcktSM055QXBtS3d2bVMtU1BFWkRkQmt6alZiYWFldVR0ZWp1N2hGMjRFLUlnMkxNTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Brazilian Farmers Delay Input Purchases as They Await Debt Relief Bill, Mosaic Says - The AgriBiz</t>
+          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>25/06/2026 07:00</t>
+          <t>26/06/2026 07:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQN2xNaUxQMDVWZl9tOVF1UFA3SG9QaHdTVndkU2Z3ci1Dazl6cElWRmV1NjVDMzVyY1Z1ckh1S2kydnFleVQ0YXpnOExKdlpBVkFPMk1xUWJodkpjODgyMzB3Q1lSdmN1Rm04SG1yb3hLbnhjb21fdUFoeFFoN0d6d3YzSHVfMmZWcF9WMHBKV2RRTUR6Z1VuRTRKM21CdTctOGh6VDdQSHhaQ0xhZV9xd1c0dU9wVkZIQ2U3c21weWtCdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
+          <t>Brazilian Farmers Delay Input Purchases as They Await Debt Relief Bill, Mosaic Says - The AgriBiz</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3734,63 +3734,63 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQN2xNaUxQMDVWZl9tOVF1UFA3SG9QaHdTVndkU2Z3ci1Dazl6cElWRmV1NjVDMzVyY1Z1ckh1S2kydnFleVQ0YXpnOExKdlpBVkFPMk1xUWJodkpjODgyMzB3Q1lSdmN1Rm04SG1yb3hLbnhjb21fdUFoeFFoN0d6d3YzSHVfMmZWcF9WMHBKV2RRTUR6Z1VuRTRKM21CdTctOGh6VDdQSHhaQ0xhZV9xd1c0dU9wVkZIQ2U3c21weWtCdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - Portal Arauto</t>
+          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>24/06/2026 18:03</t>
+          <t>25/06/2026 07:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1a fabrica de bateria de litio-enxofre do mundo - CPG Click Petróleo e Gás</t>
+          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - Portal Arauto</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>24/06/2026 07:00</t>
+          <t>24/06/2026 18:03</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQYnFCT1R2NWVCa3c3bkgyc0ZNdEJCeTkzVkN1SEZ5TXZUektSTzJabG1YaFFBdGY3dnZmQ3E1U0JBc1oxT3FuQmJ0WWZyUUYxZ2x0QW1DenRLd0FQd1d2WThZQkxLZy12bmVCT2duU2haV0ZJdUd4YXVaNkZqclBqdWNEa1UxZDJlZlF4Tk9nSHhmTVdTT0RqTHBrcTFiQlBhTTV3NG84elFoem5LVmlmU0x4WFV5QUd5YlRHQjk1VUVHQzNwaUxZQThXVjFwa2Yzc09SUUdSS3BIU1FQYUVMVlZCWFlHNjN2MThZOEhXRnVBSTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Arqueólogos encontram mosaico de deus do rio na Turquia - Aventuras na História</t>
+          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3800,19 +3800,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNdFM4Yk1jUU5RMURVMTViQklhT2I4SW1jWUxTRVI0azJDM2lmMGtrWThNNGNKTE5HcWFabEV5MUVNU2lSc2NIYkhmbm5xcWZieXAxRmRpN1BPWXlscGtIZmZyZHREWkhQc21scEQ0d3ZobjB6eER4TVNMMHpfVUNMUGRVY3lFNnRRRGVhLUxVd0l0OXBRT3RKWjdtMENVcm5RRURBZ2EyVlNXTkc2UlpjdWozMVRXMWdyVW5j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
+          <t>Arqueólogos encontram mosaico de deus do rio na Turquia - Aventuras na História</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNdFM4Yk1jUU5RMURVMTViQklhT2I4SW1jWUxTRVI0azJDM2lmMGtrWThNNGNKTE5HcWFabEV5MUVNU2lSc2NIYkhmbm5xcWZieXAxRmRpN1BPWXlscGtIZmZyZHREWkhQc21scEQ0d3ZobjB6eER4TVNMMHpfVUNMUGRVY3lFNnRRRGVhLUxVd0l0OXBRT3RKWjdtMENVcm5RRURBZ2EyVlNXTkc2UlpjdWozMVRXMWdyVW5j?oc=5</t>
         </is>
       </c>
     </row>
@@ -3851,12 +3851,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
+          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4027,12 +4027,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
+          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4071,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
+          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4086,19 +4086,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mosaico de antigo 'deus do rio' é encontrado na Turquia - Globo</t>
+          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOLTdXYW1GZW4ybGRZM2Q1OU5WWFNYNEVENXNhVDZBTG9LanM0YnM2NGlZQnAxbThZeWs0a0lOdVgyVkRfN3JQaEI4RHY1Y3BLa1lobmFuN1VvTGg5SUFiT2VvMkNxMHJDdjdyRTJGWm1HZWxpRlZNajdmQmg0WERVTGlyeW80U2g0WDctOGY0X0Vsblg5RVVLdmtFanU2bkVaaWNEQjhCdE1MWlg1cmpOZ05RQXZMcXPSAcYBQVVfeXFMUGFBczRwMXpFN0tOdm1GWWlid0hBYjV4bEFQbWRMeUEzS0hFTzZiNTdvVUI2QW5SaGg1OUY2cXV2Q1ltellaSEk1V3BHUHBzeTMwSmZJZTUxZ2FEN1UxNTVQWjY1eVBaOHFkblBqTWc3VDJWdXpzRGo0QUI1TVdYYk9MdE1uSGwxSHFnQktpX2VZYzlwT1FWT2Jub1U5dWdHWHlWRlhDZHU0ck51SmZKVjBqREhaa0JVcnFsN2tMN0dlLU0welJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
         </is>
       </c>
     </row>
@@ -4137,12 +4137,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
+          <t>Mosaico de antigo 'deus do rio' é encontrado na Turquia - Globo</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOLTdXYW1GZW4ybGRZM2Q1OU5WWFNYNEVENXNhVDZBTG9LanM0YnM2NGlZQnAxbThZeWs0a0lOdVgyVkRfN3JQaEI4RHY1Y3BLa1lobmFuN1VvTGg5SUFiT2VvMkNxMHJDdjdyRTJGWm1HZWxpRlZNajdmQmg0WERVTGlyeW80U2g0WDctOGY0X0Vsblg5RVVLdmtFanU2bkVaaWNEQjhCdE1MWlg1cmpOZ05RQXZMcXPSAcYBQVVfeXFMUGFBczRwMXpFN0tOdm1GWWlid0hBYjV4bEFQbWRMeUEzS0hFTzZiNTdvVUI2QW5SaGg1OUY2cXV2Q1ltellaSEk1V3BHUHBzeTMwSmZJZTUxZ2FEN1UxNTVQWjY1eVBaOHFkblBqTWc3VDJWdXpzRGo0QUI1TVdYYk9MdE1uSGwxSHFnQktpX2VZYzlwT1FWT2Jub1U5dWdHWHlWRlhDZHU0ck51SmZKVjBqREhaa0JVcnFsN2tMN0dlLU0welJ3?oc=5</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Sistema FAEP lamenta decisão da ANTT que impede o cultivo agrícola na faixa de domínio - Minuto Rural</t>
+          <t>Um pedido de socorro para os fertilizantes | Radar Econômico - VEJA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4196,19 +4196,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPaHp3NnFKcU5hLURNY2RlTW1XWHc4WnFkWkZQRlVxQ0RfaEpTdGlaMlFIbTF4M0pNMEs1dnpZOGNjdUFuckRlMUlUV1BmN1puMkFkMHZ0SEVQbm1kMVRKLXVLYWs1dHJtTDhBN3ptbU40NjB1NGxDcU1xUTV4bTlLc1g4T19CNDVrQVkxd0lQQmZiTmluRGhrN1hWbGc4bm1leHNod0NQdld3T29tWmc2MmwyZzBoN19IT0hZdU53VzVrY0J1N2phOG8xMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNXzNyRkc3R1RCQVRpMzZlZGRtN1J6bkJtZl9YRzBFN2JkdElMc01CN2lyaWVOanRNekgybzJrNnhwMHdZV3pDTUZEY2lkMno5dHNPZ3pCSlM2QTROUlJuSFo3cWpxQzR3cGhLUzJYRmY2SXFobEdOTGpfdEhVTS1Jc0IxMGJ0TllQMFNrVnNFa0QwZlRfTGw4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Um pedido de socorro para os fertilizantes | Radar Econômico - VEJA</t>
+          <t>Sistema FAEP lamenta decisão da ANTT que impede o cultivo agrícola na faixa de domínio - Minuto Rural</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNXzNyRkc3R1RCQVRpMzZlZGRtN1J6bkJtZl9YRzBFN2JkdElMc01CN2lyaWVOanRNekgybzJrNnhwMHdZV3pDTUZEY2lkMno5dHNPZ3pCSlM2QTROUlJuSFo3cWpxQzR3cGhLUzJYRmY2SXFobEdOTGpfdEhVTS1Jc0IxMGJ0TllQMFNrVnNFa0QwZlRfTGw4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPaHp3NnFKcU5hLURNY2RlTW1XWHc4WnFkWkZQRlVxQ0RfaEpTdGlaMlFIbTF4M0pNMEs1dnpZOGNjdUFuckRlMUlUV1BmN1puMkFkMHZ0SEVQbm1kMVRKLXVLYWs1dHJtTDhBN3ptbU40NjB1NGxDcU1xUTV4bTlLc1g4T19CNDVrQVkxd0lQQmZiTmluRGhrN1hWbGc4bm1leHNod0NQdld3T29tWmc2MmwyZzBoN19IT0hZdU53VzVrY0J1N2phOG8xMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -4291,12 +4291,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>O mistério dos 99% do enxofre desaparecido: uma simulação mostra onde pode estar guardado um dos maiores enigmas da galáxia - Olhar Digital</t>
+          <t>Compra de ativos existentes pode antecipar em dois anos o início da operação da St George em Araxá - Diário do Comércio</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4306,19 +4306,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxNdjM4WGE4cTNIOF9QMU9LMTh3NjYxVUg2ODhGLWluRVNFUV8zamxkSUEwM0pLVjdCRUJMQ1ZFb1BvQkRYVWlKVGRwY1BvZGxGOWVSUTNBdklQWm82aGllamdpQ1RmcFZMSVJjZmU0WDBFbFE4bGRabVZZWU45LWVidXVLeHVnRkQ1c21lMHpkWFJFTjVUd0lxX2VXS0FxV0hod3ZzbUpkalRDRzlMaE56OVYxWXNLTkxBZU9zUFpmOGNRQ0s5N1F1TmRCdTdYMEhrcTFHOHVvN05rcW91SDJCNlFMMTRfNmllMEZuNGpJZWhNNlFZS1BJSkRHU0p3eXc1eGltMkRmd1N0dndYNlJIZWV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE90MzZRdUdobThNWk13akRvUnVnWno1c1Q5cEU3a3EyUnExQzA2LW5MRlRPNXZIYml3dXJFYVBPRzYyeUhuMjVZTGJDWDNIYkZjRVF2XzdQank4TmMtUmdmYmhreWZfTTZQbUZaWFowNF9vNHM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Compra de ativos existentes pode antecipar em dois anos o início da operação da St George em Araxá - Diário do Comércio</t>
+          <t>O mistério dos 99% do enxofre desaparecido: uma simulação mostra onde pode estar guardado um dos maiores enigmas da galáxia - Olhar Digital</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE90MzZRdUdobThNWk13akRvUnVnWno1c1Q5cEU3a3EyUnExQzA2LW5MRlRPNXZIYml3dXJFYVBPRzYyeUhuMjVZTGJDWDNIYkZjRVF2XzdQank4TmMtUmdmYmhreWZfTTZQbUZaWFowNF9vNHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxNdjM4WGE4cTNIOF9QMU9LMTh3NjYxVUg2ODhGLWluRVNFUV8zamxkSUEwM0pLVjdCRUJMQ1ZFb1BvQkRYVWlKVGRwY1BvZGxGOWVSUTNBdklQWm82aGllamdpQ1RmcFZMSVJjZmU0WDBFbFE4bGRabVZZWU45LWVidXVLeHVnRkQ1c21lMHpkWFJFTjVUd0lxX2VXS0FxV0hod3ZzbUpkalRDRzlMaE56OVYxWXNLTkxBZU9zUFpmOGNRQ0s5N1F1TmRCdTdYMEhrcTFHOHVvN05rcW91SDJCNlFMMTRfNmllMEZuNGpJZWhNNlFZS1BJSkRHU0p3eXc1eGltMkRmd1N0dndYNlJIZWV3?oc=5</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
+          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOc2dmVzJBa0tyZGQ3T3dCOFlFZjhkQXg0SmFjUmltT3RmbVlKSDlfYm1vOHNDMG5kdTdDalcyQ3dmTTlyY00taHRwTVhRSE54ZUdjdEZNWVEwYkRmRV9JS0FOY0xIQ01ISUF3VHA5ZmVZVS1XdlA2Mzk1UUNEbHFuT1VyUFhYSWZlU2lVay0wYUl1WmFzaEg5VmpKaGw1OTFHdWlHdDBGWlpqUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
+          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOc2dmVzJBa0tyZGQ3T3dCOFlFZjhkQXg0SmFjUmltT3RmbVlKSDlfYm1vOHNDMG5kdTdDalcyQ3dmTTlyY00taHRwTVhRSE54ZUdjdEZNWVEwYkRmRV9JS0FOY0xIQ01ISUF3VHA5ZmVZVS1XdlA2Mzk1UUNEbHFuT1VyUFhYSWZlU2lVay0wYUl1WmFzaEg5VmpKaGw1OTFHdWlHdDBGWlpqUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4489,12 +4489,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
+          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4504,19 +4504,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
+          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
+          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
+          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4665,12 +4665,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
+          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
+          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4746,19 +4746,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4768,19 +4768,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
+          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
+          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4973,12 +4973,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
+          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4988,19 +4988,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
+          <t>Mosaic suspende mineração em Tapira por 30 dias e acende alerta em Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5010,19 +5010,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOMU1lSmhaSEJPbE5tbmdCU3ozeXVFcUdfX2dGZ2k3c3hGUzNaX2NCTUlfMlZiZjBLa2xXSHpFUURHbFBwLWRVZFdKOXJFVjBhb2t5SnZjVGJYcS1zRGlPNVN3dFRuVHF3WEtXeFkxelM2dUV4S0tLME41WVBFV1lZZWJSbFNZVzQwSEZNUk9teEtQM1M5eV90cnBpeWpCSW5kVDFNZl96aFd4TEd6aEV0OUMyMTLSAbwBQVVfeXFMTjl1UzR0Q2dTWHFEN0FqdktmQ0Nlc2p3YXBYLVpNTnlGVUFXOGNwUXNuMTZRdWZoQ2ttSHFzNEZsY2ltWjdqT05uUVpPSjdaUkR2YTFXYXV6RVZERU5rRk52ZGU1d2Vac2ptRDFTVXFVWGgzZTFCNzMyZ0VpZ1o4RWpLa044YUVEX2lMWEJYVDAta1RWRnhrV1BKYmZpSVpKSm56N2wzU3dCQldWV3R0VEJLNTJGbHdxY0VRdVo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
+          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5032,19 +5032,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Mosaic suspende mineração em Tapira por 30 dias e acende alerta em Uberaba - JM Online</t>
+          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5054,19 +5054,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOMU1lSmhaSEJPbE5tbmdCU3ozeXVFcUdfX2dGZ2k3c3hGUzNaX2NCTUlfMlZiZjBLa2xXSHpFUURHbFBwLWRVZFdKOXJFVjBhb2t5SnZjVGJYcS1zRGlPNVN3dFRuVHF3WEtXeFkxelM2dUV4S0tLME41WVBFV1lZZWJSbFNZVzQwSEZNUk9teEtQM1M5eV90cnBpeWpCSW5kVDFNZl96aFd4TEd6aEV0OUMyMTLSAbwBQVVfeXFMTjl1UzR0Q2dTWHFEN0FqdktmQ0Nlc2p3YXBYLVpNTnlGVUFXOGNwUXNuMTZRdWZoQ2ttSHFzNEZsY2ltWjdqT05uUVpPSjdaUkR2YTFXYXV6RVZERU5rRk52ZGU1d2Vac2ptRDFTVXFVWGgzZTFCNzMyZ0VpZ1o4RWpLa044YUVEX2lMWEJYVDAta1RWRnhrV1BKYmZpSVpKSm56N2wzU3dCQldWV3R0VEJLNTJGbHdxY0VRdVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
+          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5076,19 +5076,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
+          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Anvisa recolhe coco ralado por excesso de dióxido de enxofre; saiba quais são os riscos à saúde - Notícias ao Minuto Brasil</t>
+          <t>Anvisa manda recolher lote de coco ralado ‘Casa de Mãe’, da marca Qualicoco, por excesso de enxofre - Estadão</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPVlFOZlF1ZGhHU1NNYjlNdm1kVzNDT0IwX0pRZUVzaFkwUTVhRnFvdU1xcnhnNl9PYllWVmdnVDVkXzlFcVJhYVoydXo5TURlVHlnR3Y1bjNrRGtGMTg0SkFoODdPblU4Qy1fbW9IcGFVN1BZVWloSVlWemNpM19KVlE3OVRiV1MwZmt4UXdlUmR4ZzdqU09RNmgwdWpjVDBtcVRkNWZseF92SnZySUN4VXlCMzdxa0JIU1FDd2FkZlNBbmhUNHBLdDNEVFlfQ3gwblpPbk9qcHNheHkyb1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQYzh2cjdEME1NdHBVU0EwUEp4emJrSVMwWERxTW5FeFduT2prV3lyZ3lGbkFkOUtzcG01WV9sQUtObUl0N3FhbzhOVXI5eG1wWEwyN0ZrcDdSczdCa2plUFZTSWtGS21TODBYNGpWSDZpbTR0d0hwYWhJU29vbUlnaG5zcThDV2liYURCdHE3VDV4WWNVMlM5Um8yTUItMWI3ZFdEa0ZTZEFfa08yZHFOVksxdXo3SktXeGVrd2liNlU0b24yS0JWT2M5eHZnYU3SAdQBQVVfeXFMTmthZ3daS3ZoN1NrVzN0RXFfdXZJcHRkQTBwaVFmdmpfZGJlQVFaY0MwSmNYSDMydWZVeUN5NnVlWXZhQkNWX3BUSUpyQzQ3aUZKTk1yemJyNmhCTkNfSmM0V3NXc2t0eDEzcEQ2eHZxZkM3V3RZRlNjYkVaUmVmT2JvQ1lweDAySEZYem80MlE4TVItVGZaTi1yQ1paTktMQzhaTWNoWktGMGtiMXFjYnJLZFBocnBNbV9oYXJIWWNyaUwxSWlVNlpYR2VjS0pXZ0F3ZDk?oc=5</t>
         </is>
       </c>
     </row>
@@ -5286,29 +5286,29 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado ‘Casa de Mãe’, da marca Qualicoco, por excesso de enxofre - Estadão</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>29/05/2026 07:00</t>
+          <t>28/05/2026 07:00</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQYzh2cjdEME1NdHBVU0EwUEp4emJrSVMwWERxTW5FeFduT2prV3lyZ3lGbkFkOUtzcG01WV9sQUtObUl0N3FhbzhOVXI5eG1wWEwyN0ZrcDdSczdCa2plUFZTSWtGS21TODBYNGpWSDZpbTR0d0hwYWhJU29vbUlnaG5zcThDV2liYURCdHE3VDV4WWNVMlM5Um8yTUItMWI3ZFdEa0ZTZEFfa08yZHFOVksxdXo3SktXeGVrd2liNlU0b24yS0JWT2M5eHZnYU3SAdQBQVVfeXFMTmthZ3daS3ZoN1NrVzN0RXFfdXZJcHRkQTBwaVFmdmpfZGJlQVFaY0MwSmNYSDMydWZVeUN5NnVlWXZhQkNWX3BUSUpyQzQ3aUZKTk1yemJyNmhCTkNfSmM0V3NXc2t0eDEzcEQ2eHZxZkM3V3RZRlNjYkVaUmVmT2JvQ1lweDAySEZYem80MlE4TVItVGZaTi1yQ1paTktMQzhaTWNoWktGMGtiMXFjYnJLZFBocnBNbV9oYXJIWWNyaUwxSWlVNlpYR2VjS0pXZ0F3ZDk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
+          <t>Anvisa manda recolher e proíbe venda de lote de coco ralado por excesso de enxofre - ND Mais</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9HMUF4TXN5WUx0RTZMTUktampKOHB4MjQtTWZyR1ROQ05MOXNYQW95NHpuZjlieXJCYlNGN3U1ZjhCTzlRaEMyWlZ1eUh1TldxaFREdmktMm9IQ0VHSUpDS2U3TFJNZFNiVy1FeWZDVld1X1c2NEpqX09OVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre; confira marca - Rádio Metrópole</t>
+          <t>Anvisa manda recolher lote de coco ralado ‘Casa de Mãe’ por excesso de enxofre - InfoMoney</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQSjRVamltMjVSeTh5ZWpfTVZRQnNIRGdhc3AzNkRiQy1oSnFkQnZMczVraFl0WGNjSkhRcmRfclVoQkxtU1BROVNnaWhWaDNnd25MNHNWY28yUTVuMTNvSVpzelNBMjBvMGhCeWdXdlUtZWhwTG9HUV9kSFBDMUIwSTZxWURqQm9pc2xWd19MZ3p2bkZJdjRwUkVKS3plakJuNVdlN0FTd3BIcTdGY09PRXpoMGJtbXNuNUlqNE9zYWNqTVMwNXpXR1dtcllxUW9hM3pQODRscw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNY3VXbXR6elA5QnVDckUtalR6SlJ2eTFIdGx4VVFvOUFiY2M1RXNiOXNNZjYzR3lYbm16M1Fja0Nfb0JGT19hVmtvM0dpV0I1QUFseGtjQThVWVNQM3J6REQ5OXFVWVprYkJwZFJIRWFfdVd6cEM4M09uSHVxcTJ2MjgxNkdXRV9DcUxJWkJueU9VZ3BONVRNY1lIRWFvLWVuZ1dkQ29ET3FUMGlnSmo4a180QVDSAboBQVVfeXFMTnROSmxBSEpfdEw0TWFud0dPbTRwVmlCYUdoRld2cHVIVmpINm4zbEJjMEdjNVVURWpmZzdnSjR1Qk00Y3FLVWE0aVptWUpRc1kwUE9FemJEUjlzb3J2LXhZTGZRWEFqTGZJUjRGWllnZ0xablRHVkxzX1FBRWFDMXRqRExsZFhnNGNncVdsTXJaanNBOU1ZZW5VdEJrVlVyNDZUNTBGU2h0Y241SlJRc2hSb1hzQ1dWUUx3?oc=5</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher e proíbe venda de lote de coco ralado por excesso de enxofre - ND Mais</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de dióxido de enxofre - O POVO</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9HMUF4TXN5WUx0RTZMTUktampKOHB4MjQtTWZyR1ROQ05MOXNYQW95NHpuZjlieXJCYlNGN3U1ZjhCTzlRaEMyWlZ1eUh1TldxaFREdmktMm9IQ0VHSUpDS2U3TFJNZFNiVy1FeWZDVld1X1c2NEpqX09OVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXFuR084YlVCYWlxRWFFZElvOXhoZGFYbXh6WXBHZzZOSm40Y3VtSUVzZjh3MVdSRGxvVVhUOWRWOHh4T1lQdUQzYVFBNXhadDhJUGpPVnBmeU1MWUo3Wk81T3JBeGkxVkUyNHlDaU11eldSckM1ZlpmQjJ0VEVFWTI4M1FtYkpxUVc0UVREUXpZZFI0clA1a1ZkS3FiNl9JMzZiVmtwN24xYWNfN0xFUUhKMlYwM1VGRm5PZ3R5cmVTNTBVRkpyb3pQM2w?oc=5</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado ‘Casa de Mãe’ por excesso de enxofre - InfoMoney</t>
+          <t>Anvisa determina recolhimento de coco ralado por excesso de enxofre - O Dia</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5384,19 +5384,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNY3VXbXR6elA5QnVDckUtalR6SlJ2eTFIdGx4VVFvOUFiY2M1RXNiOXNNZjYzR3lYbm16M1Fja0Nfb0JGT19hVmtvM0dpV0I1QUFseGtjQThVWVNQM3J6REQ5OXFVWVprYkJwZFJIRWFfdVd6cEM4M09uSHVxcTJ2MjgxNkdXRV9DcUxJWkJueU9VZ3BONVRNY1lIRWFvLWVuZ1dkQ29ET3FUMGlnSmo4a180QVDSAboBQVVfeXFMTnROSmxBSEpfdEw0TWFud0dPbTRwVmlCYUdoRld2cHVIVmpINm4zbEJjMEdjNVVURWpmZzdnSjR1Qk00Y3FLVWE0aVptWUpRc1kwUE9FemJEUjlzb3J2LXhZTGZRWEFqTGZJUjRGWllnZ0xablRHVkxzX1FBRWFDMXRqRExsZFhnNGNncVdsTXJaanNBOU1ZZW5VdEJrVlVyNDZUNTBGU2h0Y241SlJRc2hSb1hzQ1dWUUx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOeTZiM28xa2hiZEFUbFNlN3RreUVCTGw5RUtYVVVOVG9Fa0o1UWxHcFJLZW1sVThVcXlqT2RWbnNjLWFZTUp4enREa0dUNC0wQUdRVVI3MGRLQWt1cGZTdmNLV2RFR3BNcDJ6aUIxWFBfcGtNV3pMQVFIMnA0T19ud1dvSVVpV3c1U3V5NVJlNzBZS3NhbHFsQklVdzBYZUozV3FvdHNvZ1ViTWx4T2FzTTFYU005TDRjbWfSAb8BQVVfeXFMTnl2N3d1N1JxS2ZqWHZaOVQ2SnBQQ0xDWTRzdWxHLXBzQkxrMVhCTHpvUnBPV2xsTUFGSFRCZEdSNEpnVy1ZMXctUVdpVUM4bkppRU5tdks4dXJuczB2eTdGbXFSbHVkcDZjMW1Id1RZc05DdDBxTWVabXFiQmVndXBUNFhBZmFPUmNYclljdHNaNTlpVjQtX1hEbEhIM1BtbFI1RGZFWVJoUjF6MWVVRVhzV3Y1WDFVZ0hwa2x6N3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre - Pleno.News</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5406,19 +5406,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdHBVZWl1TWRoenctMVBqRFhvUkhUNVVkV3hGZ3Vkc2lNX2V3eTRXTVFqdmhZU2Y1OFdZUjJDMW9KV29MSWNfTi12SGhkb3lwZ2ViRnlsalhmY0JCVmJHTElIWGlpVi11Y2VMUnRleU5STUszZ1ZMeHRQMjB1Zk5uTEEtbjVMNUJrQXdNYnNUZ0pQakEwY0JrZk1nONIBowFBVV95cUxORFQ1MVBTQ1VsdTlOQ28xemxBLUNHaEtIUFctakRUckU5aEFKM1VhNU9vdVE3WDZ6NWtFaVZnd09NWk1IUDd5XzBKZTVFbVN1R0U3a1N2Yk5sczBIZDhERmQyZjNIMG51d3NjTFd1VFJaOWN0bmRPa1RCZWQwUjVjRnV1c29kZHpoa3R2c2VOangxc2VaTlItNUNTajJmQVhBNUlV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de coco ralado por excesso de enxofre - O Dia</t>
+          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOeTZiM28xa2hiZEFUbFNlN3RreUVCTGw5RUtYVVVOVG9Fa0o1UWxHcFJLZW1sVThVcXlqT2RWbnNjLWFZTUp4enREa0dUNC0wQUdRVVI3MGRLQWt1cGZTdmNLV2RFR3BNcDJ6aUIxWFBfcGtNV3pMQVFIMnA0T19ud1dvSVVpV3c1U3V5NVJlNzBZS3NhbHFsQklVdzBYZUozV3FvdHNvZ1ViTWx4T2FzTTFYU005TDRjbWfSAb8BQVVfeXFMTnl2N3d1N1JxS2ZqWHZaOVQ2SnBQQ0xDWTRzdWxHLXBzQkxrMVhCTHpvUnBPV2xsTUFGSFRCZEdSNEpnVy1ZMXctUVdpVUM4bkppRU5tdks4dXJuczB2eTdGbXFSbHVkcDZjMW1Id1RZc05DdDBxTWVabXFiQmVndXBUNFhBZmFPUmNYclljdHNaNTlpVjQtX1hEbEhIM1BtbFI1RGZFWVJoUjF6MWVVRVhzV3Y1WDFVZ0hwa2x6N3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre; confira marca - Rádio Metrópole</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5450,19 +5450,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQSjRVamltMjVSeTh5ZWpfTVZRQnNIRGdhc3AzNkRiQy1oSnFkQnZMczVraFl0WGNjSkhRcmRfclVoQkxtU1BROVNnaWhWaDNnd25MNHNWY28yUTVuMTNvSVpzelNBMjBvMGhCeWdXdlUtZWhwTG9HUV9kSFBDMUIwSTZxWURqQm9pc2xWd19MZ3p2bkZJdjRwUkVKS3plakJuNVdlN0FTd3BIcTdGY09PRXpoMGJtbXNuNUlqNE9zYWNqTVMwNXpXR1dtcllxUW9hM3pQODRscw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de dióxido de enxofre - O POVO</t>
+          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5472,19 +5472,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXFuR084YlVCYWlxRWFFZElvOXhoZGFYbXh6WXBHZzZOSm40Y3VtSUVzZjh3MVdSRGxvVVhUOWRWOHh4T1lQdUQzYVFBNXhadDhJUGpPVnBmeU1MWUo3Wk81T3JBeGkxVkUyNHlDaU11eldSckM1ZlpmQjJ0VEVFWTI4M1FtYkpxUVc0UVREUXpZZFI0clA1a1ZkS3FiNl9JMzZiVmtwN24xYWNfN0xFUUhKMlYwM1VGRm5PZ3R5cmVTNTBVRkpyb3pQM2w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
+          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5538,19 +5538,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre - Pleno.News</t>
+          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5560,19 +5560,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdHBVZWl1TWRoenctMVBqRFhvUkhUNVVkV3hGZ3Vkc2lNX2V3eTRXTVFqdmhZU2Y1OFdZUjJDMW9KV29MSWNfTi12SGhkb3lwZ2ViRnlsalhmY0JCVmJHTElIWGlpVi11Y2VMUnRleU5STUszZ1ZMeHRQMjB1Zk5uTEEtbjVMNUJrQXdNYnNUZ0pQakEwY0JrZk1nONIBowFBVV95cUxORFQ1MVBTQ1VsdTlOQ28xemxBLUNHaEtIUFctakRUckU5aEFKM1VhNU9vdVE3WDZ6NWtFaVZnd09NWk1IUDd5XzBKZTVFbVN1R0U3a1N2Yk5sczBIZDhERmQyZjNIMG51d3NjTFd1VFJaOWN0bmRPa1RCZWQwUjVjRnV1c29kZHpoa3R2c2VOangxc2VaTlItNUNTajJmQVhBNUlV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
+          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
+          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5648,19 +5648,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
+          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5670,19 +5670,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
+          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
+          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5758,19 +5758,19 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5780,19 +5780,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5802,19 +5802,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Copa do Calcário define os semifinalistas - FERJ</t>
+          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5824,19 +5824,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
+          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
+          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5868,19 +5868,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
+          <t>Copa do Calcário define os semifinalistas - FERJ</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
         </is>
       </c>
     </row>
@@ -5919,12 +5919,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
+          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5934,19 +5934,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQcG9FWW8yeVV3REc1bWxBY1I1NFh5TmJxbE5BakhjcklocVNvMDVISHNhQjE0NU43Q2tOeGdUaDktQlpFLW5ySHQ3ck5iQ3p2Y1J2aFc3UmJHeTF6cUwxemQ5ejVYQzFxY3Y2djVrQkxTdDh0TnV1NW9vRlNjS29XR1dwSTNOUVhXNVdjTzVMQ3Y3YnpZajZDRHRRUmQ0Z04tRkFUaGFURWFHM3Q3S1gza0xOZXFBMkVNei1LMGZsY3FCV3J2bHdUWUdQOElRTG4yaFltX3VCckFkaFNEZ1R3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
+          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5956,19 +5956,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
+          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5978,19 +5978,19 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQcG9FWW8yeVV3REc1bWxBY1I1NFh5TmJxbE5BakhjcklocVNvMDVISHNhQjE0NU43Q2tOeGdUaDktQlpFLW5ySHQ3ck5iQ3p2Y1J2aFc3UmJHeTF6cUwxemQ5ejVYQzFxY3Y2djVrQkxTdDh0TnV1NW9vRlNjS29XR1dwSTNOUVhXNVdjTzVMQ3Y3YnpZajZDRHRRUmQ0Z04tRkFUaGFURWFHM3Q3S1gza0xOZXFBMkVNei1LMGZsY3FCV3J2bHdUWUdQOElRTG4yaFltX3VCckFkaFNEZ1R3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
+          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6000,19 +6000,19 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
+          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6022,19 +6022,19 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
+          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6044,19 +6044,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
+          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
+          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6110,19 +6110,19 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
+          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6132,19 +6132,19 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
+          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
+          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6198,19 +6198,19 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
+          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6220,19 +6220,19 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
+          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6242,19 +6242,19 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
+          <t>Como encontrar enxofre em Subnautica 2 - Insider Gaming</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1DeUNMSGxnbU9GRnk4Y3hGbWNzYldCMzlBd3hfM0N0R1FUcVJoeHRUMWhwYjlMUXhZRktDUU9JMHRIa2E0cTUwWl9Ld201bnF6UmZ1X1hOSl9fQ0xfbV9LVU5jNWdISk0xcE8wcERtaW4xeEZS?oc=5</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Como encontrar enxofre em Subnautica 2 - Insider Gaming</t>
+          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1DeUNMSGxnbU9GRnk4Y3hGbWNzYldCMzlBd3hfM0N0R1FUcVJoeHRUMWhwYjlMUXhZRktDUU9JMHRIa2E0cTUwWl9Ld201bnF6UmZ1X1hOSl9fQ0xfbV9LVU5jNWdISk0xcE8wcERtaW4xeEZS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
+          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6374,19 +6374,19 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
+          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
         </is>
       </c>
     </row>
@@ -6447,12 +6447,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
+          <t>Mosaic registra prejuízo no 1º trimestre e reduz produção diante da alta dos custos de matérias-primas - GlobalFert</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6462,19 +6462,19 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUFFYa0l4STNuY0phdjkxVi10MTN0WnVnTGp5bVVrWDRKajFzZm9nRU84MEtLNXdYc3dQZHE2LTNfV2poUGZHZ0xuWGlaS0pRUmRfTlBkeERWMmxYZ3FNd3VYZWQ3ZUdHc3A4eExHeU5ONTRJREpud3ZnZ0puMW81TXJlbFBmdGpWQnljWU5nMURSNDZ2T3psV2tYdjFrNjl4Y3Mya19id3NKUlU2ZEdJcFBQNE02OXRseU9HMmdmaVlBdFdwa3MyaklWX1JVRHBkbERaTWllZXhEZ2NHaFNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes tem prejuízo de US$ 422 mi com paralisações em Minas - Diário do Comércio</t>
+          <t>Ureia cai após meses de valorização - Agrolink</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6484,19 +6484,19 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1OTzdvNnBuejJSeVRQaXZRQXBnTHVzNFoxNUp6dl9JcEVDUlVoUmpEcTNpUXRlSG1nNHVKSTd4d1E0eWFTemR2UzJyWnhYZXB2SFc5RWlILXJnaGpoQjh3N0hxV0R2MVQzbU9BU2EySHpIY0VjVUJ6YWZJM1gyUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
+          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6506,19 +6506,19 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Ureia cai após meses de valorização - Agrolink</t>
+          <t>Mosaic Fertilizantes tem prejuízo de US$ 422 mi com paralisações em Minas - Diário do Comércio</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1OTzdvNnBuejJSeVRQaXZRQXBnTHVzNFoxNUp6dl9JcEVDUlVoUmpEcTNpUXRlSG1nNHVKSTd4d1E0eWFTemR2UzJyWnhYZXB2SFc5RWlILXJnaGpoQjh3N0hxV0R2MVQzbU9BU2EySHpIY0VjVUJ6YWZJM1gyUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo no 1º trimestre e reduz produção diante da alta dos custos de matérias-primas - GlobalFert</t>
+          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUFFYa0l4STNuY0phdjkxVi10MTN0WnVnTGp5bVVrWDRKajFzZm9nRU84MEtLNXdYc3dQZHE2LTNfV2poUGZHZ0xuWGlaS0pRUmRfTlBkeERWMmxYZ3FNd3VYZWQ3ZUdHc3A4eExHeU5ONTRJREpud3ZnZ0puMW81TXJlbFBmdGpWQnljWU5nMURSNDZ2T3psV2tYdjFrNjl4Y3Mya19id3NKUlU2ZEdJcFBQNE02OXRseU9HMmdmaVlBdFdwa3MyaklWX1JVRHBkbERaTWllZXhEZ2NHaFNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
+          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6594,19 +6594,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
+          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6638,19 +6638,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6660,19 +6660,19 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
+          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6682,19 +6682,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
+          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6704,19 +6704,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
+          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
+          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
         </is>
       </c>
     </row>
@@ -6821,12 +6821,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
+          <t>EUA ainda precisam importar ureia - Agrolink</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6836,19 +6836,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
+          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>EUA ainda precisam importar ureia - Agrolink</t>
+          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
+          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
+          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
+          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
+          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7012,19 +7012,19 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
+          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7034,19 +7034,19 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObWdVQ1R0NC1YZThsV1NPR1p3bnY1S3JpZ29Rd1l5dWtYNkUycTlma1FrUUNmLU91aF94eFlSa01qMmszRUgzWkoyd0xQWnhHS0RDRF9oSnd2N29lQUROVDhiUzJjUmlWcWw5SDViQnh3MWY2SGJiVVREX1dyYkN3S3RsWnlfcTBX?oc=5</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObWdVQ1R0NC1YZThsV1NPR1p3bnY1S3JpZ29Rd1l5dWtYNkUycTlma1FrUUNmLU91aF94eFlSa01qMmszRUgzWkoyd0xQWnhHS0RDRF9oSnd2N29lQUROVDhiUzJjUmlWcWw5SDViQnh3MWY2SGJiVVREX1dyYkN3S3RsWnlfcTBX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Petrobras retoma produção de ureia após 6 anos e avança no mercado de fertilizantes, na B3 - ADVFN</t>
+          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7122,19 +7122,19 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQaWlBMEcxWUtKWXVyOXU3dU95dGV3MUpDd2RkanlxMXZHUE91UTJVRmtzbXRfUm4yMnE5Zm5udUo2dm1vSEdYRVNMckxQcjVQamlvUDctYkNsQlJXSmNXaHc1SDBmOXlzLVJhaXRQSmR3Rmoya3hmcERRNTUyTmxFZ1lQNS16UFkxUEpMMEh3U2YwdEFYUTRUMmp2WnVTMVhMRWJ3MkhzN1A4cTVKeHhzZURmN0FIWTkzRnN2ZHJZcjd0MzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
+          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
+          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7166,19 +7166,19 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
+          <t>Petrobras retoma produção de ureia após 6 anos e avança no mercado de fertilizantes, na B3 - ADVFN</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQaWlBMEcxWUtKWXVyOXU3dU95dGV3MUpDd2RkanlxMXZHUE91UTJVRmtzbXRfUm4yMnE5Zm5udUo2dm1vSEdYRVNMckxQcjVQamlvUDctYkNsQlJXSmNXaHc1SDBmOXlzLVJhaXRQSmR3Rmoya3hmcERRNTUyTmxFZ1lQNS16UFkxUEpMMEh3U2YwdEFYUTRUMmp2WnVTMVhMRWJ3MkhzN1A4cTVKeHhzZURmN0FIWTkzRnN2ZHJZcjd0MzQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
+          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 - Valor Econômico</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkONIB5gFBVV95cUxORWpyQ285M1U3ekpPWWVwMER6dTNMTWlZZ3h3VFBwSmRiZ1Y0dnZvb0NtaVlXR0FSank5ZklXMkl6NUhFcG1wcWFuX3lld0VSeFktQU1PUUxESFg5VE0zRlBPaVNfb1VFZTE3ZUFsRDB4N1ZYVUo1dXMxN210RW84LU5scWp4MXppTEZLWFlEeC1mdE9hYkhOTmNoaVUzOFA2d3lvVkZ1cWxCM1A5YWxMUW0tamkxS3BqSUNxRUlWcFo1cUZ2bFVtdlIyd2xKM2FjQTBkcmJjVWdtSlI4WFNlRkxHZlBQdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
+          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 - Valor Econômico</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7276,19 +7276,19 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkONIB5gFBVV95cUxORWpyQ285M1U3ekpPWWVwMER6dTNMTWlZZ3h3VFBwSmRiZ1Y0dnZvb0NtaVlXR0FSank5ZklXMkl6NUhFcG1wcWFuX3lld0VSeFktQU1PUUxESFg5VE0zRlBPaVNfb1VFZTE3ZUFsRDB4N1ZYVUo1dXMxN210RW84LU5scWp4MXppTEZLWFlEeC1mdE9hYkhOTmNoaVUzOFA2d3lvVkZ1cWxCM1A5YWxMUW0tamkxS3BqSUNxRUlWcFo1cUZ2bFVtdlIyd2xKM2FjQTBkcmJjVWdtSlI4WFNlRkxHZlBQdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Mercado de enxofre corto de compressão varre através da cadeia de suprimentos - Sunsirs</t>
+          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBQbnRCaEVzdkRzQ0tXZHFVZWd1cmFPVlJxcDc5VDY4bnRxaUx2YmRBdXdLOW9TaEhfWTk1Vmp2SldCZktYcmRfNzRaLVozOE9pZ3p4NEZEdTZXNmk1a2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
+          <t>Mercado de enxofre corto de compressão varre através da cadeia de suprimentos - Sunsirs</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBQbnRCaEVzdkRzQ0tXZHFVZWd1cmFPVlJxcDc5VDY4bnRxaUx2YmRBdXdLOW9TaEhfWTk1Vmp2SldCZktYcmRfNzRaLVozOE9pZ3p4NEZEdTZXNmk1a2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -7371,12 +7371,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
+          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7386,19 +7386,19 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
+          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7437,12 +7437,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
+          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7452,19 +7452,19 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
+          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7701,12 +7701,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Paranaenses trazem bons resultados da Fórmula Truck no Uruguai - Bem Paraná</t>
+          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -7716,19 +7716,19 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUUlhSHF6SzZzdW5jYnJaN1dHcGVtR2oxVExheWdtbXlQVWlXSjFLbWFkVGdDZFlUT1ZJTEFqLUhkeFQtdS1QTTdUb2pXWlprYnA1VnVDZ3VFS204Q1hiSThwVFBJZllPVl8yYjRNaWVDalZvcTdfVGVleGN4WW9kYUtJS1l6U0R2anZkT1BGcXlONlZveDYwcTVMVDR6NnE1Z2fSAacBQVVfeXFMUFVRS1k5U1N2RmpuZHVwbnFxRHh6NjBMQUw2dVBEaGE5X2Uydkd5RVRPVlZSRVhCX3FGOW01aExjVW1LazdPWnVULVlJREZBN2JNM0lnTWNfVDAxRnlpUTJSNVJIbEt4Zzg5NWVUak1RNmx6MkQxNmt6ak94N1A3dG1iOXMzOEhyamN0Uk1aazBncGExNnE4N1BmME5lT3RNX0dUc3ZFeW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
+          <t>Paranaenses trazem bons resultados da Fórmula Truck no Uruguai - Bem Paraná</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -7738,19 +7738,19 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUUlhSHF6SzZzdW5jYnJaN1dHcGVtR2oxVExheWdtbXlQVWlXSjFLbWFkVGdDZFlUT1ZJTEFqLUhkeFQtdS1QTTdUb2pXWlprYnA1VnVDZ3VFS204Q1hiSThwVFBJZllPVl8yYjRNaWVDalZvcTdfVGVleGN4WW9kYUtJS1l6U0R2anZkT1BGcXlONlZveDYwcTVMVDR6NnE1Z2fSAacBQVVfeXFMUFVRS1k5U1N2RmpuZHVwbnFxRHh6NjBMQUw2dVBEaGE5X2Uydkd5RVRPVlZSRVhCX3FGOW01aExjVW1LazdPWnVULVlJREZBN2JNM0lnTWNfVDAxRnlpUTJSNVJIbEt4Zzg5NWVUak1RNmx6MkQxNmt6ak94N1A3dG1iOXMzOEhyamN0Uk1aazBncGExNnE4N1BmME5lT3RNX0dUc3ZFeW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
+          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7760,19 +7760,19 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
+          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -7782,19 +7782,19 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
+          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7804,19 +7804,19 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
+          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7855,12 +7855,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
+          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7870,19 +7870,19 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
+          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
+          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
+          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
+          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8185,12 +8185,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Biofragane</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8200,19 +8200,19 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Biofragane</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
+          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
+          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
+          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8332,19 +8332,19 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a576649f4d14a0fb389bc557577f2cc&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a577b6a6e774115926a2634232b3a12&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8354,19 +8354,19 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
+          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8493,12 +8493,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
+          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8508,19 +8508,19 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
+          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
+          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado Federal</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -8574,19 +8574,19 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
+          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado Federal</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -8596,19 +8596,19 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado Federal</t>
+          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -8618,19 +8618,19 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado Federal</t>
+          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -8640,19 +8640,19 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
+          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
         </is>
       </c>
     </row>
@@ -8845,12 +8845,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
+          <t>Agricultores de Corupá já podem solicitar calcário gratuito pelo programa Terra Boa; veja detalhes - JDV - Jornal do Vale</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -8860,19 +8860,19 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBoVzBPSUx1aFltY2FyUnN2Ym1qNExJZkxKckl1bnpsdGwzT2hZdF9PaDN1SHhFV1pQRTNmTWM1TXMtakYyUERmcmRwaVpLRk5kb2JUZ1NobzJVblFVWEp2c0xvVVh2ZDg1WEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Agricultores de Corupá já podem solicitar calcário gratuito pelo programa Terra Boa; veja detalhes - JDV - Jornal do Vale</t>
+          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBoVzBPSUx1aFltY2FyUnN2Ym1qNExJZkxKckl1bnpsdGwzT2hZdF9PaDN1SHhFV1pQRTNmTWM1TXMtakYyUERmcmRwaVpLRk5kb2JUZ1NobzJVblFVWEp2c0xvVVh2ZDg1WEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
+          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8904,19 +8904,19 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
+          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8977,12 +8977,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -8992,19 +8992,19 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
+          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -9014,19 +9014,19 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
+          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -9036,19 +9036,19 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
+          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
         </is>
       </c>
     </row>
@@ -9080,19 +9080,19 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57664a7fa24ed6993b612f43031368&amp;url=https%3a%2f%2fwww.msn.com%2fen-gb%2flifestyle%2fother%2flime-the-base-layer-fertiliser%2far-AA1XIisB&amp;c=12206964766642139602&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a577b6c107046e7b9764c41e370862c&amp;url=https%3a%2f%2fwww.msn.com%2fen-gb%2flifestyle%2fother%2flime-the-base-layer-fertiliser%2far-AA1XIisB&amp;c=12206964766642139602&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>"Cal Cruzeiro"</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
+          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -9102,19 +9102,19 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>"Cal Cruzeiro"</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
+          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9197,12 +9197,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
+          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -9212,19 +9212,19 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
+          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
+          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -9278,19 +9278,19 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
+          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio coloca em risco 41% da ureia exportada no mundo - Notícias Agrícolas</t>
+          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -9322,19 +9322,19 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNMG1PVUx2UWlmTFltaHVVQTRObV9jYlUwck4wZjNCdnJ0MkhNdzZzNUhvcEF2UlFpc1VxSmxNUVp0WXB4d3l6WHVMY2ZCTDZPOVBZYk4wd19vekcxX1FPaGUzWDhxRnlSQnRGU0N1X21ydmpTV192QTVtVWNfd2FrVk5wMVYzQXBJTWE2ZGpNaVB1aFl4Vy1POUFpOWlmc2g0MUxyZ3FRalphWWxKMnZHT0VfS1FBREh1NnEtbXdyODZSR2JYRWh1b3pucGJJcmpKNWlsNW5uZHpXd9IB3wFBVV95cUxNQW1aM3BFY25YOTdIUWpSQS0tYnVLenA2OEJScjBUdjNWeVdoelBzYlZHa1ZvT0tHODQtM0dyRGJCNFN5TDVHeVBtc0ZsMEp6X0FyZkExM01XT3BLVkZ3d0pyeFNrRTE2ZklmSTQ0MUozZDhhRWlOQnFYUnBqdFJtSS1BM0xjZGVpZ2NTN0VodExTb3JreVJpeE81bFZ3OFpaZWk1c1psRWZiUmdKd2N2cDhlbjBUVVFZcnNDVzhkaUktalhfWWVqb1ZPODNkSlJMNVl5eDQ2b052aWoxYnNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>Conflito no Oriente Médio coloca em risco 41% da ureia exportada no mundo - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNMG1PVUx2UWlmTFltaHVVQTRObV9jYlUwck4wZjNCdnJ0MkhNdzZzNUhvcEF2UlFpc1VxSmxNUVp0WXB4d3l6WHVMY2ZCTDZPOVBZYk4wd19vekcxX1FPaGUzWDhxRnlSQnRGU0N1X21ydmpTV192QTVtVWNfd2FrVk5wMVYzQXBJTWE2ZGpNaVB1aFl4Vy1POUFpOWlmc2g0MUxyZ3FRalphWWxKMnZHT0VfS1FBREh1NnEtbXdyODZSR2JYRWh1b3pucGJJcmpKNWlsNW5uZHpXd9IB3wFBVV95cUxNQW1aM3BFY25YOTdIUWpSQS0tYnVLenA2OEJScjBUdjNWeVdoelBzYlZHa1ZvT0tHODQtM0dyRGJCNFN5TDVHeVBtc0ZsMEp6X0FyZkExM01XT3BLVkZ3d0pyeFNrRTE2ZklmSTQ0MUozZDhhRWlOQnFYUnBqdFJtSS1BM0xjZGVpZ2NTN0VodExTb3JreVJpeE81bFZ3OFpaZWk1c1psRWZiUmdKd2N2cDhlbjBUVVFZcnNDVzhkaUktalhfWWVqb1ZPODNkSlJMNVl5eDQ2b052aWoxYnNr?oc=5</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
+          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
+          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -9520,19 +9520,19 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado Federal</t>
+          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -9542,19 +9542,19 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
+          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado Federal</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
         </is>
       </c>
     </row>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57664a7fa24ed6993b612f43031368&amp;url=https%3a%2f%2fwww.thescottishfarmer.co.uk%2fnews%2f25845962.grolime-brings-high-performance-benefits-scottish-soils%2f&amp;c=18200927900201231641&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a577b6c107046e7b9764c41e370862c&amp;url=https%3a%2f%2fwww.thescottishfarmer.co.uk%2fnews%2f25845962.grolime-brings-high-performance-benefits-scottish-soils%2f&amp;c=18200927900201231641&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -9857,22 +9857,22 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>CBPM reage à venda indevida de operação da Equinox Gold na Bahia - Bahia Notícias</t>
+          <t>CBIOs iniciam 2026 nos menores níveis históricos — o que explica isso? - JornalCana</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>03/02/2026 08:00</t>
+          <t>02/02/2026 08:00</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOb0dyblk0a1dSem1LdjFxOThPbld2Snp3VEd3RjU3WWVLRVJwc18wU2FLVUZ6U0tZMUlJbDNjb1FycDRNWFdMemF0T0ZvUGNZYl9CeGlZeWpHYWZRakJuMHlzSWVVeUk0dFQ5MUlnZk1vZHRlLTR3d0U5Y3M1OVpTUkFYNlJmOV9ka2NDS2pLMGtqN21mcE9BUlR1dDAwNHdhdzhQM05IOWlKQjNoZmZ1b3V3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPUy0wRmhXSWpaNGxjeGI4TnFobWctR2ZFU1ZpeHlhRlRqVG5KQXg5dXd6MEhKUWU3NkFxTEtHX2RLTFk3blFCbkFDZ3V3YXpCMFZkWDhDTlFTdDBsc21HZTFtUXBLMXdlRHFUR2pyT2xUenZUTU5Xa2dmMzRBc25qY3pnZ2UwVlBwQ3RUTm5rSTAyUlRGcHNFTF91N21WTnI3bGdFcjRZdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9901,56 +9901,56 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>CBIOs iniciam 2026 nos menores níveis históricos — o que explica isso? - JornalCana</t>
+          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>02/02/2026 08:00</t>
+          <t>01/02/2026 08:00</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPUy0wRmhXSWpaNGxjeGI4TnFobWctR2ZFU1ZpeHlhRlRqVG5KQXg5dXd6MEhKUWU3NkFxTEtHX2RLTFk3blFCbkFDZ3V3YXpCMFZkWDhDTlFTdDBsc21HZTFtUXBLMXdlRHFUR2pyT2xUenZUTU5Xa2dmMzRBc25qY3pnZ2UwVlBwQ3RUTm5rSTAyUlRGcHNFTF91N21WTnI3bGdFcjRZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
+          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>01/02/2026 08:00</t>
+          <t>30/01/2026 08:00</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
+          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9972,29 +9972,29 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
+          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>30/01/2026 08:00</t>
+          <t>27/01/2026 08:00</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
+          <t>Rio Doce oferece análise de solo gratuita para fomentar a produtividade e sustentabilidade no campo - Jornal Panorama Minas</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -10004,249 +10004,249 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQVENaMzhzbm5GOUR3UFBNU2Y5RDNlU2ppUmhXZW9GVnE1NWNxanpBS0Z6S2xrc2Y0eUh4UmFURExNeFBTc2VscUUtSi0tZkRLQ0haeUpfcTlUNV9KZ0VUZXMwZ0phYXNPVU5zcWRiRTdrZlJSQllRLUx5MzE0dktrRjZwX1RKYWg0VmtaSmVYQ2NpM0I3Mi1NZ0FJQk8zMzYxcWdxWDNiOENKN18yVTczTE9PeFY4bEl1MmhxdDdOX1FEaXM1cTQyeEk4dVkxbm43?oc=5</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Rio Doce oferece análise de solo gratuita para fomentar a produtividade e sustentabilidade no campo - Jornal Panorama Minas</t>
+          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>27/01/2026 08:00</t>
+          <t>23/01/2026 08:00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQVENaMzhzbm5GOUR3UFBNU2Y5RDNlU2ppUmhXZW9GVnE1NWNxanpBS0Z6S2xrc2Y0eUh4UmFURExNeFBTc2VscUUtSi0tZkRLQ0haeUpfcTlUNV9KZ0VUZXMwZ0phYXNPVU5zcWRiRTdrZlJSQllRLUx5MzE0dktrRjZwX1RKYWg0VmtaSmVYQ2NpM0I3Mi1NZ0FJQk8zMzYxcWdxWDNiOENKN18yVTczTE9PeFY4bEl1MmhxdDdOX1FEaXM1cTQyeEk4dVkxbm43?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
+          <t>Semig entrega 6 toneladas de calcário em Itacoatiara e reforça combate às queimadas e ao desmatamento - agenciaamazonas.am.gov.br</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>23/01/2026 08:00</t>
+          <t>20/01/2026 08:00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNLXdXUmhuMmZoYWlVWGZUWV9SMDk3aUk4S1pPWDl6X3NoT2ZXeHpBMGxQM1dsd3JXRWVyN09PN0VxU2hlVmEzM2I1cDRIcmkxV3BpWFpsdlVuU0VqendCVzFWZzVTNHJoenJuV2JCX2ZwOXQ0c29xSXBkR0MtelF5NWg3NVYwS284T0pqZWUtckVaV1pBNm12OG9naWJJZ2Y3a3ZuTEdBYTk4eGhLRWZ4eWdnOE1heVJ4ZUhQMWRrVnBrYURnZkRvd3NmNGFLZ2JiSFVrOE1ucVdhWGM4aXNEZVV0OA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
+          <t>Passa Sete abre inscrições para pedidos de calcário - radiosobradinho.com.br</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>23/01/2026 08:00</t>
+          <t>15/01/2026 08:00</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNQkVmeU43d3FMWjBLMTZ1SWJnVFZSVXFmT3JmM2dFOTdkeFkxLVNodG1ub3hvWEs2eHR4Z3NMd2c5VkFVU2t0S25XYVVEWXRtTHVkUmdVOFdQVGZ3OGJ3YkNmY2xMeGRyLWgxbktJXzhOUF9uN0FWUUcxSnk2cUtFRk5JQ1NHSXJJRHlwcE9oQUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Semig entrega 6 toneladas de calcário em Itacoatiara e reforça combate às queimadas e ao desmatamento - agenciaamazonas.am.gov.br</t>
+          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>20/01/2026 08:00</t>
+          <t>13/01/2026 08:00</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNLXdXUmhuMmZoYWlVWGZUWV9SMDk3aUk4S1pPWDl6X3NoT2ZXeHpBMGxQM1dsd3JXRWVyN09PN0VxU2hlVmEzM2I1cDRIcmkxV3BpWFpsdlVuU0VqendCVzFWZzVTNHJoenJuV2JCX2ZwOXQ0c29xSXBkR0MtelF5NWg3NVYwS284T0pqZWUtckVaV1pBNm12OG9naWJJZ2Y3a3ZuTEdBYTk4eGhLRWZ4eWdnOE1heVJ4ZUhQMWRrVnBrYURnZkRvd3NmNGFLZ2JiSFVrOE1ucVdhWGM4aXNEZVV0OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Passa Sete abre inscrições para pedidos de calcário - radiosobradinho.com.br</t>
+          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>15/01/2026 08:00</t>
+          <t>07/01/2026 08:00</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNQkVmeU43d3FMWjBLMTZ1SWJnVFZSVXFmT3JmM2dFOTdkeFkxLVNodG1ub3hvWEs2eHR4Z3NMd2c5VkFVU2t0S25XYVVEWXRtTHVkUmdVOFdQVGZ3OGJ3YkNmY2xMeGRyLWgxbktJXzhOUF9uN0FWUUcxSnk2cUtFRk5JQ1NHSXJJRHlwcE9oQUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
+          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>13/01/2026 08:00</t>
+          <t>06/01/2026 08:00</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
+          <t>Aqui está o calendário do produtor de oliveiras para 2026. - OlivoNews</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>07/01/2026 08:00</t>
+          <t>01/01/2026 08:00</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNRWI4bzhUOHRZemxDMDV5WjNnQy01V0RVZUhRblpqMUlFbENQX0QwZ2tkVVgxblRpVGt3NHZBb3h5MXh6VEpmLW1NeDV2bm12LXlweTNtbE81UUFOaXVjdWUyTm82ZWtGX1hHU3lieldMRDZvX3pUektVbDVaMk5zVE9nZ2hyTHEwOENOOERrQXpmdkxfYkQ1aw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
+          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>06/01/2026 08:00</t>
+          <t>30/12/2025 08:00</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Aqui está o calendário do produtor de oliveiras para 2026. - OlivoNews</t>
+          <t>Brasil: Chinesa CMOC adquire minas de ouro no por US$ 1 bilhão - e-global.pt</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>01/01/2026 08:00</t>
+          <t>24/12/2025 20:01</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNRWI4bzhUOHRZemxDMDV5WjNnQy01V0RVZUhRblpqMUlFbENQX0QwZ2tkVVgxblRpVGt3NHZBb3h5MXh6VEpmLW1NeDV2bm12LXlweTNtbE81UUFOaXVjdWUyTm82ZWtGX1hHU3lieldMRDZvX3pUektVbDVaMk5zVE9nZ2hyTHEwOENOOERrQXpmdkxfYkQ1aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNLWFuM2JWaW9naUMzN2w1dUU3UGktbjVNT0ROLUhpRXJnTDVsaXdQWnp3ZHp2bmd6Y1d0STgxNW5WeFRpYzR3QUUtM3NxUm5wbjV0Qkt2Mnd4aTQ1bkpfYV9QbVVCcFJqUkRZR2lQWFppeHVvbUVzVU9sWEcwM056cEdnNk9tMGpnNVJPUWZNVzBOdjZYSEFrLWtuQ3I4MmZ2OUpzRl9mOUk2MXfSAbABQVVfeXFMT000eWZFNU5UZHNSTDd2QzBrZVZQMm1tdm40akZTaGtFMEktNGp3SVlIdEJDbVQtMEx1b1RHQzR4US1xY3BuNWd6ajRYcEdzQkNXSXZmNElLRUE3bnlHSXRQVzZIVnhTRzlZbUw5a0ZrTzk0czFtQkM0RW5VaGE1bk1WMWdvZDQ3b3U5Vk00NTVuRmwwbHhIVHpCM2VYRklweEdPQm9Ba2dfUENqb2tpZEo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
+          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>30/12/2025 08:00</t>
+          <t>20/12/2025 08:00</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Brasil: Chinesa CMOC adquire minas de ouro no por US$ 1 bilhão - e-global.pt</t>
+          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>24/12/2025 20:01</t>
+          <t>19/12/2025 08:00</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNLWFuM2JWaW9naUMzN2w1dUU3UGktbjVNT0ROLUhpRXJnTDVsaXdQWnp3ZHp2bmd6Y1d0STgxNW5WeFRpYzR3QUUtM3NxUm5wbjV0Qkt2Mnd4aTQ1bkpfYV9QbVVCcFJqUkRZR2lQWFppeHVvbUVzVU9sWEcwM056cEdnNk9tMGpnNVJPUWZNVzBOdjZYSEFrLWtuQ3I4MmZ2OUpzRl9mOUk2MXfSAbABQVVfeXFMT000eWZFNU5UZHNSTDd2QzBrZVZQMm1tdm40akZTaGtFMEktNGp3SVlIdEJDbVQtMEx1b1RHQzR4US1xY3BuNWd6ajRYcEdzQkNXSXZmNElLRUE3bnlHSXRQVzZIVnhTRzlZbUw5a0ZrTzk0czFtQkM0RW5VaGE1bk1WMWdvZDQ3b3U5Vk00NTVuRmwwbHhIVHpCM2VYRklweEdPQm9Ba2dfUENqb2tpZEo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
         </is>
       </c>
     </row>
@@ -10258,39 +10258,39 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>20/12/2025 08:00</t>
+          <t>17/12/2025 08:00</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
+          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>19/12/2025 08:00</t>
+          <t>17/12/2025 08:00</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
+          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Jornal Portuário</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOejlYQmU1SzhnRGtFMFJKWU9sNFZmM01temlpNFdjTVRTQzdqeFFwM0hZUzlIVlJZa2pGaGo1UVdmTXd0dGRtX041d1ptUVdvUmNfTnNlM2ppdmFEMUtlMlZVNzBvWlZyaVlGZUpOV19CR0FKeXFKU21yWEo4Q0RoMnEzdHV2Zk1ZR0prQzRnQzNzOGR1OGwwQkFYM2hwemo0emFXQ0tkUmR6a3NnYWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
+          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10368,17 +10368,17 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>17/12/2025 08:00</t>
+          <t>16/12/2025 08:00</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
+          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
         </is>
       </c>
     </row>
@@ -10434,17 +10434,17 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>16/12/2025 08:00</t>
+          <t>15/12/2025 08:00</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
+          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
+          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
+          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
+          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10610,17 +10610,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
+          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>15/12/2025 08:00</t>
+          <t>14/12/2025 08:00</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10632,17 +10632,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>15/12/2025 08:00</t>
+          <t>14/12/2025 08:00</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -10654,127 +10654,127 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
+          <t>SUSTENTABILIDADE | CMOC Brasil é reconhecida pelo Selo ODS Brasil 2025 - Brasil Mineral</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>14/12/2025 08:00</t>
+          <t>13/12/2025 08:00</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSzczY2JlaXVTMkliamlDU3cwMU1nTFl5WWotNkFyc2tZckV5ZDl6OG80eEZtTjVOZlp2OThITVZpYVdYcDhGN1p3Yk1VTFRzblhKZGh1cnlsMjZQeHFRMm9lV1VhZGxsMWFTX2J4NV90NFZiZlA0RkRPU3NyWDdQUXJyWWhrNWUtQVFONVM3eUVYLXAzVW1xMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
+          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>14/12/2025 08:00</t>
+          <t>07/12/2025 22:00</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a577b6c107046e7b9764c41e370862c&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>SUSTENTABILIDADE | CMOC Brasil é reconhecida pelo Selo ODS Brasil 2025 - Brasil Mineral</t>
+          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>13/12/2025 08:00</t>
+          <t>02/12/2025 08:00</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSzczY2JlaXVTMkliamlDU3cwMU1nTFl5WWotNkFyc2tZckV5ZDl6OG80eEZtTjVOZlp2OThITVZpYVdYcDhGN1p3Yk1VTFRzblhKZGh1cnlsMjZQeHFRMm9lV1VhZGxsMWFTX2J4NV90NFZiZlA0RkRPU3NyWDdQUXJyWWhrNWUtQVFONVM3eUVYLXAzVW1xMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
+          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>07/12/2025 22:00</t>
+          <t>26/11/2025 06:44</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57664a7fa24ed6993b612f43031368&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
+          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>02/12/2025 08:00</t>
+          <t>24/11/2025 08:00</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
+          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>26/11/2025 06:44</t>
+          <t>19/11/2025 08:00</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
         </is>
       </c>
     </row>
@@ -10786,29 +10786,29 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
+          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>24/11/2025 08:00</t>
+          <t>19/11/2025 08:00</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
+          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
         </is>
       </c>
     </row>
@@ -10830,61 +10830,61 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>19/11/2025 08:00</t>
+          <t>17/11/2025 16:00</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a577b6a6e774115926a2634232b3a12&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
+          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>19/11/2025 08:00</t>
+          <t>17/11/2025 08:00</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
+          <t>Prefeitura de Itararé (SP) investe em distribuição de calcário para fortalecer a produção rural - Prefeitura de Itararé</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>17/11/2025 16:00</t>
+          <t>10/11/2025 08:00</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a576649f4d14a0fb389bc557577f2cc&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQYjRIbkk4bkExM1lhOUtmWVl5UXhXOU5rbkxhdnNEVUpZcGpoNE9xbGRRQy1JWVNrcWF0d3c1eEtJUDVENjJGVU15aEZjdnptLWM1VXlXdmVTUTJUX1NqVEJNU1IyTHRMYW4ybzdZMlBQUkFyNFRCVjFUZG0zM1VMVE9GRHFDZ3BnVzR0Y0tRLS13VHp4TVNRQ3NnMHVrcGhWU2ZVNHhLMXktaVJ5OWhxOGwwS1oydXhfYWZvcw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10896,479 +10896,479 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
+          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>17/11/2025 08:00</t>
+          <t>08/11/2025 08:00</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Prefeitura de Itararé (SP) investe em distribuição de calcário para fortalecer a produção rural - Prefeitura de Itararé</t>
+          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>10/11/2025 08:00</t>
+          <t>30/10/2025 07:00</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQYjRIbkk4bkExM1lhOUtmWVl5UXhXOU5rbkxhdnNEVUpZcGpoNE9xbGRRQy1JWVNrcWF0d3c1eEtJUDVENjJGVU15aEZjdnptLWM1VXlXdmVTUTJUX1NqVEJNU1IyTHRMYW4ybzdZMlBQUkFyNFRCVjFUZG0zM1VMVE9GRHFDZ3BnVzR0Y0tRLS13VHp4TVNRQ3NnMHVrcGhWU2ZVNHhLMXktaVJ5OWhxOGwwS1oydXhfYWZvcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
+          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>08/11/2025 08:00</t>
+          <t>30/10/2025 07:00</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
+          <t>Especialistas registram a maior coruja do continente que come até gambás e coalas - Revista Fórum</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>30/10/2025 07:00</t>
+          <t>20/10/2025 07:00</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOZWZIam82STB1M05WMm45bHNjdVJBTl9rRU9zanpRMV9XM0ZXbERYTmFJVVF4M25ZSlVsTWNTVEtTZmR1cXI0REt4SnU2Y3ZyaGNiUTVNenlyNXJHMnhMNTVnbHNnS2FqQjVLZTNvYTN3ZzZaYkplc21fUzB2MGZSM2tvQ0FXSnZpbEJWOG9nRmM0ME1sYnU3R3Zod1hyVzRpRGd4NVZmTjZNZ051dDFkY0FOeVZEeWVRYWtVUFlLSGFLOWowQ2ticnFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
+          <t>O composto. Fundamental para a captura de carbono no solo - vozdocampo.pt</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>30/10/2025 07:00</t>
+          <t>17/10/2025 07:00</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE5xMkJkQi05dzl4R3RabU44d0U0NnB1cmE3ZTBUQkpjTWJaVTB5c2VpVE0yUEV5VmQ1NkIySE9ma1FBdFE5NTRyRVpIRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Especialistas registram a maior coruja do continente que come até gambás e coalas - Revista Fórum</t>
+          <t>O Caminho do Peabiru é tema de seminário na Unila em Foz do Iguaçu - Brasil de Fato</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>20/10/2025 07:00</t>
+          <t>14/10/2025 07:00</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOZWZIam82STB1M05WMm45bHNjdVJBTl9rRU9zanpRMV9XM0ZXbERYTmFJVVF4M25ZSlVsTWNTVEtTZmR1cXI0REt4SnU2Y3ZyaGNiUTVNenlyNXJHMnhMNTVnbHNnS2FqQjVLZTNvYTN3ZzZaYkplc21fUzB2MGZSM2tvQ0FXSnZpbEJWOG9nRmM0ME1sYnU3R3Zod1hyVzRpRGd4NVZmTjZNZ051dDFkY0FOeVZEeWVRYWtVUFlLSGFLOWowQ2ticnFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQSXdlQlZodk0zOGYzclFlMzhEZEJIOUhhRy1YMG9MVEdCUHR4VUhlNFQ4MG1MQWppb2xBQ3VYMFg1ZnVjSzZMbnA1WXJISldSYkFfLTF4RVpvNHBXUnFIaGpzNVFYalZQbEZiSE9oTVpnTUJyb0FOTHdkTGF3eWg4ZWRCZ3JjQ3ZSRE5EYzNjdnktRXBMbnViMHlTaDBHaDVOU0RobzQtNXZMakNpeUUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>O composto. Fundamental para a captura de carbono no solo - vozdocampo.pt</t>
+          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>17/10/2025 07:00</t>
+          <t>14/10/2025 07:00</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE5xMkJkQi05dzl4R3RabU44d0U0NnB1cmE3ZTBUQkpjTWJaVTB5c2VpVE0yUEV5VmQ1NkIySE9ma1FBdFE5NTRyRVpIRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>O Caminho do Peabiru é tema de seminário na Unila em Foz do Iguaçu - Brasil de Fato</t>
+          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>14/10/2025 07:00</t>
+          <t>13/10/2025 07:00</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQSXdlQlZodk0zOGYzclFlMzhEZEJIOUhhRy1YMG9MVEdCUHR4VUhlNFQ4MG1MQWppb2xBQ3VYMFg1ZnVjSzZMbnA1WXJISldSYkFfLTF4RVpvNHBXUnFIaGpzNVFYalZQbEZiSE9oTVpnTUJyb0FOTHdkTGF3eWg4ZWRCZ3JjQ3ZSRE5EYzNjdnktRXBMbnViMHlTaDBHaDVOU0RobzQtNXZMakNpeUUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
+          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>14/10/2025 07:00</t>
+          <t>10/10/2025 07:00</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
+          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>13/10/2025 07:00</t>
+          <t>09/10/2025 07:00</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
+          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>10/10/2025 07:00</t>
+          <t>01/10/2025 07:00</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
+          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>09/10/2025 07:00</t>
+          <t>21/09/2025 07:00</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
+          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - Canal Rural</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>01/10/2025 07:00</t>
+          <t>20/09/2025 07:00</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
+          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>21/09/2025 07:00</t>
+          <t>15/09/2025 07:00</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGR6N2hWX3A2ZGR4RmJWbWNqdnBqUGktU25QbDhLZUlvSmVIVERqRVpTazJKRlFSdzBfQ2s3UzJJZFN6dHd5TllCZXR6SGYxV3llYUFwdlFlSDZEWi1jb1V0bXVfVDVQZTNjWVRXcnZ3WDVPVUlaZ2xhZXNFcmNBUXlPdGFZdVFrVkM4RTZkNjEzTXMzT3RodVJSS3ZvMkxlXy1pbDl2OU1vVlY5dU9NVHp3LVU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - Canal Rural</t>
+          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>20/09/2025 07:00</t>
+          <t>08/09/2025 08:38</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a577b6a6e774115926a2634232b3a12&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
+          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>15/09/2025 07:00</t>
+          <t>02/09/2025 17:00</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGR6N2hWX3A2ZGR4RmJWbWNqdnBqUGktU25QbDhLZUlvSmVIVERqRVpTazJKRlFSdzBfQ2s3UzJJZFN6dHd5TllCZXR6SGYxV3llYUFwdlFlSDZEWi1jb1V0bXVfVDVQZTNjWVRXcnZ3WDVPVUlaZ2xhZXNFcmNBUXlPdGFZdVFrVkM4RTZkNjEzTXMzT3RodVJSS3ZvMkxlXy1pbDl2OU1vVlY5dU9NVHp3LVU?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a577b6a6e774115926a2634232b3a12&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
+          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>08/09/2025 08:38</t>
+          <t>02/09/2025 07:00</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a576649f4d14a0fb389bc557577f2cc&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
+          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>02/09/2025 17:00</t>
+          <t>01/09/2025 07:00</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a576649f4d14a0fb389bc557577f2cc&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
+          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>02/09/2025 07:00</t>
+          <t>01/09/2025 07:00</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
+          <t>Mais de 1.600 toneladas de calcário são entregues a agricultores familiares para preparo de solo - Prefeitura Municipal de Boa Vista</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>01/09/2025 07:00</t>
+          <t>22/08/2025 07:00</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQLXdRbkZkNHpnb1NhakYtOWNSTkFBa2VTdFNJTUhPUXZZeXhrekp3dlg4UEZuUWZDWk5SZm44LUQtWDdUNkVkZUdRSWRkcXZ1QUhCUzVqRzM3YTU3TkFGYlJrcE93YXQ5LS15X29oWkE2OV82ZmVKQ2JaWXhJcjZycDl5ZURxMGhDVERtcEttT0NVb1M4V2hOdEpCd2JpZWdlWWV0STZXdk9HZUtrTm04WmNSb2JJalVsbTk5Wk43OTAyTF9ESXNobjQ0VU5XS2xMQ0dHaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
+          <t>Governo de RO entrega mais de 950 toneladas de calcário para fortalecer produção agropecuária no estado - ro.gov.br</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>01/09/2025 07:00</t>
+          <t>19/08/2025 07:00</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPTUEzVERudnBEWUlEZXBYZmZPdEJhR3RFZHRrdlpBTVZBdDlxdExmRDRRTWJNNXQtNjFfQWRxUmoxQlBadUdsWG1SRUJZTG9BbkR2clhSOTg0SG9YY1BtaF85dHBrS0ZybFRLYUdnZUhyYlNfM3ZJR29aMlRiS0wwbm53bzlpTWV4S3V2NnMtZjJScjRKcXR5RGtsVTVMcjkwLVFTdl9TeHJ5U0x3b1R2WHZzQlNoTHY4MFpxeGdQN2tDT2t3cGtjR3J1MA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Mais de 1.600 toneladas de calcário são entregues a agricultores familiares para preparo de solo - Prefeitura Municipal de Boa Vista</t>
+          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>22/08/2025 07:00</t>
+          <t>15/08/2025 07:00</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQLXdRbkZkNHpnb1NhakYtOWNSTkFBa2VTdFNJTUhPUXZZeXhrekp3dlg4UEZuUWZDWk5SZm44LUQtWDdUNkVkZUdRSWRkcXZ1QUhCUzVqRzM3YTU3TkFGYlJrcE93YXQ5LS15X29oWkE2OV82ZmVKQ2JaWXhJcjZycDl5ZURxMGhDVERtcEttT0NVb1M4V2hOdEpCd2JpZWdlWWV0STZXdk9HZUtrTm04WmNSb2JJalVsbTk5Wk43OTAyTF9ESXNobjQ0VU5XS2xMQ0dHaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11380,149 +11380,149 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Governo de RO entrega mais de 950 toneladas de calcário para fortalecer produção agropecuária no estado - ro.gov.br</t>
+          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>19/08/2025 07:00</t>
+          <t>13/08/2025 07:00</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPTUEzVERudnBEWUlEZXBYZmZPdEJhR3RFZHRrdlpBTVZBdDlxdExmRDRRTWJNNXQtNjFfQWRxUmoxQlBadUdsWG1SRUJZTG9BbkR2clhSOTg0SG9YY1BtaF85dHBrS0ZybFRLYUdnZUhyYlNfM3ZJR29aMlRiS0wwbm53bzlpTWV4S3V2NnMtZjJScjRKcXR5RGtsVTVMcjkwLVFTdl9TeHJ5U0x3b1R2WHZzQlNoTHY4MFpxeGdQN2tDT2t3cGtjR3J1MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
+          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>15/08/2025 07:00</t>
+          <t>11/08/2025 07:00</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWU80YXJ5NDJUWmw1VjJscFpVbDRWVlJsM09lZ3Vjdkg4czlKekxPUWJUWXpaQjg4WDZONGk1MjdxV29mRm1aTHZWRG5FeUFsWHpPTk50VFVhak9QU1dYak9tM3Buc21nRGxmLTljbzNSd1I2ZVlZa2luY3BrRGIwb1lTcml2RU1NMUlrdmt6WVExREs4S1psdHdXM3czY2pUcjBzeU92UDhpZ0lELTFZQjZaaHN6WVY1WjRDWmdJZklfV2dpbWk0ZDBjUk8xcDlnQjU0X05nU01idTJCZmNmUmNZUXpaRWZveHBv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
+          <t>Trabalhadores da Manserv entram em greve e exigem jornada 4×4 e melhores condições de trabalho - Badiinho</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>13/08/2025 07:00</t>
+          <t>06/08/2025 07:00</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9fN3VVZmJNM2pGMzB3V19FM1N4d3hpWnVaMUZvZUtXWXZhUFFCSXMxNXlyTUt6dnQyalF6bFNZN0ZPcW5QVWp1dDV2d1FoX19nRzg4VXJjaG93OUJYSndmTEdCUDBacHFyUVRBNTFaRmhiYzBhcVQtV9IBfkFVX3lxTFBuc1ZCZ1hCOFRSdVBxVktkYldTdUE0QUkzQzEybEZzVXplV1A2MlRscGxudmhPOW9xNTlic25DVURrMWhIaW9QS3ZfNl92OWJzS1FkeXhQMXpaWGVidUhjeWtmamR6MmNsZkV6ZTVneVdsYkQ4RnA4OEpSTFNfUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
+          <t>O futuro circular do agro: como cientistas e empresas estão transformando resíduos em fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>11/08/2025 07:00</t>
+          <t>02/08/2025 07:00</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWU80YXJ5NDJUWmw1VjJscFpVbDRWVlJsM09lZ3Vjdkg4czlKekxPUWJUWXpaQjg4WDZONGk1MjdxV29mRm1aTHZWRG5FeUFsWHpPTk50VFVhak9QU1dYak9tM3Buc21nRGxmLTljbzNSd1I2ZVlZa2luY3BrRGIwb1lTcml2RU1NMUlrdmt6WVExREs4S1psdHdXM3czY2pUcjBzeU92UDhpZ0lELTFZQjZaaHN6WVY1WjRDWmdJZklfV2dpbWk0ZDBjUk8xcDlnQjU0X05nU01idTJCZmNmUmNZUXpaRWZveHBv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOdXhBZ1hpcXVfVG11ME5ZRUZZOG1DNUM3Rk55dmNoNGNLbVVqcjZZanVVRkZJV24wc1c3VktmWUFpR2steTRQdkJzbzdLU29WQU5kb2lmalhLSlFQdmFCbU9helVFTzZWZThyWExESVhOX3VRTE1GTGZFMmtEOWo2SkY5RDV6TzZwNXN6RFY1LVM3SjRzeTBkT3ZPWURzNFp3YWtKX05NWnM0dWNEQUV0amNqbW52RzJqaUxVMFIzT3EzR0U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Trabalhadores da Manserv entram em greve e exigem jornada 4×4 e melhores condições de trabalho - Badiinho</t>
+          <t>WILSON HUSUM, Limestone Carrier - Detalhes e posição atual - IMO 9017379 - VesselFinder</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>06/08/2025 07:00</t>
+          <t>02/08/2025 00:12</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9fN3VVZmJNM2pGMzB3V19FM1N4d3hpWnVaMUZvZUtXWXZhUFFCSXMxNXlyTUt6dnQyalF6bFNZN0ZPcW5QVWp1dDV2d1FoX19nRzg4VXJjaG93OUJYSndmTEdCUDBacHFyUVRBNTFaRmhiYzBhcVQtV9IBfkFVX3lxTFBuc1ZCZ1hCOFRSdVBxVktkYldTdUE0QUkzQzEybEZzVXplV1A2MlRscGxudmhPOW9xNTlic25DVURrMWhIaW9QS3ZfNl92OWJzS1FkeXhQMXpaWGVidUhjeWtmamR6MmNsZkV6ZTVneVdsYkQ4RnA4OEpSTFNfUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9VeVpNZDZDc09nd0F4WWJFTGR0VGlYMmtiYV9OVjloQ254cllIaERRX3psSzVTaUJhNjdVcXJpZHFmQmVyUVhKc2tOSXZOYzhFaFF2OGNKMEVHNmxFU3FUeGh6VmszZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>O futuro circular do agro: como cientistas e empresas estão transformando resíduos em fertilizantes - AgFeed</t>
+          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>02/08/2025 07:00</t>
+          <t>01/08/2025 07:00</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOdXhBZ1hpcXVfVG11ME5ZRUZZOG1DNUM3Rk55dmNoNGNLbVVqcjZZanVVRkZJV24wc1c3VktmWUFpR2steTRQdkJzbzdLU29WQU5kb2lmalhLSlFQdmFCbU9helVFTzZWZThyWExESVhOX3VRTE1GTGZFMmtEOWo2SkY5RDV6TzZwNXN6RFY1LVM3SjRzeTBkT3ZPWURzNFp3YWtKX05NWnM0dWNEQUV0amNqbW52RzJqaUxVMFIzT3EzR0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNUS1oVVdaYlNDQXh3VnlEd3Fsclg5UTI5VGxKQ0ZoVzNhRF9obkZPeWg2V3RZN1N3SmhGY0FYZ0dtZVV1MURfQmdEYVJ3cWpUVlNQY0lHdkp0bkQ1RTZXbFZnbkpha292TnZ5V3pxLW1LMjZDcVNiRk93Vm1KRmRRQlJSeEVRZEJJQWtzSElKX3ozaFJTMjdnOUNjUnF3S0duODYteQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>WILSON HUSUM, Limestone Carrier - Detalhes e posição atual - IMO 9017379 - VesselFinder</t>
+          <t>Emater-MG encerra segunda etapa da entrega de agrosilício a agricultores de Minas Gerais - emater.mg.gov.br</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>02/08/2025 00:12</t>
+          <t>31/07/2025 07:00</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9VeVpNZDZDc09nd0F4WWJFTGR0VGlYMmtiYV9OVjloQ254cllIaERRX3psSzVTaUJhNjdVcXJpZHFmQmVyUVhKc2tOSXZOYzhFaFF2OGNKMEVHNmxFU3FUeGh6VmszZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxONmF2eGdidE1Nai1hZ2E4bU84U3FqMWYzTlF0dEJQdVNxOHJuNmNlSDhWdG16cjJGcFRvd3luU2dQWjlNQ2NWb3M4R3JlNHRpUFg3TjlDM2E1eElCRzFNZ01vMUVEdl90THNLMU5MeHNONkd0ajl4TWI4Tm9nejlOWm5MUk82bUxWaHotWlkyWGl6MWUtWkkyT0NkalBkaEp5ajBreEc1b3dIcC1EaFZfQkotWnA2b2RtcktJbUUtWVlCZ2tobFZIb3N0dkdzaDViRXRkX0NHNG05ZjZJTTV6MENqQXAwMHF6QS1WcXFjWmVTbEstZVp0VDdNRW5ESk1UN05HZnkxLS1ZVXZRelVQOWFsU2xxSDhxNXpV?oc=5</t>
         </is>
       </c>
     </row>
@@ -11534,83 +11534,83 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - IBRAM - Mineração do Brasil</t>
+          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - Portal Serra Dourada News</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>01/08/2025 07:00</t>
+          <t>29/07/2025 07:00</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNUS1oVVdaYlNDQXh3VnlEd3Fsclg5UTI5VGxKQ0ZoVzNhRF9obkZPeWg2V3RZN1N3SmhGY0FYZ0dtZVV1MURfQmdEYVJ3cWpUVlNQY0lHdkp0bkQ1RTZXbFZnbkpha292TnZ5V3pxLW1LMjZDcVNiRk93Vm1KRmRRQlJSeEVRZEJJQWtzSElKX3ozaFJTMjdnOUNjUnF3S0duODYteQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOZWZ1SmNscXJLQTgtcGo3S2JvMGM0UXhTRnAyVW9mYzFNYmNzMHRtTG5rNjJWWWg3c1pFeUVHczBRNEw2NVU1R3dlLW5hbTFYUXc0a0diRFBFWFBUVzFpLUkyNXpselV2TVBIcnZvNUhkNjEzN3ZzTjNvX0pvdVQzM3RJZkFmdkMtaFp3aHZRZ1gxN3kwdmZCNDJ6NFBjb2pyZHNIc2pwS0F6bUhtOEpoOVJNUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Emater-MG encerra segunda etapa da entrega de agrosilício a agricultores de Minas Gerais - emater.mg.gov.br</t>
+          <t>Prefeitura de Catalão inicia obra de reconstrução da Estrada das Mineradoras com investimento de R$ 8,7 milhões - Badiinho</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>31/07/2025 07:00</t>
+          <t>24/07/2025 07:00</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxONmF2eGdidE1Nai1hZ2E4bU84U3FqMWYzTlF0dEJQdVNxOHJuNmNlSDhWdG16cjJGcFRvd3luU2dQWjlNQ2NWb3M4R3JlNHRpUFg3TjlDM2E1eElCRzFNZ01vMUVEdl90THNLMU5MeHNONkd0ajl4TWI4Tm9nejlOWm5MUk82bUxWaHotWlkyWGl6MWUtWkkyT0NkalBkaEp5ajBreEc1b3dIcC1EaFZfQkotWnA2b2RtcktJbUUtWVlCZ2tobFZIb3N0dkdzaDViRXRkX0NHNG05ZjZJTTV6MENqQXAwMHF6QS1WcXFjWmVTbEstZVp0VDdNRW5ESk1UN05HZnkxLS1ZVXZRelVQOWFsU2xxSDhxNXpV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE8yaU9FRkxwRUQwT09aeHp0VFMzekRwYzF2RmhZYjE5Zkx5ZksyU2FpcEZNZXVOSGE3Qy1JeDBRcmFJX0ZsOGYyQUNyb2VyT2xfemNGUGpLWmN4d3JVYTB1c0Y4NW1heDVUdk9LWXhB0gFzQVVfeXFMUEVzSzlPZ2ZNRmNiU3A4NEQzR2QtMDhrY3hOaGdzUEttWDlFam9YRzNVSHFPZzlSakxqbHNZRHJsaXlCc0F2YVhxRWkzNnNiZHB3dm1QZ3dUMEJKaHBPajlNM0lBdm9tMjBlbjlLUzdKS21uQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - Portal Serra Dourada News</t>
+          <t>AGREGADOS | Carmeuse investe quase R$ 2 bilhões em novas unidades para produzir cal em MG - Brasil Mineral</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>29/07/2025 07:00</t>
+          <t>23/07/2025 07:00</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOZWZ1SmNscXJLQTgtcGo3S2JvMGM0UXhTRnAyVW9mYzFNYmNzMHRtTG5rNjJWWWg3c1pFeUVHczBRNEw2NVU1R3dlLW5hbTFYUXc0a0diRFBFWFBUVzFpLUkyNXpselV2TVBIcnZvNUhkNjEzN3ZzTjNvX0pvdVQzM3RJZkFmdkMtaFp3aHZRZ1gxN3kwdmZCNDJ6NFBjb2pyZHNIc2pwS0F6bUhtOEpoOVJNUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPcVhwQ1FTanBZbU41aHE3eUVXNTZlWGNTLUE5aS1GX1owNzd5SFFmNnFlN3Z5Q2tNOElmemM5TDhUekJOVkFpbWNjSm84cVEyT2NOalkxS19BM1c1NWQ3NTR4UEFXdWlCNVFsbnNLMWRFaUFHVktpYXZwSklETEQ4c1hrZkFxQ2JXRnFsX3JFTDVGRnYta1NaMS11clJXWTRLaFo4LUxTdFpYZzBGWGFCcTZEbGU0VXBzZHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Prefeitura de Catalão inicia obra de reconstrução da Estrada das Mineradoras com investimento de R$ 8,7 milhões - Badiinho</t>
+          <t>Uberlândia receberá investimento de R$ 200 milhões em fábrica de cal que gerará 80 vagas de emprego - G1</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>24/07/2025 07:00</t>
+          <t>23/07/2025 07:00</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE8yaU9FRkxwRUQwT09aeHp0VFMzekRwYzF2RmhZYjE5Zkx5ZksyU2FpcEZNZXVOSGE3Qy1JeDBRcmFJX0ZsOGYyQUNyb2VyT2xfemNGUGpLWmN4d3JVYTB1c0Y4NW1heDVUdk9LWXhB0gFzQVVfeXFMUEVzSzlPZ2ZNRmNiU3A4NEQzR2QtMDhrY3hOaGdzUEttWDlFam9YRzNVSHFPZzlSakxqbHNZRHJsaXlCc0F2YVhxRWkzNnNiZHB3dm1QZ3dUMEJKaHBPajlNM0lBdm9tMjBlbjlLUzdKS21uQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNSXFaOVI3bW9MNk1wUmppenNyUVE5WGhvVWl6V09EYlZXdS1KMTlhNzNwd0ZTaGFZc21PdTBGWU5TSkNrZF9xRXZqSWNtYUdMQ1pOTlBrZTBCVnpMTUhPRThYYTdUYW1pa1lXYTM4REpqekxtZklrZ25KZFNrSDVrSmk3bnlRem9zTVY3Skp3bnZrTm1LWXdhZk1PeHlQNld6d0F2R3FtM0owdm9TbzQ3aDhfMS1ZejFSc2p3R0JFcGVEZC1KR3pUQXhxeUF2bkY5czJteVZvd09kRE82aVdPaFNhUXVBQzhYZGFlMlFvbEFEWWxfUVlVetIBhwJBVV95cUxOMF9kQmhiV25CeHM1aW1GVU5vQmJLakdCc1VrT2F5NFc5b3NPeW1KMWtRbEIwX1Fadjl2bmdlVXgtT0dGR2h2UGRfaUtRVW9KWENxWlRQMjhDRVg2dGRidGZwT3FkU3JNSkl2S1RTSmhTU2NZeW4ySWxZbGxfd2N4Y3FPQWNHOHZkMjJOU20xc2RSeEV5aVBIRXBlazRXM2xfMDBSUGd5SWt2TjB2YVNZRHlTb3ljaGdfTDZfMzNVck5IY05LNGxXaDRUVEJBV0dMODJLbFF4dnQwNWZ2ZmNqNE9DU3IwVEtMY3RCeGRVN2FPRmU0dDAwUElpUTBUaHdEcWx5MzdYVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11622,59 +11622,15 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>AGREGADOS | Carmeuse investe quase R$ 2 bilhões em novas unidades para produzir cal em MG - Brasil Mineral</t>
+          <t>Uberlândia abrigará planta de multinacional belga responsável pela produção e fornecimento de cal - uberlandia.mg.gov.br</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>23/07/2025 07:00</t>
+          <t>22/07/2025 07:00</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPcVhwQ1FTanBZbU41aHE3eUVXNTZlWGNTLUE5aS1GX1owNzd5SFFmNnFlN3Z5Q2tNOElmemM5TDhUekJOVkFpbWNjSm84cVEyT2NOalkxS19BM1c1NWQ3NTR4UEFXdWlCNVFsbnNLMWRFaUFHVktpYXZwSklETEQ4c1hrZkFxQ2JXRnFsX3JFTDVGRnYta1NaMS11clJXWTRLaFo4LUxTdFpYZzBGWGFCcTZEbGU0VXBzZHc?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>Carmeuse</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>Uberlândia receberá investimento de R$ 200 milhões em fábrica de cal que gerará 80 vagas de emprego - G1</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>23/07/2025 07:00</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNSXFaOVI3bW9MNk1wUmppenNyUVE5WGhvVWl6V09EYlZXdS1KMTlhNzNwd0ZTaGFZc21PdTBGWU5TSkNrZF9xRXZqSWNtYUdMQ1pOTlBrZTBCVnpMTUhPRThYYTdUYW1pa1lXYTM4REpqekxtZklrZ25KZFNrSDVrSmk3bnlRem9zTVY3Skp3bnZrTm1LWXdhZk1PeHlQNld6d0F2R3FtM0owdm9TbzQ3aDhfMS1ZejFSc2p3R0JFcGVEZC1KR3pUQXhxeUF2bkY5czJteVZvd09kRE82aVdPaFNhUXVBQzhYZGFlMlFvbEFEWWxfUVlVetIBhwJBVV95cUxOMF9kQmhiV25CeHM1aW1GVU5vQmJLakdCc1VrT2F5NFc5b3NPeW1KMWtRbEIwX1Fadjl2bmdlVXgtT0dGR2h2UGRfaUtRVW9KWENxWlRQMjhDRVg2dGRidGZwT3FkU3JNSkl2S1RTSmhTU2NZeW4ySWxZbGxfd2N4Y3FPQWNHOHZkMjJOU20xc2RSeEV5aVBIRXBlazRXM2xfMDBSUGd5SWt2TjB2YVNZRHlTb3ljaGdfTDZfMzNVck5IY05LNGxXaDRUVEJBV0dMODJLbFF4dnQwNWZ2ZmNqNE9DU3IwVEtMY3RCeGRVN2FPRmU0dDAwUElpUTBUaHdEcWx5MzdYVQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>Carmeuse</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>Uberlândia abrigará planta de multinacional belga responsável pela produção e fornecimento de cal - uberlandia.mg.gov.br</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>22/07/2025 07:00</t>
-        </is>
-      </c>
-      <c r="D512" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOQU5uZ0sxNnlndTM4ZUF3NXBQTFdhdElLY0xNa3FWX3E2N0hBZTZ5bVUxTTJyWkRFOEdNeXlHUTBTdzczbWNaeGEwVEhRTmlhb2g0TnpKcTVqY21PeUlHUC1mNzlIaFV3MEJERzk1X2Y4eU11aHJ1VllobDctX3FhWjFydVp6MG5iOUVUU3YtaXN5ZkRrZXJTeWZ6YUxtenIwRG1zY0VNQ3huS2ZRbmFxUWxLcVNDWFlvN0pPYUN3Sl9vTXhEc1l0c2hzZlFhV0Q3bi1DUW5ZS1dfUQ?oc=5</t>
         </is>

--- a/Noticias_Calcario_20260715.xlsx
+++ b/Noticias_Calcario_20260715.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D518"/>
+  <dimension ref="A1:D517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,22 +441,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir ‘cheiro de enxofre’ do futuro dela - Jornal de Brasília</t>
+          <t>Planalto inicia entrega de 286 toneladas de calcário para produtores rurais - O Alto Uruguai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15/07/2026 13:40</t>
+          <t>15/07/2026 15:16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOR3F4ZmpKWHBhekMzRTJkVnhwUjNHdVJwSWVlbHVHMzJiTDRwbjN4Sk80SXprQzI0enRZUW1kQ2s2RVJ1XzRrNHZiUHNUZThaSmU0THRYa2pzbzI5MGJ0dVZNZC1CcF9kMHNxY3c4ck1SanczMFpmMERwZE9KamF1czBZb3doWGNwaGVETkx6R3NhRlBxQ0V6NGM2WmVaaVpSX2czVzFPU0ZFaDJNV2p1Sm5YTHpIeWMtWV9uZUlrRGFqZ3E1VGkwY3hGdEVMRVJJaGpseXV5M0tQMlJpM2hnTDNYZmVmSFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOYWpqVlRKZGxfN2NhRUZHN0pjRzlkc3FqcEVEczlGeGhoT25iVVphQ3p0bE9vdEhiNy1pbzVqWFMyYWdGbUJhNDJzUkJ6MEdfMlU5elJGQlU0XzJXQUVpUVJSdFVmZ3Q4ZTdEZWhuWUNMUnZPdU1zSkpHT1EwdkEzYTBnX2IzMnQxTjAtSDMtS3pQd1JJbEJKbUo2LUgxXzBKOURmTWJGUWtTcnkwamdFbDJWZ2xSVTg?oc=5</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia Fonseca e dispara: ‘Sinto o cheiro de enxofre’ - CARAS Brasil</t>
+          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir ‘cheiro de enxofre’ do futuro dela - Jornal de Brasília</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15/07/2026 13:10</t>
+          <t>15/07/2026 13:40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQcVBtVkxvbHluLV9INDQ1WXpUQmNnSjJ6OThtSkhMM2ZhVlBYWVRMMmI3Q2xZdE92dVlxVnd0ZTRkcEdPdHZaQVA0RmFrRjRuY0VsVTZEaVprTV9idS01dWZWRnFZMFltLWhubTU4OUVzYUhNOXhzQkVfM2R5QWRxLTVMUlA4Z2hvSlZ3RURVTjVvTXpsZ1M3RlVCOThQTlBfRzNxUW9lbW8wNlA3dmMwYzUwUTB2dXpZamtVMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOR3F4ZmpKWHBhekMzRTJkVnhwUjNHdVJwSWVlbHVHMzJiTDRwbjN4Sk80SXprQzI0enRZUW1kQ2s2RVJ1XzRrNHZiUHNUZThaSmU0THRYa2pzbzI5MGJ0dVZNZC1CcF9kMHNxY3c4ck1SanczMFpmMERwZE9KamF1czBZb3doWGNwaGVETkx6R3NhRlBxQ0V6NGM2WmVaaVpSX2czVzFPU0ZFaDJNV2p1Sm5YTHpIeWMtWV9uZUlrRGFqZ3E1VGkwY3hGdEVMRVJJaGpseXV5M0tQMlJpM2hnTDNYZmVmSFU?oc=5</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia e a chama de 'loira de laboratório' que exala 'cheiro de enxofre' - Alô Alô Bahia</t>
+          <t>Luana Piovani volta a atacar Virginia Fonseca e dispara: ‘Sinto o cheiro de enxofre’ - CARAS Brasil</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15/07/2026 12:33</t>
+          <t>15/07/2026 13:10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQZEd5VUtYUVlHZzFBYTllWkxLUlBGdzdmb0QwTzUybFJ0QTFBYVc2S3hnVERNblRNQTR3cktnMXFZNGFDUTUwLWVHdGZkMXJ5UTVoRFZVMnVvWmVYeURFeHRyazhJLWluc3JmUkJOTHRtRlZCZnpCQWxGRHplbTVIYUVfR3prLVYtUUtPSjdhMTJFRFQ3RVFUUEpqT3N4dkJEUWV4WVdXN1FQamdwZ3hqbUNtQzNQSVJKRjdKYlpXc3piRzRBUUhmM3FMQjQ1eGkyOHFUM3ZBWTExQlV5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQcVBtVkxvbHluLV9INDQ1WXpUQmNnSjJ6OThtSkhMM2ZhVlBYWVRMMmI3Q2xZdE92dVlxVnd0ZTRkcEdPdHZaQVA0RmFrRjRuY0VsVTZEaVprTV9idS01dWZWRnFZMFltLWhubTU4OUVzYUhNOXhzQkVfM2R5QWRxLTVMUlA4Z2hvSlZ3RURVTjVvTXpsZ1M3RlVCOThQTlBfRzNxUW9lbW8wNlA3dmMwYzUwUTB2dXpZamtVMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Polêmica sem fim! 'Loira feita em laboratório', dispara Luana Piovani em novo ataque a Virginia Fonseca; atriz critica envolvimento com casas de apostas: 'Sinto cheiro de enxofre' - purepeople.com.br</t>
+          <t>Luana Piovani volta a atacar Virginia e a chama de 'loira de laboratório' que exala 'cheiro de enxofre' - Alô Alô Bahia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15/07/2026 11:51</t>
+          <t>15/07/2026 12:35</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOa3EzU19ScDlIRnpUUmxUVm1ucW92dTB6WkZjRGdYdTlFUEt5bkFmdDY0bWxjWm5zSXlKU0QwVC1PQy1SZmFvc2JhQjBzYTdiWkRYd2hWVjhTYk5yQ2hTNlFKenJCYndFMEhCMmxpaG9tLUQ2UDdFVEljY2UtRVdhQXhvV1huMUt3aExpYzFNSUlJUnNIMjQ1aFhfeTZ1TGRBSnVBMVIybmEteDdScXBlQS1VY2hGYk9MU2liY191QVROSE1ISkV3MnphMGpRSnVQSEhicGhXSVJFQ1JVMXctYUFlcVRxQi1kZmJJdndxUdIB9AFBVV95cUxQdmttVnh2MFFZVWozRTJFemFYblhweEtWZnVvbzZRNFJZVTF6UlAyeVkwLWVxdHZjWHA4MUFxVDlPNlpnQXVNOG5kZFZCTUZLZ0h5OTAwUDlqbXNGcmNubEE2TDNvbGRtaUJSTXh3eXNQTEpZZTFHbHA0Ry03aTdnRnFTdHA2SURrSUJmNVdLNkZWcDREQWV1QkVLcFI1N3kxWjhFWTdLRmltam5XSUp0NFdPSWQzRWNpcG12V1NIV0g5ZVh4Mk5ESnQxSXo1ekFfaTlDYjNGQ1l4QkthM0pfd1NyMXZjdG1Ha05qS3o0VG5GM0hY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQZEd5VUtYUVlHZzFBYTllWkxLUlBGdzdmb0QwTzUybFJ0QTFBYVc2S3hnVERNblRNQTR3cktnMXFZNGFDUTUwLWVHdGZkMXJ5UTVoRFZVMnVvWmVYeURFeHRyazhJLWluc3JmUkJOTHRtRlZCZnpCQWxGRHplbTVIYUVfR3prLVYtUUtPSjdhMTJFRFQ3RVFUUEpqT3N4dkJEUWV4WVdXN1FQamdwZ3hqbUNtQzNQSVJKRjdKYlpXc3piRzRBUUhmM3FMQjQ1eGkyOHFUM3ZBWTExQlV5?oc=5</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Crise no Oriente Médio já afeta o agro: falta de enxofre reduz produção de fertilizantes no Brasil - Portal PaNoRaMa</t>
+          <t>Polêmica sem fim! 'Loira feita em laboratório', dispara Luana Piovani em novo ataque a Virginia Fonseca; atriz critica envolvimento com casas de apostas: 'Sinto cheiro de enxofre' - purepeople.com.br</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15/07/2026 11:09</t>
+          <t>15/07/2026 11:51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcUhycC1KSVpwR01nZ0oyUEZwbGtHblZ0a3Q1Nmp4WjRhTURGYTJvMU9DcUdMUlpsNDBOSlhfX21LTk9mV3ZXUWZBWmFFaFFmcGFMYTQ2bWV6M1pYLXk2RFZZb1NPdHVhdmtBdTJtb0lOTkNRaTFPVUhMMFlOaFRFdVFwTnJxeFBRZEkzX0lGWWx4WnhHRVZHekpCZ1VBTVRVc2Q1c1FqUXdnLUhUX0txMXlJVkg4YWxw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOa3EzU19ScDlIRnpUUmxUVm1ucW92dTB6WkZjRGdYdTlFUEt5bkFmdDY0bWxjWm5zSXlKU0QwVC1PQy1SZmFvc2JhQjBzYTdiWkRYd2hWVjhTYk5yQ2hTNlFKenJCYndFMEhCMmxpaG9tLUQ2UDdFVEljY2UtRVdhQXhvV1huMUt3aExpYzFNSUlJUnNIMjQ1aFhfeTZ1TGRBSnVBMVIybmEteDdScXBlQS1VY2hGYk9MU2liY191QVROSE1ISkV3MnphMGpRSnVQSEhicGhXSVJFQ1JVMXctYUFlcVRxQi1kZmJJdndxUdIB9AFBVV95cUxQdmttVnh2MFFZVWozRTJFemFYblhweEtWZnVvbzZRNFJZVTF6UlAyeVkwLWVxdHZjWHA4MUFxVDlPNlpnQXVNOG5kZFZCTUZLZ0h5OTAwUDlqbXNGcmNubEE2TDNvbGRtaUJSTXh3eXNQTEpZZTFHbHA0Ry03aTdnRnFTdHA2SURrSUJmNVdLNkZWcDREQWV1QkVLcFI1N3kxWjhFWTdLRmltam5XSUp0NFdPSWQzRWNpcG12V1NIV0g5ZVh4Mk5ESnQxSXo1ekFfaTlDYjNGQ1l4QkthM0pfd1NyMXZjdG1Ha05qS3o0VG5GM0hY?oc=5</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia, chama ela de 'loira de laboratório' e dispara: 'Sinto o cheiro de enxofre' - Globo</t>
+          <t>Crise no Oriente Médio já afeta o agro: falta de enxofre reduz produção de fertilizantes no Brasil - Portal PaNoRaMa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15/07/2026 10:17</t>
+          <t>15/07/2026 11:09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQQkdPbWpjNnBsbm0zaUw5ZzEyUzd3R3hyOXlSZnEtMlpNS0wzZXAzbHpMSVhrSXV4VFcyakNvLWlnYnlwLVg0MjF3bnBJWXZuOG83TmZ6S1dKQlU5LTNUc0x3clZnMnNUV1pBbTB3UDB1djBzaEVxWWZaR014Mk9KS0tZMElTRkhCcjE4UWExNGxuMWhkUXVValpwUlg5UEstU0Q1ZElPRGxEZHllZXdvZ21nWdIBwgFBVV95cUxPRDNHYW50ZDRBR2JVSkRRbWhYTjhWYTd2SERLcUNvOTJIS3JUdHBTZC0zWUV5ek5peHlYNW5NWWVxWGo2emtYcUhjRGFiLXNmSHpQeUFvUnI0TG56YTh6Xzl0em1vM3pBQnZ2RWtJRTFRcGJiZm5LTVo5SzByUjh4TjZmdmRUa2tuX085cDRRVGJYSmtaOUgybEpEZlc4OWRnb2loVi1pRkQ4SDJqU3VveGpjQlkwdkdFRnAyTExYTklOUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcUhycC1KSVpwR01nZ0oyUEZwbGtHblZ0a3Q1Nmp4WjRhTURGYTJvMU9DcUdMUlpsNDBOSlhfX21LTk9mV3ZXUWZBWmFFaFFmcGFMYTQ2bWV6M1pYLXk2RFZZb1NPdHVhdmtBdTJtb0lOTkNRaTFPVUhMMFlOaFRFdVFwTnJxeFBRZEkzX0lGWWx4WnhHRVZHekpCZ1VBTVRVc2Q1c1FqUXdnLUhUX0txMXlJVkg4YWxw?oc=5</t>
         </is>
       </c>
     </row>
@@ -578,39 +578,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eficiência do enxofre no solo ganha protagonismo no manejo agrícola brasileiro - Portal do Agronegócio</t>
+          <t>Luana Piovani volta a atacar Virginia, chama ela de 'loira de laboratório' e dispara: 'Sinto o cheiro de enxofre' - Globo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15/07/2026 08:00</t>
+          <t>15/07/2026 10:17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQSkZycWdLVDZKNm5qcVlpdEh5aVBvTGtGNWp5MzRPN2lxcXROR1VxanltZ29OdXY2SDNuTjA1Ym1RdFlYMGhXNlNVMF9ESzE4UFNfTDN4TzdSZnBFS3JaRE5ET3E1NVhjMUJPSG5ZYjR6VlFPNE4xUEN0RU1CaS1YRlQ3dUc1XzZnOGVtWUZGMkRobkVfMFN1R2pIcjlPZHlnbDlXbHpvY0QtV3RfTGo3ZGhRYnFfX3pnaVhoMkJ0NDh1Uk1HNXdjNmZNTmZkMlFCRXlpQ3drV3hZbUNlSEF3RXBpc0dOTzh1a3pv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQQkdPbWpjNnBsbm0zaUw5ZzEyUzd3R3hyOXlSZnEtMlpNS0wzZXAzbHpMSVhrSXV4VFcyakNvLWlnYnlwLVg0MjF3bnBJWXZuOG83TmZ6S1dKQlU5LTNUc0x3clZnMnNUV1pBbTB3UDB1djBzaEVxWWZaR014Mk9KS0tZMElTRkhCcjE4UWExNGxuMWhkUXVValpwUlg5UEstU0Q1ZElPRGxEZHllZXdvZ21nWdIBwgFBVV95cUxPRDNHYW50ZDRBR2JVSkRRbWhYTjhWYTd2SERLcUNvOTJIS3JUdHBTZC0zWUV5ek5peHlYNW5NWWVxWGo2emtYcUhjRGFiLXNmSHpQeUFvUnI0TG56YTh6Xzl0em1vM3pBQnZ2RWtJRTFRcGJiZm5LTVo5SzByUjh4TjZmdmRUa2tuX085cDRRVGJYSmtaOUgybEpEZlc4OWRnb2loVi1pRkQ4SDJqU3VveGpjQlkwdkdFRnAyTExYTklOUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Galeria de Patios and Terraces - Dietfurt Limestone Gala - 8 - ArchDaily</t>
+          <t>Eficiência do enxofre no solo ganha protagonismo no manejo agrícola brasileiro - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15/07/2026 06:10</t>
+          <t>15/07/2026 08:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxObk9lanpoTkZtUTVKWHViWTlZak5fRW5BYXdPOVA3UzU3WU1ibl9ERFJSZktqLWlHeVREUGVya24zb1ZrOHVvdU9XemJldmdEZXF1LUVHZVdoV3lDbnF5SkFJcDlSVWw2VHFCRHc2YUhWTlVCaFJ4elFJYTNFU21PNzBBbEJVVFM3T3ZvTGFnUVdycUdnajhxejhZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQSkZycWdLVDZKNm5qcVlpdEh5aVBvTGtGNWp5MzRPN2lxcXROR1VxanltZ29OdXY2SDNuTjA1Ym1RdFlYMGhXNlNVMF9ESzE4UFNfTDN4TzdSZnBFS3JaRE5ET3E1NVhjMUJPSG5ZYjR6VlFPNE4xUEN0RU1CaS1YRlQ3dUc1XzZnOGVtWUZGMkRobkVfMFN1R2pIcjlPZHlnbDlXbHpvY0QtV3RfTGo3ZGhRYnFfX3pnaVhoMkJ0NDh1Uk1HNXdjNmZNTmZkMlFCRXlpQ3drV3hZbUNlSEF3RXBpc0dOTzh1a3pv?oc=5</t>
         </is>
       </c>
     </row>
@@ -622,46 +622,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Galeria de Flooring Panels - Dietfurt Limestone - 6 - ArchDaily</t>
+          <t>Galeria de Patios and Terraces - Dietfurt Limestone Gala - 8 - ArchDaily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14/07/2026 22:11</t>
+          <t>15/07/2026 06:10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOMy10V0pjLThwV1lNZEEwQTFNLUtxbGRYZU5ZT3ZJRm5Wclhtb3ZHTFQydXkyYkhtNlJxdGt2Wk52bXkzSWxKN3lCSzE4UUpTTTZyX3lVRXdwX1pSV1NUc19faFFjQjRGODhBc3phcHVmMGg4eTU3bHNMSjd3RFVqUTkySnhlYjRFUXFGM3ZqeEhLUTYwMlZnWDdUSkNjY1dQTldBSDJtcllqaFd3cDhhTXdjcHV0Q2lycUV0eHNvMkRNZFFZQnhLakhLQzVqQ2pYc19EWUE4bmk3YjNaUi0wOFFPa3duazFPN2k2SGh5NzFKUGpHdTJpa2tB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxObk9lanpoTkZtUTVKWHViWTlZak5fRW5BYXdPOVA3UzU3WU1ibl9ERFJSZktqLWlHeVREUGVya24zb1ZrOHVvdU9XemJldmdEZXF1LUVHZVdoV3lDbnF5SkFJcDlSVWw2VHFCRHc2YUhWTlVCaFJ4elFJYTNFU21PNzBBbEJVVFM3T3ZvTGFnUVdycUdnajhxejhZdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
+          <t>Galeria de Flooring Panels - Dietfurt Limestone - 6 - ArchDaily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14/07/2026 17:57</t>
+          <t>14/07/2026 22:11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOMy10V0pjLThwV1lNZEEwQTFNLUtxbGRYZU5ZT3ZJRm5Wclhtb3ZHTFQydXkyYkhtNlJxdGt2Wk52bXkzSWxKN3lCSzE4UUpTTTZyX3lVRXdwX1pSV1NUc19faFFjQjRGODhBc3phcHVmMGg4eTU3bHNMSjd3RFVqUTkySnhlYjRFUXFGM3ZqeEhLUTYwMlZnWDdUSkNjY1dQTldBSDJtcllqaFd3cDhhTXdjcHV0Q2lycUV0eHNvMkRNZFFZQnhLakhLQzVqQ2pYc19EWUE4bmk3YjNaUi0wOFFPa3duazFPN2k2SGh5NzFKUGpHdTJpa2tB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,122 +671,122 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14/07/2026 16:52</t>
+          <t>14/07/2026 20:39</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxQYVhNZTI3UmVycEpMVFVnb1FySmhoNGRWbnN5eTJnSUgtaWliR3Nqb010TThIcERFOThuRElVbnpOd0NFeS1FQjQ4TWQ5VVRxRzU4aXZwUkdqQ1lad0ZKbUhiTWI2MDI1VXJHbklBWjQ0WkZXcm5QMFFLMUpzR3FEUWFYOWZSZ29CRW84RklmRXhyOFoya285cEFSbzF1WUI3TC1jM0dfcHhiV3ZrOWl5U09GV3lqVG1TQ045aEIzSk1qUTlpdmRwcVF4VzlBck11TTFBTDJmQVhOZm9IWmUzNnNkWU1ZY25GRnlLT0JvNVl2bzEtQTJOM3JiU1B6Slh3Wm1LTWxseEhzWUowbVNsNm43a1Q1dExKRUZoRWFuYmhVSkpm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwNBVV95cUxOdURPcGZyOTJrUWdRbHlpaTdab3FZVWY5Tng5Z191NXZzU3VDSjZFa3VfY1ppQ3h0RUhrajF6WUdmZVVCczZBTkFGOWMwYzlYTjYtem9CU0gwdi1LVUhTcFkxcmJ4TkRReFNrVjU2SllvMG1QSnRqZ1hEa2I0N3V0SzYxdGdfWGVzTGVUajdtMjdEMzJyaEU4YVV2UHlEWDMwaGQ5SEVRWk5PMGl3OGdudjZnSS1ydFhaRzBkOE5kdWlxdldaZDBhZW5zZk5aQUJOSjVHUXRMeXE2UkdWRGl3WmJVaHVibVdRc21ualN4YmdHMHZ5V19FankwdDVHdUxMZWVJTkNxZzFRamlWd2J6NkpQNVVJU3diV3A1cDQ3dXI0NGlBVFVGX3JhVmluLU1NYVhBYmU5c3A2NFlGbG1UWTBoWTl2LUw0NFpQOG40VW1TZDJUa0xIMUxCdkZOY3BQOUFDa1d6ZEdSWi1mODctNnVXdEIwRDV3VGdyNnJzejNQM1ljQms3aVBLcUxsX0c2UFFKdzkzTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Galeria de Wall and Floor Tiles - Les Classiques Collection - 5 - ArchDaily</t>
+          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14/07/2026 16:08</t>
+          <t>14/07/2026 17:57</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQWk9OdTROaURFZmt0QUttRmRQbjFVc2JSUWVDTEJnejJnWWdkSUx5OGNuODNRNXV6U2tjMHJKN1Nfcjg4cGROMkNjOGtOZTlVNE1UakQyel9sTm1OQkRkNUllQUFZMzFZcXJ5YzFLZWl2dDNFZ1lGZHhlMC16UzJtM19QUWtBdVRhdTdObVl2bXhaT1VxUTRVSktNQk1iUXNmWFo1d2pBeGgwMDNaS1ZFUXYxMzU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Passa Sete adquire distribuidor de calcário para fortalecer atendimento aos produtores rurais - radiosobradinho.com.br</t>
+          <t>Galeria de Wall and Floor Tiles - Les Classiques Collection - 5 - ArchDaily</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14/07/2026 15:28</t>
+          <t>14/07/2026 16:08</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ2R3Y1NoTFE1U1NjTnNxUV9vWnJWcjV4WUxxX2ZJNWt6Q2dmLVI5N2RxT2Y0Ung2QXZQc0ZJakF1OXpBOVNTV0FhRjlXb1NXdDRSeVRiSm55SHo1bGsxR0R3SjJJbUdNN2VEcU1rU2t2dzhiVl9MMkNPMjQ1dDBLekhoNDh6cUlodU50UGNOZFQ2ZFViMlVoT1IxaF8xdnNRSE9fc0djWnV4Nmk2bnZuR1ZveWJCcFdOamZYWWg3REpNVTVRcVdtUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQWk9OdTROaURFZmt0QUttRmRQbjFVc2JSUWVDTEJnejJnWWdkSUx5OGNuODNRNXV6U2tjMHJKN1Nfcjg4cGROMkNjOGtOZTlVNE1UakQyel9sTm1OQkRkNUllQUFZMzFZcXJ5YzFLZWl2dDNFZ1lGZHhlMC16UzJtM19QUWtBdVRhdTdObVl2bXhaT1VxUTRVSktNQk1iUXNmWFo1d2pBeGgwMDNaS1ZFUXYxMzU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fertilizante em alerta - Olhar Direto</t>
+          <t>Passa Sete adquire distribuidor de calcário para fortalecer atendimento aos produtores rurais - radiosobradinho.com.br</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14/07/2026 15:27</t>
+          <t>14/07/2026 15:28</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1zY1FWdWlnSWxfY2tCYkR5M2Z6YmFhdWUza2tRRTRtQW9hUWFNRGs3N2FGSFU1ekdyUldESy1ESDlJOUhoZWcyZFVGSFpabkl0LUJnU1kwLXQ0MDNpUVNzTzF4eVUtUllSQzJjSllwS21Tems?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ2R3Y1NoTFE1U1NjTnNxUV9vWnJWcjV4WUxxX2ZJNWt6Q2dmLVI5N2RxT2Y0Ung2QXZQc0ZJakF1OXpBOVNTV0FhRjlXb1NXdDRSeVRiSm55SHo1bGsxR0R3SjJJbUdNN2VEcU1rU2t2dzhiVl9MMkNPMjQ1dDBLekhoNDh6cUlodU50UGNOZFQ2ZFViMlVoT1IxaF8xdnNRSE9fc0djWnV4Nmk2bnZuR1ZveWJCcFdOamZYWWg3REpNVTVRcVdtUA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Antigos asteroides podem explicar cristais de enxofre encontrados por Curiosity - Aventuras na História</t>
+          <t>Fertilizante em alerta - Olhar Direto</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14/07/2026 14:58</t>
+          <t>14/07/2026 15:27</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPbk15WHdxRElHSUFTYmRCSDBMQ3hMN3gyY05ZNmo0SlV1ZFp1WnpsZHNFTHNtelcwWi1oemJLaFB6MHhzWnRudEZPajFLVks2aElOUGVDNVhmY3NFcndPZEUxaURaZm14d0daT0MwVEF3TVY4aGlPQ0hFNWY1dkJGSFk0RFhXMGFncEx0enk2WHU4ZTdkeFc3ZkNQRTZuT2JQOEV1TURqRjh4NjZ4Q1Y2cnQxYm1lTGZvUTBiZjh5SU83cW9pdkRCbkRyT3d1Q1IzOVVxYWN5SXM2Y3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1zY1FWdWlnSWxfY2tCYkR5M2Z6YmFhdWUza2tRRTRtQW9hUWFNRGs3N2FGSFU1ekdyUldESy1ESDlJOUhoZWcyZFVGSFpabkl0LUJnU1kwLXQ0MDNpUVNzTzF4eVUtUllSQzJjSllwS21Tems?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mário Neto detalha acordo do Metabase para trabalhadores desligados da Mosaic - Badiinho</t>
+          <t>Antigos asteroides podem explicar cristais de enxofre encontrados por Curiosity - Aventuras na História</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14/07/2026 14:11</t>
+          <t>14/07/2026 14:58</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9sTGRIT05leVVvVHZ3cU1qU3BmLS14TjVtM0xGdVNtNWFxNkg5UW14blZqOEpJMmNEeHNObE1LVm00WDFwT3h4cmJEeUNTLUU3THJrMTE4UHZmekJGUXJheTBybjF1MzB6N2wydzc1U3NNZlJ0alF2edIBfkFVX3lxTE9wQUs4NzNaVFN5c0tBSGlTVEhlUTA5V2h5REE1SWFmbkhfci1iWnA5V3hMTUY0bTg5dy02R0VYU1NxR3BCV0R3NU0xSUlZYUJrRS1TNmhZVDJqVDFrN2xFdG03REJhSXllMF9FYnZMaHdtVjhOSTNIc1Jkc3JhZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPbk15WHdxRElHSUFTYmRCSDBMQ3hMN3gyY05ZNmo0SlV1ZFp1WnpsZHNFTHNtelcwWi1oemJLaFB6MHhzWnRudEZPajFLVks2aElOUGVDNVhmY3NFcndPZEUxaURaZm14d0daT0MwVEF3TVY4aGlPQ0hFNWY1dkJGSFk0RFhXMGFncEx0enk2WHU4ZTdkeFc3ZkNQRTZuT2JQOEV1TURqRjh4NjZ4Q1Y2cnQxYm1lTGZvUTBiZjh5SU83cW9pdkRCbkRyT3d1Q1IzOVVxYWN5SXM2Y3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -798,61 +798,61 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação da unidade de Catalão por falta de enxofre - Badiinho</t>
+          <t>Mário Neto detalha acordo do Metabase para trabalhadores desligados da Mosaic - Badiinho</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14/07/2026 13:09</t>
+          <t>14/07/2026 14:11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBodUloejIyYmJxUW80NXhoTVUzaXZFMklTTjc1NnRHMzZDZGJOUkVtWUFXT25IWVFwd3o3RGdEeVItVi13ZDdLRk85ZEZHS0t2MFFFMk8xdDQ0VEJRZUc1elhPcHNJcjBzQlBtdUhvLVoxQdIBd0FVX3lxTE1vS1RSMUxsVldiUFVXLTZiTXQta0IyNDdwV3hqMmVFdzZFOVpPTHlxUWhHUHA2djdCRTNCd3YtQndEaTRVT1U1REowc21rMW1nVEc2cWdxcFlEZnR2UG9FTWMxdDlvT2pyaFhiTW9taVFMQmk3NkM4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9sTGRIT05leVVvVHZ3cU1qU3BmLS14TjVtM0xGdVNtNWFxNkg5UW14blZqOEpJMmNEeHNObE1LVm00WDFwT3h4cmJEeUNTLUU3THJrMTE4UHZmekJGUXJheTBybjF1MzB6N2wydzc1U3NNZlJ0alF2edIBfkFVX3lxTE9wQUs4NzNaVFN5c0tBSGlTVEhlUTA5V2h5REE1SWFmbkhfci1iWnA5V3hMTUY0bTg5dy02R0VYU1NxR3BCV0R3NU0xSUlZYUJrRS1TNmhZVDJqVDFrN2xFdG03REJhSXllMF9FYnZMaHdtVjhOSTNIc1Jkc3JhZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rejeito da indústria de celulose é testado como fertilizante agrícola em MS - Correio do Estado</t>
+          <t>Mosaic prorroga paralisação da unidade de Catalão por falta de enxofre - Badiinho</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14/07/2026 13:00</t>
+          <t>14/07/2026 13:09</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOc25Gb0RtSmNLOHdUa2U1dlhxOW5FLW0xd1g0MTNJVmtSZTI0YmkxTFRPdEZCbElYTEF3TGlMeUlYYXVkd1J5cm1sNERoTTdhamhOanIwMVB4M1I5eTZkS1N3VG5JRkQwRlJkd3huSmtEY3ozR1gwLUVvUXZIWGFMbUk3cTRSSlhqRHdJYWxKbEowaUkxWlIxcDk3REZjZ2t1ZkZ5dmR3VW9nX3dSYVBETF9kQlFld00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBodUloejIyYmJxUW80NXhoTVUzaXZFMklTTjc1NnRHMzZDZGJOUkVtWUFXT25IWVFwd3o3RGdEeVItVi13ZDdLRk85ZEZHS0t2MFFFMk8xdDQ0VEJRZUc1elhPcHNJcjBzQlBtdUhvLVoxQdIBd0FVX3lxTE1vS1RSMUxsVldiUFVXLTZiTXQta0IyNDdwV3hqMmVFdzZFOVpPTHlxUWhHUHA2djdCRTNCd3YtQndEaTRVT1U1REowc21rMW1nVEc2cWdxcFlEZnR2UG9FTWMxdDlvT2pyaFhiTW9taVFMQmk3NkM4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cientistas criam “recifes elétricos” no fundo do mar com baixa voltagem, fazem minerais grudarem como calcário e testam uma solução capaz de reconstruir barreiras naturais contra erosão costeira antes que o oceano engula praias inteiras - CPG Click Petróleo e Gás</t>
+          <t>Rejeito da indústria de celulose é testado como fertilizante agrícola em MS - Correio do Estado</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14/07/2026 11:30</t>
+          <t>14/07/2026 13:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxPS21PQWhiUmIwcS1UR3h4dXdJMlBFZ29rR2hMdmxDWmhnWVFtVy1lZUtnTFB2SlBwcWI2dkxTNDFYN1UzdDJiNHVPbEVLaEcxbzhuUjlOUkgweURHU0ptQkstNGlmZkYyeG93bmMyWEltQWl6UHpUMFk3TTlDV0h3NmxBeDVwY0Vfd2FZeXh6RDl3RFQ2bWtrVFhFcTJTWlM0dWhpdTZHajZhME52MlZEYmVfR0ZWOW9taWRGeTQ1eVo1N2JLcGwxd1pQSWxpc1pobHVveFgtSFFpVXhreVNFLU9iZUo4Wk1ORlBrUHJZWFVFYXdTQmQ1b25NNFFTaE9nem1WWHVnYjFNenU4RnNtNUhoTHhWcUhXNnIzeEZGT2oyLTlDeFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOc25Gb0RtSmNLOHdUa2U1dlhxOW5FLW0xd1g0MTNJVmtSZTI0YmkxTFRPdEZCbElYTEF3TGlMeUlYYXVkd1J5cm1sNERoTTdhamhOanIwMVB4M1I5eTZkS1N3VG5JRkQwRlJkd3huSmtEY3ozR1gwLUVvUXZIWGFMbUk3cTRSSlhqRHdJYWxKbEowaUkxWlIxcDk3REZjZ2t1ZkZ5dmR3VW9nX3dSYVBETF9kQlFld00?oc=5</t>
         </is>
       </c>
     </row>
@@ -864,83 +864,83 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Emater retoma a compra conjunta de calcário para beneficiar pequenos produtores - Rádio Santa Cruz FM</t>
+          <t>Cientistas criam “recifes elétricos” no fundo do mar com baixa voltagem, fazem minerais grudarem como calcário e testam uma solução capaz de reconstruir barreiras naturais contra erosão costeira antes que o oceano engula praias inteiras - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14/07/2026 11:14</t>
+          <t>14/07/2026 11:30</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQeGk0dGtBdVozXzVycTE3Z2tTY0VTVkd1TllzZkdlRmxCSElhSHZqUkVlNi0tS0JHZWsta3pVMmRaMkJQbVJDS1dNMHp1b3Rucm9SQWdxWTZPd3JzczJla0ZwWEh5YVZtZ0tIVjRBbDk1RG9PZHZhNk52RWdfRm52Vy1TMWhYSW1feW5xT1VhMkV3anJwdThrUjJuTlRscHpjMmx2anhWbkNPWW9fN2NxQ2N2emc2bkVDeDFJYVRBMGtvRjBZY0VmRUpFM214SURKaUpaU0c0MjBOMldF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxPS21PQWhiUmIwcS1UR3h4dXdJMlBFZ29rR2hMdmxDWmhnWVFtVy1lZUtnTFB2SlBwcWI2dkxTNDFYN1UzdDJiNHVPbEVLaEcxbzhuUjlOUkgweURHU0ptQkstNGlmZkYyeG93bmMyWEltQWl6UHpUMFk3TTlDV0h3NmxBeDVwY0Vfd2FZeXh6RDl3RFQ2bWtrVFhFcTJTWlM0dWhpdTZHajZhME52MlZEYmVfR0ZWOW9taWRGeTQ1eVo1N2JLcGwxd1pQSWxpc1pobHVveFgtSFFpVXhreVNFLU9iZUo4Wk1ORlBrUHJZWFVFYXdTQmQ1b25NNFFTaE9nem1WWHVnYjFNenU4RnNtNUhoTHhWcUhXNnIzeEZGT2oyLTlDeFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Crise da Mosaic expõe limites da ação de Uberaba - Rede 98</t>
+          <t>Emater retoma a compra conjunta de calcário para beneficiar pequenos produtores - Rádio Santa Cruz FM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14/07/2026 10:55</t>
+          <t>14/07/2026 11:14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNUjNMck12c0xrY2hEOHExdVQ1YkVNNThoV3hPVWd1TEZZSm0xMms2U1ZGRF9fSEVfajhmT2JVdmtoOFRqSHZWem5hY1g5a3BwdmVWbHE5dFYtNHVuSE92VE10TnIzbXBhRjZqTWVWT2lUTHVPakhVbGJBWkhrN20xMDRqT1FaQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQeGk0dGtBdVozXzVycTE3Z2tTY0VTVkd1TllzZkdlRmxCSElhSHZqUkVlNi0tS0JHZWsta3pVMmRaMkJQbVJDS1dNMHp1b3Rucm9SQWdxWTZPd3JzczJla0ZwWEh5YVZtZ0tIVjRBbDk1RG9PZHZhNk52RWdfRm52Vy1TMWhYSW1feW5xT1VhMkV3anJwdThrUjJuTlRscHpjMmx2anhWbkNPWW9fN2NxQ2N2emc2bkVDeDFJYVRBMGtvRjBZY0VmRUpFM214SURKaUpaU0c0MjBOMldF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Terça-feira 14 de Julho de 2026 - RRMAIS</t>
+          <t>Crise da Mosaic expõe limites da ação de Uberaba - Rede 98</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14/07/2026 10:33</t>
+          <t>14/07/2026 10:55</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTF9kdlZZV0YtSUxvaVBrVnB0ckxnMlNFeXM1SmVkV1FDdjNOOV9MWDZ1TEtBem9PMFhpY3VGdFRnZEJUNjFpR05ZLTh4N1FabkxveDE3Y0xjM0dqNXc3cUJ1eXdJa2lNYjAxMlR5R3ozS3ROUDludmRhck5WbllrRUNzTW1mQUttTV9sOWlyTTFGZUJVRVRPYXp4cWRLaHNLaEhIZndCcEZOVlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNUjNMck12c0xrY2hEOHExdVQ1YkVNNThoV3hPVWd1TEZZSm0xMms2U1ZGRF9fSEVfajhmT2JVdmtoOFRqSHZWem5hY1g5a3BwdmVWbHE5dFYtNHVuSE92VE10TnIzbXBhRjZqTWVWT2lUTHVPakhVbGJBWkhrN20xMDRqT1FaQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Escassez de enxofre paralisa fábricas da Mosaic no Brasil - SpaceMoney</t>
+          <t>Cotações Agrícolas para esta Terça-feira 14 de Julho de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14/07/2026 10:03</t>
+          <t>14/07/2026 10:33</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE05YTRCY2tDcnJuMHVGRWpBSVcwNi1NdFVVemZuQjFQT3NZUlYyM0pWM2ZfeUNRWHVvRDZzWU1zREJVcEpoQlotb3V1cFJ0bGZMQW9UOS01OHdESVVnd01YeTAxNnFlTkdiMU1rX2p2X1oyX3oxVS1GWUNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTF9kdlZZV0YtSUxvaVBrVnB0ckxnMlNFeXM1SmVkV1FDdjNOOV9MWDZ1TEtBem9PMFhpY3VGdFRnZEJUNjFpR05ZLTh4N1FabkxveDE3Y0xjM0dqNXc3cUJ1eXdJa2lNYjAxMlR5R3ozS3ROUDludmRhck5WbllrRUNzTW1mQUttTV9sOWlyTTFGZUJVRVRPYXp4cWRLaHNLaEhIZndCcEZOVlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57c110a19a4bcd9ed6b34bdcfc7c0d&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57d63d5b7148ad97fe9681cf91c9e6&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57c10fff6843e0ab0835a200afe618&amp;url=https%3a%2f%2fclickpetroleoegas.com.br%2finteligencia-artificial-decifra-as-regras-de-um-jogo-de-tabuleiro-romano-perdido-encontrado-em-uma-pedra-de-20-centimetros-na-holanda-flpc96%2f&amp;c=951759223804362979&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57d63c8a0d4aeab3f8e5eb0e6dccec&amp;url=https%3a%2f%2fclickpetroleoegas.com.br%2finteligencia-artificial-decifra-as-regras-de-um-jogo-de-tabuleiro-romano-perdido-encontrado-em-uma-pedra-de-20-centimetros-na-holanda-flpc96%2f&amp;c=951759223804362979&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57c110a19a4bcd9ed6b34bdcfc7c0d&amp;url=https%3a%2f%2fwww.em.com.br%2femfoco%2f2026%2f07%2f09%2fpare-de-jogar-as-cinzas-no-lixo-saiba-como-usar-esse-po-como-um-reforco-natural-para-suas-plantas-e-canteiros%2f&amp;c=3336525689791670118&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57d63d5b7148ad97fe9681cf91c9e6&amp;url=https%3a%2f%2fwww.em.com.br%2femfoco%2f2026%2f07%2f09%2fpare-de-jogar-as-cinzas-no-lixo-saiba-como-usar-esse-po-como-um-reforco-natural-para-suas-plantas-e-canteiros%2f&amp;c=3336525689791670118&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57c11558d74e288d08f48bdd7dc77e&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57d64236f649b8abc99445abcf0349&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -3130,17 +3130,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - MINUTO MT</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>07/07/2026 06:08</t>
+          <t>06/07/2026 22:32</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNNm9yRHRTbXM3bWkzai03Qjh6eUh5bm5XSmcyZFA0Ymx1Zl82dThtOEFaUF9ieDRLbHNCT0VtbmJ2S2UyTDZLb2pFZllibWstOWM0VHZHR3V3eFRiVU5vdWgxMUoyaEQ4NDVwd2oteDBGdWNfMGVpUnRleFYzV3BRcnZ5R0xHbzNJV2pqRmxlWXgwZnB1UFBKd2F2NkwwV0p3QUw1YWZKSDFBTUQ4djJZNkVBMWp2NE9JdUEtMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOd0ZxY1VnNE5vV1ZDUW41MHU1MGpadk82Y0lUaU1LQk5xdkM0SmJESmpRWWpmM0VPcC1SdWJaNS1DcFVTYzk5UVF5dm5KdHhqSDNQWFZhUUt2RVExLWxJUUdaQUpId3JncThlMHZKWE12Z3VPRHFzN2J1OUJnWG5JUlBfaEZiUWVOZjZwMTR1ZXBWZzdMTkw2MWxQMXBic0xEeE1DTkJsbHdHLTZESlRweERMSXd5VDBnZU9tLWdDNnFObjU3NmVCUTlsbVFYNmtyWWJQWlJ3?oc=5</t>
         </is>
       </c>
     </row>
@@ -3152,39 +3152,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - RADAR DIGITAL BRASÍLIA</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - BRASIL NOTÍCIA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>06/07/2026 22:32</t>
+          <t>06/07/2026 21:31</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOd0ZxY1VnNE5vV1ZDUW41MHU1MGpadk82Y0lUaU1LQk5xdkM0SmJESmpRWWpmM0VPcC1SdWJaNS1DcFVTYzk5UVF5dm5KdHhqSDNQWFZhUUt2RVExLWxJUUdaQUpId3JncThlMHZKWE12Z3VPRHFzN2J1OUJnWG5JUlBfaEZiUWVOZjZwMTR1ZXBWZzdMTkw2MWxQMXBic0xEeE1DTkJsbHdHLTZESlRweERMSXd5VDBnZU9tLWdDNnFObjU3NmVCUTlsbVFYNmtyWWJQWlJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOWDN6N25ybWpZZE9iX3JvejZSc29pWXVXczdzazFkNzlqMDZaTWVtcmJsQ1BLMTc0cmlQQWxsM3J4bURTMWJlOExWWDJxUkd5U1A4cUxTSGdWSzVQSG5VWkFIOHYxa2VOaXJBcVp6OHp6SmNWdldaaWhwajZ2Nk1mVnBCMm91OS10VEstR2Y4SFo4aDhvck1yNWV5Q08tMEFETmxrMEptMHVDQ1VWVFhySklFaUJ2NXNtM3dsTURCbEJxTjJRRlViNGd1c1U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - BRASIL NOTÍCIA</t>
+          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>06/07/2026 21:31</t>
+          <t>06/07/2026 10:47</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOWDN6N25ybWpZZE9iX3JvejZSc29pWXVXczdzazFkNzlqMDZaTWVtcmJsQ1BLMTc0cmlQQWxsM3J4bURTMWJlOExWWDJxUkd5U1A4cUxTSGdWSzVQSG5VWkFIOHYxa2VOaXJBcVp6OHp6SmNWdldaaWhwajZ2Nk1mVnBCMm91OS10VEstR2Y4SFo4aDhvck1yNWV5Q08tMEFETmxrMEptMHVDQ1VWVFhySklFaUJ2NXNtM3dsTURCbEJxTjJRRlViNGd1c1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
         </is>
       </c>
     </row>
@@ -3196,61 +3196,61 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
+          <t>Adolescentes de Enxofre - Minecraft</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>06/07/2026 10:47</t>
+          <t>06/07/2026 06:03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Adolescentes de Enxofre - Minecraft</t>
+          <t>Cientistas desenvolvem um novo método de produção de cimento que substitui o calcário pelo basalto para reduzir drasticamente as emissões de CO2 - Estado de Minas</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>06/07/2026 06:03</t>
+          <t>05/07/2026 16:45</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxQRmwtWFVDNTJESDhkNEZGQVhzd0tqT3lYZ0s4ai12bndGV0hRaEwzb1RQc3Z1M21nUWk5bWJvX1BfdmhzbkhfRE9VVjVRNGlvQXpKbVBCM1Vka1F2VWZ2V3pBUU1tbEk5bkZ0WFVHNlc5SVJwYzhLZDQxM0dmOFpSdUhRb2JaWC1nQlNQWlY3UFQyM0k3dVE1M2tqRnc2M3NEb0wyMEVQWU5SeTM2czlQWGR6VVZpRExLNlRsX0lIbFhZeS1wY2h3OHJrVHdPLUFxcVphY19qbzktcWJuaXAyWVFZWnJFa3hsN0RsZ0xkWVFKVFI3aWpBelJUbVNuNlF2QmszRVRHZVc4TFJUcHZFUElib2Zsdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cientistas desenvolvem um novo método de produção de cimento que substitui o calcário pelo basalto para reduzir drasticamente as emissões de CO2 - Estado de Minas</t>
+          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>05/07/2026 16:45</t>
+          <t>04/07/2026 04:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxQRmwtWFVDNTJESDhkNEZGQVhzd0tqT3lYZ0s4ai12bndGV0hRaEwzb1RQc3Z1M21nUWk5bWJvX1BfdmhzbkhfRE9VVjVRNGlvQXpKbVBCM1Vka1F2VWZ2V3pBUU1tbEk5bkZ0WFVHNlc5SVJwYzhLZDQxM0dmOFpSdUhRb2JaWC1nQlNQWlY3UFQyM0k3dVE1M2tqRnc2M3NEb0wyMEVQWU5SeTM2czlQWGR6VVZpRExLNlRsX0lIbFhZeS1wY2h3OHJrVHdPLUFxcVphY19qbzktcWJuaXAyWVFZWnJFa3hsN0RsZ0xkWVFKVFI3aWpBelJUbVNuNlF2QmszRVRHZVc4TFJUcHZFUElib2Zsdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3262,61 +3262,61 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
+          <t>Rússia prorroga proibição das exportações de enxofre - GlobalFert</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>04/07/2026 04:00</t>
+          <t>03/07/2026 15:37</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPSDYtNVczb3hScWJXUzkxcVZLMzV1dTRic3hNZ0V5RDJrM3dQalVBaHN3azdoSG5rM2laeVMzUTlVV1poeDl6N2ZCd1pETUsyVktHOHlFcjJsNmFwMXVqSFgza2hMOHZhM3hYbEMweTZYUXhRVkRDVG1jRGV4UngyY2luRXVnRGM1eDlncHhPenNsYUJUX1Q0dmVNNlI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Rússia prorroga proibição das exportações de enxofre - GlobalFert</t>
+          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>03/07/2026 15:37</t>
+          <t>03/07/2026 10:20</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPSDYtNVczb3hScWJXUzkxcVZLMzV1dTRic3hNZ0V5RDJrM3dQalVBaHN3azdoSG5rM2laeVMzUTlVV1poeDl6N2ZCd1pETUsyVktHOHlFcjJsNmFwMXVqSFgza2hMOHZhM3hYbEMweTZYUXhRVkRDVG1jRGV4UngyY2luRXVnRGM1eDlncHhPenNsYUJUX1Q0dmVNNlI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
+          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>03/07/2026 10:20</t>
+          <t>03/07/2026 04:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Alta do enxofre provoca crise na produção de fertilizantes em Minas Gerais - G1</t>
+          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQYnY2QmNpaXc4aHRDMDFLUmxTNzhRME9pNWhac1psdWtNMXMwSHJsN3oxeUJqNXZtOHVNWUNaQnNjOUJaLWRhbF91M05Sa3VIM3dsTjM2X2VLSS03ZTlPWFF4T2xLMUdzTlZLdk9tblk1WHRZUWtGT3BmUktDODYzMU1VUTEtbVc3N0VTelc4ZUROZDBkX2xZeFlma01wMjV3WHBISVdRQ0lwYmFseFA5d1ZnNXdFMVpRUk9zeHJpbEUzQ1Y0MUdpbXdiTnlSZ3o2ekJfbnZOYlNJU29nU2FaclhFR1ZqUmFx0gH3AUFVX3lxTE1sQjBVb2UzRGxTdGVBTXd6Y0lwX0pBUmYtOXIxYmU3b2EtLUtLYklfS3FHcHp3VklkU0xtdjlwMHAxYzJtNmcwNHkzOUd6TFBZZVkxa1VWVmJBRFZKLXFSLUpxQnc5al8ySjRJQkNFUnpWRXlmbTctMlp4SXd4OUJSai00ZGxocEd6dUVZbE8zZ0JXaDJ2SEllampRdER2aF9IRlBoMDZ4SHZ4UXhqT1RVYVV5ekFOSTVyUkgxQ0RJNzQ2N2ZfQThQR182WUVGQ2ZVNHBKOUtuVktNNG5LTVBnX2tUbGNHNzhOQkpuMEhjR2RBTHJYVkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
+          <t>Alta do enxofre provoca crise na produção de fertilizantes em Minas Gerais - G1</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3360,117 +3360,117 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQYnY2QmNpaXc4aHRDMDFLUmxTNzhRME9pNWhac1psdWtNMXMwSHJsN3oxeUJqNXZtOHVNWUNaQnNjOUJaLWRhbF91M05Sa3VIM3dsTjM2X2VLSS03ZTlPWFF4T2xLMUdzTlZLdk9tblk1WHRZUWtGT3BmUktDODYzMU1VUTEtbVc3N0VTelc4ZUROZDBkX2xZeFlma01wMjV3WHBISVdRQ0lwYmFseFA5d1ZnNXdFMVpRUk9zeHJpbEUzQ1Y0MUdpbXdiTnlSZ3o2ekJfbnZOYlNJU29nU2FaclhFR1ZqUmFx0gH3AUFVX3lxTE1sQjBVb2UzRGxTdGVBTXd6Y0lwX0pBUmYtOXIxYmU3b2EtLUtLYklfS3FHcHp3VklkU0xtdjlwMHAxYzJtNmcwNHkzOUd6TFBZZVkxa1VWVmJBRFZKLXFSLUpxQnc5al8ySjRJQkNFUnpWRXlmbTctMlp4SXd4OUJSai00ZGxocEd6dUVZbE8zZ0JXaDJ2SEllampRdER2aF9IRlBoMDZ4SHZ4UXhqT1RVYVV5ekFOSTVyUkgxQ0RJNzQ2N2ZfQThQR182WUVGQ2ZVNHBKOUtuVktNNG5LTVBnX2tUbGNHNzhOQkpuMEhjR2RBTHJYVkk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
+          <t>Pampa Energía avalia construir planta de ureia para atender o Brasil - Revista O Empreiteiro</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>03/07/2026 04:00</t>
+          <t>02/07/2026 17:01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1xQS16X1g0QnF4SGdXWE05VHVtSGxieGNYYzBFbmh0M2U3S3BKbC12cmFMekR1SlRVd1U1VEh5aS1SazFwQTI1TjdEYWhOYXFTRm5nQldUTGdUaFpHQzJseDNYN1pIZGJJVEdz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Pampa Energía avalia construir planta de ureia para atender o Brasil - Revista O Empreiteiro</t>
+          <t>Here’s Why Shark Tank Loved First Saturday Lime Insect Repellent</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>02/07/2026 17:01</t>
+          <t>02/07/2026 05:32</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1xQS16X1g0QnF4SGdXWE05VHVtSGxieGNYYzBFbmh0M2U3S3BKbC12cmFMekR1SlRVd1U1VEh5aS1SazFwQTI1TjdEYWhOYXFTRm5nQldUTGdUaFpHQzJseDNYN1pIZGJJVEdz?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57d63e527b4fdb8e988d262a223137&amp;url=https%3a%2f%2fsg.news.yahoo.com%2fwhy-shark-tank-loved-first-153245354.html&amp;c=11954638987694979310&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Here’s Why Shark Tank Loved First Saturday Lime Insect Repellent</t>
+          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>02/07/2026 05:32</t>
+          <t>02/07/2026 04:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57c11151b3467da82865eeb19af6e4&amp;url=https%3a%2f%2fsg.news.yahoo.com%2fwhy-shark-tank-loved-first-153245354.html&amp;c=11954638987694979310&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUHSAcYBQVVfeXFMTmU1U0hwa0N3YmVjNzRrNWU2MTNfalNtQkNTeVQtTmVWX3k5R2hQU2VnRDA3NmZ2X2RKbVBTd0F2QnJSS0FGRG1tRGx5N0Q0RzVvdlpOb3FrYkI3WmUzdGxWNjdVY0Y1bmFfdmJidF9DeV84ZlFpX1hnSWcxZk9mREwyb1I0cjloeE9vZ2ZQZ3hvMlFsSUllbk5wLUR2cDF1TU12bW01bVFfQlY1UWhzQjJpc194S1dZeENMRXpCMTZxcm1YN0pR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil - Valor Econômico</t>
+          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>02/07/2026 04:00</t>
+          <t>01/07/2026 10:48</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUHSAcYBQVVfeXFMTmU1U0hwa0N3YmVjNzRrNWU2MTNfalNtQkNTeVQtTmVWX3k5R2hQU2VnRDA3NmZ2X2RKbVBTd0F2QnJSS0FGRG1tRGx5N0Q0RzVvdlpOb3FrYkI3WmUzdGxWNjdVY0Y1bmFfdmJidF9DeV84ZlFpX1hnSWcxZk9mREwyb1I0cjloeE9vZ2ZQZ3hvMlFsSUllbk5wLUR2cDF1TU12bW01bVFfQlY1UWhzQjJpc194S1dZeENMRXpCMTZxcm1YN0pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
+          <t>Destaques da Edição 363 - JornalCana</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>01/07/2026 10:48</t>
+          <t>01/07/2026 07:37</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOZS15WnBLcU9obFdvQ3RBQmU1OURPZlhCenRTS08xNmdmTm5CUUVpd0ZVZHJJeDBTWXlGdVFuLXVXRjhxV0VGNG5IcjlEdUluR3JjdmNlczdWT3NaeENEOHk3dGw2X0FnOHpOcGhxWlNERkhQMDVWSm5hMFlpeVNLMEI2ZGVmT3FBSmozM3JqUVNRa19McFdKZ3JmWGtNeHFHZWdJTw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3482,17 +3482,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Destaques da Edição 363 - JornalCana</t>
+          <t>Prefeitura garante calcário de graça para fortalecer a agricultura nos bairros de Navegantes - Jornal nos Bairros</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>01/07/2026 07:37</t>
+          <t>30/06/2026 18:22</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOZS15WnBLcU9obFdvQ3RBQmU1OURPZlhCenRTS08xNmdmTm5CUUVpd0ZVZHJJeDBTWXlGdVFuLXVXRjhxV0VGNG5IcjlEdUluR3JjdmNlczdWT3NaeENEOHk3dGw2X0FnOHpOcGhxWlNERkhQMDVWSm5hMFlpeVNLMEI2ZGVmT3FBSmozM3JqUVNRa19McFdKZ3JmWGtNeHFHZWdJTw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNWVhCT0tJZHhMbEFaclNMWDVlMjdZQUozR3daYUszUUdoclltNzhBU1hXby16ZnlKVWV2Z01aaUxqVEhkbFNfTmowUEZZdVJSVUluSVM4VGIteTBuV0lpM1V2c2UxR3REZ1NmOXZiMk9QZEhxTXhwd1NRWjFCRFVzNUVicktKWWFBS3F6RGY3cFF4OVpJQnpXVnA1TFJsa0dPSUJ0ZEU4UFdqbi0xWlZPZTR0Q0w1ZGdFQ0hrUnVEUVFiemd6NEthUnUwV2pUbExla2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -3504,17 +3504,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Prefeitura garante calcário de graça para fortalecer a agricultura nos bairros de Navegantes - Jornal nos Bairros</t>
+          <t>Cantor Amado Batista é alvo de processo por dívida de R$ 9 mil em Goiás - G1</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>30/06/2026 18:22</t>
+          <t>30/06/2026 04:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNWVhCT0tJZHhMbEFaclNMWDVlMjdZQUozR3daYUszUUdoclltNzhBU1hXby16ZnlKVWV2Z01aaUxqVEhkbFNfTmowUEZZdVJSVUluSVM4VGIteTBuV0lpM1V2c2UxR3REZ1NmOXZiMk9QZEhxTXhwd1NRWjFCRFVzNUVicktKWWFBS3F6RGY3cFF4OVpJQnpXVnA1TFJsa0dPSUJ0ZEU4UFdqbi0xWlZPZTR0Q0w1ZGdFQ0hrUnVEUVFiemd6NEthUnUwV2pUbExla2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNb3o1UmZSV2FwVFpzU2ZTZGJmeDBwSWxkekgxaHNZVXdyT2pIZVJiTC1FczZ0NGFFNDRMOEg5TDRhSk9HbnJDNUFEaEE3cE5uZWc2RXNzMzRBRVFOZ2VCMzhUQWFiQTNKTXBVelNnNGZVSHBPRXlzNS1MYUhyN08wZU15RkJKR3g1cEw0bkhPaGp2Rk1lWjBUTmpOMFg1SzF1Z0Jwd1BNazJIUUNCX3J5MTFTNFBDXzBhWTc3NGJwbUI5VFXSAdIBQVVfeXFMTzQxTjNHRjctYkp3S1NJS3FaaTc3TTJ4T2hNWnpiNVd1cDZtYWVrVl9QcFhrQVZTZWdEOU5xOU9ldjl5SnM1d0o0ekxNakVzYjRfNkhyb0F4eVFMSk1qUk0zWEVuenNVUEx5VHZja0JrZGppMWdsUGtBWkVXdUs3WHMtV3FJT2otQ1pyX2NGa1g5SzE2b2pGT1BTR2JkSTdVVlp0NEhrel9hZUxSLUpWUUFPV3BxMTRsV3hveEU2TnJIMC1EaThONGt6N1Q5elNHenZ3?oc=5</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3543,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Cantor Amado Batista é alvo de processo por dívida de R$ 9 mil em Goiás - G1</t>
+          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3558,29 +3558,29 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNb3o1UmZSV2FwVFpzU2ZTZGJmeDBwSWxkekgxaHNZVXdyT2pIZVJiTC1FczZ0NGFFNDRMOEg5TDRhSk9HbnJDNUFEaEE3cE5uZWc2RXNzMzRBRVFOZ2VCMzhUQWFiQTNKTXBVelNnNGZVSHBPRXlzNS1MYUhyN08wZU15RkJKR3g1cEw0bkhPaGp2Rk1lWjBUTmpOMFg1SzF1Z0Jwd1BNazJIUUNCX3J5MTFTNFBDXzBhWTc3NGJwbUI5VFXSAdIBQVVfeXFMTzQxTjNHRjctYkp3S1NJS3FaaTc3TTJ4T2hNWnpiNVd1cDZtYWVrVl9QcFhrQVZTZWdEOU5xOU9ldjl5SnM1d0o0ekxNakVzYjRfNkhyb0F4eVFMSk1qUk0zWEVuenNVUEx5VHZja0JrZGppMWdsUGtBWkVXdUs3WHMtV3FJT2otQ1pyX2NGa1g5SzE2b2pGT1BTR2JkSTdVVlp0NEhrel9hZUxSLUpWUUFPV3BxMTRsV3hveEU2TnJIMC1EaThONGt6N1Q5elNHenZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
+          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>30/06/2026 04:00</t>
+          <t>29/06/2026 08:22</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
         </is>
       </c>
     </row>
@@ -3609,22 +3609,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Ureia, MAP e potássio registram queda no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>29/06/2026 08:22</t>
+          <t>29/06/2026 04:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQckZkR0twcU1KM1hzRlBoYnlKaEVXbERoOEJfSk5zLVJHSlFXc2pVS0hqRlQ0djV0b2o5NDY0azg3REJLbnBlaVJ2VWZ6Y2lzaVF4STlrWlh4TDcteXBGN29xWDdTc0hmU1pROF9UZ2d4UlR0bGFtNjd6UzZqakxCeGlHTEZRTUVReHllcG5NOFV4OFRXZ05YZTIySlg?oc=5</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
+          <t>Segundo o WSJ, a Martin Marietta e a Lhoist North America vão se fundir em um negócio de US$ 13,5 bilhões - TradingView</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE85QWpvMXdqUXlsdVlyQ1pRXzUxUWZIY24yVlhHOXpONU5hQjdGM3ZNU1QwMGxBWWxiRGN2UVA2aGFBNHJ3bVQyYVR0T1JzNjI3SWltcmQ1c3BpY25CMC1Pa3BhaXRCTk9QMzFuSzUyNWFZRnNJVFFyYQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Segundo o WSJ, a Martin Marietta e a Lhoist North America vão se fundir em um negócio de US$ 13,5 bilhões - TradingView</t>
+          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3668,19 +3668,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE85QWpvMXdqUXlsdVlyQ1pRXzUxUWZIY24yVlhHOXpONU5hQjdGM3ZNU1QwMGxBWWxiRGN2UVA2aGFBNHJ3bVQyYVR0T1JzNjI3SWltcmQ1c3BpY25CMC1Pa3BhaXRCTk9QMzFuSzUyNWFZRnNJVFFyYQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
+          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3690,85 +3690,85 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ureia, MAP e potássio registram queda no Brasil - Agrolink</t>
+          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>29/06/2026 04:00</t>
+          <t>29/06/2026 00:13</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQckZkR0twcU1KM1hzRlBoYnlKaEVXbERoOEJfSk5zLVJHSlFXc2pVS0hqRlQ0djV0b2o5NDY0azg3REJLbnBlaVJ2VWZ6Y2lzaVF4STlrWlh4TDcteXBGN29xWDdTc0hmU1pROF9UZ2d4UlR0bGFtNjd6UzZqakxCeGlHTEZRTUVReHllcG5NOFV4OFRXZ05YZTIySlg?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57d63ed2dd43c788633e50090e5921&amp;url=https%3a%2f%2fvalor.globo.com%2fempresas%2fnoticia%2f2026%2f06%2f29%2fcom-foco-em-data-centers-martin-marietta-acerta-compra-de-fornecedora-de-minerais-por-us-135-bi.ghtml&amp;c=16419230671194560723&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi</t>
+          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>29/06/2026 00:13</t>
+          <t>26/06/2026 13:47</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57c111b8bb4a3d8f23d6557e056da6&amp;url=https%3a%2f%2fvalor.globo.com%2fempresas%2fnoticia%2f2026%2f06%2f29%2fcom-foco-em-data-centers-martin-marietta-acerta-compra-de-fornecedora-de-minerais-por-us-135-bi.ghtml&amp;c=16419230671194560723&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
+          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>26/06/2026 13:47</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
         </is>
       </c>
     </row>
@@ -3807,22 +3807,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
+          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>25/06/2026 04:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3851,44 +3851,44 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
+          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - Portal Arauto</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>25/06/2026 04:00</t>
+          <t>24/06/2026 15:03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - Portal Arauto</t>
+          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>24/06/2026 15:03</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
+          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3954,73 +3954,73 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
+          <t>Secretaria de Agricultura mantém transporte de calcário para fortalecer a produção rural em Sentinela do Sul - Portal ClicR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>23/06/2026 15:47</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPSklWeDZHUDl4T0FyeFZqY3RPdkptcGdkaG04MjB6SVA5QkYxcWxHQm9qS0ZzSTBGbGtsTXVHbFRRUFVrd194V1JDQVdpdVNJXzVCRXFuQ1JXU2ZydUltajNoRE52QUZWNVYxZmJBaXdLM29QeVdnUTFiejRieEhwOGNfSmtNdUFnSVMwYlZxeGJlX3pJY2VnNW5jbkNmMGcyYjVuN0RBbGl1dWhDY0Y5dzhkMF9wWW1pZHN2SVVTZFZZaENCVmdtWmtB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Secretaria de Agricultura mantém transporte de calcário para fortalecer a produção rural em Sentinela do Sul - Portal ClicR</t>
+          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>23/06/2026 15:47</t>
+          <t>23/06/2026 07:31</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPSklWeDZHUDl4T0FyeFZqY3RPdkptcGdkaG04MjB6SVA5QkYxcWxHQm9qS0ZzSTBGbGtsTXVHbFRRUFVrd194V1JDQVdpdVNJXzVCRXFuQ1JXU2ZydUltajNoRE52QUZWNVYxZmJBaXdLM29QeVdnUTFiejRieEhwOGNfSmtNdUFnSVMwYlZxeGJlX3pJY2VnNW5jbkNmMGcyYjVuN0RBbGl1dWhDY0Y5dzhkMF9wWW1pZHN2SVVTZFZZaENCVmdtWmtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
+          <t>Expectativa pelo PL da renegociação de dívidas emperra o varejo agrícola, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>23/06/2026 07:31</t>
+          <t>23/06/2026 04:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNN3A0WWpXR1M2UEhQQlhXUk5GbGFhMXlFVzZtczVnSW9wYzMxeFROWEpUU2tsb2xmSTQyUFdDTS1oa1BoU01GNy14OElqaGlEVXhNSTRkczhTSmdiUEQ1TGdXMUQtMHVFWHhPa2p3cHluYnhpUWhMNHRrcXl5SFI1dGtyN0hKeFd5b3dVcHNLc2cyMkRycFRGWnJLT2NGZWlLRXNwY0N3X0FCWWJseE9xcEF4a2xncHFUb3lSb2tMUFJMWk5JOXh1Q0tQSG13MEhfVlNBb0h4OXYtWEpQNjFrS3JYQmd4aW1M?oc=5</t>
         </is>
       </c>
     </row>
@@ -4049,22 +4049,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Expectativa pelo PL da renegociação de dívidas emperra o varejo agrícola, diz Mosaic - The AgriBiz</t>
+          <t>Visconde conquista a Copa do Calcário 2026 - GF Esporte</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>23/06/2026 04:00</t>
+          <t>22/06/2026 19:10</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNN3A0WWpXR1M2UEhQQlhXUk5GbGFhMXlFVzZtczVnSW9wYzMxeFROWEpUU2tsb2xmSTQyUFdDTS1oa1BoU01GNy14OElqaGlEVXhNSTRkczhTSmdiUEQ1TGdXMUQtMHVFWHhPa2p3cHluYnhpUWhMNHRrcXl5SFI1dGtyN0hKeFd5b3dVcHNLc2cyMkRycFRGWnJLT2NGZWlLRXNwY0N3X0FCWWJseE9xcEF4a2xncHFUb3lSb2tMUFJMWk5JOXh1Q0tQSG13MEhfVlNBb0h4OXYtWEpQNjFrS3JYQmd4aW1M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTUpHSldydzZmQ25UUEFKS29naGtpa3pOMzg0WXBHSnhuZ2ZyRlRCbF90R0hrb0ZCMVB3aWNlX21ZLUxPT0ZfRC16SUJ4cExSNjFrMk1jRXZ4c2lmZFBqaEx2cC1YSzhxYTNmZzlPVTNWZXFtMGZKZmFEU2Y1RXFxMHZueW03VVRaR0p5dEU4SFhxNHk1NG5NTkdYTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4076,17 +4076,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Visconde conquista a Copa do Calcário 2026 - GF Esporte</t>
+          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - Portal Arauto</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>22/06/2026 19:10</t>
+          <t>22/06/2026 08:41</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTUpHSldydzZmQ25UUEFKS29naGtpa3pOMzg0WXBHSnhuZ2ZyRlRCbF90R0hrb0ZCMVB3aWNlX21ZLUxPT0ZfRC16SUJ4cExSNjFrMk1jRXZ4c2lmZFBqaEx2cC1YSzhxYTNmZzlPVTNWZXFtMGZKZmFEU2Y1RXFxMHZueW03VVRaR0p5dEU4SFhxNHk1NG5NTkdYTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4098,29 +4098,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - Portal Arauto</t>
+          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>22/06/2026 08:41</t>
+          <t>22/06/2026 04:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
+          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
+          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4186,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
+          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>22/06/2026 04:00</t>
+          <t>21/06/2026 04:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4225,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
+          <t>Mosaico de antigo 'deus do rio' é encontrado na Turquia - Globo</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4240,29 +4240,29 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOLTdXYW1GZW4ybGRZM2Q1OU5WWFNYNEVENXNhVDZBTG9LanM0YnM2NGlZQnAxbThZeWs0a0lOdVgyVkRfN3JQaEI4RHY1Y3BLa1lobmFuN1VvTGg5SUFiT2VvMkNxMHJDdjdyRTJGWm1HZWxpRlZNajdmQmg0WERVTGlyeW80U2g0WDctOGY0X0Vsblg5RVVLdmtFanU2bkVaaWNEQjhCdE1MWlg1cmpOZ05RQXZMcXPSAcYBQVVfeXFMUGFBczRwMXpFN0tOdm1GWWlid0hBYjV4bEFQbWRMeUEzS0hFTzZiNTdvVUI2QW5SaGg1OUY2cXV2Q1ltellaSEk1V3BHUHBzeTMwSmZJZTUxZ2FEN1UxNTVQWjY1eVBaOHFkblBqTWc3VDJWdXpzRGo0QUI1TVdYYk9MdE1uSGwxSHFnQktpX2VZYzlwT1FWT2Jub1U5dWdHWHlWRlhDZHU0ck51SmZKVjBqREhaa0JVcnFsN2tMN0dlLU0welJ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mosaico de antigo 'deus do rio' é encontrado na Turquia - Globo</t>
+          <t>Sistema FAEP lamenta decisão da ANTT que impede o cultivo agrícola na faixa de domínio - Minuto Rural</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>21/06/2026 04:00</t>
+          <t>20/06/2026 04:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOLTdXYW1GZW4ybGRZM2Q1OU5WWFNYNEVENXNhVDZBTG9LanM0YnM2NGlZQnAxbThZeWs0a0lOdVgyVkRfN3JQaEI4RHY1Y3BLa1lobmFuN1VvTGg5SUFiT2VvMkNxMHJDdjdyRTJGWm1HZWxpRlZNajdmQmg0WERVTGlyeW80U2g0WDctOGY0X0Vsblg5RVVLdmtFanU2bkVaaWNEQjhCdE1MWlg1cmpOZ05RQXZMcXPSAcYBQVVfeXFMUGFBczRwMXpFN0tOdm1GWWlid0hBYjV4bEFQbWRMeUEzS0hFTzZiNTdvVUI2QW5SaGg1OUY2cXV2Q1ltellaSEk1V3BHUHBzeTMwSmZJZTUxZ2FEN1UxNTVQWjY1eVBaOHFkblBqTWc3VDJWdXpzRGo0QUI1TVdYYk9MdE1uSGwxSHFnQktpX2VZYzlwT1FWT2Jub1U5dWdHWHlWRlhDZHU0ck51SmZKVjBqREhaa0JVcnFsN2tMN0dlLU0welJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPaHp3NnFKcU5hLURNY2RlTW1XWHc4WnFkWkZQRlVxQ0RfaEpTdGlaMlFIbTF4M0pNMEs1dnpZOGNjdUFuckRlMUlUV1BmN1puMkFkMHZ0SEVQbm1kMVRKLXVLYWs1dHJtTDhBN3ptbU40NjB1NGxDcU1xUTV4bTlLc1g4T19CNDVrQVkxd0lQQmZiTmluRGhrN1hWbGc4bm1leHNod0NQdld3T29tWmc2MmwyZzBoN19IT0hZdU53VzVrY0J1N2phOG8xMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -4291,22 +4291,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Sistema FAEP lamenta decisão da ANTT que impede o cultivo agrícola na faixa de domínio - Minuto Rural</t>
+          <t>ProSolos: Capão Bonito do Sul distribui calcário para 25 produtores rurais - Tua Rádio</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>20/06/2026 04:00</t>
+          <t>19/06/2026 04:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPaHp3NnFKcU5hLURNY2RlTW1XWHc4WnFkWkZQRlVxQ0RfaEpTdGlaMlFIbTF4M0pNMEs1dnpZOGNjdUFuckRlMUlUV1BmN1puMkFkMHZ0SEVQbm1kMVRKLXVLYWs1dHJtTDhBN3ptbU40NjB1NGxDcU1xUTV4bTlLc1g4T19CNDVrQVkxd0lQQmZiTmluRGhrN1hWbGc4bm1leHNod0NQdld3T29tWmc2MmwyZzBoN19IT0hZdU53VzVrY0J1N2phOG8xMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPczJPU19lVkVaMG8wVGZGVEpQbjQyb3pYbmY2VGhUNW1GVW9lazlCaEtONGlDR3ZpSHFxVWMwaGoyNXhzcTRBLXREWkVKZUQtNF9TRXFWY1pnYXIwS3RfNVBkaTJIbFh5blVtaEZuRWhDRzU3dW5ETDZ5RXBEZU5KZzR5NW9OMTluT0dHaGU5OC0taUI5Y2FzXzZLdlZkb2tjdnMwS2ZXTXZDMnBJT05xTEFXNFl0VXBpRTlFWVA5ZFFja2xCdGpPSExFNDJsdGVjbUVaYnNhYmFsSGZkbVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -4335,22 +4335,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ProSolos: Capão Bonito do Sul distribui calcário para 25 produtores rurais - Tua Rádio</t>
+          <t>Fertilizantes têm ajuste com cautela no mercado - Agrolink</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>19/06/2026 04:00</t>
+          <t>18/06/2026 04:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPczJPU19lVkVaMG8wVGZGVEpQbjQyb3pYbmY2VGhUNW1GVW9lazlCaEtONGlDR3ZpSHFxVWMwaGoyNXhzcTRBLXREWkVKZUQtNF9TRXFWY1pnYXIwS3RfNVBkaTJIbFh5blVtaEZuRWhDRzU3dW5ETDZ5RXBEZU5KZzR5NW9OMTluT0dHaGU5OC0taUI5Y2FzXzZLdlZkb2tjdnMwS2ZXTXZDMnBJT05xTEFXNFl0VXBpRTlFWVA5ZFFja2xCdGpPSExFNDJsdGVjbUVaYnNhYmFsSGZkbVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPRjZ2d3B2MFRIMEw3SHk2YXBObFNCenQ5cVFDNXNUbTdldnNEaXBQYkRpeUl1X2xXTktsQV9ZMjdhUDF6SEFZRDRwYVdXSG16dl9jRUp4OFRPbVRRZF9OZTJ2UVYyVjMwWFJOZ3BzYV9DMHlUc092ckJGM2dCNkdmUEdFaGJxS1FYY0N4eDI3eE1OMGd5MDZ6WWZZcG4?oc=5</t>
         </is>
       </c>
     </row>
@@ -4379,34 +4379,34 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Fertilizantes têm ajuste com cautela no mercado - Agrolink</t>
+          <t>Freedom Broker eleva recomendação da Mosaic com melhora nos custos de enxofre - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>18/06/2026 04:00</t>
+          <t>17/06/2026 04:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPRjZ2d3B2MFRIMEw3SHk2YXBObFNCenQ5cVFDNXNUbTdldnNEaXBQYkRpeUl1X2xXTktsQV9ZMjdhUDF6SEFZRDRwYVdXSG16dl9jRUp4OFRPbVRRZF9OZTJ2UVYyVjMwWFJOZ3BzYV9DMHlUc092ckJGM2dCNkdmUEdFaGJxS1FYY0N4eDI3eE1OMGd5MDZ6WWZZcG4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYkJCZXRNYmpPWklEMVVnLXVSYlhzYWE3cHc1UXZDcVZWbUlyb1B4bm53QjR4UG5NNm1PMEtTUm1ZUXctb2g1UEx2bXpiSEUyajB4ZHdOb21kZFVPZkhvV1QtS1d3X0ZuWUZ2N3VEV2tQX2UxcnFVbjZBYWNKSVRudGgzRzl6Y3JHWE1lZ3FTbk1rZUtfRGZBTUpZMlV0QzkwdVRKR2Vid3RWcjluY01lUFVFT0p1RGRNRFR0cUwyVzk0dzdyNU9EOFNEZndMeHl5M3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Freedom Broker eleva recomendação da Mosaic com melhora nos custos de enxofre - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4416,51 +4416,51 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYkJCZXRNYmpPWklEMVVnLXVSYlhzYWE3cHc1UXZDcVZWbUlyb1B4bm53QjR4UG5NNm1PMEtTUm1ZUXctb2g1UEx2bXpiSEUyajB4ZHdOb21kZFVPZkhvV1QtS1d3X0ZuWUZ2N3VEV2tQX2UxcnFVbjZBYWNKSVRudGgzRzl6Y3JHWE1lZ3FTbk1rZUtfRGZBTUpZMlV0QzkwdVRKR2Vid3RWcjluY01lUFVFT0p1RGRNRFR0cUwyVzk0dzdyNU9EOFNEZndMeHl5M3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
+          <t>Atualização Chaos Cubed - Minecraft</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>17/06/2026 04:00</t>
+          <t>16/06/2026 14:20</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Atualização Chaos Cubed - Minecraft</t>
+          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>16/06/2026 14:20</t>
+          <t>16/06/2026 04:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOc2dmVzJBa0tyZGQ3T3dCOFlFZjhkQXg0SmFjUmltT3RmbVlKSDlfYm1vOHNDMG5kdTdDalcyQ3dmTTlyY00taHRwTVhRSE54ZUdjdEZNWVEwYkRmRV9JS0FOY0xIQ01ISUF3VHA5ZmVZVS1XdlA2Mzk1UUNEbHFuT1VyUFhYSWZlU2lVay0wYUl1WmFzaEg5VmpKaGw1OTFHdWlHdDBGWlpqUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
+          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOc2dmVzJBa0tyZGQ3T3dCOFlFZjhkQXg0SmFjUmltT3RmbVlKSDlfYm1vOHNDMG5kdTdDalcyQ3dmTTlyY00taHRwTVhRSE54ZUdjdEZNWVEwYkRmRV9JS0FOY0xIQ01ISUF3VHA5ZmVZVS1XdlA2Mzk1UUNEbHFuT1VyUFhYSWZlU2lVay0wYUl1WmFzaEg5VmpKaGw1OTFHdWlHdDBGWlpqUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4494,17 +4494,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
+          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>16/06/2026 04:00</t>
+          <t>15/06/2026 04:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
+          <t>Visconde vence jogo de ida da final da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQRHRiYkRqaldJQUc1UDh3cWt4MGhpcmtrOUJSV3hTSlFrMkJPaTlFZktDVEZKS29ldXVmLWxYaXBISkxZemt4S2hxdXdoUy03Um01ZjJhYzNXN2JIckJvRlZTblRvLUkwdEF3eEZIOEJ6U2pQX2pBRS1JWFhndWowaFRkYUNkOE1HN0xv?oc=5</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Visconde vence jogo de ida da final da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4548,19 +4548,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQRHRiYkRqaldJQUc1UDh3cWt4MGhpcmtrOUJSV3hTSlFrMkJPaTlFZktDVEZKS29ldXVmLWxYaXBISkxZemt4S2hxdXdoUy03Um01ZjJhYzNXN2JIckJvRlZTblRvLUkwdEF3eEZIOEJ6U2pQX2pBRS1JWFhndWowaFRkYUNkOE1HN0xv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
+          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
+          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>15/06/2026 04:00</t>
+          <t>12/06/2026 04:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4604,139 +4604,139 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Pesquisa sobre Reaproveitamento de Rejeitos de Calcário será apresentada por engenheiros do DER-RO em Encontro Nacional - Eu Ideal</t>
+          <t>Prefeitura de Juína inicia distribuição de calcário para pequenos produtores rurais - Prefeitura de Juína</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>13/06/2026 04:00</t>
+          <t>11/06/2026 04:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxPTnJ1WkpzenVmZDNKcWdBdnVtb2lhaTFDWV80b242aHFxa19vbkZIaVZLbU12MFdUOWRZc0ZRcnNJYUxIUTdzejdwLS1XUFN6aU9aUmNDNnZyRXB2SWl1ZnpSLV80eVU5YjYtYUp6Y2gwenpLWEZqRWxrOER4RHRPTmJGdXcwN21xQ3pNM3JhU1dMZU5xS2hTRkpPZGVDQUNDaHlWOHMzYnlkbXFnT1JQbUdrTE84UVlzMVBKaEtXR2FKVGRrWDN3cmNuck1tU0JsQkRWLWJXUi1QV1F6bVVEV3dsdkJHYWNGVVE1dmNuakRuUHZiUEF2TXpjZmM1QjlY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdUstNlpDWGRsZW9BeDl3eVdXRHpKejc3dmpLMFRjdmhaLTdzOU5QUldHRVI4REN5VWpsN2doUTF3dXJoR1laNnZ1Q0FxU0ZhQlUxQ2xfUnVtOFVUM3NMNWJtS0lfOG5tcjREcXdCYWV3TTA3QmRIZkJOTGt2a1JzeU0xdjUtTVFocGFWRXNjUTZJMkZQRkJRQ0ZpVWlPS01HejZnaXFZZ201RFNQZkM3eDd2dE1GbzZiU0ppaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
+          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>12/06/2026 04:00</t>
+          <t>11/06/2026 04:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Prefeitura de Juína inicia distribuição de calcário para pequenos produtores rurais - Prefeitura de Juína</t>
+          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>11/06/2026 04:00</t>
+          <t>10/06/2026 04:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdUstNlpDWGRsZW9BeDl3eVdXRHpKejc3dmpLMFRjdmhaLTdzOU5QUldHRVI4REN5VWpsN2doUTF3dXJoR1laNnZ1Q0FxU0ZhQlUxQ2xfUnVtOFVUM3NMNWJtS0lfOG5tcjREcXdCYWV3TTA3QmRIZkJOTGt2a1JzeU0xdjUtTVFocGFWRXNjUTZJMkZQRkJRQ0ZpVWlPS01HejZnaXFZZ201RFNQZkM3eDd2dE1GbzZiU0ppaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
+          <t>Prefeitura de Juína inicia distribuição de calcário para fortalecer a agricultura familiar - Juína News</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>11/06/2026 04:00</t>
+          <t>10/06/2026 04:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxON1ZhNG1LR2ZxNW5vY0gtYWtuT1kxb1E4em91SWljN1JrcDI1aE84Uzd3QUROQ3dXa2JjWXhPZ2xMNWN6RVBCbGkwSEx1ZlF1NXdtOGdSdmpxM2tEUzJEc0pYdjNScU5FWkQ5eE56SUJVRy1yS0R4UmVnMGUyaWNwQU5SMmxrbi1uQXhTOWk3QXRJU1VmZS1BQVdleHp3T3hSdF8wS0hYNnVXTlpBSXBKSW5Yczd3OUpGcXNUeGhvT3VocW5yb0g4aW9NZ0U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Prefeitura de Juína inicia distribuição de calcário para fortalecer a agricultura familiar - Juína News</t>
+          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>10/06/2026 04:00</t>
+          <t>09/06/2026 04:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOamk5dF9iaUJkUFdrWHVfSWN2WXpxblhXX0M2TlBWeTNHLVFteGhWVXZuWUxGR3lVNXVmVVhOUEN3YlNEdkRDMmVUTmFUb3phYnhrblg0dzVJXzlkMGxzam5CbVJycmlqamJweW1BZFRLVnIzaTVMZXVROUFNVWpncUJYaER5alhtMGlQaVE5SUdKM1RlTi16bjBFajVJLVktSUpXcWM5aDR5TDFfRHI2YTdxNzU1b05lUmpUcUJaU0VxRjJobGdGZVpnWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
+          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>10/06/2026 04:00</t>
+          <t>09/06/2026 04:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
+          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
+          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4768,85 +4768,85 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
+          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>09/06/2026 04:00</t>
+          <t>08/06/2026 14:33</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
+          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>09/06/2026 04:00</t>
+          <t>08/06/2026 04:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
+          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>08/06/2026 14:33</t>
+          <t>08/06/2026 04:00</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4856,19 +4856,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
+          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4878,19 +4878,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4900,73 +4900,73 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
+          <t>Clube do Livro: A Próxima Democracia, de Silvio Meira e Rosario Pompeia - eusoulivres.org</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>08/06/2026 04:00</t>
+          <t>07/06/2026 23:34</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQalNYQXd2OGFubnBVeXhzZjJFaHMtVS1nWnJEMnBOdEZjajJrMWNqaS16Wm5DMkVyc1l4YmZrV1VtbEI2MTVlQkV0Ykc2N2tweVZ3NVg3ZTNtbTNWNjRTeFBpRzJFZkZLS2gycEJ5U1IzUDNZUU82VmtVRmJRRkR5ODJPOF9VVm5zZEpUNGk4VWRjRWFuLXdOVmVaSTMzUjBFSmdVdnI3ZHNKUV84cGx1UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
+          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>08/06/2026 04:00</t>
+          <t>04/06/2026 04:00</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Clube do Livro: A Próxima Democracia, de Silvio Meira e Rosario Pompeia - eusoulivres.org</t>
+          <t>Copa do Calcário 2026 tem jogos empatados nas semifinais - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>07/06/2026 23:34</t>
+          <t>03/06/2026 04:00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQalNYQXd2OGFubnBVeXhzZjJFaHMtVS1nWnJEMnBOdEZjajJrMWNqaS16Wm5DMkVyc1l4YmZrV1VtbEI2MTVlQkV0Ykc2N2tweVZ3NVg3ZTNtbTNWNjRTeFBpRzJFZkZLS2gycEJ5U1IzUDNZUU82VmtVRmJRRkR5ODJPOF9VVm5zZEpUNGk4VWRjRWFuLXdOVmVaSTMzUjBFSmdVdnI3ZHNKUV84cGx1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQM01FdlJEQnpyMGhkMDNTcWZZZTN2dGk4azUzdTRqVExKbjV4WExTSlgwVWQ4elY4TnluTHVwNzZCT3dkN1ZFWUlMbGxqNVZYdzVMMnNsRmtYVWJ0ZlVEN0lVcUxNNGU5WHY3QlN5dkRUdVA2dlpVVThPcG11UWpleF9WTXV0OWhmeFU5eQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4978,39 +4978,39 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
+          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>04/06/2026 04:00</t>
+          <t>03/06/2026 04:00</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 tem jogos empatados nas semifinais - jornaldaregiao.com</t>
+          <t>Mosaic suspende operações em Tapira, devido à falta de enxofre e custo da matéria-prima - Jornal Araxá</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>03/06/2026 04:00</t>
+          <t>02/06/2026 12:15</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQM01FdlJEQnpyMGhkMDNTcWZZZTN2dGk4azUzdTRqVExKbjV4WExTSlgwVWQ4elY4TnluTHVwNzZCT3dkN1ZFWUlMbGxqNVZYdzVMMnNsRmtYVWJ0ZlVEN0lVcUxNNGU5WHY3QlN5dkRUdVA2dlpVVThPcG11UWpleF9WTXV0OWhmeFU5eQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeGt1SzZTRTQ4QkxZbXVuRmlZQWJIWlg5RGZkX0VuVTk2ZkVzMERUUy1CZ0dyU21qZTZQclpTd0ZUaXdMb21VZGszMHVldE1oYWI3UlhmZjUwV1V4em9zblNSd2lRT3c3eGhIdjlnOWxnanl0Sk5keW5DZjQ2cUYyR0RSUGZaU1NhNkFEYUw1TDVpOFdjRnZZLWVvNUlxRjZRZlppSHhFVFJoUGxNc1pkb0ZuNUc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5022,29 +5022,29 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
+          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>03/06/2026 04:00</t>
+          <t>02/06/2026 04:00</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
+          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5054,29 +5054,29 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
+          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>02/06/2026 04:00</t>
+          <t>01/06/2026 04:00</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
         </is>
       </c>
     </row>
@@ -5127,12 +5127,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
+          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5142,19 +5142,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
+          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5193,22 +5193,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
+          <t>Votorantim compra direitos minerários da João Santos por R$ 250 milhões - Pipeline</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>01/06/2026 04:00</t>
+          <t>31/05/2026 04:00</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNN0JIVlhseElXbVBQQ0l5ZDltZnJHZXllUjk1Y2J2TUNadklUclZNWG9QQzVEQWFfVUh2SDE2VGc2YmZ6MjI2SFFFNWFBc1M4NmpKNEVVWl9iQnBWU0xLdlQxT3BQME9wQ3ZYQTl0OElZRS01WTNPVDctaGR5QWJxd2poU21oZjRRelRORUhxOHdHa3FHaEZqem9wcEptTFd0XzVaRGpWcTMzZjBKa1hMdG9aRHBVeHFGS3hLUUtxZHNmb3PSAdIBQVVfeXFMUEZFaldhc3JvYmZWM0pLV1VZNUJTMmY2eFBZQi1mS0NfX0VxNWFZbkFlWjFFMF9kSGJpLTdfbHZYeDYtRnU1UXJHbzZkb3lFY0w4WG1xcU1zUWxscFpKVmppbDJxZXNXbUl6MktMQ3VDa2txRjVvUUE2LU1fNlRpd2czWXhkcTBzY2Y3TmtGOHB5ekRybmlNcW1wWjlWY2xPMm9TSUdVNGRxTnI0X2lrakRFeUFBeUw5Wkl1TTdMMjFrY1pjckFqUkN6NkQyVEZyRGRR?oc=5</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Votorantim compra direitos minerários da João Santos por R$ 250 milhões - Pipeline</t>
+          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNN0JIVlhseElXbVBQQ0l5ZDltZnJHZXllUjk1Y2J2TUNadklUclZNWG9QQzVEQWFfVUh2SDE2VGc2YmZ6MjI2SFFFNWFBc1M4NmpKNEVVWl9iQnBWU0xLdlQxT3BQME9wQ3ZYQTl0OElZRS01WTNPVDctaGR5QWJxd2poU21oZjRRelRORUhxOHdHa3FHaEZqem9wcEptTFd0XzVaRGpWcTMzZjBKa1hMdG9aRHBVeHFGS3hLUUtxZHNmb3PSAdIBQVVfeXFMUEZFaldhc3JvYmZWM0pLV1VZNUJTMmY2eFBZQi1mS0NfX0VxNWFZbkFlWjFFMF9kSGJpLTdfbHZYeDYtRnU1UXJHbzZkb3lFY0w4WG1xcU1zUWxscFpKVmppbDJxZXNXbUl6MktMQ3VDa2txRjVvUUE2LU1fNlRpd2czWXhkcTBzY2Y3TmtGOHB5ekRybmlNcW1wWjlWY2xPMm9TSUdVNGRxTnI0X2lrakRFeUFBeUw5Wkl1TTdMMjFrY1pjckFqUkN6NkQyVEZyRGRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
+          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5274,51 +5274,51 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
+          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>31/05/2026 04:00</t>
+          <t>30/05/2026 04:00</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
+          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>30/05/2026 04:00</t>
+          <t>29/05/2026 04:00</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPWmY3TXBIbWxobnFjUi1mTUozS2xCbTlaSGxKX2o0QTExdWszWk5USkR4ZVk0Zk5vcTIxSm9HZDRzazlGVjBDLVE4a2NTTnQ4eHpQM3cyNTFDVDd1aGs0cFhxUVBmbXlaUTNLMjljT0FSRWlMRm1iVkxMYk1uc2Nvd0JZencteGFkLXNFSWxySlhTNkdpemo2Y2N4ZlFOclJPMkNLUDdGU2FrYTJsRjIzdTE3RWVQUnhGbXJpVkJhcWhjclZJaWdXM2dueTFYRjNfMWE5WjBEWEFxUdIB3wFBVV95cUxOdGxrd3ZlRXQ3X0k0Rkx5VDk0OW5yQ0FyZ1A1QW5wTGhXZDA3blVtaVdobkM5YVFBcEhsUUlYRGYwVlVodlF1UmxsbVZaY0c2Z2lScV9hWnlOdlpZYzZDNXVLWWdiU0FvRExxZlQzQ2d3N3lTbk9tY3pXZEpJOWtZaDhOYVhVOXFFWExTVkYyMU5jUnk3VURmS0dMazRJUERGYS1BS2p5MFo5bXg3eFlPcVJtZ1NMQjBYRDFrWmRRbnpRdWlMU0VmaHI3T2tHUGp2b3I3bFZZYk9oWWhDX3pN?oc=5</t>
         </is>
       </c>
     </row>
@@ -5352,17 +5352,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>29/05/2026 04:00</t>
+          <t>28/05/2026 04:00</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPWmY3TXBIbWxobnFjUi1mTUozS2xCbTlaSGxKX2o0QTExdWszWk5USkR4ZVk0Zk5vcTIxSm9HZDRzazlGVjBDLVE4a2NTTnQ4eHpQM3cyNTFDVDd1aGs0cFhxUVBmbXlaUTNLMjljT0FSRWlMRm1iVkxMYk1uc2Nvd0JZencteGFkLXNFSWxySlhTNkdpemo2Y2N4ZlFOclJPMkNLUDdGU2FrYTJsRjIzdTE3RWVQUnhGbXJpVkJhcWhjclZJaWdXM2dueTFYRjNfMWE5WjBEWEFxUdIB3wFBVV95cUxOdGxrd3ZlRXQ3X0k0Rkx5VDk0OW5yQ0FyZ1A1QW5wTGhXZDA3blVtaVdobkM5YVFBcEhsUUlYRGYwVlVodlF1UmxsbVZaY0c2Z2lScV9hWnlOdlpZYzZDNXVLWWdiU0FvRExxZlQzQ2d3N3lTbk9tY3pXZEpJOWtZaDhOYVhVOXFFWExTVkYyMU5jUnk3VURmS0dMazRJUERGYS1BS2p5MFo5bXg3eFlPcVJtZ1NMQjBYRDFrWmRRbnpRdWlMU0VmaHI3T2tHUGp2b3I3bFZZYk9oWWhDX3pN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5384,19 +5384,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5406,19 +5406,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
+          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
+          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5472,19 +5472,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
+          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5494,19 +5494,19 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
+          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
+          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
         </is>
       </c>
     </row>
@@ -5594,17 +5594,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
+          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00</t>
+          <t>27/05/2026 04:00</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -5633,12 +5633,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
+          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5648,29 +5648,29 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
+          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>27/05/2026 04:00</t>
+          <t>26/05/2026 04:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -5682,51 +5682,51 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
+          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>26/05/2026 04:00</t>
+          <t>25/05/2026 04:00</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>AGU fecha acordo de R$ 27 milhões por lavra ilegal de calcário - Jornal de Brasília</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>26/05/2026 04:00</t>
+          <t>25/05/2026 04:00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPU0tZVWlMNUF1U1ZlWXE4a1I3cmhKT1JOWmZ2bFhpNVJkWkgzOGROUEJ5S3VRSEpqVVNpUHdTOGJoc0hIQ05OVmtob1g1Q1dVbTlic0o0MjhLYTRONUZtazBxN3UtYUJVaVB6bWhERHVmcjZZODJkak5UZDZqejdack5VdzVfaHR1X1hPVGRzVVlLeERtVU11bllOWGpmWHVpMmJLMEk4bmh1NkNhS0Rj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Definidos os semifinalistas da Copa do Calcário 2026 após rodada decisiva - Serra News</t>
+          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5736,19 +5736,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxORTlOcWI2YW9vOHdRRjJSbWtFZVhpZDFYTXZaTUowOW5XOFFBako2SkdwSlk3bEIzUzllUU9VOEFyMVVFNjB2RVRiYko3XzhVMmNXUVJqMk8xRDE1UzhFcGpYbUtyZVhyV0U0SG9JTEZ6QkFseVJZQ1hBdTZ5T1ZxQkVnT2J5cnZGZy1xMGxxd1RvZF85RS1pMXEtenI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
+          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5758,19 +5758,19 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Copa do Calcário define os semifinalistas - FERJ</t>
+          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5780,19 +5780,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
+          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
         </is>
       </c>
     </row>
@@ -5831,12 +5831,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
+          <t>Definidos os semifinalistas da Copa do Calcário 2026 após rodada decisiva - Serra News</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5846,19 +5846,19 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxORTlOcWI2YW9vOHdRRjJSbWtFZVhpZDFYTXZaTUowOW5XOFFBako2SkdwSlk3bEIzUzllUU9VOEFyMVVFNjB2RVRiYko3XzhVMmNXUVJqMk8xRDE1UzhFcGpYbUtyZVhyV0U0SG9JTEZ6QkFseVJZQ1hBdTZ5T1ZxQkVnT2J5cnZGZy1xMGxxd1RvZF85RS1pMXEtenI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>Copa do Calcário define os semifinalistas - FERJ</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5868,73 +5868,73 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
+          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>25/05/2026 04:00</t>
+          <t>23/05/2026 04:00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
+          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>25/05/2026 04:00</t>
+          <t>22/05/2026 04:00</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
+          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>23/05/2026 04:00</t>
+          <t>22/05/2026 04:00</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
+          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
+          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6000,107 +6000,107 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
+          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>22/05/2026 04:00</t>
+          <t>21/05/2026 04:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
+          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>22/05/2026 04:00</t>
+          <t>21/05/2026 04:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
+          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>21/05/2026 04:00</t>
+          <t>20/05/2026 04:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
+          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>21/05/2026 04:00</t>
+          <t>20/05/2026 04:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
+          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6110,19 +6110,19 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
+          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6161,12 +6161,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
+          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6176,63 +6176,63 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
+          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>20/05/2026 04:00</t>
+          <t>19/05/2026 04:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
+          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>20/05/2026 04:00</t>
+          <t>19/05/2026 04:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
+          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6242,51 +6242,51 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
+          <t>Acidente com carreta de calcário deixa feridos na BR-282 em SC - ND Mais</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>19/05/2026 04:00</t>
+          <t>18/05/2026 04:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxObnpROGFDVUpELUEyQjBhX20xS0pHR19uYzJmZkhrLTJtdjdIQktnSFpoWXFsc1BlRTIzU1kyS0dhZENFRXJWUDMxMmJacERxMVdaVUw0aGc4Z1VJdUdpbXhoNlA5b290RG1odlZERFFDcDBkZEFranZjbFQ3c0dJb0NKYnhtbmk0bDRnbWlMam9iekJra3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
+          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>19/05/2026 04:00</t>
+          <t>18/05/2026 04:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
+          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6320,17 +6320,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
+          <t>Cidade do século 9, suspensa sobre falésias de calcário, atrai turistas no Mediterrâneo - Terra</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>18/05/2026 04:00</t>
+          <t>17/05/2026 18:07</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNR2ctaUFlZEp1YkFkMlpnTlZ0M3ZOUXF6T1FBZk9iaWpCM0plY0QyMkdZdlZzcXlXbDJpZjFfc3drZ0pTb1dWUEw3N2VrNG9WRmxhSWh1S3hMRnhpdms0TW5kak9udXA5aVcwZmNocWpmQi1yYXhZUlZZQmZmaWNLUnkyZ3FKVU44YzFBTk1lbEh0NS1VZWhiTjF6RndjTWhwYnhBZEE3TjEtWFRXWF96a05sMGhETDd5ZkVyZ0F1N3ljLUZWUWM3WTVwQksxR1E1ZmtKSTlLR3JqRWdUX0tMZGVoMk41SjZXRDc0QzZTeENuUkN1Yk5YSDRBYnU1QTJReHg4WG5n0gGGAkFVX3lxTE1HZy1pQWVkSnViQWQyWmdOVnQzdk5RcXpPUUFmT2JpakIzSmVjRDIyR1l2VnNxeVdsMmlmMV9zd2tnSlNvV1ZQTDc3ZWs0b1ZGbGFJaHVLeExGeGl2azRNbmRqT251cDlpVzBmY2hxamZCLXJheFlSVllCZmZpY0tSeTJncUpVTjhjMUFOTWVsSHQ1LVVlaGJOMXpGd2NNaHBieEFkQTdOMS1YVFdYX3prTmwwaERMN3lmRXJnQXU3eWMtRlZRYzdZNXBCSzFHUTVma0pJOUtHcmpFZ1RfS0xkZWgyTjVKNldENzRDNlN4Q25SQ3ViTlhINEFidTVBMlF4eDhYbmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6342,17 +6342,17 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Acidente com carreta de calcário deixa feridos na BR-282 em SC - ND Mais</t>
+          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>18/05/2026 04:00</t>
+          <t>17/05/2026 14:07</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxObnpROGFDVUpELUEyQjBhX20xS0pHR19uYzJmZkhrLTJtdjdIQktnSFpoWXFsc1BlRTIzU1kyS0dhZENFRXJWUDMxMmJacERxMVdaVUw0aGc4Z1VJdUdpbXhoNlA5b290RG1odlZERFFDcDBkZEFranZjbFQ3c0dJb0NKYnhtbmk0bDRnbWlMam9iekJra3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -6364,127 +6364,127 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Cidade do século 9, suspensa sobre falésias de calcário, atrai turistas no Mediterrâneo - Terra</t>
+          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>17/05/2026 18:07</t>
+          <t>16/05/2026 22:15</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNR2ctaUFlZEp1YkFkMlpnTlZ0M3ZOUXF6T1FBZk9iaWpCM0plY0QyMkdZdlZzcXlXbDJpZjFfc3drZ0pTb1dWUEw3N2VrNG9WRmxhSWh1S3hMRnhpdms0TW5kak9udXA5aVcwZmNocWpmQi1yYXhZUlZZQmZmaWNLUnkyZ3FKVU44YzFBTk1lbEh0NS1VZWhiTjF6RndjTWhwYnhBZEE3TjEtWFRXWF96a05sMGhETDd5ZkVyZ0F1N3ljLUZWUWM3WTVwQksxR1E1ZmtKSTlLR3JqRWdUX0tMZGVoMk41SjZXRDc0QzZTeENuUkN1Yk5YSDRBYnU1QTJReHg4WG5n0gGGAkFVX3lxTE1HZy1pQWVkSnViQWQyWmdOVnQzdk5RcXpPUUFmT2JpakIzSmVjRDIyR1l2VnNxeVdsMmlmMV9zd2tnSlNvV1ZQTDc3ZWs0b1ZGbGFJaHVLeExGeGl2azRNbmRqT251cDlpVzBmY2hxamZCLXJheFlSVllCZmZpY0tSeTJncUpVTjhjMUFOTWVsSHQ1LVVlaGJOMXpGd2NNaHBieEFkQTdOMS1YVFdYX3prTmwwaERMN3lmRXJnQXU3eWMtRlZRYzdZNXBCSzFHUTVma0pJOUtHcmpFZ1RfS0xkZWgyTjVKNldENzRDNlN4Q25SQ3ViTlhINEFidTVBMlF4eDhYbmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPWE5jYU0zdnFBT0JIbWFndHZweHBKUXBWUjJQaWxiNjMzWFRmcTJJRUJya1ktanJ0N0hOZm9KZnRvbzBjVlNXeFUtN0RvR1lXZ0p1WUI1NWd3RGpMS2xlM19TbFFXWkVSWENWME1aUjZjSzI3SDc4eFJUYU8tNDhsakROeUMwTXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
+          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>17/05/2026 14:07</t>
+          <t>15/05/2026 04:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
+          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>16/05/2026 22:15</t>
+          <t>15/05/2026 04:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPWE5jYU0zdnFBT0JIbWFndHZweHBKUXBWUjJQaWxiNjMzWFRmcTJJRUJya1ktanJ0N0hOZm9KZnRvbzBjVlNXeFUtN0RvR1lXZ0p1WUI1NWd3RGpMS2xlM19TbFFXWkVSWENWME1aUjZjSzI3SDc4eFJUYU8tNDhsakROeUMwTXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
+          <t>O obstáculo virou o caminho - CNN Brasil</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>15/05/2026 04:00</t>
+          <t>14/05/2026 04:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
+          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>15/05/2026 04:00</t>
+          <t>13/05/2026 04:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOcnB4VWxYOXVnTVhBMjJoMDcwZGZIdHpnMzZ2dmNNelgycGxSdGpPcDcwS0ZGdW9JODJZNXlZcExhRmZGTloxdlYxTnJlSktSWTQ4Mk85ZWhObFRIN2VGV3lpSmJpeGNwbGN1ZG44VHoxSnZpaVI0VFV2TWJkSWV2QldxM1U3VWpLV0ZQWmkzeVNrSEhxR25SOU1jdFN2ZmJWZ3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>O obstáculo virou o caminho - CNN Brasil</t>
+          <t>Ureia cai após meses de valorização - Agrolink</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>14/05/2026 04:00</t>
+          <t>12/05/2026 04:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6496,17 +6496,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
+          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>13/05/2026 04:00</t>
+          <t>12/05/2026 04:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOcnB4VWxYOXVnTVhBMjJoMDcwZGZIdHpnMzZ2dmNNelgycGxSdGpPcDcwS0ZGdW9JODJZNXlZcExhRmZGTloxdlYxTnJlSktSWTQ4Mk85ZWhObFRIN2VGV3lpSmJpeGNwbGN1ZG44VHoxSnZpaVI0VFV2TWJkSWV2QldxM1U3VWpLV0ZQWmkzeVNrSEhxR25SOU1jdFN2ZmJWZ3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
         </is>
       </c>
     </row>
@@ -6579,44 +6579,44 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
+          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Prefeitura de Paranaguá</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>12/05/2026 04:00</t>
+          <t>11/05/2026 13:42</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Ureia cai após meses de valorização - Agrolink</t>
+          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>12/05/2026 04:00</t>
+          <t>11/05/2026 04:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
         </is>
       </c>
     </row>
@@ -6628,29 +6628,29 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Prefeitura de Paranaguá</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>11/05/2026 13:42</t>
+          <t>11/05/2026 04:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6660,19 +6660,19 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6682,19 +6682,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
+          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -6755,44 +6755,44 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
+          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>11/05/2026 04:00</t>
+          <t>08/05/2026 04:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
+          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>11/05/2026 04:00</t>
+          <t>08/05/2026 04:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
         </is>
       </c>
     </row>
@@ -6821,22 +6821,22 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
+          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>08/05/2026 04:00</t>
+          <t>06/05/2026 11:23</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6848,39 +6848,39 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
+          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>08/05/2026 04:00</t>
+          <t>06/05/2026 04:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
+          <t>EUA ainda precisam importar ureia - Agrolink</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>06/05/2026 11:23</t>
+          <t>06/05/2026 04:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -6909,22 +6909,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
+          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>06/05/2026 04:00</t>
+          <t>05/05/2026 04:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6936,17 +6936,17 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EUA ainda precisam importar ureia - Agrolink</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>06/05/2026 04:00</t>
+          <t>04/05/2026 04:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
         </is>
       </c>
     </row>
@@ -6958,17 +6958,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
+          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>05/05/2026 04:00</t>
+          <t>04/05/2026 04:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
+          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6990,19 +6990,19 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
+          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7012,19 +7012,19 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
+          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7034,19 +7034,19 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObWdVQ1R0NC1YZThsV1NPR1p3bnY1S3JpZ29Rd1l5dWtYNkUycTlma1FrUUNmLU91aF94eFlSa01qMmszRUgzWkoyd0xQWnhHS0RDRF9oSnd2N29lQUROVDhiUzJjUmlWcWw5SDViQnh3MWY2SGJiVVREX1dyYkN3S3RsWnlfcTBX?oc=5</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
+          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
         </is>
       </c>
     </row>
@@ -7090,39 +7090,39 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
+          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>04/05/2026 04:00</t>
+          <t>01/05/2026 04:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>04/05/2026 04:00</t>
+          <t>30/04/2026 04:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObWdVQ1R0NC1YZThsV1NPR1p3bnY1S3JpZ29Rd1l5dWtYNkUycTlma1FrUUNmLU91aF94eFlSa01qMmszRUgzWkoyd0xQWnhHS0RDRF9oSnd2N29lQUROVDhiUzJjUmlWcWw5SDViQnh3MWY2SGJiVVREX1dyYkN3S3RsWnlfcTBX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
+          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>01/05/2026 04:00</t>
+          <t>30/04/2026 04:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
+          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7232,19 +7232,19 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
+          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Petrobras retoma produção de ureia após 6 anos e avança no mercado de fertilizantes, na B3 - ADVFN</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7276,19 +7276,19 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQaWlBMEcxWUtKWXVyOXU3dU95dGV3MUpDd2RkanlxMXZHUE91UTJVRmtzbXRfUm4yMnE5Zm5udUo2dm1vSEdYRVNMckxQcjVQamlvUDctYkNsQlJXSmNXaHc1SDBmOXlzLVJhaXRQSmR3Rmoya3hmcERRNTUyTmxFZ1lQNS16UFkxUEpMMEh3U2YwdEFYUTRUMmp2WnVTMVhMRWJ3MkhzN1A4cTVKeHhzZURmN0FIWTkzRnN2ZHJZcjd0MzQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Petrobras retoma produção de ureia após 6 anos e avança no mercado de fertilizantes, na B3 - ADVFN</t>
+          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7298,95 +7298,95 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQaWlBMEcxWUtKWXVyOXU3dU95dGV3MUpDd2RkanlxMXZHUE91UTJVRmtzbXRfUm4yMnE5Zm5udUo2dm1vSEdYRVNMckxQcjVQamlvUDctYkNsQlJXSmNXaHc1SDBmOXlzLVJhaXRQSmR3Rmoya3hmcERRNTUyTmxFZ1lQNS16UFkxUEpMMEh3U2YwdEFYUTRUMmp2WnVTMVhMRWJ3MkhzN1A4cTVKeHhzZURmN0FIWTkzRnN2ZHJZcjd0MzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
+          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>30/04/2026 04:00</t>
+          <t>28/04/2026 04:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
+          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>30/04/2026 04:00</t>
+          <t>28/04/2026 04:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
+          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>27/04/2026 04:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
+          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>27/04/2026 04:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNVTgySERJNzFBLVRJY0tDRV81b19aVkctQ0lXdzZrRmVHdUtISTRwbUloajBPNFdXNHZsdDVpU2RDNFE5V2hjU2VfZWIxT1V4Njc5TjJFLTNHejc3ZGNfbzJWVzI4SnZDR1ZISy1XQklsWGIxUHlCSWFPX09jUUVEeERud0tSNGZlQm9rLXNGQlJUb0NEdnR2aA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
+          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7430,73 +7430,73 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNVTgySERJNzFBLVRJY0tDRV81b19aVkctQ0lXdzZrRmVHdUtISTRwbUloajBPNFdXNHZsdDVpU2RDNFE5V2hjU2VfZWIxT1V4Njc5TjJFLTNHejc3ZGNfbzJWVzI4SnZDR1ZISy1XQklsWGIxUHlCSWFPX09jUUVEeERud0tSNGZlQm9rLXNGQlJUb0NEdnR2aA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
+          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>24/04/2026 04:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
+          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>22/04/2026 04:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
+          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>24/04/2026 04:00</t>
+          <t>22/04/2026 04:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
         </is>
       </c>
     </row>
@@ -7525,12 +7525,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
+          <t>Justiça anula licença para extração de calcário em área quilombola no MA e determina indenização de R$ 100 mil - G1</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7540,73 +7540,73 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQSi1hWVV3Y3VUZmNsUEFqcTVlc0lpUzZEMnBYWkdGNnJRVXU0WFF6LXkwRlVHMEFCMnRPbTVzbHJSS3BXTGI3WnpMOUVKSlJ5ZjBHSGZ1WXF0NkptY05fb0VvVzdDa3BlLXFYamQ3YTBFWWpGUi03cXZzbWJkZlFjQVRGS0lEUl9haDF1U0lfbDEyQ0ZkZ19EcGhCMzZ5d2ItYURqX1NMMUduZ2RzeGt2UUwzZ0NteVdPaUwzM0ZadnV0TnhJS2lrbk1JMnVaRkkzQlBUR2FjNWFpRnJwX3JpVWhrSUk2bjF2d3NBcVVSdVJzWGtpZ19OSW5jUTZ1Z9IBjAJBVV95cUxQdU9IMnNVTTlweXVDZ1lrR2VZeVlNdC1vQk00YVBGV1U1ajdjM0lDZDdTcmVxNF9SX2N5dWdfSVZwVFktSVVrTnZUNE9pWFQyNkxGM1VPMHg3d1l6R0Q4alZwMENMUkdTcUlydjRjYzFSZHJqTDJnSll0MHZlUVhxbnY3YmJjcXVmc1VYaE95TFRmZlBVMl9ZaTZ6YzN6UnRvUVdLekZNNC10QjV1Skwxd0tKaWxfeUphVE1QOHBMZUVzMk5MWjhfVGJLNG43TzZobmtRUFhERlpXVjlsZzZiY1l6dWU1ZGhhQjJhZVhta1FkTndJMkpwYUpVb21OVEN1S0RlLURxWUVjd0ps?oc=5</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>22/04/2026 04:00</t>
+          <t>21/04/2026 18:42</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Justiça anula licença para extração de calcário em área quilombola no MA e determina indenização de R$ 100 mil - G1</t>
+          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>22/04/2026 04:00</t>
+          <t>20/04/2026 04:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQSi1hWVV3Y3VUZmNsUEFqcTVlc0lpUzZEMnBYWkdGNnJRVXU0WFF6LXkwRlVHMEFCMnRPbTVzbHJSS3BXTGI3WnpMOUVKSlJ5ZjBHSGZ1WXF0NkptY05fb0VvVzdDa3BlLXFYamQ3YTBFWWpGUi03cXZzbWJkZlFjQVRGS0lEUl9haDF1U0lfbDEyQ0ZkZ19EcGhCMzZ5d2ItYURqX1NMMUduZ2RzeGt2UUwzZ0NteVdPaUwzM0ZadnV0TnhJS2lrbk1JMnVaRkkzQlBUR2FjNWFpRnJwX3JpVWhrSUk2bjF2d3NBcVVSdVJzWGtpZ19OSW5jUTZ1Z9IBjAJBVV95cUxQdU9IMnNVTTlweXVDZ1lrR2VZeVlNdC1vQk00YVBGV1U1ajdjM0lDZDdTcmVxNF9SX2N5dWdfSVZwVFktSVVrTnZUNE9pWFQyNkxGM1VPMHg3d1l6R0Q4alZwMENMUkdTcUlydjRjYzFSZHJqTDJnSll0MHZlUVhxbnY3YmJjcXVmc1VYaE95TFRmZlBVMl9ZaTZ6YzN6UnRvUVdLekZNNC10QjV1Skwxd0tKaWxfeUphVE1QOHBMZUVzMk5MWjhfVGJLNG43TzZobmtRUFhERlpXVjlsZzZiY1l6dWU1ZGhhQjJhZVhta1FkTndJMkpwYUpVb21OVEN1S0RlLURxWUVjd0ps?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
+          <t>Fertilizantes: energia para o​​ campo - Petrobras</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>21/04/2026 18:42</t>
+          <t>18/04/2026 16:01</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBFN2xBdUVqSm45WFdPbHdxWWNPY3lEUW0yN01OeThJMGxoYVhCU3Vfa2pJYXItMzN5NjFOS2IyTEd0OUM0LVZoSV9Oa1VBbG5DSlp6Q3VpNEtyWWFHTVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7618,61 +7618,61 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
+          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>20/04/2026 04:00</t>
+          <t>17/04/2026 04:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Fertilizantes: energia para o​​ campo - Petrobras</t>
+          <t>Santo Antônio do Caiuá distribui mais de 300 toneladas de calcário a produtores rurais - Diário do Noroeste</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>18/04/2026 16:01</t>
+          <t>16/04/2026 04:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBFN2xBdUVqSm45WFdPbHdxWWNPY3lEUW0yN01OeThJMGxoYVhCU3Vfa2pJYXItMzN5NjFOS2IyTEd0OUM0LVZoSV9Oa1VBbG5DSlp6Q3VpNEtyWWFHTVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPZzk0S1M0WnlzVGd1MGpETEIwX05pUEphT0Z4MVpaU2p1cnB5NE41R1ZqRmx6cWxVc3M2T1RYTVBOTzhHaTlkMlU4QWdUTktNc0ZhOUdVcUNXWmVueTI1UGxVWm1GcWtSRmVOTDMtN3BHM2wxNjZ0SUZseWh5Yml1MUVhdlFpN0lnejJhbF9DMnlRaUdlUEwtdTNLdjlneURmWE9pMDRnaGZQUkZyZ2lJVmZWU0ZBaTVUa044?oc=5</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
+          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>17/04/2026 04:00</t>
+          <t>14/04/2026 04:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOYnNGV1RwZHFmRTFzOFBsdlY0dEVxRVAwS09KYW50NG1mNWp0b3pQYzZobXZzYVlZaDdkbnZlV0VSQUxWc2FoMENDVUZ2NWpHMy1aU0lsaEFtTW55S09YRmJRNHpCRndhLU52M1dZQjhjWWstZFMwY05FaFlMQjF2dzA3MkVDSGZHS1lJMWZUa2phNl9TS05xbVhONHZTTENSMldvMWpmN0FoNjNnb1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -7684,51 +7684,51 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Santo Antônio do Caiuá distribui mais de 300 toneladas de calcário a produtores rurais - Diário do Noroeste</t>
+          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>16/04/2026 04:00</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPZzk0S1M0WnlzVGd1MGpETEIwX05pUEphT0Z4MVpaU2p1cnB5NE41R1ZqRmx6cWxVc3M2T1RYTVBOTzhHaTlkMlU4QWdUTktNc0ZhOUdVcUNXWmVueTI1UGxVWm1GcWtSRmVOTDMtN3BHM2wxNjZ0SUZseWh5Yml1MUVhdlFpN0lnejJhbF9DMnlRaUdlUEwtdTNLdjlneURmWE9pMDRnaGZQUkZyZ2lJVmZWU0ZBaTVUa044?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
+          <t>Paranaenses trazem bons resultados da Fórmula Truck no Uruguai - Bem Paraná</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>14/04/2026 04:00</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOYnNGV1RwZHFmRTFzOFBsdlY0dEVxRVAwS09KYW50NG1mNWp0b3pQYzZobXZzYVlZaDdkbnZlV0VSQUxWc2FoMENDVUZ2NWpHMy1aU0lsaEFtTW55S09YRmJRNHpCRndhLU52M1dZQjhjWWstZFMwY05FaFlMQjF2dzA3MkVDSGZHS1lJMWZUa2phNl9TS05xbVhONHZTTENSMldvMWpmN0FoNjNnb1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUUlhSHF6SzZzdW5jYnJaN1dHcGVtR2oxVExheWdtbXlQVWlXSjFLbWFkVGdDZFlUT1ZJTEFqLUhkeFQtdS1QTTdUb2pXWlprYnA1VnVDZ3VFS204Q1hiSThwVFBJZllPVl8yYjRNaWVDalZvcTdfVGVleGN4WW9kYUtJS1l6U0R2anZkT1BGcXlONlZveDYwcTVMVDR6NnE1Z2fSAacBQVVfeXFMUFVRS1k5U1N2RmpuZHVwbnFxRHh6NjBMQUw2dVBEaGE5X2Uydkd5RVRPVlZSRVhCX3FGOW01aExjVW1LazdPWnVULVlJREZBN2JNM0lnTWNfVDAxRnlpUTJSNVJIbEt4Zzg5NWVUak1RNmx6MkQxNmt6ak94N1A3dG1iOXMzOEhyamN0Uk1aazBncGExNnE4N1BmME5lT3RNX0dUc3ZFeW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
+          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7750,51 +7750,51 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
+          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Paranaenses trazem bons resultados da Fórmula Truck no Uruguai - Bem Paraná</t>
+          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUUlhSHF6SzZzdW5jYnJaN1dHcGVtR2oxVExheWdtbXlQVWlXSjFLbWFkVGdDZFlUT1ZJTEFqLUhkeFQtdS1QTTdUb2pXWlprYnA1VnVDZ3VFS204Q1hiSThwVFBJZllPVl8yYjRNaWVDalZvcTdfVGVleGN4WW9kYUtJS1l6U0R2anZkT1BGcXlONlZveDYwcTVMVDR6NnE1Z2fSAacBQVVfeXFMUFVRS1k5U1N2RmpuZHVwbnFxRHh6NjBMQUw2dVBEaGE5X2Uydkd5RVRPVlZSRVhCX3FGOW01aExjVW1LazdPWnVULVlJREZBN2JNM0lnTWNfVDAxRnlpUTJSNVJIbEt4Zzg5NWVUak1RNmx6MkQxNmt6ak94N1A3dG1iOXMzOEhyamN0Uk1aazBncGExNnE4N1BmME5lT3RNX0dUc3ZFeW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
+          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7816,51 +7816,51 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
+          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>09/04/2026 04:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
+          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>09/04/2026 04:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
+          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7870,19 +7870,19 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
+          <t>Mosaic coloca ativos de fertilizantes à venda no Brasil - BNamericas</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNkRQQ0V3N0JuU05aaVV3LU1zcGlRLTA3dFRCZndyZnEwUjhvcDFVa1k5eVdsa3ZMbWxFRWtHSGFvSlQyUXpaR2l2Y1NKNmczUlBUN25TWkpHOXlOTWpWanlobVBSY0dZbXV1MUJsNGhvZ1BLRzMwTmZtWkJ0bU5pUFg2MjZLODFVeWdhRkdUZF8zSkVlUDUyZGZn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7904,29 +7904,29 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
+          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>09/04/2026 04:00</t>
+          <t>08/04/2026 04:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
+          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7980,19 +7980,19 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
+          <t>Copa do Calcário 2026 inicia em abril com sete clubes da Região Centro-Norte - O Fluminense</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -8002,19 +8002,19 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTFV2aE9QamdoTlhzd051c1VfLWpKQTdQcnNoM250c0dZd0VUd2NTMG5MWW1laWY3N2hEVkp4cUNNelJDam1WWFZOMHVrNUdONzVFVlZrNS1CaHBSVmNwV1Q2QmxyM0tqVnF3MmhDLTA0ajJXeGUyRUN0WlQ1dU9CeVZPTHl5WkdHN2xSVDBfdXo5Z2dFaUN5UnY4RFN4clpkU2taZ2hDOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews - InvestNews</t>
+          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
+          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNVM2Q3ktX2tVc29Wb3RHZGdacTN1TXFhS0xET1k1YmVVWXY2MUI4NVNIUUJENUl6M1ZDM1lIQzNBUi1zYmVYcWJvM3JxSHJLSU13R3NCNG0yS0NfRUpWaGVSRV8wUUt4M2taUGdzX01qUHA3dFpPQ1QzSFpnLTU1TC1oZXBzQVAtcXl3cHhKZ25aNG9FbGt5TVdsNlRqOG1EVmxqNS1vSHZUNVFPWjJZcVZJT01KeGIza3FYYzUtWllscFVtSnlmMkVBMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
+          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -8134,51 +8134,51 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 inicia em abril com sete clubes da Região Centro-Norte - O Fluminense</t>
+          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>08/04/2026 04:00</t>
+          <t>07/04/2026 04:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTFV2aE9QamdoTlhzd051c1VfLWpKQTdQcnNoM250c0dZd0VUd2NTMG5MWW1laWY3N2hEVkp4cUNNelJDam1WWFZOMHVrNUdONzVFVlZrNS1CaHBSVmNwV1Q2QmxyM0tqVnF3MmhDLTA0ajJXeGUyRUN0WlQ1dU9CeVZPTHl5WkdHN2xSVDBfdXo5Z2dFaUN5UnY4RFN4clpkU2taZ2hDOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
+          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>07/04/2026 04:00</t>
+          <t>06/04/2026 04:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
+          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
         </is>
       </c>
     </row>
@@ -8212,61 +8212,61 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Agricultores já acessaram mais de 80% da cota de calcário no Extremo Oeste - Rede Peperi</t>
+          <t>Transporte de calcário fortalece produção rural em VG - FOLHAMAX</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>06/04/2026 04:00</t>
+          <t>04/04/2026 04:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPVnZNZFc2dnk0bEpPQ3gxZ1hIaVlnbktoWndsRGZEeFlEdXZTdzFUbVFRYS04TzRKb1NmZ0ZuOFhWZWdMN3ppc05vemlqdVV5MEczNGpaaUF1RW5RTDQ5bWctNHVyRmRURGdTbnpiZUcyUEhjOEtNQUNVa3N4ZEZnaE9jVEZWR0k4bXdQXy1xeTlmOE5nZ2JhQWQzTk5yZThYaFR3ZzZZZ0VORkpMYzZvXzl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPaEJ5Zkt0Q0dZY21rM3hDSjJndThldFlqWVV2Y3pfTmFfN3VtbGVNZTlmU2tzakN1bUZUclhRdk9NamJpWURucGR1WFNKam5mbHVPY3ZmZ3hRb0pxWm01d1ZFWkJmUzEwLVBHUGhacm5LSjNKNElQY1g3aGJxeHRGeUV6LTlXMkczZERYUU8wdnZzUFhvZjlrVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
+          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>06/04/2026 04:00</t>
+          <t>02/04/2026 17:10</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande - Página Inicial</t>
+          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>02/04/2026 17:10</t>
+          <t>01/04/2026 04:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
         </is>
       </c>
     </row>
@@ -8295,22 +8295,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>01/04/2026 04:00</t>
+          <t>31/03/2026 04:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
+          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8332,73 +8332,73 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
+          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>31/03/2026 04:00</t>
+          <t>30/03/2026 04:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
+          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>30/03/2026 04:00</t>
+          <t>27/03/2026 04:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>27/03/2026 04:00</t>
+          <t>25/03/2026 08:19</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57d63d5b7148ad97fe9681cf91c9e6&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -8410,29 +8410,29 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>25/03/2026 08:19</t>
+          <t>25/03/2026 04:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57c110a19a4bcd9ed6b34bdcfc7c0d&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
+          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -8442,19 +8442,19 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
+          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -8464,51 +8464,51 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
+          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>25/03/2026 04:00</t>
+          <t>23/03/2026 04:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcHkzSlA3V284QW9KcWRCR0hnbmpYZVFlNWVTVl93TmRPbG5QbUdLcWliZEcxZ0N2T1JlMWQ0NTJwRXFPVjZ5b1I1V1pzZVdySlJkdmNtTW9jVWlWUVY4dk5GLXlpdjhoSk1MRTZPc0hwX0tXYm9qZUo2Vk5ubjc1bWhUdE8xTnNQRlFtdGtsVEs1T3lzZnZjeVVQMWV5dERkMVZHemxkQ09CdnBWRURXcEdMNXlGZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>23/03/2026 04:00</t>
+          <t>21/03/2026 04:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZGVwSXBCbHh2T2tRbE1KQk9NRFZIQ1JuaUl3S2lKcVZ2bXlhb3dnOHZHRGp4dVgxRU9ObWxMM0hoTFZXQkh4RlJHVktzUUppdGFINFVBeWNRSVVHR1o1eHVpQU1HZTROWmM5REhaa25xYS0wc0p3ckVsZkNmRGp5Ml9Cd055NUxHWkE5OUEyMlM0WmRuT0o5RWNob0NEdmFFUW5qejJpR00ycTdUQjFMWXVTZFpwaWliTTBJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
         </is>
       </c>
     </row>
@@ -8520,17 +8520,17 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>21/03/2026 04:00</t>
+          <t>20/03/2026 18:35</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
         </is>
       </c>
     </row>
@@ -8542,51 +8542,51 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
+          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>20/03/2026 18:35</t>
+          <t>20/03/2026 14:42</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
+          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>20/03/2026 14:42</t>
+          <t>20/03/2026 04:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
+          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -8596,19 +8596,19 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
+          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -8618,41 +8618,41 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
+          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>20/03/2026 04:00</t>
+          <t>19/03/2026 04:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
+          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado Federal</t>
+          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado Federal</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -8684,19 +8684,19 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
+          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado Federal</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -8706,19 +8706,19 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
+          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -8728,19 +8728,19 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
+          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
         </is>
       </c>
     </row>
@@ -8762,39 +8762,39 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado Federal</t>
+          <t>Calcário para uso agrícola deve ficar mais barato - Senado Federal</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>19/03/2026 04:00</t>
+          <t>18/03/2026 04:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Calcário para uso agrícola deve ficar mais barato - Senado Federal</t>
+          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>18/03/2026 04:00</t>
+          <t>17/03/2026 04:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8806,73 +8806,73 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
+          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>17/03/2026 04:00</t>
+          <t>16/03/2026 04:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
+          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - Portal Arauto</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>16/03/2026 04:00</t>
+          <t>14/03/2026 04:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - Portal Arauto</t>
+          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>14/03/2026 04:00</t>
+          <t>13/03/2026 04:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
+          <t>Limestone: a pedra calcária em evidência na arquitetura - Archtrends - Portobello</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -8882,41 +8882,41 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Limestone: a pedra calcária em evidência na arquitetura - Archtrends - Portobello</t>
+          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>13/03/2026 04:00</t>
+          <t>11/03/2026 04:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
+          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
+          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -8948,19 +8948,19 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
+          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8999,12 +8999,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
+          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
         </is>
       </c>
     </row>
@@ -9026,51 +9026,51 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
+          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>11/03/2026 04:00</t>
+          <t>10/03/2026 12:14</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
+          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>10/03/2026 12:14</t>
+          <t>09/03/2026 04:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQanphVHkycWR3c05tQ1VBYkl5b3pncV9sRGlGVmJvLVpOUUZRcWRvOFdXc1hhSVFqbDBZMlFNSEdVcnNCVGppQ2ZGMVl5WFN5SUJNWS1FLUVuRUpPRFh3VFZHdk54TndBaU4yZW0zQ3dVeWN3MWpFZTVpRUZudm81MlZTa1NoV2hxSWNxLWltS1piVXJwU3QzdXd2emZWa0RHeDVSV0FNWWhIbzdFeGFycTJjdXIwVm1hZkw5ZGNsazczaURkV0cxek9aQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
+          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
+          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57c11151b3467da82865eeb19af6e4&amp;url=https%3a%2f%2fwww.msn.com%2fen-gb%2flifestyle%2fother%2flime-the-base-layer-fertiliser%2far-AA1XIisB&amp;c=12206964766642139602&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57d63e527b4fdb8e988d262a223137&amp;url=https%3a%2f%2fwww.msn.com%2fen-gb%2flifestyle%2fother%2flime-the-base-layer-fertiliser%2far-AA1XIisB&amp;c=12206964766642139602&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -9285,12 +9285,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
+          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -9300,19 +9300,19 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
+          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
         </is>
       </c>
     </row>
@@ -9351,22 +9351,22 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
+          <t>Conflito no Oriente Médio coloca em risco 41% da ureia exportada no mundo - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>04/03/2026 05:00</t>
+          <t>03/03/2026 05:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNMG1PVUx2UWlmTFltaHVVQTRObV9jYlUwck4wZjNCdnJ0MkhNdzZzNUhvcEF2UlFpc1VxSmxNUVp0WXB4d3l6WHVMY2ZCTDZPOVBZYk4wd19vekcxX1FPaGUzWDhxRnlSQnRGU0N1X21ydmpTV192QTVtVWNfd2FrVk5wMVYzQXBJTWE2ZGpNaVB1aFl4Vy1POUFpOWlmc2g0MUxyZ3FRalphWWxKMnZHT0VfS1FBREh1NnEtbXdyODZSR2JYRWh1b3pucGJJcmpKNWlsNW5uZHpXd9IB3wFBVV95cUxNQW1aM3BFY25YOTdIUWpSQS0tYnVLenA2OEJScjBUdjNWeVdoelBzYlZHa1ZvT0tHODQtM0dyRGJCNFN5TDVHeVBtc0ZsMEp6X0FyZkExM01XT3BLVkZ3d0pyeFNrRTE2ZklmSTQ0MUozZDhhRWlOQnFYUnBqdFJtSS1BM0xjZGVpZ2NTN0VodExTb3JreVJpeE81bFZ3OFpaZWk1c1psRWZiUmdKd2N2cDhlbjBUVVFZcnNDVzhkaUktalhfWWVqb1ZPODNkSlJMNVl5eDQ2b052aWoxYnNr?oc=5</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio coloca em risco 41% da ureia exportada no mundo - Notícias Agrícolas</t>
+          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNMG1PVUx2UWlmTFltaHVVQTRObV9jYlUwck4wZjNCdnJ0MkhNdzZzNUhvcEF2UlFpc1VxSmxNUVp0WXB4d3l6WHVMY2ZCTDZPOVBZYk4wd19vekcxX1FPaGUzWDhxRnlSQnRGU0N1X21ydmpTV192QTVtVWNfd2FrVk5wMVYzQXBJTWE2ZGpNaVB1aFl4Vy1POUFpOWlmc2g0MUxyZ3FRalphWWxKMnZHT0VfS1FBREh1NnEtbXdyODZSR2JYRWh1b3pucGJJcmpKNWlsNW5uZHpXd9IB3wFBVV95cUxNQW1aM3BFY25YOTdIUWpSQS0tYnVLenA2OEJScjBUdjNWeVdoelBzYlZHa1ZvT0tHODQtM0dyRGJCNFN5TDVHeVBtc0ZsMEp6X0FyZkExM01XT3BLVkZ3d0pyeFNrRTE2ZklmSTQ0MUozZDhhRWlOQnFYUnBqdFJtSS1BM0xjZGVpZ2NTN0VodExTb3JreVJpeE81bFZ3OFpaZWk1c1psRWZiUmdKd2N2cDhlbjBUVVFZcnNDVzhkaUktalhfWWVqb1ZPODNkSlJMNVl5eDQ2b052aWoxYnNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9417,22 +9417,22 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia dispara com conflito no Oriente Médio - Farmnews</t>
+          <t>Emenda de Sinésio Campos viabiliza três toneladas de calcário para fortalecer a agricultura familiar e reduzir queimadas - Assembleia Legislativa do Estado do Amazonas</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>03/03/2026 05:00</t>
+          <t>28/02/2026 05:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNTVFkcXZvVHN3dmdlVmU3LXI0Smh4SnJPOENuSHF6VkUxbzllQUpYOEQtQTNObEJnOHRuUFhCeDdKLWY5YzN6WGY0Uml3NUdJYmtpc3ROQVFHX3p3M1JQR3pydm5NY1pyUzFCUTYtcmpqNmt6bzRiYU44XzZOeC01ZmFrMmNOZHpxaExxTjVqdHNPcU9vTkNV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUWQ5TDJaY2ktbkxjR0p6QUozbGxFbDF4T3hzbXlEcUxpODRsTVJobUZBU19TRVBGYWs4Q0RjLUZJZi1nbDZWdHBJRzV3Y00ya2tsaGR6aDBOcldKTlY0SFc4TGtqTTB4TDlBUHVhdmg3SkFucTJOUk9mTG5UWE1qbjdwZWJiTnlYV09PWU5iMXNUdTBwUGZtSjR0dGNSUktJaXU4d2MxZVoxLURzWUxibmR1Snlrb21FbVlEN2pLa3gtVHdVUl9JbWpwVlppNG8zT1pVZDdfWVB5M2t2ODBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -9444,17 +9444,17 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
+          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>03/03/2026 05:00</t>
+          <t>27/02/2026 05:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
         </is>
       </c>
     </row>
@@ -9466,105 +9466,105 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Emenda de Sinésio Campos viabiliza três toneladas de calcário para fortalecer a agricultura familiar e reduzir queimadas - Assembleia Legislativa do Estado do Amazonas</t>
+          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>28/02/2026 05:00</t>
+          <t>26/02/2026 05:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUWQ5TDJaY2ktbkxjR0p6QUozbGxFbDF4T3hzbXlEcUxpODRsTVJobUZBU19TRVBGYWs4Q0RjLUZJZi1nbDZWdHBJRzV3Y00ya2tsaGR6aDBOcldKTlY0SFc4TGtqTTB4TDlBUHVhdmg3SkFucTJOUk9mTG5UWE1qbjdwZWJiTnlYV09PWU5iMXNUdTBwUGZtSjR0dGNSUktJaXU4d2MxZVoxLURzWUxibmR1Snlrb21FbVlEN2pLa3gtVHdVUl9JbWpwVlppNG8zT1pVZDdfWVB5M2t2ODBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
+          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>27/02/2026 05:00</t>
+          <t>25/02/2026 05:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
+          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>26/02/2026 05:00</t>
+          <t>25/02/2026 05:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
+          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>25/02/2026 05:00</t>
+          <t>20/02/2026 05:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
+          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado Federal</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>25/02/2026 05:00</t>
+          <t>20/02/2026 05:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
+          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
+          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -9608,129 +9608,129 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado Federal</t>
+          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>19/02/2026 05:00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
+          <t>Fechamento parcial do Estreito de Ormuz pode afetar exportação de adubo - CNN Brasil</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>18/02/2026 05:00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPX3IwUGNvbTRzV21HeWt2UnZpUnhLZjNybFh3M0dZckYzT1otNFczeWFjQzdlNGx1ckFuaThmVjhsVWgxd19SSE42SldPNzdlZEhocHJZNmJYVkl3LXpsdUdUWkprREVjMkFnSDF6UVJsdktBMFFqN2xKeUtfNzNiQ3ppcXNER1Q2VmRTTzZkdm5BcEdSRGl6Y3R5UG9KV3BoQ1g0cDVFUi1kQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
+          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - ParaibaOnline</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>19/02/2026 05:00</t>
+          <t>18/02/2026 05:00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - ParaibaOnline</t>
+          <t>Grolime brings high-performance benefits for Scottish soils</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>18/02/2026 05:00</t>
+          <t>14/02/2026 06:00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57d63e527b4fdb8e988d262a223137&amp;url=https%3a%2f%2fwww.thescottishfarmer.co.uk%2fnews%2f25845962.grolime-brings-high-performance-benefits-scottish-soils%2f&amp;c=18200927900201231641&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Grolime brings high-performance benefits for Scottish soils</t>
+          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>14/02/2026 06:00</t>
+          <t>13/02/2026 05:00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57c11151b3467da82865eeb19af6e4&amp;url=https%3a%2f%2fwww.thescottishfarmer.co.uk%2fnews%2f25845962.grolime-brings-high-performance-benefits-scottish-soils%2f&amp;c=18200927900201231641&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
+          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -9740,29 +9740,29 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
+          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>13/02/2026 05:00</t>
+          <t>12/02/2026 05:00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -9774,17 +9774,17 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
+          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>12/02/2026 05:00</t>
+          <t>11/02/2026 05:00</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -9796,39 +9796,39 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
+          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>11/02/2026 05:00</t>
+          <t>06/02/2026 05:00</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
+          <t>Estado da Bahia questiona venda de US$1 bilhão da Equinox Gold - BNamericas</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>06/02/2026 05:00</t>
+          <t>05/02/2026 05:00</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOTnkzbHIzdDBtODZNZEFjelo2S0UycE01VVYwREI0R25wVjZYUS1VYnJkQU5UbjAzNWhMeDBwMW04VHZpRlcydVQtUDBmNzRYeTlSaFQ4NjRKdEsyRE5mX25rTDUxWnVha3kwNXNmWC1WYnk2aVlmMGxzMTVPUTY5ZWNZWk8tWU55N0ZzeC05NzlpMTdTZDJPQ3BSY0tZdVB3cEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -9840,17 +9840,17 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Estado da Bahia questiona venda de US$1 bilhão da Equinox Gold - BNamericas</t>
+          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>05/02/2026 05:00</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOTnkzbHIzdDBtODZNZEFjelo2S0UycE01VVYwREI0R25wVjZYUS1VYnJkQU5UbjAzNWhMeDBwMW04VHZpRlcydVQtUDBmNzRYeTlSaFQ4NjRKdEsyRE5mX25rTDUxWnVha3kwNXNmWC1WYnk2aVlmMGxzMTVPUTY5ZWNZWk8tWU55N0ZzeC05NzlpMTdTZDJPQ3BSY0tZdVB3cEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -9872,41 +9872,41 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
+          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado Federal</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado Federal</t>
+          <t>CBPM reage à venda indevida de operação da Equinox Gold na Bahia - Bahia Notícias</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOb0dyblk0a1dSem1LdjFxOThPbld2Snp3VEd3RjU3WWVLRVJwc18wU2FLVUZ6U0tZMUlJbDNjb1FycDRNWFdMemF0T0ZvUGNZYl9CeGlZeWpHYWZRakJuMHlzSWVVeUk0dFQ5MUlnZk1vZHRlLTR3d0U5Y3M1OVpTUkFYNlJmOV9ka2NDS2pLMGtqN21mcE9BUlR1dDAwNHdhdzhQM05IOWlKQjNoZmZ1b3V3?oc=5</t>
         </is>
       </c>
     </row>
@@ -9950,17 +9950,17 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>CBPM reage à venda indevida de operação da Equinox Gold na Bahia - Bahia Notícias</t>
+          <t>China vai investir quase US$ 1 bilhão para assumir minas de ouro no Brasil, controlar milhões de onças do metal e reforçar sua posição global no setor de mineração estratégica - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>03/02/2026 05:00</t>
+          <t>02/02/2026 05:00</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOb0dyblk0a1dSem1LdjFxOThPbld2Snp3VEd3RjU3WWVLRVJwc18wU2FLVUZ6U0tZMUlJbDNjb1FycDRNWFdMemF0T0ZvUGNZYl9CeGlZeWpHYWZRakJuMHlzSWVVeUk0dFQ5MUlnZk1vZHRlLTR3d0U5Y3M1OVpTUkFYNlJmOV9ka2NDS2pLMGtqN21mcE9BUlR1dDAwNHdhdzhQM05IOWlKQjNoZmZ1b3V3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQMkQtMmxTWjZWVEdwcmZYell3OU1VRTl6Z1BTS012WVV3UndnYnZMZ0dLR3pIeElIUndoTlhXLTlQUTVIQnVzcTc4UTgtcm1HSmtjWnhOVkxJdktFSS15dm9jSXpJR19zd1RhcTVzV2ljV21mMnYyMzNoWngyTkt2RmRKN1doQmFEZDAya3BYQ0VOYkN3d01UZkZET3dKWFFSNTdZMEI0bG80Z0pLMXpyWWtQR0ktUG5ab2pISlZVWFhGWVA0cV84RUR6R051Uno1WVd2RVdmQmdiSEhpZ25HQmJjMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -9994,51 +9994,51 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>China vai investir quase US$ 1 bilhão para assumir minas de ouro no Brasil, controlar milhões de onças do metal e reforçar sua posição global no setor de mineração estratégica - CPG Click Petróleo e Gás</t>
+          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>02/02/2026 05:00</t>
+          <t>01/02/2026 05:00</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQMkQtMmxTWjZWVEdwcmZYell3OU1VRTl6Z1BTS012WVV3UndnYnZMZ0dLR3pIeElIUndoTlhXLTlQUTVIQnVzcTc4UTgtcm1HSmtjWnhOVkxJdktFSS15dm9jSXpJR19zd1RhcTVzV2ljV21mMnYyMzNoWngyTkt2RmRKN1doQmFEZDAya3BYQ0VOYkN3d01UZkZET3dKWFFSNTdZMEI0bG80Z0pLMXpyWWtQR0ktUG5ab2pISlZVWFhGWVA0cV84RUR6R051Uno1WVd2RVdmQmdiSEhpZ25HQmJjMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
+          <t>Cientistas descobrem molécula no espaço que indica a origem da vida - CNN Brasil</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>01/02/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMUU2NHlFRDNUSjdSQUdPUllVQi1ZbC1UeEhUTEpiQzhITm8teWR1czBGQ2JYaUZDdEdhS2NxUGF2eHU3WjNCQThrOTV3d3BoNC0zOW1oMnhNY0NiMm9ubXdBVk1xa01IcmpMemNaYjhjeTJhV1BJOElvdEQ3bTM5azVVSDZZejdxU0hwb1Jzbnp0OE9ybkFRWjk0bjBqZXJrNllQdXUtRTU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Cientistas descobrem molécula no espaço que indica a origem da vida - CNN Brasil</t>
+          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -10048,19 +10048,19 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMUU2NHlFRDNUSjdSQUdPUllVQi1ZbC1UeEhUTEpiQzhITm8teWR1czBGQ2JYaUZDdEdhS2NxUGF2eHU3WjNCQThrOTV3d3BoNC0zOW1oMnhNY0NiMm9ubXdBVk1xa01IcmpMemNaYjhjeTJhV1BJOElvdEQ3bTM5azVVSDZZejdxU0hwb1Jzbnp0OE9ybkFRWjk0bjBqZXJrNllQdXUtRTU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
+          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -10070,29 +10070,29 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
+          <t>Rio Doce oferece análise de solo gratuita para fomentar a produtividade e sustentabilidade no campo - Jornal Panorama Minas</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>27/01/2026 05:00</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQVENaMzhzbm5GOUR3UFBNU2Y5RDNlU2ppUmhXZW9GVnE1NWNxanpBS0Z6S2xrc2Y0eUh4UmFURExNeFBTc2VscUUtSi0tZkRLQ0haeUpfcTlUNV9KZ0VUZXMwZ0phYXNPVU5zcWRiRTdrZlJSQllRLUx5MzE0dktrRjZwX1RKYWg0VmtaSmVYQ2NpM0I3Mi1NZ0FJQk8zMzYxcWdxWDNiOENKN18yVTczTE9PeFY4bEl1MmhxdDdOX1FEaXM1cTQyeEk4dVkxbm43?oc=5</t>
         </is>
       </c>
     </row>
@@ -10121,22 +10121,22 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Rio Doce oferece análise de solo gratuita para fomentar a produtividade e sustentabilidade no campo - Jornal Panorama Minas</t>
+          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>27/01/2026 05:00</t>
+          <t>23/01/2026 05:00</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQVENaMzhzbm5GOUR3UFBNU2Y5RDNlU2ppUmhXZW9GVnE1NWNxanpBS0Z6S2xrc2Y0eUh4UmFURExNeFBTc2VscUUtSi0tZkRLQ0haeUpfcTlUNV9KZ0VUZXMwZ0phYXNPVU5zcWRiRTdrZlJSQllRLUx5MzE0dktrRjZwX1RKYWg0VmtaSmVYQ2NpM0I3Mi1NZ0FJQk8zMzYxcWdxWDNiOENKN18yVTczTE9PeFY4bEl1MmhxdDdOX1FEaXM1cTQyeEk4dVkxbm43?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
+          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -10158,29 +10158,29 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
+          <t>Como um sabonete de enxofre virou um hit de vendas na Granado - Valor Econômico</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>23/01/2026 05:00</t>
+          <t>14/01/2026 05:00</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOd0MzT0JQQ0NDVURyWFJKaHdOUDQ5c0sxbUM5RmxYVVFjZ1R3X00xNndfT2lMNWx4VjJfOEx6OFVTZE82bVJKMm1sdGVEeHBtc3pXM0djSllfOHRod01TRUEzdGdtNGIydDVjX3IzeW03Rlk2LUdrTTlfdF9PYzNxU3BYZW84c09pSHV4ZHNIM2VhOWdCQXVzSjhYejBRVWxYeGY2WktaS3NuR08yVnl6YnczMFROYktWUG02NVh2YTVxcVlWcGt5b3NZV2FHUTFjMlJ6T2lQR3dIZnPSAeoBQVVfeXFMTkMwSmdaUTlwTllwcnNxNDVqc2hPRHB5WDdROVdMWXRWaGs3U3M2cmU4MWNnNHFRd2dYeVM0bDNER0pKaTFRTThOcV9nYmNLTmU4TERRWmRsaVpzcmxvSE5xUmtmMldaODY0d2t1a280SFVmMXdCcUJYOENrUkxCcC0yWGVBeUZlYXVQN2lnWS1HdFdvTFIzdWJ5NTY2Tng0UlQ2M2RVTmlQTVNGV3RLVWRZYWxfNUYzZjNwalFfaFBIT212TmtiR1hpYS1rN3lwb2dWQzRvRHdHODdSd1Jrcms5X2wxMzdhaXB3?oc=5</t>
         </is>
       </c>
     </row>
@@ -10192,29 +10192,29 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Como um sabonete de enxofre virou um hit de vendas na Granado - Valor Econômico</t>
+          <t>Combinação Potássio e Enxofre maximiza potencial da soja - Agrolink</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>14/01/2026 05:00</t>
+          <t>13/01/2026 05:00</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOd0MzT0JQQ0NDVURyWFJKaHdOUDQ5c0sxbUM5RmxYVVFjZ1R3X00xNndfT2lMNWx4VjJfOEx6OFVTZE82bVJKMm1sdGVEeHBtc3pXM0djSllfOHRod01TRUEzdGdtNGIydDVjX3IzeW03Rlk2LUdrTTlfdF9PYzNxU3BYZW84c09pSHV4ZHNIM2VhOWdCQXVzSjhYejBRVWxYeGY2WktaS3NuR08yVnl6YnczMFROYktWUG02NVh2YTVxcVlWcGt5b3NZV2FHUTFjMlJ6T2lQR3dIZnPSAeoBQVVfeXFMTkMwSmdaUTlwTllwcnNxNDVqc2hPRHB5WDdROVdMWXRWaGs3U3M2cmU4MWNnNHFRd2dYeVM0bDNER0pKaTFRTThOcV9nYmNLTmU4TERRWmRsaVpzcmxvSE5xUmtmMldaODY0d2t1a280SFVmMXdCcUJYOENrUkxCcC0yWGVBeUZlYXVQN2lnWS1HdFdvTFIzdWJ5NTY2Tng0UlQ2M2RVTmlQTVNGV3RLVWRZYWxfNUYzZjNwalFfaFBIT212TmtiR1hpYS1rN3lwb2dWQzRvRHdHODdSd1Jrcms5X2wxMzdhaXB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Combinação Potássio e Enxofre maximiza potencial da soja - Agrolink</t>
+          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -10224,29 +10224,29 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
+          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>13/01/2026 05:00</t>
+          <t>07/01/2026 05:00</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
         </is>
       </c>
     </row>
@@ -10258,39 +10258,39 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
+          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>07/01/2026 05:00</t>
+          <t>06/01/2026 05:00</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
+          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>06/01/2026 05:00</t>
+          <t>30/12/2025 05:00</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
         </is>
       </c>
     </row>
@@ -10319,22 +10319,22 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
+          <t>Brasil: Chinesa CMOC adquire minas de ouro no por US$ 1 bilhão - e-global.pt</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>30/12/2025 05:00</t>
+          <t>24/12/2025 17:01</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNLWFuM2JWaW9naUMzN2w1dUU3UGktbjVNT0ROLUhpRXJnTDVsaXdQWnp3ZHp2bmd6Y1d0STgxNW5WeFRpYzR3QUUtM3NxUm5wbjV0Qkt2Mnd4aTQ1bkpfYV9QbVVCcFJqUkRZR2lQWFppeHVvbUVzVU9sWEcwM056cEdnNk9tMGpnNVJPUWZNVzBOdjZYSEFrLWtuQ3I4MmZ2OUpzRl9mOUk2MXfSAbABQVVfeXFMT000eWZFNU5UZHNSTDd2QzBrZVZQMm1tdm40akZTaGtFMEktNGp3SVlIdEJDbVQtMEx1b1RHQzR4US1xY3BuNWd6ajRYcEdzQkNXSXZmNElLRUE3bnlHSXRQVzZIVnhTRzlZbUw5a0ZrTzk0czFtQkM0RW5VaGE1bk1WMWdvZDQ3b3U5Vk00NTVuRmwwbHhIVHpCM2VYRklweEdPQm9Ba2dfUENqb2tpZEo?oc=5</t>
         </is>
       </c>
     </row>
@@ -10346,73 +10346,73 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Brasil: Chinesa CMOC adquire minas de ouro no por US$ 1 bilhão - e-global.pt</t>
+          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>24/12/2025 17:01</t>
+          <t>20/12/2025 05:00</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNLWFuM2JWaW9naUMzN2w1dUU3UGktbjVNT0ROLUhpRXJnTDVsaXdQWnp3ZHp2bmd6Y1d0STgxNW5WeFRpYzR3QUUtM3NxUm5wbjV0Qkt2Mnd4aTQ1bkpfYV9QbVVCcFJqUkRZR2lQWFppeHVvbUVzVU9sWEcwM056cEdnNk9tMGpnNVJPUWZNVzBOdjZYSEFrLWtuQ3I4MmZ2OUpzRl9mOUk2MXfSAbABQVVfeXFMT000eWZFNU5UZHNSTDd2QzBrZVZQMm1tdm40akZTaGtFMEktNGp3SVlIdEJDbVQtMEx1b1RHQzR4US1xY3BuNWd6ajRYcEdzQkNXSXZmNElLRUE3bnlHSXRQVzZIVnhTRzlZbUw5a0ZrTzk0czFtQkM0RW5VaGE1bk1WMWdvZDQ3b3U5Vk00NTVuRmwwbHhIVHpCM2VYRklweEdPQm9Ba2dfUENqb2tpZEo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
+          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>20/12/2025 05:00</t>
+          <t>19/12/2025 05:00</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>19/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
+          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10444,19 +10444,19 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
+          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Jornal Portuário</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOejlYQmU1SzhnRGtFMFJKWU9sNFZmM01temlpNFdjTVRTQzdqeFFwM0hZUzlIVlJZa2pGaGo1UVdmTXd0dGRtX041d1ptUVdvUmNfTnNlM2ppdmFEMUtlMlZVNzBvWlZyaVlGZUpOV19CR0FKeXFKU21yWEo4Q0RoMnEzdHV2Zk1ZR0prQzRnQzNzOGR1OGwwQkFYM2hwemo0emFXQ0tkUmR6a3NnYWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Jornal Portuário</t>
+          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOejlYQmU1SzhnRGtFMFJKWU9sNFZmM01temlpNFdjTVRTQzdqeFFwM0hZUzlIVlJZa2pGaGo1UVdmTXd0dGRtX041d1ptUVdvUmNfTnNlM2ppdmFEMUtlMlZVNzBvWlZyaVlGZUpOV19CR0FKeXFKU21yWEo4Q0RoMnEzdHV2Zk1ZR0prQzRnQzNzOGR1OGwwQkFYM2hwemo0emFXQ0tkUmR6a3NnYWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10522,17 +10522,17 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
+          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10561,12 +10561,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10605,12 +10605,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
+          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -10620,19 +10620,19 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -10642,29 +10642,29 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
+          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
+          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
+          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
+          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
+          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10830,17 +10830,17 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>14/12/2025 05:00</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
+          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10874,183 +10874,183 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
+          <t>SUSTENTABILIDADE | CMOC Brasil é reconhecida pelo Selo ODS Brasil 2025 - Brasil Mineral</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>14/12/2025 05:00</t>
+          <t>13/12/2025 05:00</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSzczY2JlaXVTMkliamlDU3cwMU1nTFl5WWotNkFyc2tZckV5ZDl6OG80eEZtTjVOZlp2OThITVZpYVdYcDhGN1p3Yk1VTFRzblhKZGh1cnlsMjZQeHFRMm9lV1VhZGxsMWFTX2J4NV90NFZiZlA0RkRPU3NyWDdQUXJyWWhrNWUtQVFONVM3eUVYLXAzVW1xMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>SUSTENTABILIDADE | CMOC Brasil é reconhecida pelo Selo ODS Brasil 2025 - Brasil Mineral</t>
+          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>13/12/2025 05:00</t>
+          <t>07/12/2025 19:00</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSzczY2JlaXVTMkliamlDU3cwMU1nTFl5WWotNkFyc2tZckV5ZDl6OG80eEZtTjVOZlp2OThITVZpYVdYcDhGN1p3Yk1VTFRzblhKZGh1cnlsMjZQeHFRMm9lV1VhZGxsMWFTX2J4NV90NFZiZlA0RkRPU3NyWDdQUXJyWWhrNWUtQVFONVM3eUVYLXAzVW1xMg?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57d63e527b4fdb8e988d262a223137&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
+          <t>Parabenos e dióxido de enxofre fazem mal à saúde? Conheça esses conservantes - Olhar Digital</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>07/12/2025 19:00</t>
+          <t>05/12/2025 05:00</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57c11151b3467da82865eeb19af6e4&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNdWF2bGw2UWZLUTRmVzV4TE1UYlVkQjl6Q1NQMFZ6VVBsZzBMYUk0aWhfYmp2czBONHFCejlJeFVfNGVQQ3RDd2JuTUhJdFFPbHgzSV8tRU9BZTk2aS1ncFZDOUhBZkV4TGh0ZmthdnVjRnFwQng5VGhUQW9MZENYVG9ReDBGTC1IS0VtZkhCaS02VG5wV21UQ2xvc2xva1NHQWh6M1M5cG5CZHk3UkFXMjNpdllxeVQ4TW84bHFWcWhUMzlOR0tOckRua0w?oc=5</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Parabenos e dióxido de enxofre fazem mal à saúde? Conheça esses conservantes - Olhar Digital</t>
+          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>05/12/2025 05:00</t>
+          <t>02/12/2025 05:00</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNdWF2bGw2UWZLUTRmVzV4TE1UYlVkQjl6Q1NQMFZ6VVBsZzBMYUk0aWhfYmp2czBONHFCejlJeFVfNGVQQ3RDd2JuTUhJdFFPbHgzSV8tRU9BZTk2aS1ncFZDOUhBZkV4TGh0ZmthdnVjRnFwQng5VGhUQW9MZENYVG9ReDBGTC1IS0VtZkhCaS02VG5wV21UQ2xvc2xva1NHQWh6M1M5cG5CZHk3UkFXMjNpdllxeVQ4TW84bHFWcWhUMzlOR0tOckRua0w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
+          <t>Escalada global do enxofre pressiona mercado - Agrolink</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>02/12/2025 05:00</t>
+          <t>01/12/2025 05:00</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXVxLVFyVkN1SnNXVXZMa3hWU2VjVkNuZXRuWTZ4QTJ3bjl5ZTdEb1FFaXV1RC1aWjdBcVZWR09LNm9pWS1LdUdHbTZ2bThXc2l1WVV5eDYyQ081cXZEOW14UVh3T2RFTWFtTi1yUWstM0RMS2JiLTVLLWx2dFl5R2xFbEdUMnRxNVZVVm5sUGpCNU1WTnA3OQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Escalada global do enxofre pressiona mercado - Agrolink</t>
+          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>01/12/2025 05:00</t>
+          <t>26/11/2025 03:44</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXVxLVFyVkN1SnNXVXZMa3hWU2VjVkNuZXRuWTZ4QTJ3bjl5ZTdEb1FFaXV1RC1aWjdBcVZWR09LNm9pWS1LdUdHbTZ2bThXc2l1WVV5eDYyQ081cXZEOW14UVh3T2RFTWFtTi1yUWstM0RMS2JiLTVLLWx2dFl5R2xFbEdUMnRxNVZVVm5sUGpCNU1WTnA3OQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
+          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>26/11/2025 03:44</t>
+          <t>24/11/2025 05:00</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
+          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>24/11/2025 05:00</t>
+          <t>19/11/2025 05:00</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
+          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
         </is>
       </c>
     </row>
@@ -11094,73 +11094,73 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>19/11/2025 05:00</t>
+          <t>17/11/2025 13:00</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57d63d5b7148ad97fe9681cf91c9e6&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
+          <t>Alta do enxofre supera 130% em 2025 - Agrolink</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>17/11/2025 13:00</t>
+          <t>11/11/2025 05:00</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57c110a19a4bcd9ed6b34bdcfc7c0d&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Alta do enxofre supera 130% em 2025 - Agrolink</t>
+          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>11/11/2025 05:00</t>
+          <t>30/10/2025 04:00</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
+          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -11170,29 +11170,29 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
+          <t>Alta explosiva: preço do enxofre dispara 115% e ameaça elevar custos da agricultura - CompreRural</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>30/10/2025 04:00</t>
+          <t>29/10/2025 04:00</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOaVRLcmRCTmtsX0FhdlRBTDJXVXpacVE1a1pOdi1yTlBPSlg1TndpelpzMjBIeTFseEd5MjU2ZWdCRVNNVUZleWtDRjVaUnZxRVUzZkN2bjhaZENsSU1ZSktHNlMzaDF0YTNOY0VmdnYyUllnWFVJVWJSaUVFVmQ0VnRZUFRDQ2thRVFLaEhpcXNlWWp4ZGF2WWJNbTI3d0xpQjFUdE5KTEw5a09XN2Rv?oc=5</t>
         </is>
       </c>
     </row>
@@ -11204,215 +11204,215 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Alta explosiva: preço do enxofre dispara 115% e ameaça elevar custos da agricultura - CompreRural</t>
+          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>29/10/2025 04:00</t>
+          <t>27/10/2025 04:00</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOaVRLcmRCTmtsX0FhdlRBTDJXVXpacVE1a1pOdi1yTlBPSlg1TndpelpzMjBIeTFseEd5MjU2ZWdCRVNNVUZleWtDRjVaUnZxRVUzZkN2bjhaZENsSU1ZSktHNlMzaDF0YTNOY0VmdnYyUllnWFVJVWJSaUVFVmQ0VnRZUFRDQ2thRVFLaEhpcXNlWWp4ZGF2WWJNbTI3d0xpQjFUdE5KTEw5a09XN2Rv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
+          <t>O composto. Fundamental para a captura de carbono no solo - vozdocampo.pt</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>27/10/2025 04:00</t>
+          <t>17/10/2025 04:00</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE5xMkJkQi05dzl4R3RabU44d0U0NnB1cmE3ZTBUQkpjTWJaVTB5c2VpVE0yUEV5VmQ1NkIySE9ma1FBdFE5NTRyRVpIRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>O composto. Fundamental para a captura de carbono no solo - vozdocampo.pt</t>
+          <t>O Caminho do Peabiru é tema de seminário na Unila em Foz do Iguaçu - Brasil de Fato</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>17/10/2025 04:00</t>
+          <t>14/10/2025 04:00</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE5xMkJkQi05dzl4R3RabU44d0U0NnB1cmE3ZTBUQkpjTWJaVTB5c2VpVE0yUEV5VmQ1NkIySE9ma1FBdFE5NTRyRVpIRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQSXdlQlZodk0zOGYzclFlMzhEZEJIOUhhRy1YMG9MVEdCUHR4VUhlNFQ4MG1MQWppb2xBQ3VYMFg1ZnVjSzZMbnA1WXJISldSYkFfLTF4RVpvNHBXUnFIaGpzNVFYalZQbEZiSE9oTVpnTUJyb0FOTHdkTGF3eWg4ZWRCZ3JjQ3ZSRE5EYzNjdnktRXBMbnViMHlTaDBHaDVOU0RobzQtNXZMakNpeUUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>O Caminho do Peabiru é tema de seminário na Unila em Foz do Iguaçu - Brasil de Fato</t>
+          <t>De 100 mil a 1,2 milhão: UGC faz sabonete de enxofre da Granado multiplicar as vendas - Mundo do Marketing</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>14/10/2025 04:00</t>
+          <t>13/10/2025 04:00</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQSXdlQlZodk0zOGYzclFlMzhEZEJIOUhhRy1YMG9MVEdCUHR4VUhlNFQ4MG1MQWppb2xBQ3VYMFg1ZnVjSzZMbnA1WXJISldSYkFfLTF4RVpvNHBXUnFIaGpzNVFYalZQbEZiSE9oTVpnTUJyb0FOTHdkTGF3eWg4ZWRCZ3JjQ3ZSRE5EYzNjdnktRXBMbnViMHlTaDBHaDVOU0RobzQtNXZMakNpeUUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTWprTW9RT3lxQkVOTjZ3QzVvX2R0RHhCZUxFeE1BNGtMY3VKc1Z4NWViSEYyLXdFQnRkWlYwTEZSOHg4UHpQLTJ3RDEySk9Ld2xkaGp4WnVLQWUtcFdrVzcyQ01pUGxfS2lwbzNERGp3WVdYYmdTd2h6SUxVdEhnUHdDRG5Hb2lRZjlBNUQ5QU1MYnlDV3kyRHpFR3lRcXNMa2xDMTR6Y2ZSaE1JczI2RkpENGU1VE0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>De 100 mil a 1,2 milhão: UGC faz sabonete de enxofre da Granado multiplicar as vendas - Mundo do Marketing</t>
+          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>13/10/2025 04:00</t>
+          <t>10/10/2025 04:00</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTWprTW9RT3lxQkVOTjZ3QzVvX2R0RHhCZUxFeE1BNGtMY3VKc1Z4NWViSEYyLXdFQnRkWlYwTEZSOHg4UHpQLTJ3RDEySk9Ld2xkaGp4WnVLQWUtcFdrVzcyQ01pUGxfS2lwbzNERGp3WVdYYmdTd2h6SUxVdEhnUHdDRG5Hb2lRZjlBNUQ5QU1MYnlDV3kyRHpFR3lRcXNMa2xDMTR6Y2ZSaE1JczI2RkpENGU1VE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
+          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>10/10/2025 04:00</t>
+          <t>09/10/2025 04:00</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
+          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>09/10/2025 04:00</t>
+          <t>01/10/2025 04:00</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
+          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>01/10/2025 04:00</t>
+          <t>21/09/2025 04:00</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
+          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>21/09/2025 04:00</t>
+          <t>15/09/2025 04:00</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGR6N2hWX3A2ZGR4RmJWbWNqdnBqUGktU25QbDhLZUlvSmVIVERqRVpTazJKRlFSdzBfQ2s3UzJJZFN6dHd5TllCZXR6SGYxV3llYUFwdlFlSDZEWi1jb1V0bXVfVDVQZTNjWVRXcnZ3WDVPVUlaZ2xhZXNFcmNBUXlPdGFZdVFrVkM4RTZkNjEzTXMzT3RodVJSS3ZvMkxlXy1pbDl2OU1vVlY5dU9NVHp3LVU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
+          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>15/09/2025 04:00</t>
+          <t>08/09/2025 05:38</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGR6N2hWX3A2ZGR4RmJWbWNqdnBqUGktU25QbDhLZUlvSmVIVERqRVpTazJKRlFSdzBfQ2s3UzJJZFN6dHd5TllCZXR6SGYxV3llYUFwdlFlSDZEWi1jb1V0bXVfVDVQZTNjWVRXcnZ3WDVPVUlaZ2xhZXNFcmNBUXlPdGFZdVFrVkM4RTZkNjEzTXMzT3RodVJSS3ZvMkxlXy1pbDl2OU1vVlY5dU9NVHp3LVU?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57d63d5b7148ad97fe9681cf91c9e6&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -11424,61 +11424,61 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
+          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>08/09/2025 05:38</t>
+          <t>02/09/2025 14:00</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57c110a19a4bcd9ed6b34bdcfc7c0d&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57d63d5b7148ad97fe9681cf91c9e6&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
+          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>02/09/2025 14:00</t>
+          <t>02/09/2025 04:00</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a57c110a19a4bcd9ed6b34bdcfc7c0d&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
+          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>02/09/2025 04:00</t>
+          <t>01/09/2025 04:00</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
+          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -11500,205 +11500,205 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
+          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>15/08/2025 04:00</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
+          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>15/08/2025 04:00</t>
+          <t>13/08/2025 04:00</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
+          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>13/08/2025 04:00</t>
+          <t>11/08/2025 04:00</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWU80YXJ5NDJUWmw1VjJscFpVbDRWVlJsM09lZ3Vjdkg4czlKekxPUWJUWXpaQjg4WDZONGk1MjdxV29mRm1aTHZWRG5FeUFsWHpPTk50VFVhak9QU1dYak9tM3Buc21nRGxmLTljbzNSd1I2ZVlZa2luY3BrRGIwb1lTcml2RU1NMUlrdmt6WVExREs4S1psdHdXM3czY2pUcjBzeU92UDhpZ0lELTFZQjZaaHN6WVY1WjRDWmdJZklfV2dpbWk0ZDBjUk8xcDlnQjU0X05nU01idTJCZmNmUmNZUXpaRWZveHBv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
+          <t>Trabalhadores da Manserv entram em greve e exigem jornada 4×4 e melhores condições de trabalho - Badiinho</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>11/08/2025 04:00</t>
+          <t>06/08/2025 04:00</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWU80YXJ5NDJUWmw1VjJscFpVbDRWVlJsM09lZ3Vjdkg4czlKekxPUWJUWXpaQjg4WDZONGk1MjdxV29mRm1aTHZWRG5FeUFsWHpPTk50VFVhak9QU1dYak9tM3Buc21nRGxmLTljbzNSd1I2ZVlZa2luY3BrRGIwb1lTcml2RU1NMUlrdmt6WVExREs4S1psdHdXM3czY2pUcjBzeU92UDhpZ0lELTFZQjZaaHN6WVY1WjRDWmdJZklfV2dpbWk0ZDBjUk8xcDlnQjU0X05nU01idTJCZmNmUmNZUXpaRWZveHBv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9fN3VVZmJNM2pGMzB3V19FM1N4d3hpWnVaMUZvZUtXWXZhUFFCSXMxNXlyTUt6dnQyalF6bFNZN0ZPcW5QVWp1dDV2d1FoX19nRzg4VXJjaG93OUJYSndmTEdCUDBacHFyUVRBNTFaRmhiYzBhcVQtV9IBfkFVX3lxTFBuc1ZCZ1hCOFRSdVBxVktkYldTdUE0QUkzQzEybEZzVXplV1A2MlRscGxudmhPOW9xNTlic25DVURrMWhIaW9QS3ZfNl92OWJzS1FkeXhQMXpaWGVidUhjeWtmamR6MmNsZkV6ZTVneVdsYkQ4RnA4OEpSTFNfUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Trabalhadores da Manserv entram em greve e exigem jornada 4×4 e melhores condições de trabalho - Badiinho</t>
+          <t>O futuro circular do agro: como cientistas e empresas estão transformando resíduos em fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>06/08/2025 04:00</t>
+          <t>02/08/2025 04:00</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9fN3VVZmJNM2pGMzB3V19FM1N4d3hpWnVaMUZvZUtXWXZhUFFCSXMxNXlyTUt6dnQyalF6bFNZN0ZPcW5QVWp1dDV2d1FoX19nRzg4VXJjaG93OUJYSndmTEdCUDBacHFyUVRBNTFaRmhiYzBhcVQtV9IBfkFVX3lxTFBuc1ZCZ1hCOFRSdVBxVktkYldTdUE0QUkzQzEybEZzVXplV1A2MlRscGxudmhPOW9xNTlic25DVURrMWhIaW9QS3ZfNl92OWJzS1FkeXhQMXpaWGVidUhjeWtmamR6MmNsZkV6ZTVneVdsYkQ4RnA4OEpSTFNfUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOdXhBZ1hpcXVfVG11ME5ZRUZZOG1DNUM3Rk55dmNoNGNLbVVqcjZZanVVRkZJV24wc1c3VktmWUFpR2steTRQdkJzbzdLU29WQU5kb2lmalhLSlFQdmFCbU9helVFTzZWZThyWExESVhOX3VRTE1GTGZFMmtEOWo2SkY5RDV6TzZwNXN6RFY1LVM3SjRzeTBkT3ZPWURzNFp3YWtKX05NWnM0dWNEQUV0amNqbW52RzJqaUxVMFIzT3EzR0U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>O futuro circular do agro: como cientistas e empresas estão transformando resíduos em fertilizantes - AgFeed</t>
+          <t>WILSON HUSUM, Limestone Carrier - Detalhes e posição atual - IMO 9017379 - VesselFinder</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>02/08/2025 04:00</t>
+          <t>01/08/2025 21:12</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOdXhBZ1hpcXVfVG11ME5ZRUZZOG1DNUM3Rk55dmNoNGNLbVVqcjZZanVVRkZJV24wc1c3VktmWUFpR2steTRQdkJzbzdLU29WQU5kb2lmalhLSlFQdmFCbU9helVFTzZWZThyWExESVhOX3VRTE1GTGZFMmtEOWo2SkY5RDV6TzZwNXN6RFY1LVM3SjRzeTBkT3ZPWURzNFp3YWtKX05NWnM0dWNEQUV0amNqbW52RzJqaUxVMFIzT3EzR0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9VeVpNZDZDc09nd0F4WWJFTGR0VGlYMmtiYV9OVjloQ254cllIaERRX3psSzVTaUJhNjdVcXJpZHFmQmVyUVhKc2tOSXZOYzhFaFF2OGNKMEVHNmxFU3FUeGh6VmszZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>WILSON HUSUM, Limestone Carrier - Detalhes e posição atual - IMO 9017379 - VesselFinder</t>
+          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>01/08/2025 21:12</t>
+          <t>01/08/2025 04:00</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9VeVpNZDZDc09nd0F4WWJFTGR0VGlYMmtiYV9OVjloQ254cllIaERRX3psSzVTaUJhNjdVcXJpZHFmQmVyUVhKc2tOSXZOYzhFaFF2OGNKMEVHNmxFU3FUeGh6VmszZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNUS1oVVdaYlNDQXh3VnlEd3Fsclg5UTI5VGxKQ0ZoVzNhRF9obkZPeWg2V3RZN1N3SmhGY0FYZ0dtZVV1MURfQmdEYVJ3cWpUVlNQY0lHdkp0bkQ1RTZXbFZnbkpha292TnZ5V3pxLW1LMjZDcVNiRk93Vm1KRmRRQlJSeEVRZEJJQWtzSElKX3ozaFJTMjdnOUNjUnF3S0duODYteQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - IBRAM - Mineração do Brasil</t>
+          <t>Emater-MG encerra segunda etapa da entrega de agrosilício a agricultores de Minas Gerais - emater.mg.gov.br</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>01/08/2025 04:00</t>
+          <t>31/07/2025 04:00</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNUS1oVVdaYlNDQXh3VnlEd3Fsclg5UTI5VGxKQ0ZoVzNhRF9obkZPeWg2V3RZN1N3SmhGY0FYZ0dtZVV1MURfQmdEYVJ3cWpUVlNQY0lHdkp0bkQ1RTZXbFZnbkpha292TnZ5V3pxLW1LMjZDcVNiRk93Vm1KRmRRQlJSeEVRZEJJQWtzSElKX3ozaFJTMjdnOUNjUnF3S0duODYteQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxONmF2eGdidE1Nai1hZ2E4bU84U3FqMWYzTlF0dEJQdVNxOHJuNmNlSDhWdG16cjJGcFRvd3luU2dQWjlNQ2NWb3M4R3JlNHRpUFg3TjlDM2E1eElCRzFNZ01vMUVEdl90THNLMU5MeHNONkd0ajl4TWI4Tm9nejlOWm5MUk82bUxWaHotWlkyWGl6MWUtWkkyT0NkalBkaEp5ajBreEc1b3dIcC1EaFZfQkotWnA2b2RtcktJbUUtWVlCZ2tobFZIb3N0dkdzaDViRXRkX0NHNG05ZjZJTTV6MENqQXAwMHF6QS1WcXFjWmVTbEstZVp0VDdNRW5ESk1UN05HZnkxLS1ZVXZRelVQOWFsU2xxSDhxNXpV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Emater-MG encerra segunda etapa da entrega de agrosilício a agricultores de Minas Gerais - emater.mg.gov.br</t>
+          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - Portal Serra Dourada News</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>31/07/2025 04:00</t>
+          <t>29/07/2025 04:00</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxONmF2eGdidE1Nai1hZ2E4bU84U3FqMWYzTlF0dEJQdVNxOHJuNmNlSDhWdG16cjJGcFRvd3luU2dQWjlNQ2NWb3M4R3JlNHRpUFg3TjlDM2E1eElCRzFNZ01vMUVEdl90THNLMU5MeHNONkd0ajl4TWI4Tm9nejlOWm5MUk82bUxWaHotWlkyWGl6MWUtWkkyT0NkalBkaEp5ajBreEc1b3dIcC1EaFZfQkotWnA2b2RtcktJbUUtWVlCZ2tobFZIb3N0dkdzaDViRXRkX0NHNG05ZjZJTTV6MENqQXAwMHF6QS1WcXFjWmVTbEstZVp0VDdNRW5ESk1UN05HZnkxLS1ZVXZRelVQOWFsU2xxSDhxNXpV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOZWZ1SmNscXJLQTgtcGo3S2JvMGM0UXhTRnAyVW9mYzFNYmNzMHRtTG5rNjJWWWg3c1pFeUVHczBRNEw2NVU1R3dlLW5hbTFYUXc0a0diRFBFWFBUVzFpLUkyNXpselV2TVBIcnZvNUhkNjEzN3ZzTjNvX0pvdVQzM3RJZkFmdkMtaFp3aHZRZ1gxN3kwdmZCNDJ6NFBjb2pyZHNIc2pwS0F6bUhtOEpoOVJNUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11710,39 +11710,39 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - Portal Serra Dourada News</t>
+          <t>Prefeitura de Catalão inicia obra de reconstrução da Estrada das Mineradoras com investimento de R$ 8,7 milhões - Badiinho</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>29/07/2025 04:00</t>
+          <t>24/07/2025 04:00</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOZWZ1SmNscXJLQTgtcGo3S2JvMGM0UXhTRnAyVW9mYzFNYmNzMHRtTG5rNjJWWWg3c1pFeUVHczBRNEw2NVU1R3dlLW5hbTFYUXc0a0diRFBFWFBUVzFpLUkyNXpselV2TVBIcnZvNUhkNjEzN3ZzTjNvX0pvdVQzM3RJZkFmdkMtaFp3aHZRZ1gxN3kwdmZCNDJ6NFBjb2pyZHNIc2pwS0F6bUhtOEpoOVJNUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE8yaU9FRkxwRUQwT09aeHp0VFMzekRwYzF2RmhZYjE5Zkx5ZksyU2FpcEZNZXVOSGE3Qy1JeDBRcmFJX0ZsOGYyQUNyb2VyT2xfemNGUGpLWmN4d3JVYTB1c0Y4NW1heDVUdk9LWXhB0gFzQVVfeXFMUEVzSzlPZ2ZNRmNiU3A4NEQzR2QtMDhrY3hOaGdzUEttWDlFam9YRzNVSHFPZzlSakxqbHNZRHJsaXlCc0F2YVhxRWkzNnNiZHB3dm1QZ3dUMEJKaHBPajlNM0lBdm9tMjBlbjlLUzdKS21uQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Prefeitura de Catalão inicia obra de reconstrução da Estrada das Mineradoras com investimento de R$ 8,7 milhões - Badiinho</t>
+          <t>AGREGADOS | Carmeuse investe quase R$ 2 bilhões em novas unidades para produzir cal em MG - Brasil Mineral</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>24/07/2025 04:00</t>
+          <t>23/07/2025 04:00</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE8yaU9FRkxwRUQwT09aeHp0VFMzekRwYzF2RmhZYjE5Zkx5ZksyU2FpcEZNZXVOSGE3Qy1JeDBRcmFJX0ZsOGYyQUNyb2VyT2xfemNGUGpLWmN4d3JVYTB1c0Y4NW1heDVUdk9LWXhB0gFzQVVfeXFMUEVzSzlPZ2ZNRmNiU3A4NEQzR2QtMDhrY3hOaGdzUEttWDlFam9YRzNVSHFPZzlSakxqbHNZRHJsaXlCc0F2YVhxRWkzNnNiZHB3dm1QZ3dUMEJKaHBPajlNM0lBdm9tMjBlbjlLUzdKS21uQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPcVhwQ1FTanBZbU41aHE3eUVXNTZlWGNTLUE5aS1GX1owNzd5SFFmNnFlN3Z5Q2tNOElmemM5TDhUekJOVkFpbWNjSm84cVEyT2NOalkxS19BM1c1NWQ3NTR4UEFXdWlCNVFsbnNLMWRFaUFHVktpYXZwSklETEQ4c1hrZkFxQ2JXRnFsX3JFTDVGRnYta1NaMS11clJXWTRLaFo4LUxTdFpYZzBGWGFCcTZEbGU0VXBzZHc?oc=5</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>AGREGADOS | Carmeuse investe quase R$ 2 bilhões em novas unidades para produzir cal em MG - Brasil Mineral</t>
+          <t>Uberlândia receberá investimento de R$ 200 milhões em fábrica de cal que gerará 80 vagas de emprego - G1</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPcVhwQ1FTanBZbU41aHE3eUVXNTZlWGNTLUE5aS1GX1owNzd5SFFmNnFlN3Z5Q2tNOElmemM5TDhUekJOVkFpbWNjSm84cVEyT2NOalkxS19BM1c1NWQ3NTR4UEFXdWlCNVFsbnNLMWRFaUFHVktpYXZwSklETEQ4c1hrZkFxQ2JXRnFsX3JFTDVGRnYta1NaMS11clJXWTRLaFo4LUxTdFpYZzBGWGFCcTZEbGU0VXBzZHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNSXFaOVI3bW9MNk1wUmppenNyUVE5WGhvVWl6V09EYlZXdS1KMTlhNzNwd0ZTaGFZc21PdTBGWU5TSkNrZF9xRXZqSWNtYUdMQ1pOTlBrZTBCVnpMTUhPRThYYTdUYW1pa1lXYTM4REpqekxtZklrZ25KZFNrSDVrSmk3bnlRem9zTVY3Skp3bnZrTm1LWXdhZk1PeHlQNld6d0F2R3FtM0owdm9TbzQ3aDhfMS1ZejFSc2p3R0JFcGVEZC1KR3pUQXhxeUF2bkY5czJteVZvd09kRE82aVdPaFNhUXVBQzhYZGFlMlFvbEFEWWxfUVlVetIBhwJBVV95cUxOMF9kQmhiV25CeHM1aW1GVU5vQmJLakdCc1VrT2F5NFc5b3NPeW1KMWtRbEIwX1Fadjl2bmdlVXgtT0dGR2h2UGRfaUtRVW9KWENxWlRQMjhDRVg2dGRidGZwT3FkU3JNSkl2S1RTSmhTU2NZeW4ySWxZbGxfd2N4Y3FPQWNHOHZkMjJOU20xc2RSeEV5aVBIRXBlazRXM2xfMDBSUGd5SWt2TjB2YVNZRHlTb3ljaGdfTDZfMzNVck5IY05LNGxXaDRUVEJBV0dMODJLbFF4dnQwNWZ2ZmNqNE9DU3IwVEtMY3RCeGRVN2FPRmU0dDAwUElpUTBUaHdEcWx5MzdYVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11776,37 +11776,15 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Uberlândia receberá investimento de R$ 200 milhões em fábrica de cal que gerará 80 vagas de emprego - G1</t>
+          <t>Uberlândia abrigará planta de multinacional belga responsável pela produção e fornecimento de cal - uberlandia.mg.gov.br</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>23/07/2025 04:00</t>
+          <t>22/07/2025 04:00</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNSXFaOVI3bW9MNk1wUmppenNyUVE5WGhvVWl6V09EYlZXdS1KMTlhNzNwd0ZTaGFZc21PdTBGWU5TSkNrZF9xRXZqSWNtYUdMQ1pOTlBrZTBCVnpMTUhPRThYYTdUYW1pa1lXYTM4REpqekxtZklrZ25KZFNrSDVrSmk3bnlRem9zTVY3Skp3bnZrTm1LWXdhZk1PeHlQNld6d0F2R3FtM0owdm9TbzQ3aDhfMS1ZejFSc2p3R0JFcGVEZC1KR3pUQXhxeUF2bkY5czJteVZvd09kRE82aVdPaFNhUXVBQzhYZGFlMlFvbEFEWWxfUVlVetIBhwJBVV95cUxOMF9kQmhiV25CeHM1aW1GVU5vQmJLakdCc1VrT2F5NFc5b3NPeW1KMWtRbEIwX1Fadjl2bmdlVXgtT0dGR2h2UGRfaUtRVW9KWENxWlRQMjhDRVg2dGRidGZwT3FkU3JNSkl2S1RTSmhTU2NZeW4ySWxZbGxfd2N4Y3FPQWNHOHZkMjJOU20xc2RSeEV5aVBIRXBlazRXM2xfMDBSUGd5SWt2TjB2YVNZRHlTb3ljaGdfTDZfMzNVck5IY05LNGxXaDRUVEJBV0dMODJLbFF4dnQwNWZ2ZmNqNE9DU3IwVEtMY3RCeGRVN2FPRmU0dDAwUElpUTBUaHdEcWx5MzdYVQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>Carmeuse</t>
-        </is>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>Uberlândia abrigará planta de multinacional belga responsável pela produção e fornecimento de cal - uberlandia.mg.gov.br</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>22/07/2025 04:00</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOQU5uZ0sxNnlndTM4ZUF3NXBQTFdhdElLY0xNa3FWX3E2N0hBZTZ5bVUxTTJyWkRFOEdNeXlHUTBTdzczbWNaeGEwVEhRTmlhb2g0TnpKcTVqY21PeUlHUC1mNzlIaFV3MEJERzk1X2Y4eU11aHJ1VllobDctX3FhWjFydVp6MG5iOUVUU3YtaXN5ZkRrZXJTeWZ6YUxtenIwRG1zY0VNQ3huS2ZRbmFxUWxLcVNDWFlvN0pPYUN3Sl9vTXhEc1l0c2hzZlFhV0Q3bi1DUW5ZS1dfUQ?oc=5</t>
         </is>
